--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008070568476657996</v>
+        <v>0.008070568476657972</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008649430685339621</v>
+        <v>0.008649430685339623</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007971146938878954</v>
+        <v>0.007971146938878935</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007850883114475482</v>
+        <v>0.007850883114475469</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007909101955302323</v>
+        <v>0.007909101955302306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008279748254400839</v>
+        <v>0.008279748254400825</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007938164710140683</v>
+        <v>0.007938164710140661</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007996513839249653</v>
+        <v>0.007996513839249656</v>
       </c>
       <c r="J2" t="n">
         <v>0.008075509314101337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008144501909231341</v>
+        <v>0.008144501909231329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008167670604934682</v>
+        <v>0.008167670604934686</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008334625958265791</v>
+        <v>0.00833462595826579</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008030157049052388</v>
+        <v>0.008030157049052378</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01187320089392809</v>
+        <v>0.01187320089392808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008083143401512317</v>
+        <v>0.008083143401512305</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007892576748689581</v>
+        <v>0.00789257674868956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007895408344501018</v>
+        <v>0.007895408344501</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008016486815291149</v>
+        <v>0.008016486815291135</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00800903989444504</v>
+        <v>0.008009039894445033</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01075811888898601</v>
+        <v>0.01075811888898602</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007881818384683588</v>
+        <v>0.007881818384683582</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01006503608470116</v>
+        <v>0.01006503608470118</v>
       </c>
       <c r="X2" t="n">
-        <v>0.008002071771757657</v>
+        <v>0.008002071771757661</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008037524831450621</v>
+        <v>0.008037524831450602</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009671343554648092</v>
+        <v>0.009671343554648082</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.008039478639284546</v>
+        <v>0.008039478639284555</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008346123887881349</v>
+        <v>0.008346123887881345</v>
       </c>
     </row>
     <row r="3">
@@ -674,34 +674,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009573736511715837</v>
+        <v>0.00957373651171585</v>
       </c>
       <c r="C3" t="n">
         <v>0.008965592393237796</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008879131382262734</v>
+        <v>0.008879131382262736</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008014386431655886</v>
+        <v>0.00801438643165589</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008436856131459475</v>
+        <v>0.00843685613145948</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01106641431207568</v>
+        <v>0.01106641431207567</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00864689013312258</v>
+        <v>0.008646890133122604</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009062067724367708</v>
+        <v>0.009062067724367719</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009615926767430097</v>
+        <v>0.009615926767430104</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01011867867560889</v>
+        <v>0.01011867867560888</v>
       </c>
       <c r="L3" t="n">
         <v>0.01027574707603581</v>
@@ -710,37 +710,37 @@
         <v>0.01147833338111221</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009297812105708788</v>
+        <v>0.009297812105708778</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01562592437792493</v>
+        <v>0.01562592437792492</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009665207209558498</v>
+        <v>0.009665207209558492</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0083151937067581</v>
+        <v>0.008315193706758098</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008338755154427419</v>
+        <v>0.008338755154427429</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009192603642603599</v>
+        <v>0.009192603642603594</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009150872160088875</v>
+        <v>0.009150872160088872</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443059450896397</v>
+        <v>0.01443059450896398</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008232606088727501</v>
+        <v>0.008232606088727527</v>
       </c>
       <c r="W3" t="n">
         <v>0.01205056880566337</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00909898541473363</v>
+        <v>0.009098985414733625</v>
       </c>
       <c r="Y3" t="n">
         <v>0.009348240474912863</v>
@@ -749,10 +749,10 @@
         <v>0.01137561584108399</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009362920038894372</v>
+        <v>0.009362920038894371</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01155342633579034</v>
+        <v>0.01155342633579032</v>
       </c>
     </row>
     <row r="4">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03301302157366445</v>
+        <v>0.03301302157366444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02976837038946777</v>
+        <v>0.02976837038946778</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03189000956828321</v>
+        <v>0.03189000956828322</v>
       </c>
       <c r="E4" t="n">
         <v>0.03053157434755337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03118918293668252</v>
+        <v>0.03118918293668253</v>
       </c>
       <c r="G4" t="n">
         <v>0.03537580339072172</v>
@@ -798,7 +798,7 @@
         <v>0.03598469812457877</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03255655590868392</v>
+        <v>0.03255655590868393</v>
       </c>
       <c r="O4" t="n">
         <v>0.03255299833429338</v>
@@ -816,10 +816,10 @@
         <v>0.03240214432973248</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0323180279330229</v>
+        <v>0.03231802793302291</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0337979912352619</v>
+        <v>0.03379799123526189</v>
       </c>
       <c r="V4" t="n">
         <v>0.03085144728866308</v>
@@ -834,7 +834,7 @@
         <v>0.03257148620493142</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03126972924980842</v>
+        <v>0.03126972924980841</v>
       </c>
       <c r="AA4" t="n">
         <v>0.0326618475584998</v>
@@ -850,43 +850,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1021805665037111</v>
+        <v>0.1021805665037112</v>
       </c>
       <c r="C5" t="n">
         <v>0.04316245035066515</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08846373304814539</v>
+        <v>0.08846373304814546</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05729439784773608</v>
+        <v>0.05729439784773604</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07467325867195988</v>
+        <v>0.07467325867195977</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1496140944637644</v>
+        <v>0.1496140944637643</v>
       </c>
       <c r="H5" t="n">
         <v>0.08283630130434537</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09535806539251539</v>
+        <v>0.09535806539251536</v>
       </c>
       <c r="J5" t="n">
         <v>0.1074171230310372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.129265658506733</v>
+        <v>0.1292656585067332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1296099418995556</v>
+        <v>0.1296099418995557</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1774577834637421</v>
+        <v>0.1774577834637422</v>
       </c>
       <c r="N5" t="n">
-        <v>0.121561836812349</v>
+        <v>0.1215618368123488</v>
       </c>
       <c r="O5" t="n">
         <v>0.09213618341654344</v>
@@ -895,40 +895,40 @@
         <v>0.1060649026030222</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06870263667330945</v>
+        <v>0.06870263667330939</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07133911258511223</v>
+        <v>0.07133911258511222</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09276179171281618</v>
+        <v>0.09276179171281602</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09785389355279636</v>
+        <v>0.09785389355279626</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1228715643342146</v>
+        <v>0.1228715643342145</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06277593181594239</v>
+        <v>0.06277593181594236</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07389972772570677</v>
+        <v>0.07389972772570672</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09498811271392049</v>
+        <v>0.09498811271392042</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1008087023147113</v>
+        <v>0.1008087023147111</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07078854177084008</v>
+        <v>0.07078854177083996</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1016900579796482</v>
+        <v>0.1016900579796481</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1845233751562141</v>
+        <v>0.1845233751562138</v>
       </c>
     </row>
     <row r="6">
@@ -938,82 +938,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03378437733235942</v>
+        <v>0.03548377092332964</v>
       </c>
       <c r="C6" t="n">
         <v>0.03223911973913299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03266136532697819</v>
+        <v>0.03266136532697815</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03300232369721858</v>
+        <v>0.0313029301062483</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03196053869537749</v>
+        <v>0.03365993228634773</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03614715914941671</v>
+        <v>0.03784655274038694</v>
       </c>
       <c r="H6" t="n">
         <v>0.03398820947177475</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03464728972698621</v>
+        <v>0.03294789613601593</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03383565847894796</v>
+        <v>0.03553505206991821</v>
       </c>
       <c r="K6" t="n">
         <v>0.03461948946433466</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03658058413140106</v>
+        <v>0.03488119054043078</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03675605388327373</v>
+        <v>0.03675605388327371</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03333680153735812</v>
+        <v>0.03333680153735818</v>
       </c>
       <c r="O6" t="n">
         <v>0.03502042722720625</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03562249196454697</v>
+        <v>0.03562249196454698</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03177387888471592</v>
+        <v>0.03177387888471588</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0335052566529747</v>
+        <v>0.03180586306200443</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03487289367939769</v>
+        <v>0.03487289367939768</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03308938369171788</v>
+        <v>0.03308938369171784</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03463763918924474</v>
+        <v>0.03463763918924469</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03332219663832829</v>
+        <v>0.0333221966383283</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03216310397282379</v>
+        <v>0.03378110617602278</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03471006913143945</v>
+        <v>0.03471006913143946</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03347435162126301</v>
+        <v>0.03347435162126306</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0320410850085034</v>
+        <v>0.03204108500850335</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03513259690816502</v>
+        <v>0.03343320331719474</v>
       </c>
       <c r="AB6" t="n">
         <v>0.03689284768952369</v>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03410427570388844</v>
+        <v>0.03410427570388843</v>
       </c>
       <c r="C7" t="n">
         <v>0.03085962451969178</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03298126369850722</v>
+        <v>0.03298126369850721</v>
       </c>
       <c r="E7" t="n">
         <v>0.03162282847777736</v>
@@ -1041,7 +1041,7 @@
         <v>0.03228043706690652</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03646705752094571</v>
+        <v>0.03646705752094574</v>
       </c>
       <c r="H7" t="n">
         <v>0.03260871425233354</v>
@@ -1056,7 +1056,7 @@
         <v>0.03493938783586373</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03520108891195983</v>
+        <v>0.03520108891195984</v>
       </c>
       <c r="M7" t="n">
         <v>0.03707595225480277</v>
@@ -1065,7 +1065,7 @@
         <v>0.03364781003890793</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0336441151438719</v>
+        <v>0.03364411514387189</v>
       </c>
       <c r="P7" t="n">
         <v>0.03424617794422391</v>
@@ -1080,13 +1080,13 @@
         <v>0.03349339845995648</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03340928206324691</v>
+        <v>0.0334092820632469</v>
       </c>
       <c r="U7" t="n">
         <v>0.03495584282844987</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03194270141888709</v>
+        <v>0.03194270141888708</v>
       </c>
       <c r="W7" t="n">
         <v>0.03240493059451966</v>
@@ -1095,7 +1095,7 @@
         <v>0.03333057391199826</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03373103253044327</v>
+        <v>0.03373103253044325</v>
       </c>
       <c r="Z7" t="n">
         <v>0.03236098338003241</v>
@@ -1104,7 +1104,7 @@
         <v>0.03375310168872381</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03717745057168901</v>
+        <v>0.037177450571689</v>
       </c>
     </row>
     <row r="8">
@@ -1114,31 +1114,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0355572757885352</v>
+        <v>0.03555727578853521</v>
       </c>
       <c r="C8" t="n">
         <v>0.03436584140447731</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03648748058329273</v>
+        <v>0.03648748058329275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0351290453625629</v>
+        <v>0.03403576798265461</v>
       </c>
       <c r="F8" t="n">
         <v>0.03405330433252735</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03997327440573126</v>
+        <v>0.04039902228468284</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03611493113711906</v>
+        <v>0.03611493113711907</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03677401139233052</v>
+        <v>0.03677401139233053</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03766177373526256</v>
+        <v>0.03766177373526257</v>
       </c>
       <c r="K8" t="n">
         <v>0.03844560472064926</v>
@@ -1150,49 +1150,49 @@
         <v>0.04058216913958829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0355624404078214</v>
+        <v>0.03556244040782141</v>
       </c>
       <c r="O8" t="n">
         <v>0.03599626462735618</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03649111458140705</v>
+        <v>0.03649111458140707</v>
       </c>
       <c r="Q8" t="n">
         <v>0.03314327337735617</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03563197831831902</v>
+        <v>0.03563197831831903</v>
       </c>
       <c r="S8" t="n">
-        <v>0.036999615344742</v>
+        <v>0.03699961534474201</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03691549894803244</v>
+        <v>0.03691549894803246</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03719917841952979</v>
+        <v>0.03746039977339392</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0354489183036726</v>
+        <v>0.03488641195631403</v>
       </c>
       <c r="W8" t="n">
         <v>0.03591155099494248</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03456825143246543</v>
+        <v>0.03456825143246544</v>
       </c>
       <c r="Y8" t="n">
         <v>0.03927665139504363</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03586720026481795</v>
+        <v>0.03377584390851722</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03725931857350935</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04282842409114324</v>
+        <v>0.04282842409114323</v>
       </c>
     </row>
     <row r="9">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03817089402436963</v>
+        <v>0.03817089402436964</v>
       </c>
       <c r="C9" t="n">
         <v>0.03654272192609005</v>
@@ -1211,19 +1211,19 @@
         <v>0.03866436110490549</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03730592588417563</v>
+        <v>0.03693284927533342</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03796353447330479</v>
+        <v>0.03423710871162101</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04215015492734403</v>
+        <v>0.04215015514924787</v>
       </c>
       <c r="H9" t="n">
         <v>0.03829181165873181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03895089191394328</v>
+        <v>0.03895089191394327</v>
       </c>
       <c r="J9" t="n">
         <v>0.03983865425687529</v>
@@ -1232,10 +1232,10 @@
         <v>0.040622485242262</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04088418631835812</v>
+        <v>0.04088418631835811</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04275904966120104</v>
+        <v>0.04275904966120105</v>
       </c>
       <c r="N9" t="n">
         <v>0.0393309074453062</v>
@@ -1247,22 +1247,22 @@
         <v>0.04058161738804313</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03777687488454708</v>
+        <v>0.03777687488454707</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03780885883993176</v>
+        <v>0.03780885883993177</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03917649586635476</v>
+        <v>0.03917649586635474</v>
       </c>
       <c r="T9" t="n">
         <v>0.03909237946964518</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04064063496717202</v>
+        <v>0.04064063496717201</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03762579882528536</v>
+        <v>0.03949117936053614</v>
       </c>
       <c r="W9" t="n">
         <v>0.03808802800091794</v>
@@ -1271,16 +1271,16 @@
         <v>0.03901367131839653</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03941412993684154</v>
+        <v>0.03941412993684153</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0380440807864307</v>
+        <v>0.03706948772866704</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03943619909512208</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04286054797808729</v>
+        <v>0.04286054797808728</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007087019050252357</v>
+        <v>0.007087019050252352</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007759858464943851</v>
+        <v>0.007759858464943848</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007104730246695211</v>
+        <v>0.007104730246695206</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007096342198106136</v>
+        <v>0.007096342198106129</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007131185259532307</v>
+        <v>0.007131185259532302</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007124201644364823</v>
+        <v>0.007124201644364817</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007112209018167672</v>
+        <v>0.007112209018167665</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007110347981813148</v>
+        <v>0.007110347981813142</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007130958023724032</v>
+        <v>0.00713095802372403</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007133306494169708</v>
+        <v>0.007133306494169704</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007180996352157781</v>
+        <v>0.007180996352157775</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007107997597808675</v>
+        <v>0.007107997597808672</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007127936455719707</v>
+        <v>0.0071279364557197</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01062823355859137</v>
+        <v>0.01062823355859138</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007135497932484666</v>
+        <v>0.007135497932484662</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007100990451986462</v>
+        <v>0.007100990451986456</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007197399094691696</v>
+        <v>0.007197399094691691</v>
       </c>
       <c r="S2" t="n">
         <v>0.007153696350260988</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007125702551383346</v>
+        <v>0.007125702551383339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008905216686168603</v>
+        <v>0.008905216686168605</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007134117431097452</v>
+        <v>0.007134117431097447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008616650659506439</v>
+        <v>0.008616650659506427</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00729890477103234</v>
+        <v>0.007298904771032338</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007206154791370295</v>
+        <v>0.007206154791370289</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008778301413149624</v>
+        <v>0.008778301413149619</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007204803315408693</v>
+        <v>0.007204803315408684</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007087699893524348</v>
+        <v>0.007087699893524343</v>
       </c>
     </row>
     <row r="3">
@@ -1534,37 +1534,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00674402778041684</v>
+        <v>0.006744027780416843</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007969082234202698</v>
+        <v>0.007969082234202699</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006871175683764958</v>
+        <v>0.006871175683764956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006809694785654244</v>
+        <v>0.00680969478565424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007060495802139089</v>
+        <v>0.007060495802139088</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007007724076142649</v>
+        <v>0.007007724076142644</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0069258304339784</v>
+        <v>0.006925830433978398</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00691178532581286</v>
+        <v>0.006911785325812859</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007056960435172174</v>
+        <v>0.007056960435172166</v>
       </c>
       <c r="K3" t="n">
         <v>0.007073421998890671</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007411559946903463</v>
+        <v>0.007411559946903467</v>
       </c>
       <c r="M3" t="n">
         <v>0.006907033181464825</v>
@@ -1573,46 +1573,46 @@
         <v>0.007037186015270947</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01298801403781341</v>
+        <v>0.01298801403781343</v>
       </c>
       <c r="P3" t="n">
         <v>0.007087895778289351</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00684398775597947</v>
+        <v>0.006843987755979474</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00753574974076543</v>
+        <v>0.007535749740765432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007217208168930554</v>
+        <v>0.007217208168930562</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007021705073259039</v>
+        <v>0.007021705073259033</v>
       </c>
       <c r="U3" t="n">
         <v>0.009997670203780709</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007078265390828646</v>
+        <v>0.007078265390828647</v>
       </c>
       <c r="W3" t="n">
         <v>0.009775782519781378</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008254781164499965</v>
+        <v>0.008254781164499956</v>
       </c>
       <c r="Y3" t="n">
         <v>0.007595679813784322</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009701706629436957</v>
+        <v>0.009701706629436964</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007585758247962451</v>
+        <v>0.007585758247962453</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006757421485468434</v>
+        <v>0.006757421485468438</v>
       </c>
     </row>
     <row r="4">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02823057206109944</v>
+        <v>0.02823057206109945</v>
       </c>
       <c r="C4" t="n">
         <v>0.02846541725346752</v>
@@ -1631,49 +1631,49 @@
         <v>0.02843062817247442</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02833588130496777</v>
+        <v>0.02833588130496778</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02872944971237647</v>
+        <v>0.02872944971237648</v>
       </c>
       <c r="G4" t="n">
         <v>0.0286505665664381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02851510433666067</v>
+        <v>0.02851510433666068</v>
       </c>
       <c r="I4" t="n">
         <v>0.02849408307491731</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02872371918302537</v>
+        <v>0.02872371918302536</v>
       </c>
       <c r="K4" t="n">
         <v>0.02875341003342216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02929208891781591</v>
+        <v>0.02929208891781592</v>
       </c>
       <c r="M4" t="n">
         <v>0.02849003903451627</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0290581828808579</v>
+        <v>0.02905818288085791</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02877816333730096</v>
+        <v>0.02877816333730097</v>
       </c>
       <c r="Q4" t="n">
         <v>0.02838838547084847</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02947736544037091</v>
+        <v>0.02947736544037092</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0289837228377703</v>
+        <v>0.02898372283777031</v>
       </c>
       <c r="T4" t="n">
         <v>0.02866752000166364</v>
@@ -1682,25 +1682,25 @@
         <v>0.02870939025147388</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02874221290307827</v>
+        <v>0.02874221290307828</v>
       </c>
       <c r="W4" t="n">
         <v>0.02927319852248172</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03062391874955655</v>
+        <v>0.03062391874955656</v>
       </c>
       <c r="Y4" t="n">
         <v>0.02953225616434834</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02857600907506026</v>
+        <v>0.02857600907506027</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02956099951947914</v>
+        <v>0.02956099951947915</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02825151827194241</v>
+        <v>0.02825151827194242</v>
       </c>
     </row>
     <row r="5">
@@ -1713,31 +1713,31 @@
         <v>0.03179738669800947</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03621460613136775</v>
+        <v>0.03621460613136777</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03572034140887296</v>
+        <v>0.03572034140887297</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03320766568864925</v>
+        <v>0.03320766568864927</v>
       </c>
       <c r="F5" t="n">
         <v>0.04126946305489031</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03835624040396979</v>
+        <v>0.03835624040396982</v>
       </c>
       <c r="H5" t="n">
         <v>0.03787693262262354</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03710983569261313</v>
+        <v>0.03710983569261312</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0402292412487327</v>
+        <v>0.04022924124873268</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04054632642942948</v>
+        <v>0.04054632642942947</v>
       </c>
       <c r="L5" t="n">
         <v>0.04891969307866089</v>
@@ -1746,49 +1746,49 @@
         <v>0.03693230620353951</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O5" t="n">
         <v>0.04466323305676482</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04037955553666701</v>
+        <v>0.04037955553666696</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03471574176495862</v>
+        <v>0.03471574176495863</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05588772259466597</v>
+        <v>0.05588772259466598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0437195029316628</v>
+        <v>0.04371950293166277</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04035013987318183</v>
+        <v>0.04035013987318185</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0401095886203352</v>
+        <v>0.04010958862033519</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04019861511391373</v>
+        <v>0.04019861511391377</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05044479353406204</v>
+        <v>0.05044479353406203</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07335781419822467</v>
+        <v>0.07335781419822458</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05631038927525585</v>
+        <v>0.05631038927525582</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03693480974519791</v>
+        <v>0.03693480974519792</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05589735543189114</v>
+        <v>0.05589735543189117</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03285831971092944</v>
+        <v>0.03285831971092947</v>
       </c>
     </row>
     <row r="6">
@@ -1798,82 +1798,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02989654567931875</v>
+        <v>0.02885975178248708</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03013139087168683</v>
+        <v>0.02909459697485516</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03009660179069373</v>
+        <v>0.03009660179069374</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03000185492318708</v>
+        <v>0.0289650610263554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03039542333059578</v>
+        <v>0.02935862943376411</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02927974628782572</v>
+        <v>0.03031654018465741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02914428405804831</v>
+        <v>0.03018107795487998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02912326279630493</v>
+        <v>0.03016005669313662</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02935289890441299</v>
+        <v>0.03038969280124468</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03041938365164146</v>
+        <v>0.02938258975480979</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02992126863920355</v>
+        <v>0.03095806253603523</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02911921875590389</v>
+        <v>0.03015601265273558</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O6" t="n">
         <v>0.03077124542969605</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02937024009953203</v>
+        <v>0.03045791245200359</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03005435908906777</v>
+        <v>0.03005435908906778</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03010654516175854</v>
+        <v>0.03114333905859023</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02961290255915794</v>
+        <v>0.03064969645598961</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03033349361988295</v>
+        <v>0.02929669972305127</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02938257887068826</v>
+        <v>0.03041937276751994</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0293713926244659</v>
+        <v>0.03040818652129759</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02996971254897851</v>
+        <v>0.02996971254897852</v>
       </c>
       <c r="X6" t="n">
         <v>0.03125309847094419</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03028094611673977</v>
+        <v>0.03028094611673983</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03024198269327956</v>
+        <v>0.02920518879644789</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03019017924086677</v>
+        <v>0.03019017924086678</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02888028568858137</v>
@@ -1889,19 +1889,19 @@
         <v>0.02888615153036343</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02912099672273151</v>
+        <v>0.0291209967227315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0290862076417384</v>
+        <v>0.02908620764173841</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02899146077423175</v>
+        <v>0.02899146077423176</v>
       </c>
       <c r="F7" t="n">
         <v>0.02938502918164045</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02930614603570208</v>
+        <v>0.02930614603570209</v>
       </c>
       <c r="H7" t="n">
         <v>0.02917068380592466</v>
@@ -1916,13 +1916,13 @@
         <v>0.02940898950268614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02994766838707989</v>
+        <v>0.0299476683870799</v>
       </c>
       <c r="M7" t="n">
         <v>0.02914561850378025</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O7" t="n">
         <v>0.02971364626597216</v>
@@ -1937,16 +1937,16 @@
         <v>0.03013294490963489</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02963930230703429</v>
+        <v>0.02963930230703428</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02932309947092762</v>
+        <v>0.02932309947092763</v>
       </c>
       <c r="U7" t="n">
         <v>0.02940754940281597</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02939779237234225</v>
+        <v>0.02939779237234226</v>
       </c>
       <c r="W7" t="n">
         <v>0.02992877799174571</v>
@@ -1958,13 +1958,13 @@
         <v>0.03023184453143907</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02923158854432424</v>
+        <v>0.02923158854432425</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03021657898874312</v>
+        <v>0.03021657898874313</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02890709774120639</v>
+        <v>0.0289070977412064</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02990546090643817</v>
+        <v>0.02990546090643818</v>
       </c>
       <c r="C8" t="n">
         <v>0.03150435489779586</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03146956581680275</v>
+        <v>0.03146956581680276</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03137481894929611</v>
+        <v>0.03064850320078888</v>
       </c>
       <c r="F8" t="n">
         <v>0.03061684141860222</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03168950421076643</v>
+        <v>0.03197234861517672</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03155404198098899</v>
+        <v>0.03155404198098901</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03153302071924563</v>
+        <v>0.03153302071924565</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03176265682735369</v>
+        <v>0.0317626568273537</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03179234767775047</v>
+        <v>0.03179234767775051</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03233102656214425</v>
+        <v>0.03233102656214426</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03152897667884461</v>
+        <v>0.03152897667884448</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03133032786860625</v>
+        <v>0.03133032786860626</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03097908177253185</v>
+        <v>0.03097908177253187</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02979520759433383</v>
+        <v>0.02979520759433384</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03251630308469924</v>
+        <v>0.03251630308469926</v>
       </c>
       <c r="S8" t="n">
         <v>0.03202266048209863</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03170645764599196</v>
+        <v>0.03170645764599199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03095201663229451</v>
+        <v>0.03112554513574556</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03178115054740659</v>
+        <v>0.03140721301079875</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0323124042413194</v>
+        <v>0.03231240424131941</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03215575865577582</v>
+        <v>0.03215575865577583</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03396970448544312</v>
+        <v>0.03396970448544313</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03161494671938858</v>
+        <v>0.03022556001366647</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03259993716380747</v>
+        <v>0.03259993716380748</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03271531894657047</v>
+        <v>0.0327153189465705</v>
       </c>
     </row>
     <row r="9">
@@ -2062,22 +2062,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03013749192700095</v>
+        <v>0.03013749192700094</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03103021306900173</v>
+        <v>0.03103021306900174</v>
       </c>
       <c r="D9" t="n">
         <v>0.03099542398800863</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03090067712050198</v>
+        <v>0.03074884241866589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03129424552791068</v>
+        <v>0.02977766126115987</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03121536238197231</v>
+        <v>0.03121536288107527</v>
       </c>
       <c r="H9" t="n">
         <v>0.03107990015219489</v>
@@ -2098,22 +2098,22 @@
         <v>0.03105483485005048</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04055672468437398</v>
+        <v>0.04055672468437393</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03184099858919056</v>
+        <v>0.03184099858919057</v>
       </c>
       <c r="P9" t="n">
         <v>0.03160839452317941</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03095318178548564</v>
+        <v>0.03095318178548565</v>
       </c>
       <c r="R9" t="n">
         <v>0.03204216125590512</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03154851865330451</v>
+        <v>0.03154851865330452</v>
       </c>
       <c r="T9" t="n">
         <v>0.03123231581719785</v>
@@ -2122,7 +2122,7 @@
         <v>0.03131819496483484</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03130700871861247</v>
+        <v>0.03206618391064633</v>
       </c>
       <c r="W9" t="n">
         <v>0.03183799433801593</v>
@@ -2134,13 +2134,13 @@
         <v>0.03214106087770929</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03114080489059446</v>
+        <v>0.03074416439176618</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03212579533501335</v>
+        <v>0.03212579533501336</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03081631408747663</v>
+        <v>0.03081631408747662</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007812205858297563</v>
+        <v>0.007812205858297572</v>
       </c>
       <c r="C2" t="n">
         <v>0.008435247021676882</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007762608233699207</v>
+        <v>0.007762608233699218</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007635059921863115</v>
+        <v>0.007635059921863117</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007658577957734105</v>
+        <v>0.007658577957734115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007945996965898056</v>
+        <v>0.007945996965898067</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007626590706570358</v>
+        <v>0.007626590706570366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007691430670925737</v>
+        <v>0.007691430670925745</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007822900083201809</v>
+        <v>0.007822900083201814</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007886972730914895</v>
+        <v>0.00788697273091489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007951417630756481</v>
+        <v>0.007951417630756489</v>
       </c>
       <c r="M2" t="n">
         <v>0.007964489613667971</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007745711762666754</v>
+        <v>0.007745711762666765</v>
       </c>
       <c r="O2" t="n">
         <v>0.01149882919994524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007961284613029449</v>
+        <v>0.007961284613029463</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007664589240630391</v>
+        <v>0.007664589240630403</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007626502215554416</v>
+        <v>0.007626502215554424</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007815891518758458</v>
+        <v>0.007815891518758472</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007739857137123085</v>
+        <v>0.007739857137123095</v>
       </c>
       <c r="U2" t="n">
         <v>0.01032752990255842</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007627770942455811</v>
+        <v>0.007627770942455822</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00974334107871184</v>
+        <v>0.009743341078711837</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007826790822068712</v>
+        <v>0.007826790822068722</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007801948429646253</v>
+        <v>0.00780194842964627</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009390109462242955</v>
+        <v>0.009390109462242979</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007781814380215963</v>
+        <v>0.007781814380215983</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008136833574102258</v>
+        <v>0.008136833574102246</v>
       </c>
     </row>
     <row r="3">
@@ -2394,82 +2394,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008964653217429676</v>
+        <v>0.008964653217429697</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008779031997382626</v>
+        <v>0.008779031997382628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008624121003269734</v>
+        <v>0.008624121003269751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007707649576583432</v>
+        <v>0.007707649576583445</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007879677852904611</v>
+        <v>0.007879677852904617</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009919173625745873</v>
+        <v>0.009919173625745887</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007652071196064299</v>
+        <v>0.007652071196064312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008115379522421293</v>
+        <v>0.00811537952242131</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009046689388410599</v>
+        <v>0.009046689388410608</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009503957286381193</v>
+        <v>0.009503957286381221</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009966035523166156</v>
+        <v>0.009966035523166172</v>
       </c>
       <c r="M3" t="n">
         <v>0.01007097250625765</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008500507418790666</v>
+        <v>0.008500507418790684</v>
       </c>
       <c r="O3" t="n">
         <v>0.01487918366873302</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01002716660805134</v>
+        <v>0.01002716660805137</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007920995977514172</v>
+        <v>0.007920995977514176</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007650802877390452</v>
+        <v>0.007650802877390462</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008993734106077693</v>
+        <v>0.008993734106077705</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008461170779997185</v>
+        <v>0.008461170779997199</v>
       </c>
       <c r="U3" t="n">
         <v>0.01365037444977659</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007653675995955912</v>
+        <v>0.007653675995955931</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01188114615801947</v>
+        <v>0.01188114615801948</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009081371617693769</v>
+        <v>0.009081371617693781</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008899418870793466</v>
+        <v>0.008899418870793478</v>
       </c>
       <c r="Z3" t="n">
         <v>0.01085501788024672</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008756557629659144</v>
+        <v>0.008756557629659148</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01128756163087331</v>
@@ -2512,13 +2512,13 @@
         <v>0.03279843740511074</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03352637219494008</v>
+        <v>0.03352637219494006</v>
       </c>
       <c r="M4" t="n">
         <v>0.03367456235418533</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0312028297854921</v>
+        <v>0.03120282978549209</v>
       </c>
       <c r="O4" t="n">
         <v>0.03160462887197107</v>
@@ -2533,19 +2533,19 @@
         <v>0.02985630311175717</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03199554241483083</v>
+        <v>0.03199554241483084</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03113669909671552</v>
+        <v>0.03113669909671551</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03299304142262458</v>
+        <v>0.0329930414226246</v>
       </c>
       <c r="V4" t="n">
         <v>0.02983969314203338</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03137731308928141</v>
+        <v>0.0313773130892814</v>
       </c>
       <c r="X4" t="n">
         <v>0.03211865505964725</v>
@@ -2557,7 +2557,7 @@
         <v>0.03047225186406096</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03161062545873512</v>
+        <v>0.03161062545873511</v>
       </c>
       <c r="AB4" t="n">
         <v>0.03557154405361934</v>
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08426342723312576</v>
+        <v>0.08426342723312577</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04165428239583652</v>
+        <v>0.0416542823958365</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08115010638950967</v>
+        <v>0.08115010638950955</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05048729464238608</v>
+        <v>0.0504872946423861</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05783421796662901</v>
+        <v>0.05783421796662903</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1126411174146192</v>
+        <v>0.1126411174146193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05138519401281481</v>
+        <v>0.05138519401281483</v>
       </c>
       <c r="I5" t="n">
         <v>0.06553487457484172</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08971885790568625</v>
+        <v>0.08971885790568633</v>
       </c>
       <c r="K5" t="n">
         <v>0.1033956940782509</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1183450064325445</v>
+        <v>0.1183450064325446</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1274594756902176</v>
+        <v>0.1274594756902179</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1056604471414007</v>
+        <v>0.1056604471414006</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07695577569811485</v>
+        <v>0.07695577569811486</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1152856446663396</v>
+        <v>0.1152856446663397</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05823673348821939</v>
+        <v>0.0582367334882194</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05101216257357812</v>
+        <v>0.05101216257357816</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08659454652297532</v>
+        <v>0.08659454652297553</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07597155893232344</v>
+        <v>0.07597155893232341</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1075000673122688</v>
+        <v>0.1075000673122687</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04781413917492064</v>
+        <v>0.04781413917492058</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07829016664917242</v>
+        <v>0.07829016664917243</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09439969226778899</v>
+        <v>0.09439969226778924</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08650715522368245</v>
+        <v>0.08650715522368256</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05925661507511276</v>
+        <v>0.05925661507511271</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08267226278012464</v>
+        <v>0.08267226278012467</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1708782931756533</v>
+        <v>0.1708782931756531</v>
       </c>
     </row>
     <row r="6">
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03412265970965683</v>
+        <v>0.03267341884062924</v>
       </c>
       <c r="C6" t="n">
         <v>0.03160202902051566</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0321131908547563</v>
+        <v>0.03356243172378388</v>
       </c>
       <c r="E6" t="n">
         <v>0.03067247399744529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03238736190046678</v>
+        <v>0.0309381210314392</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03563389181695468</v>
+        <v>0.03418465094792709</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03057681031468218</v>
+        <v>0.03202605118370976</v>
       </c>
       <c r="I6" t="n">
         <v>0.03130920753993333</v>
@@ -2685,7 +2685,7 @@
         <v>0.0342387234265155</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03351794506130269</v>
+        <v>0.03496718593033027</v>
       </c>
       <c r="L6" t="n">
         <v>0.03424587985113201</v>
@@ -2694,28 +2694,28 @@
         <v>0.03439407001037727</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03192789128063836</v>
+        <v>0.03192789128063839</v>
       </c>
       <c r="O6" t="n">
         <v>0.03376433095559107</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03579752799230695</v>
+        <v>0.03579752799230699</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03100602123707949</v>
+        <v>0.03245526210610707</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0305758107679491</v>
+        <v>0.03202505163697668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03271505007102276</v>
+        <v>0.03416429094005035</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03330544762193503</v>
+        <v>0.03185620675290744</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03521119848157968</v>
+        <v>0.03376195761255209</v>
       </c>
       <c r="V6" t="n">
         <v>0.03200844166725288</v>
@@ -2724,16 +2724,16 @@
         <v>0.03353700100372765</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03283816271583918</v>
+        <v>0.03428740358486676</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03261313539670407</v>
+        <v>0.03261313539670409</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0311917595202529</v>
+        <v>0.03264100038928047</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03377937398395462</v>
+        <v>0.03233013311492705</v>
       </c>
       <c r="AB6" t="n">
         <v>0.03632445996878021</v>
@@ -2752,7 +2752,7 @@
         <v>0.03034618871790933</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03230659142117756</v>
+        <v>0.03230659142117757</v>
       </c>
       <c r="E7" t="n">
         <v>0.03086587456386655</v>
@@ -2761,16 +2761,16 @@
         <v>0.03113152159786046</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03437805151434837</v>
+        <v>0.03437805151434836</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03077021088110344</v>
+        <v>0.03077021088110345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03150260810635459</v>
+        <v>0.0315026081063546</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03298288312390919</v>
+        <v>0.03298288312390918</v>
       </c>
       <c r="K7" t="n">
         <v>0.03371134562772395</v>
@@ -2782,13 +2782,13 @@
         <v>0.03458747057679854</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03211573800810528</v>
+        <v>0.03211573800810529</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03251740973639266</v>
+        <v>0.03251740973639267</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03455060516317097</v>
+        <v>0.03455060516317098</v>
       </c>
       <c r="Q7" t="n">
         <v>0.03119942180350075</v>
@@ -2800,7 +2800,7 @@
         <v>0.03290845063744403</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0320496073193287</v>
+        <v>0.03204960731932871</v>
       </c>
       <c r="U7" t="n">
         <v>0.03395387419209746</v>
@@ -2824,7 +2824,7 @@
         <v>0.03252353368134831</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03648445227623255</v>
+        <v>0.03648445227623254</v>
       </c>
     </row>
     <row r="8">
@@ -2834,22 +2834,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03414064226366584</v>
+        <v>0.03414064226366583</v>
       </c>
       <c r="C8" t="n">
         <v>0.03338784095017636</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0353482436534446</v>
+        <v>0.03534824365344461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03390752679613358</v>
+        <v>0.03296620980135214</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03268075161011345</v>
+        <v>0.03268075161011346</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03741970374661541</v>
+        <v>0.03778627468397661</v>
       </c>
       <c r="H8" t="n">
         <v>0.03381186311337048</v>
@@ -2861,16 +2861,16 @@
         <v>0.03602453535617621</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03675299785999097</v>
+        <v>0.03675299785999098</v>
       </c>
       <c r="L8" t="n">
         <v>0.0374809326498203</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03762912280906557</v>
+        <v>0.03762912280906545</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03378702672276573</v>
+        <v>0.03378702672276571</v>
       </c>
       <c r="O8" t="n">
         <v>0.0345654136024247</v>
@@ -2888,31 +2888,31 @@
         <v>0.03595010286971106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03509125955159575</v>
+        <v>0.03509125955159573</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03590819305462384</v>
+        <v>0.03613310513386437</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03379425359691361</v>
+        <v>0.03330991956014984</v>
       </c>
       <c r="W8" t="n">
         <v>0.03533222097304096</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0341199923927467</v>
+        <v>0.03411999239274672</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03754852321311445</v>
+        <v>0.03754852321311446</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0344268123189412</v>
+        <v>0.03262614460505101</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03556518591361534</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04137275011462888</v>
+        <v>0.04137275011462886</v>
       </c>
     </row>
     <row r="9">
@@ -2928,28 +2928,28 @@
         <v>0.03447862055656704</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03643902325983528</v>
+        <v>0.03643902325983529</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03499830640252427</v>
+        <v>0.03471626206671932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03526395343651818</v>
+        <v>0.03244678991087167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03851048335300607</v>
+        <v>0.03851048368055156</v>
       </c>
       <c r="H9" t="n">
         <v>0.03490264271976116</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03563503994501232</v>
+        <v>0.03563503994501231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03711531496256689</v>
+        <v>0.0371153149625669</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03784377746638166</v>
+        <v>0.03784377746638168</v>
       </c>
       <c r="L9" t="n">
         <v>0.03857171225621098</v>
@@ -2958,22 +2958,22 @@
         <v>0.03871990241545625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.036248169846763</v>
+        <v>0.03624816984676301</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03705495576008661</v>
+        <v>0.03705495576008662</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03917622880206422</v>
+        <v>0.03917622880206423</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03533185396970395</v>
+        <v>0.03533185396970393</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03490164317302808</v>
+        <v>0.03490164317302809</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03704088247610173</v>
+        <v>0.03704088247610175</v>
       </c>
       <c r="T9" t="n">
         <v>0.03618203915798642</v>
@@ -2982,19 +2982,19 @@
         <v>0.03808779001763109</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03488503320330429</v>
+        <v>0.03629525382699957</v>
       </c>
       <c r="W9" t="n">
         <v>0.03642265315055232</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03716399512091816</v>
+        <v>0.03716399512091815</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03688338887044153</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03551759192533187</v>
+        <v>0.03478080344474445</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03665596552000602</v>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007716196104872071</v>
+        <v>0.007716196104872069</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008401714362643347</v>
+        <v>0.008401714362643352</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007769936218398017</v>
+        <v>0.007769936218398019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007600973083329831</v>
+        <v>0.00760097308332983</v>
       </c>
       <c r="F2" t="n">
         <v>0.00763095173073115</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007882185371576679</v>
+        <v>0.007882185371576676</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007559142078163909</v>
+        <v>0.007559142078163906</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007723393103297962</v>
+        <v>0.00772339310329796</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007760587161908875</v>
+        <v>0.007760587161908868</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007773412559847552</v>
+        <v>0.007773412559847549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007851858586812761</v>
+        <v>0.00785185858681276</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007782629461371197</v>
+        <v>0.007782629461371202</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007647360030016356</v>
+        <v>0.007647360030016355</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01135652609948907</v>
+        <v>0.01135652609948906</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007920286016067229</v>
+        <v>0.007920286016067233</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007616045729135565</v>
+        <v>0.007616045729135562</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007554819103786569</v>
+        <v>0.007554819103786571</v>
       </c>
       <c r="S2" t="n">
         <v>0.00775899260556678</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007673283521582069</v>
+        <v>0.007673283521582068</v>
       </c>
       <c r="U2" t="n">
         <v>0.01029689152578921</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007617887346549943</v>
+        <v>0.00761788734654994</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009718754560138272</v>
+        <v>0.009718754560138276</v>
       </c>
       <c r="X2" t="n">
         <v>0.007839502164807161</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007939365071357106</v>
+        <v>0.007939365071357113</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009343475328616719</v>
+        <v>0.009343475328616711</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007755549697360643</v>
+        <v>0.007755549697360641</v>
       </c>
       <c r="AB2" t="n">
         <v>0.008063297599010096</v>
@@ -3254,37 +3254,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008509418453688465</v>
+        <v>0.008509418453688463</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008722898687445389</v>
+        <v>0.008722898687445396</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008903193267760427</v>
+        <v>0.00890319326776043</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007691354514574572</v>
+        <v>0.007691354514574569</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007908787733852255</v>
+        <v>0.007908787733852254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009689039362650089</v>
+        <v>0.009689039362650096</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007396469071251446</v>
+        <v>0.007396469071251454</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008571790008574623</v>
+        <v>0.008571790008574626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0088280153609208</v>
+        <v>0.008828015360920809</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008916580213232293</v>
+        <v>0.008916580213232295</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009481765669695854</v>
+        <v>0.009481765669695852</v>
       </c>
       <c r="M3" t="n">
         <v>0.009005883503152972</v>
@@ -3293,43 +3293,43 @@
         <v>0.008024962213946933</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01441426046963476</v>
+        <v>0.01441426046963478</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009959705043865138</v>
+        <v>0.009959705043865154</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007800367870889373</v>
+        <v>0.007800367870889374</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007364899653369829</v>
+        <v>0.00736489965336982</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008814137410258252</v>
+        <v>0.008814137410258266</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008212395546497329</v>
+        <v>0.008212395546497331</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0135755740736743</v>
+        <v>0.01357557407367431</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007808467798804009</v>
+        <v>0.007808467798804011</v>
       </c>
       <c r="W3" t="n">
         <v>0.01185506732388593</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009398975054975719</v>
+        <v>0.009398975054975726</v>
       </c>
       <c r="Y3" t="n">
         <v>0.01010706801569395</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01078560389632198</v>
+        <v>0.01078560389632199</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008796241975809034</v>
+        <v>0.008796241975809032</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01099138210712916</v>
@@ -3345,13 +3345,13 @@
         <v>0.031150938557525</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02924693038029631</v>
+        <v>0.0292469303802963</v>
       </c>
       <c r="D4" t="n">
         <v>0.03175795786147416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02984944152399676</v>
+        <v>0.02984944152399677</v>
       </c>
       <c r="F4" t="n">
         <v>0.03018806413725375</v>
@@ -3363,16 +3363,16 @@
         <v>0.0293769410774345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03123223196552829</v>
+        <v>0.0312322319655283</v>
       </c>
       <c r="J4" t="n">
         <v>0.03164806687136509</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03179722473734271</v>
+        <v>0.03179722473734272</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03268330869887002</v>
+        <v>0.03268330869887003</v>
       </c>
       <c r="M4" t="n">
         <v>0.03191902366685607</v>
@@ -3381,10 +3381,10 @@
         <v>0.03037340342587074</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03094275889987668</v>
+        <v>0.0309427588998767</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03345622799047199</v>
+        <v>0.03345622799047202</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03001969399213206</v>
@@ -3393,13 +3393,13 @@
         <v>0.02932811109317606</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0316343447202348</v>
+        <v>0.03163434472023481</v>
       </c>
       <c r="T4" t="n">
         <v>0.03066622118850084</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03276839433259779</v>
+        <v>0.03276839433259781</v>
       </c>
       <c r="V4" t="n">
         <v>0.03001252007264519</v>
@@ -3408,7 +3408,7 @@
         <v>0.03122154917456049</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03254373722808179</v>
+        <v>0.03254373722808181</v>
       </c>
       <c r="Y4" t="n">
         <v>0.03363006045519847</v>
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07008864480170748</v>
+        <v>0.07008864480170755</v>
       </c>
       <c r="C5" t="n">
         <v>0.03929865342991704</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08612567447102407</v>
+        <v>0.08612567447102416</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04929193369521558</v>
+        <v>0.04929193369521564</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0570814072090217</v>
+        <v>0.05708140720902168</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1006313233642811</v>
+        <v>0.100631323364281</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0428340313663847</v>
+        <v>0.04283403136638469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07723014681922065</v>
+        <v>0.07723014681922076</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07987297202586761</v>
+        <v>0.07987297202586764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08090003911393617</v>
+        <v>0.0809000391139362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09932483585965364</v>
+        <v>0.0993248358596537</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09026306440552712</v>
+        <v>0.09026306440552719</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09707603641932323</v>
+        <v>0.0970760364193235</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06481401897778737</v>
+        <v>0.06481401897778745</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1075897947996043</v>
+        <v>0.1075897947996047</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05304892314571934</v>
+        <v>0.05304892314571942</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04159927408209085</v>
+        <v>0.04159927408209087</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07826442466783831</v>
+        <v>0.07826442466783855</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06630729934705777</v>
+        <v>0.06630729934705792</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09951270156762199</v>
+        <v>0.09951270156762232</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05077504843916981</v>
+        <v>0.05077504843916956</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0743240093278552</v>
+        <v>0.07432400932785514</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09965354954577342</v>
+        <v>0.09965354954577361</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1172028097437504</v>
+        <v>0.1172028097437505</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05491424841654675</v>
+        <v>0.05491424841654678</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08103667299277834</v>
+        <v>0.08103667299277829</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1536552021957285</v>
@@ -3518,37 +3518,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03315517841381251</v>
+        <v>0.03183646733316828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02993245915593958</v>
+        <v>0.02993245915593959</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03376219771776167</v>
+        <v>0.03376219771776168</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03053497029964004</v>
+        <v>0.03053497029964005</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03087359291289702</v>
+        <v>0.03219230399354127</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03503010354007632</v>
+        <v>0.03371139245943208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03006246985307778</v>
+        <v>0.03006246985307779</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03323647182181581</v>
+        <v>0.03191776074117158</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0336523067276526</v>
+        <v>0.03365230672765261</v>
       </c>
       <c r="K6" t="n">
-        <v>0.032482753512986</v>
+        <v>0.03380146459363024</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03468754855515755</v>
+        <v>0.03336883747451331</v>
       </c>
       <c r="M6" t="n">
         <v>0.03392326352314361</v>
@@ -3557,46 +3557,46 @@
         <v>0.03106475311483504</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03293962192728432</v>
+        <v>0.031634108588841</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03545308346699264</v>
+        <v>0.03545308346699266</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03202393384841958</v>
+        <v>0.03202393384841959</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03133235094946358</v>
+        <v>0.03133235094946359</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03231987349587806</v>
+        <v>0.03231987349587808</v>
       </c>
       <c r="T6" t="n">
         <v>0.03135174996414412</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03481430843045707</v>
+        <v>0.03349559734981285</v>
       </c>
       <c r="V6" t="n">
         <v>0.03201675992893271</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03321840167063167</v>
+        <v>0.03197623371043964</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03322926600372506</v>
+        <v>0.03322926600372509</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03441102549246033</v>
+        <v>0.03441102549246034</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03231224672958784</v>
+        <v>0.03099353564894361</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03228098426387365</v>
+        <v>0.03359969534451789</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03574111548756469</v>
+        <v>0.0357411154875647</v>
       </c>
     </row>
     <row r="7">
@@ -3606,13 +3606,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03196435361746793</v>
+        <v>0.03196435361746795</v>
       </c>
       <c r="C7" t="n">
         <v>0.03006034544023924</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0325713729214171</v>
+        <v>0.03257137292141711</v>
       </c>
       <c r="E7" t="n">
         <v>0.0306628565839397</v>
@@ -3633,10 +3633,10 @@
         <v>0.03246148193130802</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03261063979728564</v>
+        <v>0.03261063979728566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03349672375881296</v>
+        <v>0.03349672375881297</v>
       </c>
       <c r="M7" t="n">
         <v>0.03273243872679901</v>
@@ -3645,10 +3645,10 @@
         <v>0.03118681848581368</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03175605513476314</v>
+        <v>0.03175605513476315</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03426952422535843</v>
+        <v>0.03426952422535846</v>
       </c>
       <c r="Q7" t="n">
         <v>0.030833109052075</v>
@@ -3657,13 +3657,13 @@
         <v>0.030141526153119</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03244775978017773</v>
+        <v>0.03244775978017775</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03147963624844377</v>
+        <v>0.03147963624844378</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03362202732195563</v>
+        <v>0.03362202732195566</v>
       </c>
       <c r="V7" t="n">
         <v>0.03082593513258813</v>
@@ -3675,7 +3675,7 @@
         <v>0.03335715228802474</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03448514975671314</v>
+        <v>0.03448514975671316</v>
       </c>
       <c r="Z7" t="n">
         <v>0.03112142193324327</v>
@@ -3697,82 +3697,82 @@
         <v>0.03312669666958942</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03282253095014936</v>
+        <v>0.03282253095014937</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03533355843132722</v>
+        <v>0.03533355843132723</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03342504209384983</v>
+        <v>0.03257317317752331</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03241305900645987</v>
+        <v>0.03241305900645988</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03660146425364186</v>
+        <v>0.03693320200925242</v>
       </c>
       <c r="H8" t="n">
         <v>0.03295254164728757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03480783253538136</v>
+        <v>0.03480783253538137</v>
       </c>
       <c r="J8" t="n">
         <v>0.03522366744121815</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03537282530719577</v>
+        <v>0.03537282530719579</v>
       </c>
       <c r="L8" t="n">
         <v>0.03625890926872308</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03549462423670913</v>
+        <v>0.03549462423670903</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03270885844306502</v>
+        <v>0.03270885844306503</v>
       </c>
       <c r="O8" t="n">
         <v>0.03361901668282834</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03604894678059945</v>
+        <v>0.03604894678059947</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03168104654667964</v>
+        <v>0.03168104654667965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03290371166302912</v>
+        <v>0.03290371166302913</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03520994529008785</v>
+        <v>0.03520994529008788</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03424182175835389</v>
+        <v>0.03424182175835391</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03540023611907594</v>
+        <v>0.03560377087342737</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03358812064249826</v>
+        <v>0.03314971632508475</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0347974641590677</v>
+        <v>0.03479746415906772</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03435171852268074</v>
+        <v>0.03435171852268075</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03883624902398797</v>
+        <v>0.038836249023988</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03388360744315339</v>
+        <v>0.03225404709036935</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03517105605808343</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04027367576526659</v>
+        <v>0.04027367576526661</v>
       </c>
     </row>
     <row r="9">
@@ -3782,28 +3782,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03439110146019858</v>
+        <v>0.03439110146019859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03353310735472617</v>
+        <v>0.03353310735472616</v>
       </c>
       <c r="D9" t="n">
         <v>0.03604413483590403</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03413561849842662</v>
+        <v>0.03389420318874579</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0344742411116836</v>
+        <v>0.03206289239192105</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03731204065821868</v>
+        <v>0.03731204127114683</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03366311805186438</v>
+        <v>0.03366311805186437</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03551840893995817</v>
+        <v>0.03551840893995818</v>
       </c>
       <c r="J9" t="n">
         <v>0.03593424384579495</v>
@@ -3812,10 +3812,10 @@
         <v>0.0360834017117726</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03696948567329989</v>
+        <v>0.03696948567329988</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03620520064128595</v>
+        <v>0.03620520064128594</v>
       </c>
       <c r="N9" t="n">
         <v>0.03465958040030061</v>
@@ -3824,43 +3824,43 @@
         <v>0.03557558438409995</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03816444344478705</v>
+        <v>0.03816444344478706</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03430587157949008</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03361428806760592</v>
+        <v>0.03361428806760593</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03592052169466466</v>
+        <v>0.03592052169466468</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0349523981629307</v>
+        <v>0.03495239816293071</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03709624554859939</v>
+        <v>0.03709624554859942</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03429869704707505</v>
+        <v>0.03550577468261967</v>
       </c>
       <c r="W9" t="n">
         <v>0.03550772614899036</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03682991420251167</v>
+        <v>0.03682991420251168</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03795791167120009</v>
+        <v>0.0379579116712001</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03459418384773019</v>
+        <v>0.03396353062104861</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03588163246266023</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03931308294624448</v>
+        <v>0.03931308294624449</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007827568819477311</v>
+        <v>0.007827568819477305</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008391724928521339</v>
+        <v>0.008391724928521336</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007825425062878024</v>
+        <v>0.00782542506287803</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007709826960248843</v>
+        <v>0.007709826960248852</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007797463905026714</v>
+        <v>0.007797463905026722</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00798019011653967</v>
+        <v>0.007980190116539677</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007700769151549492</v>
+        <v>0.007700769151549489</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007854455920922491</v>
+        <v>0.007854455920922498</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007878720114733458</v>
+        <v>0.007878720114733452</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007964070884178749</v>
+        <v>0.007964070884178744</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007939692413115226</v>
+        <v>0.007939692413115235</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007883487254700661</v>
+        <v>0.00788348725470066</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007737599302715881</v>
+        <v>0.007737599302715885</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01150324730757608</v>
+        <v>0.01150324730757606</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008017875410086058</v>
+        <v>0.008017875410086063</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007759673135342198</v>
+        <v>0.007759673135342202</v>
       </c>
       <c r="R2" t="n">
-        <v>0.00773424491342837</v>
+        <v>0.007734244913428378</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007883747285333998</v>
+        <v>0.007883747285334006</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007826853953485237</v>
+        <v>0.007826853953485242</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01004378413303806</v>
+        <v>0.01004378413303807</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007832953920077507</v>
+        <v>0.007832953920077516</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009501639196994623</v>
+        <v>0.00950163919699463</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007998625433601024</v>
+        <v>0.007998625433601025</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008361405853053184</v>
+        <v>0.008361405853053186</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009464869673200961</v>
+        <v>0.009464869673200963</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007919288649098997</v>
+        <v>0.007919288649099004</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008155149619928899</v>
+        <v>0.008155149619928895</v>
       </c>
     </row>
     <row r="3">
@@ -4114,82 +4114,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008454194710010784</v>
+        <v>0.008454194710010793</v>
       </c>
       <c r="C3" t="n">
         <v>0.008599701700770478</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008446081973338147</v>
+        <v>0.008446081973338158</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007618241762552116</v>
+        <v>0.007618241762552113</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008248264872517093</v>
+        <v>0.0082482648725171</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009536948960351479</v>
+        <v>0.009536948960351475</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007558530454319375</v>
+        <v>0.007558530454319369</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008656635562318589</v>
+        <v>0.00865663556231859</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008820752383318534</v>
+        <v>0.008820752383318536</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00942730633886677</v>
+        <v>0.009427306338866771</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00925576760936231</v>
+        <v>0.009255767609362314</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008873968975894025</v>
+        <v>0.008873968975894023</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007819784128693465</v>
+        <v>0.007819784128693457</v>
       </c>
       <c r="O3" t="n">
         <v>0.0143858349558243</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009804071095207209</v>
+        <v>0.009804071095207216</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007975549668087474</v>
+        <v>0.007975549668087476</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007797883758512672</v>
+        <v>0.007797883758512676</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008854935210885753</v>
+        <v>0.008854935210885756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008459978301210059</v>
+        <v>0.00845997830121006</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01326057284125438</v>
+        <v>0.01326057284125439</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008490716180117647</v>
+        <v>0.008490716180117645</v>
       </c>
       <c r="W3" t="n">
         <v>0.01111779855718265</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00968175480896589</v>
+        <v>0.009681754808965897</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01227554938243166</v>
+        <v>0.01227554938243167</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0108269172315799</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009116683119692447</v>
+        <v>0.009116683119692451</v>
       </c>
       <c r="AB3" t="n">
         <v>0.01079581240235641</v>
@@ -4229,7 +4229,7 @@
         <v>0.03151950807780197</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03248728051115227</v>
+        <v>0.03248728051115228</v>
       </c>
       <c r="L4" t="n">
         <v>0.03221191446583926</v>
@@ -4244,7 +4244,7 @@
         <v>0.03066616356385807</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03309502738258027</v>
+        <v>0.03309502738258026</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03017851391043366</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06352790724788099</v>
+        <v>0.06352790724788102</v>
       </c>
       <c r="C5" t="n">
         <v>0.03816177832456365</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06682429788443645</v>
+        <v>0.0668242978844365</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04227362143955751</v>
+        <v>0.04227362143955753</v>
       </c>
       <c r="F5" t="n">
         <v>0.06214155529079396</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09064396575285098</v>
+        <v>0.09064396575285107</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04302135859627989</v>
+        <v>0.0430213585962799</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07436471825424171</v>
+        <v>0.07436471825424176</v>
       </c>
       <c r="J5" t="n">
         <v>0.07451444678890243</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09022268988220901</v>
+        <v>0.09022268988220909</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08662288411220875</v>
+        <v>0.08662288411220885</v>
       </c>
       <c r="M5" t="n">
         <v>0.07976592511153867</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09994715337407716</v>
+        <v>0.09994715337407729</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05853799033587109</v>
+        <v>0.05853799033587113</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09721932075889163</v>
+        <v>0.09721932075889174</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05303677525994156</v>
+        <v>0.0530367752599416</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04993459917933137</v>
+        <v>0.04993459917933143</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07464338032197633</v>
+        <v>0.07464338032197643</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06902629187066284</v>
+        <v>0.06902629187066289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1033351924227972</v>
+        <v>0.103335192422797</v>
       </c>
       <c r="V5" t="n">
         <v>0.06358881718843162</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06328116715254709</v>
+        <v>0.06328116715254706</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1011841382857817</v>
+        <v>0.1011841382857818</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1760503741394919</v>
+        <v>0.176050374139492</v>
       </c>
       <c r="Z5" t="n">
         <v>0.05117383882445293</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08593489568283362</v>
+        <v>0.0859348956828337</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1412844959682218</v>
+        <v>0.141284495968222</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03184363490514402</v>
+        <v>0.03323230529774924</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03020974604543101</v>
+        <v>0.030209746045431</v>
       </c>
       <c r="D6" t="n">
         <v>0.03181942018817841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03051368644122732</v>
+        <v>0.03190235683383253</v>
       </c>
       <c r="F6" t="n">
         <v>0.03150358604747976</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03356756266472888</v>
+        <v>0.03495623305733409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03180004471777551</v>
+        <v>0.03041137432517029</v>
       </c>
       <c r="I6" t="n">
         <v>0.03214733708464521</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03241771608664853</v>
+        <v>0.03380638647925373</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03477415891260401</v>
+        <v>0.03477415891260402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03311012247468581</v>
+        <v>0.03449879286729102</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03249667486218511</v>
+        <v>0.0324966748621851</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0308385386999159</v>
+        <v>0.03083853869991588</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03157552244731925</v>
+        <v>0.03295587318170159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03538472669141509</v>
+        <v>0.0339160202188951</v>
       </c>
       <c r="Q6" t="n">
         <v>0.03246539231188542</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03217816884780873</v>
+        <v>0.03217816884780872</v>
       </c>
       <c r="S6" t="n">
         <v>0.03386686691297173</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03183556016490905</v>
+        <v>0.03322423055751427</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03560409726662646</v>
+        <v>0.03421542687402125</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03326919423029413</v>
+        <v>0.03188052383768891</v>
       </c>
       <c r="W6" t="n">
         <v>0.03301528438414737</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03377579805160155</v>
+        <v>0.03377579805160156</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03794957550687245</v>
+        <v>0.03794957550687244</v>
       </c>
       <c r="Z6" t="n">
         <v>0.03255446380187671</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03426832296653254</v>
+        <v>0.03426832296653255</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0355319601406477</v>
+        <v>0.03553196014064769</v>
       </c>
     </row>
     <row r="7">
@@ -4478,10 +4478,10 @@
         <v>0.03035164317202134</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03134154277827379</v>
+        <v>0.03134154277827378</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03340551939552291</v>
+        <v>0.0334055193955229</v>
       </c>
       <c r="H7" t="n">
         <v>0.03024933105596432</v>
@@ -4490,7 +4490,7 @@
         <v>0.03198529381543923</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03225567281744256</v>
+        <v>0.03225567281744255</v>
       </c>
       <c r="K7" t="n">
         <v>0.03322344525079284</v>
@@ -4502,7 +4502,7 @@
         <v>0.03233463159297913</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03066534455609528</v>
+        <v>0.03066534455609527</v>
       </c>
       <c r="O7" t="n">
         <v>0.03140220788394625</v>
@@ -4514,16 +4514,16 @@
         <v>0.03091467865007424</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03062745518599754</v>
+        <v>0.03062745518599753</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03231615325116055</v>
+        <v>0.03231615325116056</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03167351689570308</v>
+        <v>0.03167351689570309</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03405212037776119</v>
+        <v>0.0340521203777612</v>
       </c>
       <c r="V7" t="n">
         <v>0.03171848056848294</v>
@@ -4532,10 +4532,10 @@
         <v>0.03146174453529124</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0336137547823956</v>
+        <v>0.03361375478239559</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03771152650734584</v>
+        <v>0.03771152650734586</v>
       </c>
       <c r="Z7" t="n">
         <v>0.03100375014006553</v>
@@ -4563,13 +4563,13 @@
         <v>0.03457277921518465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03326704546823356</v>
+        <v>0.03237811619145409</v>
       </c>
       <c r="F8" t="n">
         <v>0.03284758158477757</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03632092169173511</v>
+        <v>0.0366670916217838</v>
       </c>
       <c r="H8" t="n">
         <v>0.03316473335217654</v>
@@ -4578,7 +4578,7 @@
         <v>0.03490069611165145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03517107511365477</v>
+        <v>0.03517107511365476</v>
       </c>
       <c r="K8" t="n">
         <v>0.03613884754700505</v>
@@ -4587,13 +4587,13 @@
         <v>0.03586348150169205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03525003388919137</v>
+        <v>0.0352500338891913</v>
       </c>
       <c r="N8" t="n">
         <v>0.0322866490538137</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03337926211258746</v>
+        <v>0.03337926211258745</v>
       </c>
       <c r="P8" t="n">
         <v>0.0357209525938963</v>
@@ -4608,31 +4608,31 @@
         <v>0.03523155554737276</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0345889191919153</v>
+        <v>0.03458891919191529</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03594066584865809</v>
+        <v>0.03615306729222439</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03463388286469515</v>
+        <v>0.03417662201287846</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03437747492469945</v>
+        <v>0.03437747492469944</v>
       </c>
       <c r="X8" t="n">
         <v>0.0346846379350464</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04228530312683813</v>
+        <v>0.04228530312683814</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03391915243627775</v>
+        <v>0.03221869843671888</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03563301160093358</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04000156344935685</v>
+        <v>0.04000156344935683</v>
       </c>
     </row>
     <row r="9">
@@ -4651,34 +4651,34 @@
         <v>0.03487864650686757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03357291275991646</v>
+        <v>0.03334277582119929</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0345628123661689</v>
+        <v>0.03226411632448363</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03662678898341802</v>
+        <v>0.03662678956965627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03347060064385944</v>
+        <v>0.03347060064385943</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03520656340333434</v>
+        <v>0.03520656340333433</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03547694240533767</v>
+        <v>0.03547694240533766</v>
       </c>
       <c r="K9" t="n">
         <v>0.03644471483868795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03616934879337495</v>
+        <v>0.03616934879337494</v>
       </c>
       <c r="M9" t="n">
         <v>0.03555590118087425</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03388661414399038</v>
+        <v>0.03388661414399037</v>
       </c>
       <c r="O9" t="n">
         <v>0.03495405178060151</v>
@@ -4702,7 +4702,7 @@
         <v>0.03727465319271039</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03493975015637805</v>
+        <v>0.03609043609448213</v>
       </c>
       <c r="W9" t="n">
         <v>0.03468301412318636</v>
@@ -4714,7 +4714,7 @@
         <v>0.04093279609524095</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03422501972796064</v>
+        <v>0.03362382917409964</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03593887889261647</v>
@@ -4886,43 +4886,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007237802745885161</v>
+        <v>0.007237802745885184</v>
       </c>
       <c r="C2" t="n">
         <v>0.00804737264499779</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007294089668222658</v>
+        <v>0.00729408966822266</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007247030948687086</v>
+        <v>0.007247030948687095</v>
       </c>
       <c r="F2" t="n">
         <v>0.007234617962870104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007303435344876071</v>
+        <v>0.007303435344876076</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007281342129161842</v>
+        <v>0.007281342129161853</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007275557861570503</v>
+        <v>0.007275557861570512</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007291017370547252</v>
+        <v>0.00729101737054726</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007351584838067542</v>
+        <v>0.007351584838067543</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007371659200097742</v>
+        <v>0.007371659200097746</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007339348758789324</v>
+        <v>0.007339348758789318</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007322148446117484</v>
+        <v>0.007322148446117486</v>
       </c>
       <c r="O2" t="n">
         <v>0.0107360727740867</v>
@@ -4931,40 +4931,40 @@
         <v>0.007325210422375578</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007274328723402093</v>
+        <v>0.007274328723402102</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007287378974354271</v>
+        <v>0.007287378974354284</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007290415984700488</v>
+        <v>0.007290415984700504</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007252232616918775</v>
+        <v>0.007252232616918778</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009726354198831744</v>
+        <v>0.009726354198831767</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007229227126276363</v>
+        <v>0.007229227126276365</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009265013187894754</v>
+        <v>0.009265013187894779</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007312252668139312</v>
+        <v>0.007312252668139338</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007237949192145885</v>
+        <v>0.00723794919214589</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008961054030580694</v>
+        <v>0.008961054030580692</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007318675632806142</v>
+        <v>0.007318675632806145</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007338354361868917</v>
+        <v>0.007338354361868918</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007094583672737364</v>
+        <v>0.007094583672737374</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00822785299169118</v>
+        <v>0.008227852991691174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00749982472897882</v>
+        <v>0.007499824728978832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007161142672513674</v>
+        <v>0.007161142672513682</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007074544052494899</v>
+        <v>0.00707454405249491</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00755870227916646</v>
+        <v>0.007558702279166478</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007410742007702545</v>
+        <v>0.007410742007702543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007367853401690306</v>
+        <v>0.007367853401690304</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007473027037794959</v>
+        <v>0.007473027037794973</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007905317298558248</v>
+        <v>0.007905317298558277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00804350123559756</v>
+        <v>0.008043501235597572</v>
       </c>
       <c r="M3" t="n">
         <v>0.007827846666103212</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007697935036642151</v>
+        <v>0.007697935036642164</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01293018431242074</v>
+        <v>0.01293018431242073</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007716309129661648</v>
+        <v>0.007716309129661664</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007356429773681478</v>
+        <v>0.00735642977368149</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007453532759299359</v>
+        <v>0.007453532759299369</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007465185806015942</v>
+        <v>0.007465185806015952</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007199701813541841</v>
+        <v>0.007199701813541853</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01184695008632507</v>
+        <v>0.01184695008632508</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0070336996596518</v>
+        <v>0.007033699659651833</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01098363483635853</v>
+        <v>0.01098363483635856</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007629015553180016</v>
+        <v>0.007629015553180026</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007097323502016382</v>
+        <v>0.0070973235020164</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01014216724099402</v>
+        <v>0.01014216724099403</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007673633144172948</v>
+        <v>0.00767363314417296</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007818041724867575</v>
+        <v>0.00781804172486757</v>
       </c>
     </row>
     <row r="4">
@@ -5080,10 +5080,10 @@
         <v>0.02958625408137228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02933670104649874</v>
+        <v>0.02933670104649873</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02927136508316004</v>
+        <v>0.02927136508316003</v>
       </c>
       <c r="J4" t="n">
         <v>0.0294423272872949</v>
@@ -5092,7 +5092,7 @@
         <v>0.03013012475683108</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03035687391062488</v>
+        <v>0.03035687391062489</v>
       </c>
       <c r="M4" t="n">
         <v>0.03000763747704185</v>
@@ -5113,10 +5113,10 @@
         <v>0.02940488999003322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02943919441898759</v>
+        <v>0.0294391944189876</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02900789571467597</v>
+        <v>0.02900789571467596</v>
       </c>
       <c r="U4" t="n">
         <v>0.03015365528131589</v>
@@ -5125,7 +5125,7 @@
         <v>0.02872434035887433</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0299583396901045</v>
+        <v>0.02995833969010449</v>
       </c>
       <c r="X4" t="n">
         <v>0.02968584980379974</v>
@@ -5150,25 +5150,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03942281154134882</v>
+        <v>0.03942281154134884</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03258097173859001</v>
+        <v>0.03258097173859</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05340101903043144</v>
+        <v>0.05340101903043145</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04178126914291698</v>
+        <v>0.04178126914291699</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04023886216627132</v>
+        <v>0.04023886216627138</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05104622309063136</v>
+        <v>0.05104622309063142</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05173355946820753</v>
+        <v>0.05173355946820754</v>
       </c>
       <c r="I5" t="n">
         <v>0.04960501287634863</v>
@@ -5177,22 +5177,22 @@
         <v>0.05003243058450206</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06298127551894153</v>
+        <v>0.06298127551894146</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06443904349426577</v>
+        <v>0.06443904349426578</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06139677210376693</v>
+        <v>0.0613967721037669</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06330830701438248</v>
+        <v>0.06330830701438252</v>
       </c>
       <c r="O5" t="n">
         <v>0.04131620048193621</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05691868914992429</v>
+        <v>0.0569186891499243</v>
       </c>
       <c r="Q5" t="n">
         <v>0.04786802646986433</v>
@@ -5201,34 +5201,34 @@
         <v>0.05285907516027764</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04793380449784628</v>
+        <v>0.04793380449784627</v>
       </c>
       <c r="T5" t="n">
         <v>0.04369004994608502</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06368540357939105</v>
+        <v>0.06368540357939104</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03774589772323327</v>
+        <v>0.03774589772323319</v>
       </c>
       <c r="W5" t="n">
-        <v>0.061564157353589</v>
+        <v>0.06156415735358899</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05703577433323095</v>
+        <v>0.05703577433323096</v>
       </c>
       <c r="Y5" t="n">
         <v>0.04039656365872749</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04628489264410727</v>
+        <v>0.04628489264410724</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05772713699099037</v>
+        <v>0.05772713699099039</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06404620641598273</v>
+        <v>0.06404620641598267</v>
       </c>
     </row>
     <row r="6">
@@ -5238,40 +5238,40 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02951634123017744</v>
+        <v>0.02951634123017742</v>
       </c>
       <c r="C6" t="n">
         <v>0.03028700867200759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03134600400139049</v>
+        <v>0.03015212791124297</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03081445411615565</v>
+        <v>0.02962057802600812</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03067424373109714</v>
+        <v>0.03067424373109715</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03025769162826696</v>
+        <v>0.03145156771841447</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03000813859339341</v>
+        <v>0.0300081385933934</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03113667872020223</v>
+        <v>0.0299428026300547</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03011376483418959</v>
+        <v>0.03011376483418958</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03199543839387327</v>
+        <v>0.03080156230372575</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03222218754766708</v>
+        <v>0.03102831145751955</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03067907502393653</v>
+        <v>0.03187295111408404</v>
       </c>
       <c r="N6" t="n">
         <v>0.03047034177655115</v>
@@ -5280,40 +5280,40 @@
         <v>0.0308345221460269</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03169418053768953</v>
+        <v>0.03043618861216263</v>
       </c>
       <c r="Q6" t="n">
         <v>0.03112279503915844</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0312702036270754</v>
+        <v>0.03007632753692788</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03130450805602979</v>
+        <v>0.03011063196588226</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02967933326157065</v>
+        <v>0.03087320935171816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03204003737039657</v>
+        <v>0.03084616128024906</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02939577790576902</v>
+        <v>0.03058965399591652</v>
       </c>
       <c r="W6" t="n">
         <v>0.03069617608179066</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03035728735069443</v>
+        <v>0.0303572873506944</v>
       </c>
       <c r="Y6" t="n">
         <v>0.02956929045237721</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02993851598916659</v>
+        <v>0.0311323920793141</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03042983769131593</v>
+        <v>0.03162371378146344</v>
       </c>
       <c r="AB6" t="n">
         <v>0.03065861741692566</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02959600645030787</v>
+        <v>0.02959600645030788</v>
       </c>
       <c r="C7" t="n">
         <v>0.02917279780199053</v>
@@ -5338,7 +5338,7 @@
         <v>0.02970024324613858</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02956003286108008</v>
+        <v>0.02956003286108007</v>
       </c>
       <c r="G7" t="n">
         <v>0.0303373568483974</v>
@@ -5347,7 +5347,7 @@
         <v>0.03008780381352386</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03002246785018517</v>
+        <v>0.03002246785018516</v>
       </c>
       <c r="J7" t="n">
         <v>0.03019343005432003</v>
@@ -5356,7 +5356,7 @@
         <v>0.0308812275238562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03110797667765</v>
+        <v>0.03110797667765001</v>
       </c>
       <c r="M7" t="n">
         <v>0.03075874024406698</v>
@@ -5365,16 +5365,16 @@
         <v>0.03054872993537093</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02972352952653517</v>
+        <v>0.02972352952653516</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03058319063689374</v>
+        <v>0.03058319063689375</v>
       </c>
       <c r="Q7" t="n">
         <v>0.03000858416914138</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03015599275705835</v>
+        <v>0.03015599275705834</v>
       </c>
       <c r="S7" t="n">
         <v>0.03019029718601272</v>
@@ -5386,7 +5386,7 @@
         <v>0.030924595181807</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02947544312589946</v>
+        <v>0.02947544312589945</v>
       </c>
       <c r="W7" t="n">
         <v>0.03070944245712962</v>
@@ -5395,7 +5395,7 @@
         <v>0.03043695257082486</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02959766062819127</v>
+        <v>0.02959766062819128</v>
       </c>
       <c r="Z7" t="n">
         <v>0.03001818120929703</v>
@@ -5404,7 +5404,7 @@
         <v>0.03050950291144637</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03073208834101166</v>
+        <v>0.03073208834101165</v>
       </c>
     </row>
     <row r="8">
@@ -5414,22 +5414,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03072873441612899</v>
+        <v>0.030728734416129</v>
       </c>
       <c r="C8" t="n">
         <v>0.03183975902436886</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03289875435375176</v>
+        <v>0.03289875435375175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03236720446851691</v>
+        <v>0.03155027051648584</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03093177643728568</v>
+        <v>0.03093177643728569</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03300431807077574</v>
+        <v>0.03332245133110956</v>
       </c>
       <c r="H8" t="n">
         <v>0.03275476503590218</v>
@@ -5441,13 +5441,13 @@
         <v>0.03286039127669838</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03354818874623454</v>
+        <v>0.03354818874623453</v>
       </c>
       <c r="L8" t="n">
         <v>0.03377493790002834</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03342570146644532</v>
+        <v>0.03342570146644516</v>
       </c>
       <c r="N8" t="n">
         <v>0.03202640371223479</v>
@@ -5459,7 +5459,7 @@
         <v>0.03230770358260999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03083980028293096</v>
+        <v>0.03083980028293095</v>
       </c>
       <c r="R8" t="n">
         <v>0.03282295397943668</v>
@@ -5468,13 +5468,13 @@
         <v>0.03285725840839106</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03242595970407943</v>
+        <v>0.03242595970407942</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03264789593371755</v>
+        <v>0.0328430921424392</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03214240434827779</v>
+        <v>0.0317221302350249</v>
       </c>
       <c r="W8" t="n">
         <v>0.0333767052001161</v>
@@ -5486,13 +5486,13 @@
         <v>0.03378860931227307</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03268514243167537</v>
+        <v>0.03112241000471409</v>
       </c>
       <c r="AA8" t="n">
         <v>0.0331764641338247</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03500168449019254</v>
+        <v>0.03500168449019253</v>
       </c>
     </row>
     <row r="9">
@@ -5505,25 +5505,25 @@
         <v>0.03170925913265717</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03222499957709214</v>
+        <v>0.03222499957709215</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03328399490647503</v>
+        <v>0.03328399490647504</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0327524450212402</v>
+        <v>0.03253573976825012</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03261223463618169</v>
+        <v>0.03044770008988872</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03338955862349902</v>
+        <v>0.0333895591015433</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03314000558862547</v>
+        <v>0.03314000558862548</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03307466962528678</v>
+        <v>0.03307466962528679</v>
       </c>
       <c r="J9" t="n">
         <v>0.03324563182942165</v>
@@ -5538,16 +5538,16 @@
         <v>0.03381094201916859</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03360093171047255</v>
+        <v>0.03360093171047256</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03308702416688465</v>
+        <v>0.03308702416688467</v>
       </c>
       <c r="P9" t="n">
         <v>0.03401435868670534</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03306078642228726</v>
+        <v>0.03306078642228727</v>
       </c>
       <c r="R9" t="n">
         <v>0.03320819453215996</v>
@@ -5559,13 +5559,13 @@
         <v>0.0328112002568027</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03397802827548113</v>
+        <v>0.03397802827548114</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03252764490100107</v>
+        <v>0.03361117202216007</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03376164423223123</v>
+        <v>0.03376164423223124</v>
       </c>
       <c r="X9" t="n">
         <v>0.03348915434592648</v>
@@ -5574,10 +5574,10 @@
         <v>0.03264986240329289</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03307038298439865</v>
+        <v>0.03250428036590615</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03356170468654798</v>
+        <v>0.03356170468654799</v>
       </c>
       <c r="AB9" t="n">
         <v>0.03378429011611327</v>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007170991679834608</v>
+        <v>0.0071709916798346</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008034288054307451</v>
+        <v>0.008034288054307455</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007170309342722282</v>
+        <v>0.00717030934272227</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007206400049154975</v>
+        <v>0.007206400049154966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007206417610019807</v>
+        <v>0.007206417610019798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007190397754920609</v>
+        <v>0.007190397754920597</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007195541070481053</v>
+        <v>0.007195541070481042</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007193032904358897</v>
+        <v>0.007193032904358898</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007198939742702337</v>
+        <v>0.007198939742702343</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007177328143401661</v>
+        <v>0.007177328143401656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007207191966299931</v>
+        <v>0.007207191966299916</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007159300786195245</v>
+        <v>0.007159300786195248</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007206888055681562</v>
+        <v>0.007206888055681556</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01067838283664722</v>
+        <v>0.01067838283664721</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007199135401869403</v>
+        <v>0.007199135401869389</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007161071741473856</v>
+        <v>0.007161071741473846</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007268625082024288</v>
+        <v>0.007268625082024281</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007206236704288386</v>
+        <v>0.007206236704288377</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007171164018006035</v>
+        <v>0.007171164018006021</v>
       </c>
       <c r="U2" t="n">
         <v>0.009547261519045454</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007199022931968491</v>
+        <v>0.007199022931968483</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009219745921195167</v>
+        <v>0.009219745921195151</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007347355599109361</v>
+        <v>0.007347355599109352</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007196013671653999</v>
+        <v>0.007196013671653996</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008900604224501604</v>
+        <v>0.008900604224501592</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007234435896035581</v>
+        <v>0.007234435896035571</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007141835683788823</v>
+        <v>0.007141835683788822</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006948376056116209</v>
+        <v>0.006948376056116198</v>
       </c>
       <c r="C3" t="n">
         <v>0.008376382539026001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006944710531648485</v>
+        <v>0.006944710531648475</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007200982026945675</v>
+        <v>0.007200982026945659</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007202818633547205</v>
+        <v>0.007202818633547201</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007084842700229071</v>
+        <v>0.007084842700229066</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007126835206859498</v>
+        <v>0.007126835206859495</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007107620119902648</v>
+        <v>0.007107620119902635</v>
       </c>
       <c r="J3" t="n">
         <v>0.00714683859059066</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006994015400340834</v>
+        <v>0.006994015400340829</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007202937113973388</v>
+        <v>0.007202937113973371</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006881748055189103</v>
+        <v>0.006881748055189107</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007204966723097731</v>
+        <v>0.007204966723097727</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01295131436419625</v>
+        <v>0.01295131436419624</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007148147872489242</v>
+        <v>0.007148147872489246</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00687795784024915</v>
+        <v>0.006877957840249142</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00764906665859193</v>
+        <v>0.007649066658591924</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007196739641532477</v>
+        <v>0.007196739641532471</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006950813152510263</v>
+        <v>0.006950813152510253</v>
       </c>
       <c r="U3" t="n">
         <v>0.01078448066992393</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007146672194295774</v>
+        <v>0.007146672194295757</v>
       </c>
       <c r="W3" t="n">
-        <v>0.010844865488293</v>
+        <v>0.01084486548829299</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008205553285322438</v>
+        <v>0.008205553285322437</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007128179622438702</v>
+        <v>0.007128179622438697</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0100681414692265</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00740233945603907</v>
+        <v>0.007402339456039062</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006752835147428506</v>
+        <v>0.006752835147428499</v>
       </c>
     </row>
     <row r="4">
@@ -5931,16 +5931,16 @@
         <v>0.02852728749257379</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02893494862427644</v>
+        <v>0.02893494862427643</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02893514698232303</v>
+        <v>0.02893514698232304</v>
       </c>
       <c r="G4" t="n">
         <v>0.0287541953494801</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02881229146477739</v>
+        <v>0.02881229146477738</v>
       </c>
       <c r="I4" t="n">
         <v>0.02878396057461429</v>
@@ -5949,22 +5949,22 @@
         <v>0.02884757444780396</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02860656807505532</v>
+        <v>0.0286065680750553</v>
       </c>
       <c r="L4" t="n">
         <v>0.0289438936927285</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02843199421062217</v>
+        <v>0.02843199421062216</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02894046088248823</v>
+        <v>0.02894046088248824</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0289790847701963</v>
+        <v>0.02897908477019631</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02885289109128285</v>
+        <v>0.02885289109128286</v>
       </c>
       <c r="Q4" t="n">
         <v>0.02842294453696633</v>
@@ -5982,25 +5982,25 @@
         <v>0.02834496488333185</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02883163565081179</v>
+        <v>0.0288316356508118</v>
       </c>
       <c r="W4" t="n">
         <v>0.02959767087344163</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03052710640376766</v>
+        <v>0.03052710640376767</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02880695028945067</v>
+        <v>0.02880695028945068</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02908601238396497</v>
+        <v>0.02908601238396496</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02925162641191952</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02822575196861339</v>
+        <v>0.02822575196861341</v>
       </c>
     </row>
     <row r="5">
@@ -6010,46 +6010,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03588365087000685</v>
+        <v>0.03588365087000686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03653352858239372</v>
+        <v>0.03653352858239373</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03637145798822671</v>
+        <v>0.03637145798822668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04290291152590989</v>
+        <v>0.04290291152590993</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04379324414663423</v>
+        <v>0.04379324414663421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03870573763098674</v>
+        <v>0.03870573763098673</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04247177344860406</v>
+        <v>0.04247177344860405</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04128965424056451</v>
+        <v>0.04128965424056453</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04094358347239483</v>
+        <v>0.04094358347239482</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03736496197934927</v>
+        <v>0.03736496197934926</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04114531308883729</v>
+        <v>0.0411453130888373</v>
       </c>
       <c r="M5" t="n">
         <v>0.03459318891146897</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03356474378346948</v>
+        <v>0.03356474378346947</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04251834126758808</v>
+        <v>0.04251834126758806</v>
       </c>
       <c r="P5" t="n">
         <v>0.04094061672146972</v>
@@ -6058,37 +6058,37 @@
         <v>0.03409923776070775</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05739745301966333</v>
+        <v>0.05739745301966341</v>
       </c>
       <c r="S5" t="n">
         <v>0.04127591642788681</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03654363472414036</v>
+        <v>0.03654363472414034</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03297992720729555</v>
+        <v>0.03297992720729556</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04054941037521424</v>
+        <v>0.04054941037521434</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0538955329508372</v>
+        <v>0.05389553295083718</v>
       </c>
       <c r="X5" t="n">
-        <v>0.070318922800111</v>
+        <v>0.07031892280011107</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04151493799194289</v>
+        <v>0.0415149379919429</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0441192687964986</v>
+        <v>0.04411926879649862</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04915901638931054</v>
+        <v>0.0491590163893105</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0312603998461664</v>
+        <v>0.03126039984616639</v>
       </c>
     </row>
     <row r="6">
@@ -6101,10 +6101,10 @@
         <v>0.02918201800088314</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03025464765599321</v>
+        <v>0.02918558412075601</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02917431068930878</v>
+        <v>0.02917431068930877</v>
       </c>
       <c r="E6" t="n">
         <v>0.03065103535624862</v>
@@ -6113,67 +6113,67 @@
         <v>0.03065123371429522</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03047028208145228</v>
+        <v>0.02940121854621508</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03052837819674957</v>
+        <v>0.02945931466151237</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02943098377134928</v>
+        <v>0.02943098377134927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03056366117977614</v>
+        <v>0.02949459764453894</v>
       </c>
       <c r="K6" t="n">
         <v>0.02925359127179029</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03065998042470067</v>
+        <v>0.03065998042470068</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02907901740735714</v>
+        <v>0.03014808094259434</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02958630020791261</v>
+        <v>0.02958630020791263</v>
       </c>
       <c r="O6" t="n">
         <v>0.02962492409562069</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03056204240243321</v>
+        <v>0.02943416602718187</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03013903126893852</v>
+        <v>0.02906996773370132</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03135389572743678</v>
+        <v>0.03135389572743677</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03064919030083801</v>
+        <v>0.02958012676560081</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03025302817504608</v>
+        <v>0.03025302817504607</v>
       </c>
       <c r="U6" t="n">
         <v>0.02900266750304932</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02947865884754678</v>
+        <v>0.03054772238278398</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03030511044599342</v>
+        <v>0.03030511044599339</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03117412960050265</v>
+        <v>0.03117412960050266</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0295122102344383</v>
+        <v>0.02951221023443831</v>
       </c>
       <c r="Z6" t="n">
         <v>0.03080209911593714</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0298986496086545</v>
+        <v>0.0309677131438917</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02886892430828477</v>
@@ -6192,7 +6192,7 @@
         <v>0.02919191669977346</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02918064326832624</v>
+        <v>0.02918064326832623</v>
       </c>
       <c r="E7" t="n">
         <v>0.02958830440002888</v>
@@ -6201,7 +6201,7 @@
         <v>0.02958850275807548</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02940755112523255</v>
+        <v>0.02940755112523254</v>
       </c>
       <c r="H7" t="n">
         <v>0.02946564724052983</v>
@@ -6216,7 +6216,7 @@
         <v>0.02925992385080775</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02959724946848095</v>
+        <v>0.02959724946848094</v>
       </c>
       <c r="M7" t="n">
         <v>0.02908534998637461</v>
@@ -6225,13 +6225,13 @@
         <v>0.02959381665824069</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02963232315658385</v>
+        <v>0.02963232315658384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02950612947767039</v>
+        <v>0.02950612947767038</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02907630031271878</v>
+        <v>0.02907630031271877</v>
       </c>
       <c r="R7" t="n">
         <v>0.03029116477121703</v>
@@ -6243,7 +6243,7 @@
         <v>0.02919029721882634</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0290078918941854</v>
+        <v>0.02900789189418539</v>
       </c>
       <c r="V7" t="n">
         <v>0.02948499142656424</v>
@@ -6252,13 +6252,13 @@
         <v>0.03025102664919408</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03118046217952011</v>
+        <v>0.03118046217952012</v>
       </c>
       <c r="Y7" t="n">
         <v>0.0294709854881856</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02973936815971741</v>
+        <v>0.0297393681597174</v>
       </c>
       <c r="AA7" t="n">
         <v>0.02990498218767196</v>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03021084301797315</v>
+        <v>0.03021084301797316</v>
       </c>
       <c r="C8" t="n">
         <v>0.03158588567854353</v>
@@ -6283,13 +6283,13 @@
         <v>0.0315746122470963</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03198227337879895</v>
+        <v>0.03125200257693469</v>
       </c>
       <c r="F8" t="n">
         <v>0.03082465521238345</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03180152010400261</v>
+        <v>0.03208590469904393</v>
       </c>
       <c r="H8" t="n">
         <v>0.0318596162192999</v>
@@ -6307,13 +6307,13 @@
         <v>0.03199121844725102</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03147931896514467</v>
+        <v>0.03147931896514443</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03092466187490111</v>
+        <v>0.0309246618749011</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03125544140330694</v>
+        <v>0.03125544140330695</v>
       </c>
       <c r="P8" t="n">
         <v>0.03105763331739679</v>
@@ -6328,16 +6328,16 @@
         <v>0.03198042832338833</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0315842661975964</v>
+        <v>0.03158426619759641</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0305583128127947</v>
+        <v>0.03073280182159302</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03187896040533431</v>
+        <v>0.03150326827726398</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03264526516224472</v>
+        <v>0.03264526516224471</v>
       </c>
       <c r="X8" t="n">
         <v>0.03205912672498583</v>
@@ -6346,10 +6346,10 @@
         <v>0.03322726881592058</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03213333713848748</v>
+        <v>0.03073638471694027</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03229895116644203</v>
+        <v>0.03229895116644202</v>
       </c>
       <c r="AB8" t="n">
         <v>0.03270569865075547</v>
@@ -6371,25 +6371,25 @@
         <v>0.03166809823001222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03207575936171488</v>
+        <v>0.03189458751488278</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03207595771976148</v>
+        <v>0.03026634204169052</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03189500608691854</v>
+        <v>0.03189500674432504</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03195310220221582</v>
+        <v>0.03195310220221581</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03192477131205274</v>
+        <v>0.03192477131205273</v>
       </c>
       <c r="J9" t="n">
         <v>0.03198838518524239</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03174737881249375</v>
+        <v>0.03174737881249374</v>
       </c>
       <c r="L9" t="n">
         <v>0.03208470443016694</v>
@@ -6398,22 +6398,22 @@
         <v>0.03157280494806059</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03208127161992667</v>
+        <v>0.03208127161992666</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03238004084350904</v>
+        <v>0.03238004084350903</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03231042416883118</v>
+        <v>0.03231042416883117</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03156375593181128</v>
+        <v>0.03156375593181127</v>
       </c>
       <c r="R9" t="n">
         <v>0.03277861973290302</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03207391430630426</v>
+        <v>0.03207391430630425</v>
       </c>
       <c r="T9" t="n">
         <v>0.03167775218051232</v>
@@ -6422,7 +6422,7 @@
         <v>0.03149645504375276</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03197244638825024</v>
+        <v>0.0328783079717395</v>
       </c>
       <c r="W9" t="n">
         <v>0.03273848161088007</v>
@@ -6434,7 +6434,7 @@
         <v>0.03195844044987159</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0322268231214034</v>
+        <v>0.0317535445758684</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03239243714935795</v>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007327777503651216</v>
+        <v>0.00732777750365122</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008028798722223649</v>
+        <v>0.008028798722223647</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007311058885359619</v>
+        <v>0.007311058885359621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007360860646408185</v>
+        <v>0.007360860646408189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007330313206946</v>
+        <v>0.007330313206946005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007304033377702061</v>
+        <v>0.007304033377702066</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007306527003450248</v>
+        <v>0.007306527003450253</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007301726149730828</v>
+        <v>0.007301726149730831</v>
       </c>
       <c r="J2" t="n">
         <v>0.007323369701420997</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007296040135238505</v>
+        <v>0.007296040135238512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007350477465755624</v>
+        <v>0.007350477465755627</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007288628882486103</v>
+        <v>0.007288628882486101</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007317177951451477</v>
+        <v>0.007317177951451484</v>
       </c>
       <c r="O2" t="n">
         <v>0.0108995105508291</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007347437083801068</v>
+        <v>0.007347437083801075</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007289833489674256</v>
+        <v>0.007289833489674258</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007408173118091296</v>
+        <v>0.007408173118091298</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007333097915964715</v>
+        <v>0.007333097915964723</v>
       </c>
       <c r="T2" t="n">
         <v>0.007297254119345895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009241112977212662</v>
+        <v>0.009241112977212654</v>
       </c>
       <c r="V2" t="n">
         <v>0.007338218415470961</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009020268270277255</v>
+        <v>0.009020268270277253</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007527396558219082</v>
+        <v>0.00752739655821908</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007325075381169222</v>
+        <v>0.007325075381169224</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009005795292526117</v>
+        <v>0.00900579529252612</v>
       </c>
       <c r="AA2" t="n">
         <v>0.007374525630388218</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007284356575872968</v>
+        <v>0.007284356575872967</v>
       </c>
     </row>
     <row r="3">
@@ -6694,40 +6694,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007268757341952418</v>
+        <v>0.007268757341952415</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008329159860513621</v>
+        <v>0.008329159860513618</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007151754216654393</v>
+        <v>0.007151754216654387</v>
       </c>
       <c r="E3" t="n">
         <v>0.007503622530582068</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007290002875419558</v>
+        <v>0.007290002875419557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007099798085464699</v>
+        <v>0.0070997980854647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007120569347320523</v>
+        <v>0.007120569347320522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007085625167481982</v>
+        <v>0.00708562516748198</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007238015720822652</v>
+        <v>0.007238015720822645</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007044282775700418</v>
+        <v>0.007044282775700417</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007428565011542394</v>
+        <v>0.007428565011542395</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007007994342863791</v>
+        <v>0.007007994342863789</v>
       </c>
       <c r="N3" t="n">
         <v>0.007195097144095631</v>
@@ -6736,43 +6736,43 @@
         <v>0.01332309801573729</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007407657230097177</v>
+        <v>0.007407657230097179</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00699975967702286</v>
+        <v>0.006999759677022858</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007848184834696088</v>
+        <v>0.007848184834696084</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007306033754262708</v>
+        <v>0.007306033754262709</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007053400022591276</v>
+        <v>0.007053400022591272</v>
       </c>
       <c r="U3" t="n">
         <v>0.01022738358651022</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007342571371399005</v>
+        <v>0.007342571371399015</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01035949635653896</v>
+        <v>0.01035949635653897</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008690737754197177</v>
+        <v>0.00869073775419717</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007251873883690043</v>
+        <v>0.007251873883690039</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01008984896406454</v>
+        <v>0.01008984896406455</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007604654330935519</v>
+        <v>0.007604654330935516</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006971392679956212</v>
+        <v>0.00697139267995621</v>
       </c>
     </row>
     <row r="4">
@@ -6791,16 +6791,16 @@
         <v>0.02876893241219983</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02933146621318533</v>
+        <v>0.02933146621318534</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02898641883194353</v>
+        <v>0.02898641883194354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02868957607131454</v>
+        <v>0.02868957607131455</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02871774272126482</v>
+        <v>0.02871774272126483</v>
       </c>
       <c r="I4" t="n">
         <v>0.02866351487000215</v>
@@ -6812,7 +6812,7 @@
         <v>0.02859928872061546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0292141834112156</v>
+        <v>0.02921418341121561</v>
       </c>
       <c r="M4" t="n">
         <v>0.02854534560104173</v>
@@ -6851,16 +6851,16 @@
         <v>0.03121256594739374</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02892621005923377</v>
+        <v>0.02892621005923378</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02906688805100515</v>
+        <v>0.02906688805100516</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02948581849344297</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02848509236448547</v>
+        <v>0.02848509236448548</v>
       </c>
     </row>
     <row r="5">
@@ -6870,37 +6870,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0405601415950496</v>
+        <v>0.04056014159504961</v>
       </c>
       <c r="C5" t="n">
         <v>0.03806327427312799</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03842161239729229</v>
+        <v>0.03842161239729228</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04652123220207793</v>
+        <v>0.04652123220207797</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04269814077760147</v>
+        <v>0.04269814077760149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03607762523838933</v>
+        <v>0.03607762523838932</v>
       </c>
       <c r="H5" t="n">
         <v>0.03811706678271982</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03680543670277334</v>
+        <v>0.03680543670277332</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04004808864863586</v>
+        <v>0.04004808864863588</v>
       </c>
       <c r="K5" t="n">
         <v>0.03527511042681435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04395341747970378</v>
+        <v>0.04395341747970376</v>
       </c>
       <c r="M5" t="n">
         <v>0.03454449483508518</v>
@@ -6912,13 +6912,13 @@
         <v>0.04536921351383907</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04375622775762653</v>
+        <v>0.0437562277576265</v>
       </c>
       <c r="Q5" t="n">
         <v>0.03391805593490024</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0595442641575494</v>
+        <v>0.05954426415754944</v>
       </c>
       <c r="S5" t="n">
         <v>0.04126255190891742</v>
@@ -6927,25 +6927,25 @@
         <v>0.03575238512089073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03390807014255255</v>
+        <v>0.03390807014255256</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04226179249355604</v>
+        <v>0.04226179249355606</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05161552319388423</v>
+        <v>0.05161552319388416</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07903503863844734</v>
+        <v>0.07903503863844731</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04126494763047769</v>
+        <v>0.04126494763047771</v>
       </c>
       <c r="Z5" t="n">
         <v>0.04156710608861369</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05106713282331664</v>
+        <v>0.0510671328233166</v>
       </c>
       <c r="AB5" t="n">
         <v>0.03368995975346877</v>
@@ -6964,49 +6964,49 @@
         <v>0.03075388692361686</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03076874195149835</v>
+        <v>0.03076874195149834</v>
       </c>
       <c r="E6" t="n">
         <v>0.03133127575248384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02983039795698661</v>
+        <v>0.03098622837124204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02953355519635762</v>
+        <v>0.03068938561061307</v>
       </c>
       <c r="H6" t="n">
         <v>0.02956172184630791</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03066332440930067</v>
+        <v>0.02950749399504523</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03090472082263245</v>
+        <v>0.02974889040837701</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02944326784565854</v>
+        <v>0.03059909825991397</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03121399295051412</v>
+        <v>0.03121399295051411</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03054515514034024</v>
+        <v>0.03054515514034025</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02967963455622658</v>
+        <v>0.02967963455622657</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03012988939930483</v>
+        <v>0.0312723064845758</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03116383289714009</v>
+        <v>0.03116383289714008</v>
       </c>
       <c r="Q6" t="n">
         <v>0.03052899134306771</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03186569188495685</v>
+        <v>0.03070986147070141</v>
       </c>
       <c r="S6" t="n">
         <v>0.02986185252638253</v>
@@ -7021,19 +7021,19 @@
         <v>0.02989992485021616</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03155216961475859</v>
+        <v>0.0315521696147586</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03321237548669225</v>
+        <v>0.03205654507243681</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02983072809214462</v>
+        <v>0.02983072809214463</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03106669759030367</v>
+        <v>0.02991086717604824</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03148562803274147</v>
+        <v>0.03032979761848604</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02932444566530245</v>
@@ -7052,19 +7052,19 @@
         <v>0.02933491909584415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02934977412372564</v>
+        <v>0.02934977412372563</v>
       </c>
       <c r="E7" t="n">
         <v>0.02991230792471113</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02956726054346933</v>
+        <v>0.02956726054346932</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02927041778284034</v>
+        <v>0.02927041778284035</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02929858443279063</v>
+        <v>0.02929858443279062</v>
       </c>
       <c r="I7" t="n">
         <v>0.02924435658152795</v>
@@ -7076,7 +7076,7 @@
         <v>0.02918013043214126</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02979502512274141</v>
+        <v>0.0297950251227414</v>
       </c>
       <c r="M7" t="n">
         <v>0.02912618731256753</v>
@@ -7085,7 +7085,7 @@
         <v>0.02941889179014266</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0298690273074199</v>
+        <v>0.02986902730741991</v>
       </c>
       <c r="P7" t="n">
         <v>0.02976056328411885</v>
@@ -7097,7 +7097,7 @@
         <v>0.03044672405718413</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02959871511286525</v>
+        <v>0.02959871511286524</v>
       </c>
       <c r="T7" t="n">
         <v>0.02919384294109453</v>
@@ -7106,10 +7106,10 @@
         <v>0.02912323827702001</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02963678743669888</v>
+        <v>0.02963678743669887</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03014900195910687</v>
+        <v>0.03014900195910686</v>
       </c>
       <c r="X7" t="n">
         <v>0.03179340765891953</v>
@@ -7143,40 +7143,40 @@
         <v>0.03189179133469092</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03245432513567643</v>
+        <v>0.03168932773547792</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03089640353181417</v>
+        <v>0.03089640353181416</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03181243499380563</v>
+        <v>0.03211034294152543</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03184060164375591</v>
+        <v>0.0318406016437559</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03178637379249323</v>
+        <v>0.03178637379249322</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03202777020582503</v>
+        <v>0.03202777020582501</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03172214764310655</v>
+        <v>0.03172214764310654</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0323370423337067</v>
+        <v>0.03233704233370669</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03166820452353281</v>
+        <v>0.03166820452353253</v>
       </c>
       <c r="N8" t="n">
         <v>0.03084723046977641</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03160353384310175</v>
+        <v>0.03160353384310174</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03142004992987534</v>
+        <v>0.03142004992987533</v>
       </c>
       <c r="Q8" t="n">
         <v>0.02993300305864808</v>
@@ -7185,34 +7185,34 @@
         <v>0.03298874126814941</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03214073232383054</v>
+        <v>0.03214073232383053</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03173586015205982</v>
+        <v>0.03173586015205981</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03078157680123516</v>
+        <v>0.03096436567290643</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03217880464766417</v>
+        <v>0.03178529023332768</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03269130152154832</v>
+        <v>0.0326913015215483</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03274806310077693</v>
+        <v>0.03274806310077692</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03347727736360798</v>
+        <v>0.03347727736360795</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03218974697349625</v>
+        <v>0.03072636521435735</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03260867741593405</v>
+        <v>0.03260867741593404</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03310869874573762</v>
+        <v>0.03310869874573761</v>
       </c>
     </row>
     <row r="9">
@@ -7231,13 +7231,13 @@
         <v>0.03168370314882727</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03224623694981277</v>
+        <v>0.0320717507813247</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03190118956857096</v>
+        <v>0.03015835297322957</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03160434680794198</v>
+        <v>0.03160434745251182</v>
       </c>
       <c r="H9" t="n">
         <v>0.03163251345789226</v>
@@ -7255,46 +7255,46 @@
         <v>0.03212895414784304</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03146011633766916</v>
+        <v>0.03146011633766917</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0317528208152443</v>
+        <v>0.03175282081524431</v>
       </c>
       <c r="O9" t="n">
         <v>0.03245362103135762</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03239964618787402</v>
+        <v>0.03239964618787401</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03144395318496648</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03278065308228577</v>
+        <v>0.03278065308228576</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03193264413796688</v>
+        <v>0.03193264413796687</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03152777196619617</v>
+        <v>0.03152777196619616</v>
       </c>
       <c r="U9" t="n">
         <v>0.03145827421597033</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03197071646180052</v>
+        <v>0.03284314961083651</v>
       </c>
       <c r="W9" t="n">
         <v>0.03248293098420851</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03412733668402117</v>
+        <v>0.03412733668402116</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03184202591690341</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03198165878763259</v>
+        <v>0.03152584534410496</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03240058923007041</v>
@@ -7466,49 +7466,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00764697887409972</v>
+        <v>0.007646978874099716</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008353800746814613</v>
+        <v>0.008353800746814619</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007642665262954472</v>
+        <v>0.00764266526295447</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007557632556277145</v>
+        <v>0.007557632556277147</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007568922740321221</v>
+        <v>0.007568922740321223</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007868280842122974</v>
+        <v>0.007868280842122977</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007565984540407228</v>
+        <v>0.007565984540407232</v>
       </c>
       <c r="I2" t="n">
         <v>0.007644600464303371</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007734932819345004</v>
+        <v>0.007734932819344997</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007725761605560371</v>
+        <v>0.007725761605560373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007851494050158378</v>
+        <v>0.007851494050158375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007901170514725716</v>
+        <v>0.007901170514725714</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007736892182816405</v>
+        <v>0.007736892182816404</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0112534894271153</v>
+        <v>0.01125348942711531</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007805120565690679</v>
+        <v>0.00780512056569068</v>
       </c>
       <c r="Q2" t="n">
         <v>0.007592744108356592</v>
@@ -7517,31 +7517,31 @@
         <v>0.007601769144771115</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007669833426083864</v>
+        <v>0.00766983342608386</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007637885325412542</v>
+        <v>0.007637885325412541</v>
       </c>
       <c r="U2" t="n">
         <v>0.01020153659204057</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007552413055748854</v>
+        <v>0.007552413055748856</v>
       </c>
       <c r="W2" t="n">
         <v>0.009586200018475337</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007776578157230366</v>
+        <v>0.007776578157230368</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007706597468601484</v>
+        <v>0.007706597468601489</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009316077940578609</v>
+        <v>0.009316077940578607</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007694457264878155</v>
+        <v>0.007694457264878158</v>
       </c>
       <c r="AB2" t="n">
         <v>0.007996203351260389</v>
@@ -7554,82 +7554,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008169666462349588</v>
+        <v>0.008169666462349581</v>
       </c>
       <c r="C3" t="n">
         <v>0.008582721722271739</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008148157546282253</v>
+        <v>0.008148157546282245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007536466547268288</v>
+        <v>0.007536466547268289</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007620082080554142</v>
+        <v>0.007620082080554139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009740173268289871</v>
+        <v>0.009740173268289876</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007600814338465372</v>
+        <v>0.007600814338465374</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008162103784143502</v>
+        <v>0.008162103784143499</v>
       </c>
       <c r="J3" t="n">
         <v>0.008797013870014778</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008732453997859784</v>
+        <v>0.00873245399785978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009629243505007521</v>
+        <v>0.009629243505007523</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009985110366901116</v>
+        <v>0.009985110366901121</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008819297804857304</v>
+        <v>0.008819297804857297</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01401111571101075</v>
+        <v>0.01401111571101074</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009296064773068054</v>
+        <v>0.009296064773068052</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007788419367895857</v>
+        <v>0.007788419367895856</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007856785207676676</v>
+        <v>0.007856785207676674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008330164182276461</v>
+        <v>0.008330164182276459</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008113820556781944</v>
+        <v>0.008113820556781941</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01322718327543077</v>
+        <v>0.01322718327543078</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007497715976159734</v>
+        <v>0.007497715976159736</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01125804849437937</v>
+        <v>0.01125804849437938</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009104392865808011</v>
+        <v>0.009104392865808017</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008600080558578927</v>
+        <v>0.008600080558578929</v>
       </c>
       <c r="Z3" t="n">
         <v>0.0107467254112469</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008514312415864502</v>
+        <v>0.008514312415864499</v>
       </c>
       <c r="AB3" t="n">
         <v>0.0106661326785317</v>
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03065654848777619</v>
+        <v>0.03065654848777625</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02909003872427113</v>
+        <v>0.02909003872427117</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03060782426553157</v>
+        <v>0.0306078242655316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02964734072663348</v>
+        <v>0.02964734072663354</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02977486854915261</v>
+        <v>0.02977486854915265</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03315625602053398</v>
+        <v>0.03315625602053403</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02974168022948531</v>
+        <v>0.02974168022948534</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03062968325500398</v>
+        <v>0.03062968325500402</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0316453411938365</v>
+        <v>0.03164534119383655</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03154643568147133</v>
+        <v>0.03154643568147138</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03296664148298784</v>
+        <v>0.0329666414829879</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0335250112557967</v>
+        <v>0.03352501125579672</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03167216067189678</v>
+        <v>0.0316721606718968</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0304277923260615</v>
+        <v>0.03042779232606153</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03244283164306858</v>
+        <v>0.03244283164306856</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03004394185948284</v>
+        <v>0.03004394185948289</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03014588379750677</v>
+        <v>0.03014588379750684</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03091470116605053</v>
+        <v>0.03091470116605061</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03055383267211555</v>
+        <v>0.0305538326721156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03233697523806939</v>
+        <v>0.03233697523806943</v>
       </c>
       <c r="V4" t="n">
         <v>0.0295577364924954</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03041260761546516</v>
+        <v>0.03041260761546518</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03212043200935271</v>
+        <v>0.03212043200935274</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03128313862832589</v>
+        <v>0.03128313862832592</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03028674330111483</v>
+        <v>0.03028674330111489</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03119283875275758</v>
+        <v>0.03119283875275763</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0345611279221518</v>
+        <v>0.03456112792215185</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06326404076673214</v>
+        <v>0.06326404076673216</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03702911866279639</v>
+        <v>0.03702911866279644</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06750249354307006</v>
+        <v>0.06750249354306999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04666759761144472</v>
+        <v>0.0466675976114448</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05076787524975988</v>
+        <v>0.05076787524975987</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1055582885813774</v>
+        <v>0.1055582885813775</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05108711232250985</v>
+        <v>0.05108711232250988</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06799066452763572</v>
+        <v>0.06799066452763577</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08183026278157443</v>
+        <v>0.08183026278157454</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08037427768902272</v>
+        <v>0.08037427768902267</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1069108215157653</v>
+        <v>0.1069108215157654</v>
       </c>
       <c r="M5" t="n">
         <v>0.1190350530494667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0960853831339387</v>
+        <v>0.09608538313393876</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05857917894618056</v>
+        <v>0.05857917894618058</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09577821179426153</v>
+        <v>0.09577821179426155</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05492281822903954</v>
+        <v>0.05492281822903958</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05904918858300139</v>
+        <v>0.05904918858300141</v>
       </c>
       <c r="S5" t="n">
         <v>0.06669007415862184</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0663579724416663</v>
+        <v>0.06635797244166633</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09679702701036765</v>
+        <v>0.09679702701036778</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04468867796186982</v>
+        <v>0.04468867796186981</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06189293933786518</v>
+        <v>0.06189293933786524</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09637653967158376</v>
+        <v>0.09637653967158394</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07872948711401859</v>
+        <v>0.0787294871140186</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05711996275675735</v>
+        <v>0.0571199627567574</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07662446074124715</v>
+        <v>0.07662446074124722</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1514432225456999</v>
+        <v>0.1514432225456998</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03277130941300274</v>
+        <v>0.03277130941300278</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0297875827366272</v>
+        <v>0.02978758273662727</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0327225851907581</v>
+        <v>0.03272258519075813</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03176210165186003</v>
+        <v>0.03176210165186006</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03188962947437916</v>
+        <v>0.03188962947437917</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03385380003289006</v>
+        <v>0.03385380003289012</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03185644115471183</v>
+        <v>0.03185644115471185</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03132722726736008</v>
+        <v>0.03132722726736011</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03376010211906302</v>
+        <v>0.03234288520619266</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03224397969382743</v>
+        <v>0.03224397969382747</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03366418549534393</v>
+        <v>0.03508140240821442</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0356397721810232</v>
+        <v>0.03563977218102323</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03237444731855569</v>
+        <v>0.03237444731855575</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0311300789727204</v>
+        <v>0.03113007897272049</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03455682262258122</v>
+        <v>0.03455682262258124</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03074148587183895</v>
+        <v>0.03215870278470941</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03226064472273329</v>
+        <v>0.03226064472273336</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03302946209127706</v>
+        <v>0.03302946209127713</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03266859359734207</v>
+        <v>0.0312513766844717</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03449856547355227</v>
+        <v>0.03449856547355233</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0302552805048515</v>
+        <v>0.03167249741772192</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0311790478407579</v>
+        <v>0.03117904784075794</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03423519293457924</v>
+        <v>0.03281797602170885</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03208096705100937</v>
+        <v>0.0320809670510095</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03098428731347093</v>
+        <v>0.03098428731347099</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03330759967798413</v>
+        <v>0.03330759967798416</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03528790704284576</v>
+        <v>0.03528790704284579</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03153173648249139</v>
+        <v>0.03153173648249141</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02996522671898631</v>
+        <v>0.02996522671898633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03148301226024677</v>
+        <v>0.03148301226024676</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03052252872134868</v>
+        <v>0.03052252872134871</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03065005654386779</v>
+        <v>0.0306500565438678</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03403144401524917</v>
+        <v>0.03403144401524919</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03061686822420046</v>
+        <v>0.0306168682242005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03150487124971919</v>
+        <v>0.03150487124971917</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03252052918855174</v>
+        <v>0.03252052918855172</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03242162367618651</v>
+        <v>0.03242162367618653</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03384182947770301</v>
+        <v>0.03384182947770307</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0344001992505119</v>
+        <v>0.03440019925051188</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03254734866661195</v>
+        <v>0.03254734866661196</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03130285331622742</v>
+        <v>0.03130285331622746</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03331789263323442</v>
+        <v>0.03331789263323449</v>
       </c>
       <c r="Q7" t="n">
         <v>0.03091912985419805</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03102107179222198</v>
+        <v>0.031021071792222</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03178988916076574</v>
+        <v>0.03178988916076576</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03142902066683077</v>
+        <v>0.03142902066683076</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03325739552410913</v>
+        <v>0.03325739552410915</v>
       </c>
       <c r="V7" t="n">
         <v>0.03043292448721056</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03128779561018031</v>
+        <v>0.03128779561018034</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03299562000406791</v>
+        <v>0.0329956200040679</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03220515593329745</v>
+        <v>0.03220515593329747</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03116193129583004</v>
+        <v>0.03116193129583006</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03206802674747278</v>
+        <v>0.03206802674747279</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.035436315916867</v>
+        <v>0.03543631591686701</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03277665051396283</v>
+        <v>0.03277665051396288</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03292803350141274</v>
+        <v>0.03292803350141279</v>
       </c>
       <c r="D8" t="n">
         <v>0.03444581904267321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03348533550377511</v>
+        <v>0.03257060828860579</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03216259818847098</v>
+        <v>0.03216259818847104</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03699425079767561</v>
+        <v>0.03735046705059915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03357967500662691</v>
+        <v>0.03357967500662695</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03446767803214556</v>
+        <v>0.03446767803214563</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03548333597097811</v>
+        <v>0.03548333597097817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03538443045861293</v>
+        <v>0.03538443045861299</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03680463626012944</v>
+        <v>0.03680463626012952</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03736300603293829</v>
+        <v>0.0373630060329382</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03417850116978751</v>
+        <v>0.03417850116978754</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03330008298232633</v>
+        <v>0.03330008298232637</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03522541907293349</v>
+        <v>0.03522541907293355</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03182643875118234</v>
+        <v>0.03182643875118239</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03398387857464841</v>
+        <v>0.03398387857464845</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03475269594319218</v>
+        <v>0.03475269594319221</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03439182744925716</v>
+        <v>0.03439182744925721</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03516362785787058</v>
+        <v>0.03538217957697761</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03339573126963701</v>
+        <v>0.03292494874606933</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0342509400075104</v>
+        <v>0.03425094000751046</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03406037718503255</v>
+        <v>0.03406037718503257</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03687407549354085</v>
+        <v>0.03687407549354089</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03412473807825647</v>
+        <v>0.03237493458750405</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03503083352989922</v>
+        <v>0.03503083352989925</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04019360532529628</v>
+        <v>0.04019360532529631</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03435882543833738</v>
+        <v>0.0343588254383374</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03397759287126219</v>
+        <v>0.03397759287126223</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03549537841252266</v>
+        <v>0.03549537841252267</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03453489487362457</v>
+        <v>0.03426133791750485</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03466242269614368</v>
+        <v>0.03193003494963897</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03804381016752507</v>
+        <v>0.03804381040953976</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03462923437647637</v>
+        <v>0.03462923437647641</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03551723740199502</v>
+        <v>0.03551723740199508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0365328953408276</v>
+        <v>0.03653289534082764</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03643398982846238</v>
+        <v>0.03643398982846244</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0378541956299789</v>
+        <v>0.03785419562997897</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03841256540278773</v>
+        <v>0.03841256540278779</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03655971481888785</v>
+        <v>0.03655971481888788</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03570814610617954</v>
+        <v>0.03570814610617961</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03780861255145084</v>
+        <v>0.03780861255145085</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03493149624848856</v>
+        <v>0.03493149624848861</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03503343794449786</v>
+        <v>0.0350334379444979</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03580225531304164</v>
+        <v>0.03580225531304168</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03544138681910661</v>
+        <v>0.03544138681910668</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03727135869531684</v>
+        <v>0.03727135869531687</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03444529063948647</v>
+        <v>0.03581307399635688</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03530016176245622</v>
+        <v>0.03530016176245625</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03700798615634374</v>
+        <v>0.0370079861563438</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03621752208557334</v>
+        <v>0.0362175220855734</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03517429744810593</v>
+        <v>0.03445968079372075</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03608039289974869</v>
+        <v>0.03608039289974872</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0394486820691429</v>
+        <v>0.03944868206914292</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007325526189382606</v>
+        <v>0.007325526189382612</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008209013152153454</v>
+        <v>0.008209013152153452</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007355540781406788</v>
+        <v>0.007355540781406789</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007356533126073557</v>
+        <v>0.007356533126073559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00736377631193052</v>
+        <v>0.007363776311930523</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007636644473487574</v>
+        <v>0.007636644473487572</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007355408208402323</v>
+        <v>0.00735540820840232</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007358389551097771</v>
+        <v>0.007358389551097768</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007459635860187091</v>
+        <v>0.007459635860187087</v>
       </c>
       <c r="K2" t="n">
         <v>0.007389508488955599</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007519563793931656</v>
+        <v>0.007519563793931654</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007364639700927475</v>
+        <v>0.00736463970092748</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007385408096828879</v>
+        <v>0.007385408096828882</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01087266205278983</v>
+        <v>0.01087266205278982</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007500558789053852</v>
+        <v>0.007500558789053848</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007372895135385089</v>
+        <v>0.007372895135385088</v>
       </c>
       <c r="R2" t="n">
         <v>0.007438348539486446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007405563143498803</v>
+        <v>0.0074055631434988</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007365352374848417</v>
+        <v>0.007365352374848415</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009760245869944806</v>
+        <v>0.009760245869944801</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007357988647968666</v>
+        <v>0.00735798864796867</v>
       </c>
       <c r="W2" t="n">
         <v>0.009400236682944169</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007529467091106922</v>
+        <v>0.007529467091106918</v>
       </c>
       <c r="Y2" t="n">
         <v>0.007602219656454245</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009011286643109856</v>
+        <v>0.009011286643109857</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00738750674787175</v>
+        <v>0.007387506747871755</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007635197515347588</v>
+        <v>0.007635197515347558</v>
       </c>
     </row>
     <row r="3">
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006955029492133269</v>
+        <v>0.006955029492133262</v>
       </c>
       <c r="C3" t="n">
         <v>0.00852139150419709</v>
@@ -8423,76 +8423,76 @@
         <v>0.007170431261489201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007175861713991865</v>
+        <v>0.007175861713991863</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007229354256995968</v>
+        <v>0.007229354256995967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009159186786508244</v>
+        <v>0.00915918678650823</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007171033447772435</v>
+        <v>0.007171033447772431</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007191457922477272</v>
+        <v>0.007191457922477274</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00790710580974361</v>
+        <v>0.007907105809743607</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007410244029308724</v>
+        <v>0.007410244029308725</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008332769440449009</v>
+        <v>0.008332769440449011</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007250619570230702</v>
+        <v>0.007250619570230696</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007383739539611453</v>
+        <v>0.007383739539611448</v>
       </c>
       <c r="O3" t="n">
         <v>0.01303642355015504</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008198386919754065</v>
+        <v>0.008198386919754056</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007292208652368222</v>
+        <v>0.007292208652368224</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007764912269639668</v>
+        <v>0.007764912269639669</v>
       </c>
       <c r="S3" t="n">
         <v>0.007522415287599823</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007240919607386849</v>
+        <v>0.007240919607386841</v>
       </c>
       <c r="U3" t="n">
         <v>0.01121514188223752</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007185317174114711</v>
+        <v>0.007185317174114705</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01103648388014384</v>
+        <v>0.01103648388014385</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008411401219219324</v>
+        <v>0.008411401219219319</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008929656809919112</v>
+        <v>0.008929656809919109</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009925256864635508</v>
+        <v>0.009925256864635499</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007398100251742222</v>
+        <v>0.007398100251742224</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009161964006713491</v>
+        <v>0.009161964006713451</v>
       </c>
     </row>
     <row r="4">
@@ -8505,82 +8505,82 @@
         <v>0.02859999729166273</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02882040622653633</v>
+        <v>0.02882040622653632</v>
       </c>
       <c r="D4" t="n">
         <v>0.02893902591597025</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02895023490548264</v>
+        <v>0.02895023490548262</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02903205002176711</v>
+        <v>0.0290320500217671</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03211422143210999</v>
+        <v>0.03211422143210995</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02893752844289825</v>
+        <v>0.02893752844289824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02897120408012875</v>
+        <v>0.02897120408012876</v>
       </c>
       <c r="J4" t="n">
         <v>0.0301106125929918</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02932270679865161</v>
+        <v>0.0293227067986516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03079174129675222</v>
+        <v>0.0307917412967522</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02907130244116155</v>
+        <v>0.02907130244116153</v>
       </c>
       <c r="N4" t="n">
         <v>0.02927639098330675</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02906986373981588</v>
+        <v>0.02906986373981587</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03057707102392331</v>
+        <v>0.03057707102392332</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02913505132755239</v>
+        <v>0.02913505132755238</v>
       </c>
       <c r="R4" t="n">
         <v>0.02987437763693077</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02950405150722305</v>
+        <v>0.02950405150722306</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02904985237744945</v>
+        <v>0.02904985237744944</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02905889451966458</v>
+        <v>0.02905889451966457</v>
       </c>
       <c r="V4" t="n">
         <v>0.02893917687798001</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02995054358919821</v>
+        <v>0.02995054358919822</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03090360359408859</v>
+        <v>0.03090360359408857</v>
       </c>
       <c r="Y4" t="n">
         <v>0.03168574886314058</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02898982312860096</v>
+        <v>0.02898982312860094</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02930009621226322</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03207315603297697</v>
+        <v>0.03207315603297698</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03290926605778367</v>
+        <v>0.03290926605778365</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03715100713175318</v>
+        <v>0.03715100713175316</v>
       </c>
       <c r="D5" t="n">
-        <v>0.039520228450251</v>
+        <v>0.03952022845025098</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0388623910443477</v>
+        <v>0.03886239104434772</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04124096864269357</v>
+        <v>0.04124096864269359</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08661218061327829</v>
+        <v>0.08661218061327799</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04029614485988315</v>
+        <v>0.04029614485988314</v>
       </c>
       <c r="I5" t="n">
         <v>0.04044944063667563</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05706936344131381</v>
+        <v>0.05706936344131372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04495034679038509</v>
+        <v>0.04495034679038511</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06798613241367839</v>
+        <v>0.06798613241367836</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04145600903018171</v>
+        <v>0.04145600903018169</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04127772053137623</v>
+        <v>0.04127772053137622</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04017078157344605</v>
+        <v>0.04017078157344611</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0648408187730352</v>
+        <v>0.06484081877303526</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0419085773735238</v>
+        <v>0.04190857737352379</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05786580619212588</v>
+        <v>0.05786580619212583</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04690797059052693</v>
+        <v>0.04690797059052695</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04172006366400408</v>
+        <v>0.04172006366400403</v>
       </c>
       <c r="U5" t="n">
         <v>0.04109985249211374</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03864234097502951</v>
+        <v>0.03864234097502953</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0572028225968341</v>
+        <v>0.05720282259683411</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07408524096757738</v>
+        <v>0.07408524096757735</v>
       </c>
       <c r="Y5" t="n">
         <v>0.08811020065840171</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03888523776516625</v>
+        <v>0.03888523776516621</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04566086632780739</v>
+        <v>0.04566086632780743</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09963739470589746</v>
+        <v>0.09963739470589737</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03045630959113389</v>
+        <v>0.02922260339774392</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03067671852600748</v>
+        <v>0.03067671852600747</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02956163202205145</v>
+        <v>0.02956163202205143</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02957284101156384</v>
+        <v>0.03080654720495378</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02965465612784828</v>
+        <v>0.03088836232123825</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03397053373158112</v>
+        <v>0.03273682753819114</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02956013454897943</v>
+        <v>0.03079384074236939</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02959381018620995</v>
+        <v>0.03082751637959991</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03196692489246297</v>
+        <v>0.03073321869907299</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02994531290473277</v>
+        <v>0.03117901909812275</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03264805359622337</v>
+        <v>0.03141434740283339</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02969390854724274</v>
+        <v>0.03092761474063268</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02990019254069839</v>
+        <v>0.02990019254069829</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03092439574932737</v>
+        <v>0.02969366529720747</v>
       </c>
       <c r="P6" t="n">
         <v>0.03113555598427608</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02975765743363358</v>
+        <v>0.03099136362702353</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03173068993640194</v>
+        <v>0.03173068993640191</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03012665761330425</v>
+        <v>0.03012665761330424</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02967245848353066</v>
+        <v>0.02967245848353064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03095483524351543</v>
+        <v>0.02972112905012545</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03079548917745117</v>
+        <v>0.03079548917745116</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03063608445909259</v>
+        <v>0.0306360844590926</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03275991589355975</v>
+        <v>0.03152620970016975</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03239364867730705</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02961242923468215</v>
+        <v>0.02961242923468213</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03115640851173438</v>
+        <v>0.03115640851173437</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03271307630328633</v>
+        <v>0.03271307630328636</v>
       </c>
     </row>
     <row r="7">
@@ -8766,82 +8766,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02931986601306161</v>
+        <v>0.02931986601306162</v>
       </c>
       <c r="C7" t="n">
         <v>0.02954027494793521</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02965889463736913</v>
+        <v>0.02965889463736912</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02967010362688152</v>
+        <v>0.02967010362688151</v>
       </c>
       <c r="F7" t="n">
-        <v>0.029751918743166</v>
+        <v>0.02975191874316598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03283409015350886</v>
+        <v>0.03283409015350883</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02965739716429713</v>
+        <v>0.02965739716429712</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02969107280152763</v>
+        <v>0.02969107280152764</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0308304813143907</v>
+        <v>0.03083048131439068</v>
       </c>
       <c r="K7" t="n">
         <v>0.03004257552005048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03151161001815109</v>
+        <v>0.03151161001815108</v>
       </c>
       <c r="M7" t="n">
         <v>0.02979117116256042</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02999625970470562</v>
+        <v>0.02999625970470563</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02978961487439407</v>
+        <v>0.02978961487439406</v>
       </c>
       <c r="P7" t="n">
         <v>0.03129682215850151</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02985492004895127</v>
+        <v>0.02985492004895126</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03059424635832966</v>
+        <v>0.03059424635832965</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03022392022862193</v>
+        <v>0.03022392022862194</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02976972109884833</v>
+        <v>0.02976972109884834</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02981668603899395</v>
+        <v>0.02981668603899396</v>
       </c>
       <c r="V7" t="n">
         <v>0.0296590455993789</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0306704123105971</v>
+        <v>0.03067041231059709</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03162347231548747</v>
+        <v>0.03162347231548745</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03244524600891917</v>
+        <v>0.03244524600891916</v>
       </c>
       <c r="Z7" t="n">
         <v>0.02970969184999982</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03001996493366209</v>
+        <v>0.0300199649336621</v>
       </c>
       <c r="AB7" t="n">
         <v>0.03279302475437586</v>
@@ -8857,25 +8857,25 @@
         <v>0.03041040517695098</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03211085420832179</v>
+        <v>0.03211085420832178</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03222947389775572</v>
+        <v>0.0322294738977557</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03224068288726811</v>
+        <v>0.0314526051943766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03107303085646977</v>
+        <v>0.03107303085646976</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03540466941389544</v>
+        <v>0.03571156536945347</v>
       </c>
       <c r="H8" t="n">
         <v>0.0322279764246837</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03226165206191423</v>
+        <v>0.03226165206191422</v>
       </c>
       <c r="J8" t="n">
         <v>0.03340106057477726</v>
@@ -8884,10 +8884,10 @@
         <v>0.03261315478043705</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03408218927853767</v>
+        <v>0.03408218927853766</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03236175042294701</v>
+        <v>0.03236175042294685</v>
       </c>
       <c r="N8" t="n">
         <v>0.0314195602849374</v>
@@ -8896,43 +8896,43 @@
         <v>0.03152831518429994</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03295823919692063</v>
+        <v>0.03295823919692059</v>
       </c>
       <c r="Q8" t="n">
         <v>0.03065459755366764</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03316482561871624</v>
+        <v>0.03316482561871623</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03279449948900853</v>
+        <v>0.03279449948900851</v>
       </c>
       <c r="T8" t="n">
         <v>0.03234030035923492</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03147707571141101</v>
+        <v>0.03166535241674918</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03222962485976548</v>
+        <v>0.03182375016800683</v>
       </c>
       <c r="W8" t="n">
         <v>0.03324128244105994</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03255879843580358</v>
+        <v>0.03255879843580357</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03648529009382297</v>
+        <v>0.03648529009382298</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03228027111038643</v>
+        <v>0.0307727385092596</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03259054419404869</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03690962965429979</v>
+        <v>0.03690962965429978</v>
       </c>
     </row>
     <row r="9">
@@ -8942,67 +8942,67 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03147933610438698</v>
+        <v>0.03147933610438697</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03263955524773838</v>
+        <v>0.03263955524773837</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03275817493717231</v>
+        <v>0.03275817493717229</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03276938392668469</v>
+        <v>0.03255248016631668</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03285119904296914</v>
+        <v>0.0306846789917798</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03593337045331202</v>
+        <v>0.03593337123637166</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0327566774641003</v>
+        <v>0.03275667746410028</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03279035310133081</v>
+        <v>0.0327903531013308</v>
       </c>
       <c r="J9" t="n">
         <v>0.03392976161419384</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03314185581985365</v>
+        <v>0.03314185581985364</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03461089031795426</v>
+        <v>0.03461089031795423</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03289045146236359</v>
+        <v>0.03289045146236358</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0330955400045088</v>
+        <v>0.03309554000450878</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03320046567609577</v>
+        <v>0.03320046567609576</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0347754084552984</v>
+        <v>0.03477540845529839</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0329542011318141</v>
+        <v>0.03295420113181409</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03369352665813283</v>
+        <v>0.03369352665813281</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0333232005284251</v>
+        <v>0.03332320052842509</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0328690013986515</v>
+        <v>0.03286900139865149</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03291767196524633</v>
+        <v>0.03291767196524632</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03275832589918206</v>
+        <v>0.0338428473642117</v>
       </c>
       <c r="W9" t="n">
         <v>0.03376969261040026</v>
@@ -9011,16 +9011,16 @@
         <v>0.03472275261529061</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03554452630872233</v>
+        <v>0.03554452630872232</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03280897214980299</v>
+        <v>0.03224235047621964</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03311924523346527</v>
+        <v>0.03311924523346525</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03589230505417903</v>
+        <v>0.03589230505417901</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.008070568476657972</v>
+        <v>0.007696119316465227</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008649430685339623</v>
+        <v>0.00835751589742101</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007971146938878935</v>
+        <v>0.00766398996484345</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007850883114475469</v>
+        <v>0.007532857204365965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007909101955302306</v>
+        <v>0.007601892993471674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008279748254400825</v>
+        <v>0.007669938811594633</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007938164710140661</v>
+        <v>0.007640597959649022</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007996513839249656</v>
+        <v>0.007700649880570455</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008075509314101337</v>
+        <v>0.007676659024118826</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008144501909231329</v>
+        <v>0.007852395958222631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008167670604934686</v>
+        <v>0.007685870680996753</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00833462595826579</v>
+        <v>0.008197333323082864</v>
       </c>
       <c r="N2" t="n">
-        <v>0.008030157049052378</v>
+        <v>0.007741686195258334</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01187320089392808</v>
+        <v>0.01139099494745044</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008083143401512305</v>
+        <v>0.007641030059721635</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00789257674868956</v>
+        <v>0.007582667962853031</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007895408344501</v>
+        <v>0.007601730932066128</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008016486815291135</v>
+        <v>0.007660498933037447</v>
       </c>
       <c r="T2" t="n">
-        <v>0.008009039894445033</v>
+        <v>0.007708121364560504</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01075811888898602</v>
+        <v>0.01038529570442292</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007881818384683582</v>
+        <v>0.007573857199177973</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01006503608470118</v>
+        <v>0.009749805636603917</v>
       </c>
       <c r="X2" t="n">
-        <v>0.008002071771757661</v>
+        <v>0.007584749341131482</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008037524831450602</v>
+        <v>0.007613965609021909</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009671343554648082</v>
+        <v>0.009323951350409159</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.008039478639284555</v>
+        <v>0.007749259791342908</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008346123887881345</v>
+        <v>0.007829396634781364</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00957373651171585</v>
+        <v>0.008728089609870215</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008965592393237796</v>
+        <v>0.008728972402224972</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008879131382262736</v>
+        <v>0.008510774966525867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00801438643165589</v>
+        <v>0.007569007474841865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00843685613145948</v>
+        <v>0.008067899138149709</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01106641431207567</v>
+        <v>0.008544279507279999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008646890133122604</v>
+        <v>0.008346951847014186</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009062067724367719</v>
+        <v>0.008774501165475698</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009615926767430104</v>
+        <v>0.008595825283516193</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01011867867560888</v>
+        <v>0.009858091890570537</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01027574707603581</v>
+        <v>0.008661704951327084</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01147833338111221</v>
+        <v>0.01230766807697448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009297812105708778</v>
+        <v>0.009063259260790353</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01562592437792492</v>
+        <v>0.01471836742337259</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009665207209558492</v>
+        <v>0.008337586633331171</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008315193706758098</v>
+        <v>0.007927353251508203</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008338755154427429</v>
+        <v>0.008066803731645414</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009192603642603594</v>
+        <v>0.008477378777870441</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009150872160088872</v>
+        <v>0.008827148237065981</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443059450896398</v>
+        <v>0.01373441383133869</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008232606088727527</v>
+        <v>0.007859492656936633</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01205056880566337</v>
+        <v>0.01178212099043783</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009098985414733625</v>
+        <v>0.007942737282818592</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009348240474912863</v>
+        <v>0.008149312327877243</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01137561584108399</v>
+        <v>0.01081382258053577</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009362920038894371</v>
+        <v>0.009115906340264235</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01155342633579032</v>
+        <v>0.009690675843926291</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03301302157366444</v>
+        <v>0.03112177053871399</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02976837038946778</v>
+        <v>0.02885739444140565</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03189000956828322</v>
+        <v>0.03075885473191409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03053157434755337</v>
+        <v>0.02927764987827068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03118918293668253</v>
+        <v>0.03005744087425168</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03537580339072172</v>
+        <v>0.03082604969257335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03151746012210954</v>
+        <v>0.03049463127238889</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03217654037732099</v>
+        <v>0.03117294534444505</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03306430272025302</v>
+        <v>0.03089867374285789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03384813370563972</v>
+        <v>0.03288698709817079</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03410983478173583</v>
+        <v>0.03100600748649231</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03598469812457877</v>
+        <v>0.0367374107700861</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03255655590868393</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03255299833429338</v>
+        <v>0.0309005763312085</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03315506113464541</v>
+        <v>0.03049951204148502</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03100252312602095</v>
+        <v>0.0298402853094631</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03103450730330949</v>
+        <v>0.03005561031612415</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03240214432973248</v>
+        <v>0.03071942192171124</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03231802793302291</v>
+        <v>0.03125733919316506</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03379799123526189</v>
+        <v>0.03225265958849392</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03085144728866308</v>
+        <v>0.02971963333495604</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03131367646429567</v>
+        <v>0.03041468461808935</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03223931978177425</v>
+        <v>0.0298637954345995</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03257148620493142</v>
+        <v>0.0301652046913144</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03126972924980841</v>
+        <v>0.02987443694668444</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0326618475584998</v>
+        <v>0.0317220166482836</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03608619644146501</v>
+        <v>0.03260628497095551</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1021805665037112</v>
+        <v>0.08249636566526927</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04316245035066515</v>
+        <v>0.04169803500020147</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08846373304814546</v>
+        <v>0.08231673608608184</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05729439784773604</v>
+        <v>0.04900173767693296</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07467325867195977</v>
+        <v>0.06837801034458185</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1496140944637643</v>
+        <v>0.07834887823190348</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08283630130434537</v>
+        <v>0.07885424930307507</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09535806539251536</v>
+        <v>0.09189339500903346</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1074171230310372</v>
+        <v>0.08200394012308759</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1292656585067332</v>
+        <v>0.1267501229451507</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1296099418995557</v>
+        <v>0.08418316700212583</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1774577834637422</v>
+        <v>0.2117939049501719</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1215618368123488</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O5" t="n">
-        <v>0.09213618341654344</v>
+        <v>0.07723745435558069</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1060649026030222</v>
+        <v>0.07155339864743018</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06870263667330939</v>
+        <v>0.06202228225095356</v>
       </c>
       <c r="R5" t="n">
-        <v>0.07133911258511222</v>
+        <v>0.06837754114812182</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09276179171281602</v>
+        <v>0.07648224913763062</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09785389355279626</v>
+        <v>0.09319036316711354</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1228715643342145</v>
+        <v>0.1081895460815459</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06277593181594236</v>
+        <v>0.05703848503095547</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07389972772570672</v>
+        <v>0.07270760973012436</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09498811271392042</v>
+        <v>0.06281021432539735</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1008087023147111</v>
+        <v>0.06830115859139436</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07078854177083996</v>
+        <v>0.06007965772860182</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1016900579796481</v>
+        <v>0.09966602555880219</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1845233751562138</v>
+        <v>0.1259082719160553</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03548377092332964</v>
+        <v>0.03189208807784966</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03223911973913299</v>
+        <v>0.03108061161156589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03266136532697815</v>
+        <v>0.03298207190207433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0313029301062483</v>
+        <v>0.03150086704843091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03365993228634773</v>
+        <v>0.03082775841338734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03784655274038694</v>
+        <v>0.03304926686273357</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03398820947177475</v>
+        <v>0.03271784844254911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03294789613601593</v>
+        <v>0.03194326288358072</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03553505206991821</v>
+        <v>0.03166899128199355</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03461948946433466</v>
+        <v>0.03511020426833102</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03488119054043078</v>
+        <v>0.03322922465665253</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03675605388327371</v>
+        <v>0.03896062794024636</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03333680153735818</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03502042722720625</v>
+        <v>0.03167901511466375</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03562249196454698</v>
+        <v>0.03271034522951451</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03177387888471588</v>
+        <v>0.03206350247962333</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03180586306200443</v>
+        <v>0.03227882748628438</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03487289367939768</v>
+        <v>0.03148973946084691</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03308938369171784</v>
+        <v>0.03202765673230071</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03463763918924469</v>
+        <v>0.03305157905688432</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0333221966383283</v>
+        <v>0.03194285050511626</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03378110617602278</v>
+        <v>0.03262551714935978</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03471006913143946</v>
+        <v>0.03208701260475972</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03347435162126306</v>
+        <v>0.03102982220368663</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03204108500850335</v>
+        <v>0.0306447544858201</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03343320331719474</v>
+        <v>0.03394523381844384</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03689284768952369</v>
+        <v>0.03339774842348164</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03410427570388843</v>
+        <v>0.03208915683151731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03085962451969178</v>
+        <v>0.02982478073420897</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03298126369850721</v>
+        <v>0.03172624102471741</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03162282847777736</v>
+        <v>0.03024503617107399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03228043706690652</v>
+        <v>0.03102482716705498</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03646705752094574</v>
+        <v>0.03179343598537666</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03260871425233354</v>
+        <v>0.03146201756519219</v>
       </c>
       <c r="I7" t="n">
-        <v>0.033267794507545</v>
+        <v>0.03214033163724837</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03415555685047702</v>
+        <v>0.0318660600356612</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03493938783586373</v>
+        <v>0.03385437339097411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03520108891195984</v>
+        <v>0.03197339377929563</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03707595225480277</v>
+        <v>0.03770479706288943</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03364781003890793</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03364411514387189</v>
+        <v>0.03186782567874123</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03424617794422391</v>
+        <v>0.03146676138901774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03209377725624494</v>
+        <v>0.03080767160226641</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03212576143353349</v>
+        <v>0.03102299660892747</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03349339845995648</v>
+        <v>0.03168680821451455</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0334092820632469</v>
+        <v>0.03222472548596836</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03495584282844987</v>
+        <v>0.03324772941870802</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03194270141888708</v>
+        <v>0.03068701962775934</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03240493059451966</v>
+        <v>0.03138207091089265</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03333057391199826</v>
+        <v>0.03083118172740281</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03373103253044325</v>
+        <v>0.03116119291337244</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03236098338003241</v>
+        <v>0.03084182323948776</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03375310168872381</v>
+        <v>0.03268940294108691</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.037177450571689</v>
+        <v>0.03357367126375881</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03555727578853521</v>
+        <v>0.03345373040786254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03436584140447731</v>
+        <v>0.03306378991388972</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03648748058329275</v>
+        <v>0.03496525020439815</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03403576798265461</v>
+        <v>0.03248596368441473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03405330433252735</v>
+        <v>0.03268141590337922</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04039902228468284</v>
+        <v>0.03542112159820566</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03611493113711907</v>
+        <v>0.03470102674487294</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03677401139233053</v>
+        <v>0.03537934081692912</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03766177373526257</v>
+        <v>0.03510506921534196</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03844560472064926</v>
+        <v>0.03709338257065486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03870730579674538</v>
+        <v>0.03521240295897638</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04058216913958829</v>
+        <v>0.04094380624257026</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03556244040782141</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03599626462735618</v>
+        <v>0.03405326796484282</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03649111458140707</v>
+        <v>0.03355432624871105</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03314327337735617</v>
+        <v>0.0318038758007104</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03563197831831903</v>
+        <v>0.03426200578860823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03699961534474201</v>
+        <v>0.03492581739419533</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03691549894803246</v>
+        <v>0.03546373466564912</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03746039977339392</v>
+        <v>0.03557216438800805</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03488641195631403</v>
+        <v>0.03341304933266174</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03591155099494248</v>
+        <v>0.03462144847064884</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03456825143246544</v>
+        <v>0.03199918167331311</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03927665139504363</v>
+        <v>0.03626287473980418</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03377584390851722</v>
+        <v>0.03217157821218127</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03725931857350935</v>
+        <v>0.03592841212076766</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04282842409114323</v>
+        <v>0.03877068516867014</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03817089402436964</v>
+        <v>0.03517095222648742</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03654272192609005</v>
+        <v>0.03419733818558954</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03866436110490549</v>
+        <v>0.03609879847609798</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03693284927533342</v>
+        <v>0.03431969032755118</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03423710871162101</v>
+        <v>0.03242182694518193</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04215015514924787</v>
+        <v>0.03616599255635839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03829181165873181</v>
+        <v>0.03583457501657278</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03895089191394327</v>
+        <v>0.03651288908862894</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03983865425687529</v>
+        <v>0.0362386174870418</v>
       </c>
       <c r="K9" t="n">
-        <v>0.040622485242262</v>
+        <v>0.03822693084235471</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04088418631835811</v>
+        <v>0.0363459512306762</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04275904966120105</v>
+        <v>0.04207735451427001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0393309074453062</v>
+        <v>0.0987789753098786</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03986304921883253</v>
+        <v>0.03666827575861643</v>
       </c>
       <c r="P9" t="n">
-        <v>0.04058161738804313</v>
+        <v>0.03636024118241415</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03777687488454707</v>
+        <v>0.03518022817324816</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03780885883993177</v>
+        <v>0.03539555406030807</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03917649586635474</v>
+        <v>0.03605936566589515</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03909237946964518</v>
+        <v>0.03659728293734897</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04064063496717201</v>
+        <v>0.03762120526193256</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03949117936053614</v>
+        <v>0.0365490854355164</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03808802800091794</v>
+        <v>0.03575462836227324</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03901367131839653</v>
+        <v>0.03520373917878338</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03941412993684153</v>
+        <v>0.03553375036475303</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03706948772866704</v>
+        <v>0.03443616560029664</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03943619909512208</v>
+        <v>0.0370619603924675</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04286054797808728</v>
+        <v>0.03794622871513941</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007087019050252352</v>
+        <v>0.007102043182795017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007759858464943848</v>
+        <v>0.007774872993368593</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007104730246695206</v>
+        <v>0.007119545097264866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007096342198106129</v>
+        <v>0.007110842871831146</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007131185259532302</v>
+        <v>0.007145960523021039</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007124201644364817</v>
+        <v>0.007134499321804168</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007112209018167665</v>
+        <v>0.00712713094013656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007110347981813142</v>
+        <v>0.007126297354616812</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00713095802372403</v>
+        <v>0.007144945698305421</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007133306494169704</v>
+        <v>0.007149309046164588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007180996352157775</v>
+        <v>0.0071934926982334</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007107997597808672</v>
+        <v>0.007127511893938396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0071279364557197</v>
+        <v>0.007143670112066662</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01062823355859138</v>
+        <v>0.0106446137239978</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007135497932484662</v>
+        <v>0.007149947860654156</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007100990451986456</v>
+        <v>0.007115697387655985</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007197399094691691</v>
+        <v>0.007212643807988792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007153696350260988</v>
+        <v>0.007166809653533706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007125702551383339</v>
+        <v>0.007142036434390505</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008905216686168605</v>
+        <v>0.008906118136871234</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007134117431097447</v>
+        <v>0.007148663739136373</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008616650659506427</v>
+        <v>0.008628733597425881</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007298904771032338</v>
+        <v>0.00731194987548418</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007206154791370289</v>
+        <v>0.007220983412744571</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008778301413149619</v>
+        <v>0.00879261655011118</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007204803315408684</v>
+        <v>0.007219434459328455</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007087699893524343</v>
+        <v>0.007100993650783291</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006744027780416843</v>
+        <v>0.006761845910665035</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007969082234202699</v>
+        <v>0.007985442416176918</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006871175683764956</v>
+        <v>0.006887519648231667</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00680969478565424</v>
+        <v>0.006823857824328769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007060495802139088</v>
+        <v>0.007076551013106992</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007007724076142644</v>
+        <v>0.006992045809602896</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006925830433978398</v>
+        <v>0.006942933887903045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006911785325812859</v>
+        <v>0.006936231893780178</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007056960435172166</v>
+        <v>0.007067471382474629</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007073421998890671</v>
+        <v>0.007098221859773187</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007411559946903467</v>
+        <v>0.007411448897470647</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006907033181464825</v>
+        <v>0.006956527735630858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007037186015270947</v>
+        <v>0.00706007604250826</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01298801403781343</v>
+        <v>0.01300667008021278</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007087895778289351</v>
+        <v>0.007101641355318426</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006843987755979474</v>
+        <v>0.006859556889374682</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007535749740765432</v>
+        <v>0.007555158837532472</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007217208168930562</v>
+        <v>0.007221472154537964</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007021705073259033</v>
+        <v>0.007048901352248262</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009997670203780709</v>
+        <v>0.009928943215366619</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007078265390828647</v>
+        <v>0.007092706454601366</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009775782519781378</v>
+        <v>0.009785499253209548</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008254781164499956</v>
+        <v>0.008258507625146769</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007595679813784322</v>
+        <v>0.007612099927590172</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009701706629436964</v>
+        <v>0.009717031650558783</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007585758247962453</v>
+        <v>0.007600767753164808</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006757421485468438</v>
+        <v>0.006762897922553177</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02823057206109945</v>
+        <v>0.02805832155463595</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02846541725346752</v>
+        <v>0.02829016643501352</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02843062817247442</v>
+        <v>0.02825601372985135</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02833588130496778</v>
+        <v>0.02815771809035598</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02872944971237648</v>
+        <v>0.02855438811546346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0286505665664381</v>
+        <v>0.0284249285753059</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02851510433666068</v>
+        <v>0.0283416993147473</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02849408307491731</v>
+        <v>0.02833228358283338</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02872371918302536</v>
+        <v>0.02853977687055208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02875341003342216</v>
+        <v>0.02859221122476643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02929208891781592</v>
+        <v>0.02909128590036807</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02849003903451627</v>
+        <v>0.02836776790765971</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02905818288085791</v>
+        <v>0.028883002966595</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02877816333730097</v>
+        <v>0.02859942692829552</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02838838547084847</v>
+        <v>0.02821255207978518</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02947736544037092</v>
+        <v>0.0293076064950009</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02898372283777031</v>
+        <v>0.02878988863567794</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02866752000166364</v>
+        <v>0.02851006372921162</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02870939025147388</v>
+        <v>0.0284065383796258</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02874221290307828</v>
+        <v>0.02856466918620933</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02927319852248172</v>
+        <v>0.02909426382873706</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03062391874955656</v>
+        <v>0.03042931421040933</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02953225616434834</v>
+        <v>0.02935848808350407</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02857600907506027</v>
+        <v>0.02840099104848181</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02956099951947915</v>
+        <v>0.02938431002573633</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02825151827194242</v>
+        <v>0.02805979780498933</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03179738669800947</v>
+        <v>0.03169416672244479</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03621460613136777</v>
+        <v>0.0360702029569763</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03572034140887297</v>
+        <v>0.03558541156868455</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03320766568864927</v>
+        <v>0.03304177341375188</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04126946305489031</v>
+        <v>0.04112340195813569</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03835624040396982</v>
+        <v>0.03743136014709225</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03787693262262354</v>
+        <v>0.03776096578260136</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03710983569261312</v>
+        <v>0.03720438981700309</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04022924124873268</v>
+        <v>0.03996565043625971</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04054632642942947</v>
+        <v>0.04063790142879156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04891969307866089</v>
+        <v>0.04836939076553773</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03693230620353951</v>
+        <v>0.03772935817291707</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04466323305676482</v>
+        <v>0.04451980316792376</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04037955553666696</v>
+        <v>0.04017487372252267</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03471574176495863</v>
+        <v>0.03455684977667046</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05588772259466598</v>
+        <v>0.05583720914522036</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04371950293166277</v>
+        <v>0.04327783171516873</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04035013987318185</v>
+        <v>0.04052433145750613</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04010958862033519</v>
+        <v>0.03796275911133244</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04019861511391377</v>
+        <v>0.04001724025209758</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05044479353406203</v>
+        <v>0.05022345056311965</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07335781419822458</v>
+        <v>0.0728761994427083</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05631038927525582</v>
+        <v>0.0561667403831948</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03693480974519792</v>
+        <v>0.03679375340947513</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05589735543189117</v>
+        <v>0.05571363172911617</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03285831971092947</v>
+        <v>0.03239369276787112</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02885975178248708</v>
+        <v>0.0286884225432419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02909459697485516</v>
+        <v>0.02995801890840354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03009660179069374</v>
+        <v>0.02888611471845729</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0289650610263554</v>
+        <v>0.02982557056374599</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02935862943376411</v>
+        <v>0.03022224058885347</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03031654018465741</v>
+        <v>0.02905502956391185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03018107795487998</v>
+        <v>0.02897180030335326</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03016005669313662</v>
+        <v>0.02896238457143933</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03038969280124468</v>
+        <v>0.0302076293439421</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02938258975480979</v>
+        <v>0.02922231221337237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03095806253603523</v>
+        <v>0.03075913837375808</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03015601265273558</v>
+        <v>0.02899786889626567</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03077124542969605</v>
+        <v>0.0305978565799218</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03045791245200359</v>
+        <v>0.02919237543722827</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03005435908906778</v>
+        <v>0.02884265306839114</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03114333905859023</v>
+        <v>0.02993770748360685</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03064969645598961</v>
+        <v>0.03045774110906795</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02929669972305127</v>
+        <v>0.02914016471781756</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03041937276751994</v>
+        <v>0.03011770893663696</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03040818652129759</v>
+        <v>0.02919477017481528</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02996971254897852</v>
+        <v>0.02979173722260467</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03125309847094419</v>
+        <v>0.03209716668379933</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03028094611673983</v>
+        <v>0.03010740429423167</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02920518879644789</v>
+        <v>0.02903109203708776</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03019017924086678</v>
+        <v>0.03105216249912634</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02888028568858137</v>
+        <v>0.02868947150737794</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02888615153036343</v>
+        <v>0.02871642070484531</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0291209967227315</v>
+        <v>0.02894826558522288</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02908620764173841</v>
+        <v>0.0289141128800607</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02899146077423176</v>
+        <v>0.02881581724056534</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02938502918164045</v>
+        <v>0.02921248726567281</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02930614603570209</v>
+        <v>0.02908302772551526</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02917068380592466</v>
+        <v>0.02899979846495666</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02914966254418129</v>
+        <v>0.02899038273304274</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02937929865228935</v>
+        <v>0.02919787602076144</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02940898950268614</v>
+        <v>0.02925031037497578</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0299476683870799</v>
+        <v>0.02974938505057742</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02914561850378025</v>
+        <v>0.02902586705786907</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02971364626597216</v>
+        <v>0.02954098588503205</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02943362672241523</v>
+        <v>0.02925740984673256</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02904396494011244</v>
+        <v>0.02887065122999454</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03013294490963489</v>
+        <v>0.02996570564521025</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02963930230703428</v>
+        <v>0.0294479877858873</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02932309947092763</v>
+        <v>0.02916816287942097</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02940754940281597</v>
+        <v>0.02910664460323763</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02939779237234226</v>
+        <v>0.02922276833641869</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02992877799174571</v>
+        <v>0.02975236297894641</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03127949821882053</v>
+        <v>0.03108741336061868</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03023184453143907</v>
+        <v>0.03005990531733457</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02923158854432425</v>
+        <v>0.02905909019869116</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03021657898874313</v>
+        <v>0.03004240917594568</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0289070977412064</v>
+        <v>0.02871789695519868</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02990546090643818</v>
+        <v>0.02973569909518978</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03150435489779586</v>
+        <v>0.03133226843474911</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03146956581680276</v>
+        <v>0.03129811572958693</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03064850320078888</v>
+        <v>0.03047314457245763</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03061684141860222</v>
+        <v>0.03044437377686809</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03197234861517672</v>
+        <v>0.03175001508199615</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03155404198098901</v>
+        <v>0.03138380131448289</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03153302071924565</v>
+        <v>0.03137438558256896</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0317626568273537</v>
+        <v>0.03158187887028766</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03179234767775051</v>
+        <v>0.03163431322450201</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03233102656214426</v>
+        <v>0.03213338790010366</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03152897667884448</v>
+        <v>0.03140986990739528</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03133032786860626</v>
+        <v>0.03115793249104403</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03097908177253187</v>
+        <v>0.03080309461926666</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02979520759433384</v>
+        <v>0.02962173011582959</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03251630308469926</v>
+        <v>0.03234970849473647</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03202266048209863</v>
+        <v>0.03183199063541352</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03170645764599199</v>
+        <v>0.03155216572894719</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03112554513574556</v>
+        <v>0.03082492874517943</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03140721301079875</v>
+        <v>0.03123275014657776</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03231240424131941</v>
+        <v>0.03213663403579273</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03215575865577583</v>
+        <v>0.0319635719548018</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03396970448544313</v>
+        <v>0.03379923864694042</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03022556001366647</v>
+        <v>0.03005301813156557</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03259993716380748</v>
+        <v>0.0324264120254719</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0327153189465705</v>
+        <v>0.03252746861861674</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03013749192700094</v>
+        <v>0.03021264187155829</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03103021306900174</v>
+        <v>0.03117038839267649</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03099542398800863</v>
+        <v>0.0311362356875143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03074884241866589</v>
+        <v>0.03087040528015794</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02977766126115987</v>
+        <v>0.02976120804613738</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03121536288107527</v>
+        <v>0.03130515101388557</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03107990015219489</v>
+        <v>0.03122192127241026</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03105887889045152</v>
+        <v>0.03121250554049633</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03128851499855957</v>
+        <v>0.03141999882821505</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03131820584895637</v>
+        <v>0.03147243318242938</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03185688473335013</v>
+        <v>0.03197150785803103</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03105483485005048</v>
+        <v>0.03124798986532267</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04055672468437393</v>
+        <v>0.04059939329079139</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03184099858919057</v>
+        <v>0.03200378841780435</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03160839452317941</v>
+        <v>0.0317725307073855</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03095318178548565</v>
+        <v>0.03109277451836487</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03204216125590512</v>
+        <v>0.03218782845266385</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03154851865330452</v>
+        <v>0.03167011059334089</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03123231581719785</v>
+        <v>0.03139028568687457</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03131819496483484</v>
+        <v>0.03133007842090992</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03206618391064633</v>
+        <v>0.03228256650750855</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03183799433801593</v>
+        <v>0.03197448578640003</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03318871456509076</v>
+        <v>0.03330953616807229</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03214106087770929</v>
+        <v>0.03228202812478817</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03074416439176618</v>
+        <v>0.03084355905743734</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03212579533501336</v>
+        <v>0.03226453198339928</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03081631408747662</v>
+        <v>0.03094001976265228</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007812205858297572</v>
+        <v>0.0075443296316659</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008435247021676882</v>
+        <v>0.008246681699950058</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007762608233699218</v>
+        <v>0.007527995385463261</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007635059921863117</v>
+        <v>0.007424240227779351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007658577957734115</v>
+        <v>0.00744059723406823</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007945996965898067</v>
+        <v>0.007556691107137547</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007626590706570366</v>
+        <v>0.007433003993414603</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007691430670925745</v>
+        <v>0.007497652399365143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007822900083201814</v>
+        <v>0.007565228509074531</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00788697273091489</v>
+        <v>0.007689172124900509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007951417630756489</v>
+        <v>0.007557834672974867</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007964489613667971</v>
+        <v>0.008033673242063517</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007745711762666765</v>
+        <v>0.007551855453321665</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01149882919994524</v>
+        <v>0.01114487375238056</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007961284613029463</v>
+        <v>0.007564353905890818</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007664589240630403</v>
+        <v>0.007449513052714194</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007626502215554424</v>
+        <v>0.007437725116933323</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007815891518758472</v>
+        <v>0.007551582254587908</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007739857137123095</v>
+        <v>0.007535941869378593</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01032752990255842</v>
+        <v>0.01003893072635196</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007627770942455822</v>
+        <v>0.007424156752661849</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009743341078711837</v>
+        <v>0.009534187549401395</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007826790822068722</v>
+        <v>0.007507396827526695</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00780194842964627</v>
+        <v>0.007495674992106719</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009390109462242979</v>
+        <v>0.009151499581998047</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007781814380215983</v>
+        <v>0.007577737316377063</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008136833574102246</v>
+        <v>0.007712908977996584</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008964653217429697</v>
+        <v>0.00827734994479897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008779031997382628</v>
+        <v>0.008632281780872881</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008624121003269751</v>
+        <v>0.008170962483138547</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007707649576583445</v>
+        <v>0.007425301391133398</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007879677852904617</v>
+        <v>0.007545545227237475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009919173625745887</v>
+        <v>0.008367128587065916</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007652071196064312</v>
+        <v>0.007492553981582662</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00811537952242131</v>
+        <v>0.007954530817480931</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009046689388410608</v>
+        <v>0.008432107362248349</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009503957286381221</v>
+        <v>0.009314417981099464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009966035523166172</v>
+        <v>0.008379512550381839</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01007097250625765</v>
+        <v>0.01176899182302802</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008500507418790684</v>
+        <v>0.008339137640073551</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01487918366873302</v>
+        <v>0.01409313403702244</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01002716660805137</v>
+        <v>0.008421193463878327</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007920995977514176</v>
+        <v>0.007607950047760536</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007650802877390462</v>
+        <v>0.007525795118049151</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008993734106077705</v>
+        <v>0.008331028571739932</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008461170779997199</v>
+        <v>0.008227766076801576</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01365037444977659</v>
+        <v>0.01290460283286494</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007653675995955931</v>
+        <v>0.007423058672636131</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01188114615801948</v>
+        <v>0.011688991127637</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009081371617693781</v>
+        <v>0.008022277743802814</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008899418870793478</v>
+        <v>0.007936008597657312</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01085501788024672</v>
+        <v>0.01044409119865304</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008756557629659148</v>
+        <v>0.008522240134174181</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01128756163087331</v>
+        <v>0.009488221277131661</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03195391118443731</v>
+        <v>0.03035302691637391</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02943328049529614</v>
+        <v>0.028681825088084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03139368319856437</v>
+        <v>0.03016852409139066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02995296634125336</v>
+        <v>0.0289965618556202</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03021861337524727</v>
+        <v>0.02918132176624775</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03346514329173517</v>
+        <v>0.03049265546838581</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02985730265849024</v>
+        <v>0.02909555262000178</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0305896998837414</v>
+        <v>0.02982578610494909</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03206997490129599</v>
+        <v>0.03058512910377428</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03279843740511074</v>
+        <v>0.03198908950829767</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03352637219494006</v>
+        <v>0.03050557257058464</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03367456235418533</v>
+        <v>0.03583645196724628</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03120282978549209</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03160462887197107</v>
+        <v>0.03009214811745576</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03363782429874938</v>
+        <v>0.03057921030536559</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03028651358088756</v>
+        <v>0.02928203003933307</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02985630311175717</v>
+        <v>0.02914887988196981</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03199554241483084</v>
+        <v>0.03043494862864941</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03113669909671551</v>
+        <v>0.0302582832827775</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0329930414226246</v>
+        <v>0.03130252058136029</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02983969314203338</v>
+        <v>0.02896990963168201</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0313773130892814</v>
+        <v>0.03060108759015018</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03211865505964725</v>
+        <v>0.02993585390369219</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03178864027543504</v>
+        <v>0.02971119270846767</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03047225186406096</v>
+        <v>0.02934426227200649</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03161062545873511</v>
+        <v>0.03073038208348072</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03557154405361934</v>
+        <v>0.03223244831166086</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08426342723312577</v>
+        <v>0.06851764147022656</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0416542823958365</v>
+        <v>0.04064354295782927</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08115010638950955</v>
+        <v>0.07069675373887668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0504872946423861</v>
+        <v>0.04567023906179268</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05783421796662903</v>
+        <v>0.05111190029294106</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1126411174146193</v>
+        <v>0.07202208304774559</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05138519401281483</v>
+        <v>0.05015873132064579</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06553487457484172</v>
+        <v>0.06428733883161317</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08971885790568633</v>
+        <v>0.07609218463308888</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1033956940782509</v>
+        <v>0.1012985496127537</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1183450064325446</v>
+        <v>0.07461454720269778</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1274594756902179</v>
+        <v>0.185013424484701</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1056604471414006</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07695577569811486</v>
+        <v>0.0631063676824194</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1152856446663397</v>
+        <v>0.07331111415610014</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0582367334882194</v>
+        <v>0.0523332269424039</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05101216257357816</v>
+        <v>0.05091467987338842</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08659454652297553</v>
+        <v>0.07113236148996283</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07597155893232341</v>
+        <v>0.07244348837745418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1075000673122687</v>
+        <v>0.09001497859277786</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04781413917492058</v>
+        <v>0.04471074536908257</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07829016664917243</v>
+        <v>0.07683950234141068</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09439969226778924</v>
+        <v>0.0653676702311109</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08650715522368256</v>
+        <v>0.0614127384519283</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05925661507511271</v>
+        <v>0.05154875643726826</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08267226278012467</v>
+        <v>0.07924420041175072</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1708782931756531</v>
+        <v>0.1158243396496397</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03267341884062924</v>
+        <v>0.03101492586976711</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03160202902051566</v>
+        <v>0.03062367775413035</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03356243172378388</v>
+        <v>0.03083042304478386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03067247399744529</v>
+        <v>0.03093841452166655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0309381210314392</v>
+        <v>0.02984322071964094</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03418465094792709</v>
+        <v>0.03243450813443213</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03202605118370976</v>
+        <v>0.03103740528604813</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03130920753993333</v>
+        <v>0.03176763877099543</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0342387234265155</v>
+        <v>0.03252698176982063</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03496718593033027</v>
+        <v>0.03265098846169086</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03424587985113201</v>
+        <v>0.03244742523663097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03439407001037727</v>
+        <v>0.03777830463329263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03192789128063839</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03376433095559107</v>
+        <v>0.03075779937348064</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03579752799230699</v>
+        <v>0.03252733924008088</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03245526210610707</v>
+        <v>0.02994392899272628</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03202505163697668</v>
+        <v>0.03109073254801615</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03416429094005035</v>
+        <v>0.03109684758204262</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03185620675290744</v>
+        <v>0.03092018223617069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03376195761255209</v>
+        <v>0.03205667720659884</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03200844166725288</v>
+        <v>0.02963180858507521</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03353700100372765</v>
+        <v>0.03133643666781063</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03428740358486676</v>
+        <v>0.03187770656973853</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03261313539670409</v>
+        <v>0.03051923912085962</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03264100038928047</v>
+        <v>0.0300061612253997</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03233013311492705</v>
+        <v>0.03267223474952708</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03632445996878021</v>
+        <v>0.03291140311257812</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0328668194070505</v>
+        <v>0.03120144440116373</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03034618871790933</v>
+        <v>0.02953024257287382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03230659142117757</v>
+        <v>0.03101694157618048</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03086587456386655</v>
+        <v>0.02984497934041002</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03113152159786046</v>
+        <v>0.03002973925103757</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03437805151434836</v>
+        <v>0.03134107295317561</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03077021088110345</v>
+        <v>0.0299439701047916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0315026081063546</v>
+        <v>0.03067420358973892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03298288312390918</v>
+        <v>0.03143354658856411</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03371134562772395</v>
+        <v>0.03283750699308748</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03443928041755327</v>
+        <v>0.03135399005537449</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03458747057679854</v>
+        <v>0.0366848694520361</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03211573800810529</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03251740973639267</v>
+        <v>0.03094044054054025</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03455060516317098</v>
+        <v>0.03142750272845008</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03119942180350075</v>
+        <v>0.03013044752412289</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03076921133437037</v>
+        <v>0.02999729736675963</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03290845063744403</v>
+        <v>0.03128336611343924</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03204960731932871</v>
+        <v>0.03110670076756732</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03395387419209746</v>
+        <v>0.0322420709304115</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03075260136464656</v>
+        <v>0.02981832711647183</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03229022131189459</v>
+        <v>0.03144950507493999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03303156328226044</v>
+        <v>0.03078427138848201</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03275095703178382</v>
+        <v>0.03065186786510283</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03138516008667416</v>
+        <v>0.03019267975679632</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03252353368134831</v>
+        <v>0.03157879956827054</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03648445227623254</v>
+        <v>0.03308086579645068</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03414064226366583</v>
+        <v>0.03242577547537955</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03338784095017636</v>
+        <v>0.03242279867280356</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03534824365344461</v>
+        <v>0.03390949767611022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03296620980135214</v>
+        <v>0.03184925482374834</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03268075161011346</v>
+        <v>0.03151396028727513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03778627468397661</v>
+        <v>0.03457954637964848</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03381186311337048</v>
+        <v>0.03283652620472135</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03454426033862163</v>
+        <v>0.03356675968966865</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03602453535617621</v>
+        <v>0.03432610268849386</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03675299785999098</v>
+        <v>0.03573006309301723</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0374809326498203</v>
+        <v>0.03424654615530418</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03762912280906545</v>
+        <v>0.0395774255519661</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03378702672276571</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0345654136024247</v>
+        <v>0.03289533802449576</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03650629826147102</v>
+        <v>0.03329529048620667</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03212582583912884</v>
+        <v>0.03102693430546235</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0338108635666374</v>
+        <v>0.03288985346668938</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03595010286971106</v>
+        <v>0.03417592221336898</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03509125955159573</v>
+        <v>0.03399925686749705</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03613310513386437</v>
+        <v>0.0343207386897843</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03330991956014984</v>
+        <v>0.03225407760493521</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03533222097304096</v>
+        <v>0.03434238902867581</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03411999239274672</v>
+        <v>0.03183365430811307</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03754852321311446</v>
+        <v>0.03520177671616924</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03262614460505101</v>
+        <v>0.03138602269470713</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03556518591361534</v>
+        <v>0.03447135566820028</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04137275011462886</v>
+        <v>0.03771602243025384</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03577719937216808</v>
+        <v>0.03359008280986087</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03447862055656704</v>
+        <v>0.03296697772782702</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03643902325983529</v>
+        <v>0.03445367673113367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03471626206671932</v>
+        <v>0.03303981745277722</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03244678991087167</v>
+        <v>0.03105032635203219</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03851048368055156</v>
+        <v>0.03477780734284578</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03490264271976116</v>
+        <v>0.0333807052597448</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03563503994501231</v>
+        <v>0.0341109387446921</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0371153149625669</v>
+        <v>0.03487028174351731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03784377746638168</v>
+        <v>0.03627424214804068</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03857171225621098</v>
+        <v>0.03479072521032765</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03871990241545625</v>
+        <v>0.04012160460698933</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03624816984676301</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03705495576008662</v>
+        <v>0.03472463762764579</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03917622880206423</v>
+        <v>0.03528723979201657</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03533185396970393</v>
+        <v>0.03356718191379306</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03490164317302809</v>
+        <v>0.03343403252171282</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03704088247610175</v>
+        <v>0.03472010126839242</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03618203915798642</v>
+        <v>0.0345434359225205</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03808779001763109</v>
+        <v>0.03567993089294865</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03629525382699957</v>
+        <v>0.03446454048871529</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03642265315055232</v>
+        <v>0.03488624022989319</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03716399512091815</v>
+        <v>0.03422100654343522</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03688338887044153</v>
+        <v>0.03408860302005603</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03478080344474445</v>
+        <v>0.0329975054702708</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03665596552000602</v>
+        <v>0.03501553472322372</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.04061688411489027</v>
+        <v>0.03651760095140388</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007716196104872069</v>
+        <v>0.007481092212630256</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008401714362643352</v>
+        <v>0.008224086087521504</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007769936218398019</v>
+        <v>0.007543235702440631</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00760097308332983</v>
+        <v>0.007411277708572469</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00763095173073115</v>
+        <v>0.007418878629181418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007882185371576676</v>
+        <v>0.007525318604194777</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007559142078163906</v>
+        <v>0.007385020659844198</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00772339310329796</v>
+        <v>0.007536066997825747</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007760587161908868</v>
+        <v>0.007535671433113979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007773412559847549</v>
+        <v>0.007575583103447042</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00785185858681276</v>
+        <v>0.007500573148253161</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007782629461371202</v>
+        <v>0.007923708481175986</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007647360030016355</v>
+        <v>0.007462459950291301</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01135652609948906</v>
+        <v>0.01103558447693143</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007920286016067233</v>
+        <v>0.007537485802788431</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007616045729135562</v>
+        <v>0.007419293732054192</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007554819103786571</v>
+        <v>0.007385109738930029</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00775899260556678</v>
+        <v>0.00751522369731546</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007673283521582068</v>
+        <v>0.007488999687191106</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01029689152578921</v>
+        <v>0.009946127144837889</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00761788734654994</v>
+        <v>0.00742463233218986</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009718754560138276</v>
+        <v>0.009502292836053446</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007839502164807161</v>
+        <v>0.00753359881186381</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007939365071357113</v>
+        <v>0.007580219287009815</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009343475328616711</v>
+        <v>0.009126443204132006</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007755549697360641</v>
+        <v>0.007562379358743845</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008063297599010096</v>
+        <v>0.00766702231543299</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008509418453688463</v>
+        <v>0.00794164391313649</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008722898687445396</v>
+        <v>0.008565287920587089</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00890319326776043</v>
+        <v>0.008392955524302881</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007691354514574569</v>
+        <v>0.007446203676463131</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007908787733852254</v>
+        <v>0.007503247577263921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009689039362650096</v>
+        <v>0.008255753460605147</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007396469071251454</v>
+        <v>0.007262408134722215</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008571790008574626</v>
+        <v>0.008343167871000897</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008828015360920809</v>
+        <v>0.008334254627385478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008916580213232295</v>
+        <v>0.008613857962036077</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009481765669695852</v>
+        <v>0.008083903208969009</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009005883503152972</v>
+        <v>0.01110151588006763</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008024962213946933</v>
+        <v>0.007813886118031681</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01441426046963478</v>
+        <v>0.01369290260572012</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009959705043865154</v>
+        <v>0.008342080219746731</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007800367870889374</v>
+        <v>0.007504750908412333</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00736489965336982</v>
+        <v>0.007262479220377227</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008814137410258266</v>
+        <v>0.008184661330949392</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008212395546497331</v>
+        <v>0.008005593340023513</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01357557407367431</v>
+        <v>0.01226616358183895</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007808467798804011</v>
+        <v>0.007538639168532593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01185506732388593</v>
+        <v>0.01148199462098838</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009398975054975726</v>
+        <v>0.00832282400881113</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01010706801569395</v>
+        <v>0.008652737612451817</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01078560389632199</v>
+        <v>0.01040394428701783</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008796241975809032</v>
+        <v>0.008526202469607582</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01099138210712916</v>
+        <v>0.009275338085448634</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.031150938557525</v>
+        <v>0.02979561951882236</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0292469303802963</v>
+        <v>0.02854501308519653</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03175795786147416</v>
+        <v>0.0304975588236481</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02984944152399677</v>
+        <v>0.02900703257923105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03018806413725375</v>
+        <v>0.02909288847410532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03302586368378881</v>
+        <v>0.03029517695668897</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0293769410774345</v>
+        <v>0.02871044713500601</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0312322319655283</v>
+        <v>0.03041658500725607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03164806687136509</v>
+        <v>0.03040849750940008</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03179722473734272</v>
+        <v>0.03086293759855515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03268330869887003</v>
+        <v>0.03001566564835623</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03191902366685607</v>
+        <v>0.03476194221082976</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03037340342587074</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0309427588998767</v>
+        <v>0.02956035371592474</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03345622799047202</v>
+        <v>0.03043261106199193</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03001969399213206</v>
+        <v>0.02909757725201012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02932811109317606</v>
+        <v>0.02871145332425889</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03163434472023481</v>
+        <v>0.03018115033960048</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03066622118850084</v>
+        <v>0.02988493808160509</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03276839433259781</v>
+        <v>0.0302548451737963</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03001252007264519</v>
+        <v>0.02913444123551822</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03122154917456049</v>
+        <v>0.03020694201044729</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03254373722808181</v>
+        <v>0.03038870571139439</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03363006045519847</v>
+        <v>0.03085098916890276</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03030800687330033</v>
+        <v>0.02927472419772466</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03159545548823037</v>
+        <v>0.03071379522810998</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03502690597181462</v>
+        <v>0.03187450711361332</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.07008864480170755</v>
+        <v>0.05793178179688308</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03929865342991704</v>
+        <v>0.03789331280184381</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08612567447102416</v>
+        <v>0.07438392791408427</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04929193369521564</v>
+        <v>0.04545056424681013</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05708140720902168</v>
+        <v>0.04841789483858337</v>
       </c>
       <c r="G5" t="n">
-        <v>0.100631323364281</v>
+        <v>0.06597107182235198</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04283403136638469</v>
+        <v>0.04207177445458506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07723014681922076</v>
+        <v>0.07366471938871047</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07987297202586764</v>
+        <v>0.07042604551935754</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0809000391139362</v>
+        <v>0.07568340181995019</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0993248358596537</v>
+        <v>0.06349384034694644</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09026306440552719</v>
+        <v>0.155591320553717</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0970760364193235</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06481401897778745</v>
+        <v>0.05283297005590821</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1075897947996047</v>
+        <v>0.06813693343818995</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05304892314571942</v>
+        <v>0.04774458935360805</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04159927408209087</v>
+        <v>0.0417969414189364</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07826442466783855</v>
+        <v>0.06444960269866837</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06630729934705792</v>
+        <v>0.06340515039199905</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09951270156762232</v>
+        <v>0.06771338250896221</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05077504843916956</v>
+        <v>0.04660410178555912</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07432400932785514</v>
+        <v>0.06738522713613626</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09965354954577361</v>
+        <v>0.07175775775447757</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1172028097437505</v>
+        <v>0.07961064053515415</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05491424841654678</v>
+        <v>0.04838394391763711</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08103667299277829</v>
+        <v>0.07645564246728148</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1536552021957285</v>
+        <v>0.1041645559971452</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03183646733316828</v>
+        <v>0.03164390661184542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02993245915593959</v>
+        <v>0.02920855876578983</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03376219771776168</v>
+        <v>0.03234584591667116</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03053497029964005</v>
+        <v>0.03085531967225411</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03219230399354127</v>
+        <v>0.02975643415469862</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03371139245943208</v>
+        <v>0.03095872263728227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03006246985307779</v>
+        <v>0.02937399281559931</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03191776074117158</v>
+        <v>0.03108013068784938</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03365230672765261</v>
+        <v>0.03225678460242314</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03380146459363024</v>
+        <v>0.03271122469157821</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03336883747451331</v>
+        <v>0.03186395274137929</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03392326352314361</v>
+        <v>0.03542548789142303</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03106475311483504</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O6" t="n">
-        <v>0.031634108588841</v>
+        <v>0.03140738840010798</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03545308346699266</v>
+        <v>0.03228116071993831</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03202393384841959</v>
+        <v>0.03094586434503318</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03133235094946359</v>
+        <v>0.02937499900485219</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03231987349587808</v>
+        <v>0.03202943743262354</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03135174996414412</v>
+        <v>0.0305484837621984</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03349559734981285</v>
+        <v>0.03098270711013342</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03201675992893271</v>
+        <v>0.03098272832854128</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03197623371043964</v>
+        <v>0.03205375960083968</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03322926600372509</v>
+        <v>0.03105225139198768</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03441102549246034</v>
+        <v>0.03163255448248716</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03099353564894361</v>
+        <v>0.03112301129074772</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03359969534451789</v>
+        <v>0.03256208232113304</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0357411154875647</v>
+        <v>0.03254666347487276</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03196435361746795</v>
+        <v>0.03056538093685765</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03006034544023924</v>
+        <v>0.02931477450323181</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03257137292141711</v>
+        <v>0.03126732024168337</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0306628565839397</v>
+        <v>0.02977679399726633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03100147919719668</v>
+        <v>0.0298626498921406</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03383927874373176</v>
+        <v>0.03106493837472426</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03019035613737744</v>
+        <v>0.02948020855304129</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03204564702547123</v>
+        <v>0.03118634642529135</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03246148193130802</v>
+        <v>0.03117825892743536</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03261063979728566</v>
+        <v>0.03163269901659042</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03349672375881297</v>
+        <v>0.03078542706639151</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03273243872679901</v>
+        <v>0.03553170362886503</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03118681848581368</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03175605513476315</v>
+        <v>0.03032999800630683</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03426952422535846</v>
+        <v>0.03120225535237403</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.030833109052075</v>
+        <v>0.02986733867004539</v>
       </c>
       <c r="R7" t="n">
-        <v>0.030141526153119</v>
+        <v>0.02948121474229417</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03244775978017775</v>
+        <v>0.03095091175763576</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03147963624844378</v>
+        <v>0.03065469949964036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03362202732195566</v>
+        <v>0.03108752753200402</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03082593513258813</v>
+        <v>0.02990420265355349</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03203496423450343</v>
+        <v>0.03097670342848256</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03335715228802474</v>
+        <v>0.03115846712942966</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03448514975671316</v>
+        <v>0.03168506684268185</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03112142193324327</v>
+        <v>0.03004448561575994</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0324088705481733</v>
+        <v>0.03148355664614526</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03584032103175755</v>
+        <v>0.03264426853164859</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03312669666958942</v>
+        <v>0.03168754043985508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03282253095014937</v>
+        <v>0.03196084526942956</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03533355843132723</v>
+        <v>0.03391339100788113</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03257317317752331</v>
+        <v>0.0316114269684195</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03241305900645988</v>
+        <v>0.0312222169595927</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03693320200925242</v>
+        <v>0.03402700206869191</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03295254164728757</v>
+        <v>0.03212627931923903</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03480783253538137</v>
+        <v>0.03383241719148909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03522366744121815</v>
+        <v>0.03382432969363312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03537282530719579</v>
+        <v>0.03427876978278818</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03625890926872308</v>
+        <v>0.03343149783258927</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03549462423670903</v>
+        <v>0.0381777743950634</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03270885844306503</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03361901668282834</v>
+        <v>0.03211952742372912</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03604894678059947</v>
+        <v>0.0329122106770685</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03168104654667965</v>
+        <v>0.03069001482829871</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03290371166302913</v>
+        <v>0.03212728550849192</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03520994529008788</v>
+        <v>0.03359698252383352</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03424182175835391</v>
+        <v>0.03330077026583812</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03560377087342737</v>
+        <v>0.03299020230124296</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03314971632508475</v>
+        <v>0.0321326729302132</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03479746415906772</v>
+        <v>0.03362307368670959</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03435171852268075</v>
+        <v>0.03212081278289178</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.038836249023988</v>
+        <v>0.03584463332411716</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03225404709036935</v>
+        <v>0.03113833768468146</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03517105605808343</v>
+        <v>0.03412962741234302</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04027367576526661</v>
+        <v>0.03688219203946477</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03439110146019859</v>
+        <v>0.03256832043924216</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03353310735472616</v>
+        <v>0.03222458651359311</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03604413483590403</v>
+        <v>0.03417713225204468</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03389420318874579</v>
+        <v>0.03247730312462758</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03206289239192105</v>
+        <v>0.03068187395365026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03731204127114683</v>
+        <v>0.03397474985567524</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03366311805186437</v>
+        <v>0.03239002056340259</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03551840893995818</v>
+        <v>0.03409615843565265</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03593424384579495</v>
+        <v>0.03408807093779666</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0360834017117726</v>
+        <v>0.03454251102695172</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03696948567329988</v>
+        <v>0.03369523907675281</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03620520064128594</v>
+        <v>0.03844151563922634</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03465958040030061</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03557558438409995</v>
+        <v>0.03354046280116058</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03816444344478706</v>
+        <v>0.03447808161140435</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03430587157949008</v>
+        <v>0.03277715015099637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03361428806760593</v>
+        <v>0.03239102675265548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03592052169466468</v>
+        <v>0.03386072376799706</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03495239816293071</v>
+        <v>0.03356451151000166</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03709624554859942</v>
+        <v>0.0339987348579367</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03550577468261967</v>
+        <v>0.03386052382566147</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03550772614899036</v>
+        <v>0.03388651543884387</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03682991420251168</v>
+        <v>0.03406827913979097</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0379579116712001</v>
+        <v>0.03459487885304316</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03396353062104861</v>
+        <v>0.03240753393583813</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03588163246266023</v>
+        <v>0.03439336865650656</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03931308294624449</v>
+        <v>0.0355540805420099</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007827568819477305</v>
+        <v>0.007442871364654496</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008391724928521336</v>
+        <v>0.007992881077880048</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00782542506287803</v>
+        <v>0.007454710015921661</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007709826960248852</v>
+        <v>0.007367446389494956</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007797463905026722</v>
+        <v>0.007416890822354559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007980190116539677</v>
+        <v>0.007490515446361968</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007700769151549489</v>
+        <v>0.007367668761145762</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007854455920922498</v>
+        <v>0.007506074024950227</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007878720114733452</v>
+        <v>0.007505257487954521</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007964070884178744</v>
+        <v>0.007602955034147556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007939692413115235</v>
+        <v>0.007464613552584954</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00788348725470066</v>
+        <v>0.00780619353238025</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007737599302715885</v>
+        <v>0.007399661908215388</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01150324730757606</v>
+        <v>0.01099748239706914</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008017875410086063</v>
+        <v>0.007497950387116007</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007759673135342202</v>
+        <v>0.007398352201380029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007734244913428378</v>
+        <v>0.007401590444100451</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007883747285334006</v>
+        <v>0.007487153535406462</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007826853953485242</v>
+        <v>0.007486112368008678</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01004378413303807</v>
+        <v>0.009307240109582199</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007832953920077516</v>
+        <v>0.007450887950810063</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00950163919699463</v>
+        <v>0.008894756892727508</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007998625433601025</v>
+        <v>0.007536035361137734</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008361405853053186</v>
+        <v>0.007687650871134873</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009464869673200963</v>
+        <v>0.009088541692710351</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007919288649099004</v>
+        <v>0.007565414387709814</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.008155149619928895</v>
+        <v>0.007623334722469011</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008454194710010793</v>
+        <v>0.007776702308175517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008599701700770478</v>
+        <v>0.008175491834692298</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008446081973338158</v>
+        <v>0.007866363878466761</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007618241762552113</v>
+        <v>0.007241096012581428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0082482648725171</v>
+        <v>0.007597615377276059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009536948960351475</v>
+        <v>0.008114573241440708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007558530454319369</v>
+        <v>0.007247246474768863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00865663556231859</v>
+        <v>0.00823606162778495</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008820752383318536</v>
+        <v>0.008224145418745466</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009427306338866771</v>
+        <v>0.008916849696444065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009255767609362314</v>
+        <v>0.007933933360867972</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008873968975894023</v>
+        <v>0.01036599316217175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007819784128693457</v>
+        <v>0.007474014727826175</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0143858349558243</v>
+        <v>0.01361370461209229</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009804071095207216</v>
+        <v>0.00816709611282407</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007975549668087476</v>
+        <v>0.00746317548438988</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007797883758512676</v>
+        <v>0.007489825414846129</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008854935210885756</v>
+        <v>0.008092473983327273</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00845997830121006</v>
+        <v>0.008094041213886204</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01326057284125439</v>
+        <v>0.01121869642688095</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008490716180117645</v>
+        <v>0.007832417432241057</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01111779855718265</v>
+        <v>0.01011730497784809</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009681754808965897</v>
+        <v>0.00844644325535927</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01227554938243167</v>
+        <v>0.009530861288186211</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0108269172315799</v>
+        <v>0.0102790017357928</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009116683119692451</v>
+        <v>0.008657148381475868</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01079581240235641</v>
+        <v>0.009069769710583996</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03094542689629749</v>
+        <v>0.02956135878390836</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02931153803658446</v>
+        <v>0.02850227808351988</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03092121217933187</v>
+        <v>0.0296950817960196</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02961547843238078</v>
+        <v>0.02870939899227867</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03060537803863321</v>
+        <v>0.02926789660699073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03266935465588234</v>
+        <v>0.0300995206041548</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02951316631632376</v>
+        <v>0.02871191078237047</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03124912907579867</v>
+        <v>0.03027526190660888</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03151950807780197</v>
+        <v>0.03026271036785023</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03248728051115228</v>
+        <v>0.03136957747295885</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03221191446583926</v>
+        <v>0.02980694679848354</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03159846685333857</v>
+        <v>0.03364200235167233</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0299291798164547</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03066616356385807</v>
+        <v>0.02949968020661994</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03309502738258026</v>
+        <v>0.03018350168021333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03017851391043366</v>
+        <v>0.02905849435489634</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02989129044635697</v>
+        <v>0.02909507179608883</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03157998851151998</v>
+        <v>0.03006154627335687</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03093735215606251</v>
+        <v>0.03004978580863818</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03328512761649781</v>
+        <v>0.03026529266210696</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03098231582884237</v>
+        <v>0.02963045688007014</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03072557979565068</v>
+        <v>0.02943580504785048</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03287759004275503</v>
+        <v>0.03061368898174234</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0369432705190284</v>
+        <v>0.03227903125661983</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03026758540042496</v>
+        <v>0.02912182111148044</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03198144456508079</v>
+        <v>0.03094553860189397</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03460612335881012</v>
+        <v>0.03157958760454527</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06352790724788102</v>
+        <v>0.05298552436115461</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03816177832456365</v>
+        <v>0.03675010563135804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0668242978844365</v>
+        <v>0.05802909422149736</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04227362143955753</v>
+        <v>0.03931927279075519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06214155529079396</v>
+        <v>0.05107940764866583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09064396575285107</v>
+        <v>0.06138068018514217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0430213585962799</v>
+        <v>0.04172855647337101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07436471825424176</v>
+        <v>0.06990234841168924</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07451444678890243</v>
+        <v>0.06658065956518383</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09022268988220909</v>
+        <v>0.08373465140924569</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08662288411220885</v>
+        <v>0.05839460987786833</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07976592511153867</v>
+        <v>0.129756770314089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09994715337407729</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05853799033587113</v>
+        <v>0.05159625405982938</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09721932075889174</v>
+        <v>0.06258583482015505</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0530367752599416</v>
+        <v>0.04627257062139727</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04993459917933143</v>
+        <v>0.04875320515066761</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07464338032197643</v>
+        <v>0.06169100882781992</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06902629187066289</v>
+        <v>0.06614604006180133</v>
       </c>
       <c r="U5" t="n">
-        <v>0.103335192422797</v>
+        <v>0.06597677571024316</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06358881718843162</v>
+        <v>0.05378845965408752</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06328116715254706</v>
+        <v>0.05334724273366663</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1011841382857818</v>
+        <v>0.07409808184696874</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.176050374139492</v>
+        <v>0.1055954178856139</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05117383882445293</v>
+        <v>0.04485349439444131</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0859348956828337</v>
+        <v>0.08049885470723309</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.141284495968222</v>
+        <v>0.0970038524623046</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03323230529774924</v>
+        <v>0.03024438879428697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.030209746045431</v>
+        <v>0.02918530809389848</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03181942018817841</v>
+        <v>0.03155525101198631</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03190235683383253</v>
+        <v>0.03056956820824539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03150358604747976</v>
+        <v>0.02995092661736934</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03495623305733409</v>
+        <v>0.0307825506145334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03041137432517029</v>
+        <v>0.03057207999833717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03214733708464521</v>
+        <v>0.03095829191698748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03380638647925373</v>
+        <v>0.03212287958381695</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03477415891260402</v>
+        <v>0.03322974668892557</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03449879286729102</v>
+        <v>0.03048997680886216</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0324966748621851</v>
+        <v>0.03432503236205092</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03083853869991588</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03295587318170159</v>
+        <v>0.03038543629827072</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0339160202188951</v>
+        <v>0.03204678621191787</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03246539231188542</v>
+        <v>0.03091866357086305</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03217816884780872</v>
+        <v>0.03095524101205555</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03386686691297173</v>
+        <v>0.03074457628373545</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03322423055751427</v>
+        <v>0.03190995502460492</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03421542687402125</v>
+        <v>0.03217268653519442</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03188052383768891</v>
+        <v>0.03031348689044874</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03301528438414737</v>
+        <v>0.03018910577477274</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03377579805160156</v>
+        <v>0.03129671899212093</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03794957550687244</v>
+        <v>0.03309168413951881</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03255446380187671</v>
+        <v>0.02980485112185904</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03426832296653255</v>
+        <v>0.03280570781786066</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03553196014064769</v>
+        <v>0.03227853219121329</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03168159163593805</v>
+        <v>0.03032001137118202</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03004770277622502</v>
+        <v>0.02926093067079354</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03165737691897244</v>
+        <v>0.03045373438329326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03035164317202134</v>
+        <v>0.02946805157955232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03134154277827378</v>
+        <v>0.03002654919426439</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0334055193955229</v>
+        <v>0.03085817319142846</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03024933105596432</v>
+        <v>0.02947056336964414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03198529381543923</v>
+        <v>0.03103391449388254</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03225567281744255</v>
+        <v>0.03102136295512389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03322344525079284</v>
+        <v>0.03212823006023251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03294807920547983</v>
+        <v>0.03056559938575719</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03233463159297913</v>
+        <v>0.03440065493894599</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03066534455609527</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03140220788394625</v>
+        <v>0.03025821499116957</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03383107170266844</v>
+        <v>0.03094203646476295</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03091467865007424</v>
+        <v>0.02981714694217</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03062745518599753</v>
+        <v>0.02985372438336249</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03231615325116056</v>
+        <v>0.03082019886063052</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03167351689570309</v>
+        <v>0.03080843839591186</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0340521203777612</v>
+        <v>0.03106979765395018</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03171848056848294</v>
+        <v>0.0303891094673438</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03146174453529124</v>
+        <v>0.03019445763512415</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03361375478239559</v>
+        <v>0.03137234156901601</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03771152650734586</v>
+        <v>0.03308490850101423</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03100375014006553</v>
+        <v>0.02988047369875409</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03271760930472135</v>
+        <v>0.03170419118916763</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03534228809845069</v>
+        <v>0.03233824019181893</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03292755069774723</v>
+        <v>0.03142793772478503</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03296310507243724</v>
+        <v>0.03187353311878951</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03457277921518465</v>
+        <v>0.03306633683128923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03237811619145409</v>
+        <v>0.03127945839248999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03284758158477757</v>
+        <v>0.03136888649782883</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0366670916217838</v>
+        <v>0.03378278002963694</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03316473335217654</v>
+        <v>0.03208316581764011</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03490069611165145</v>
+        <v>0.03364651694187851</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03517107511365476</v>
+        <v>0.03363396540311986</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03613884754700505</v>
+        <v>0.03474083250822847</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03586348150169205</v>
+        <v>0.03317820183375318</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0352500338891913</v>
+        <v>0.03701325738694285</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0322866490538137</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03337926211258745</v>
+        <v>0.03202508971159963</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0357209525938963</v>
+        <v>0.03263034149550485</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03183255401320034</v>
+        <v>0.03062937010071876</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03354285748220975</v>
+        <v>0.03246632683135846</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03523155554737276</v>
+        <v>0.0334328013086265</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03458891919191529</v>
+        <v>0.03342104084390782</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03615306729222439</v>
+        <v>0.03294838786757504</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03417662201287846</v>
+        <v>0.03258938897820457</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03437747492469944</v>
+        <v>0.0328073557948946</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0346846379350464</v>
+        <v>0.0323224712813359</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04228530312683814</v>
+        <v>0.03719191304467907</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03221869843671888</v>
+        <v>0.03096044992141643</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03563301160093358</v>
+        <v>0.03431679363716361</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04000156344935683</v>
+        <v>0.03652260263920224</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0339057145299801</v>
+        <v>0.03214205419631892</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03326897236412014</v>
+        <v>0.03193538206462079</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03487864650686757</v>
+        <v>0.03312818577712051</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03334277582119929</v>
+        <v>0.03194577023687616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03226411632448363</v>
+        <v>0.03073596672870856</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03662678956965627</v>
+        <v>0.03353262417475231</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03347060064385943</v>
+        <v>0.0321450147634714</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03520656340333433</v>
+        <v>0.03370836588770978</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03547694240533766</v>
+        <v>0.03369581434895114</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03644471483868795</v>
+        <v>0.03480268145405976</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03616934879337494</v>
+        <v>0.03324005077958445</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03555590118087425</v>
+        <v>0.03707510633277325</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03388661414399037</v>
+        <v>0.04730731015945099</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03495405178060151</v>
+        <v>0.03321527072470754</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0374547835230956</v>
+        <v>0.03396052826272011</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03413594882420759</v>
+        <v>0.03249159792549386</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03384872477389266</v>
+        <v>0.03252817577718972</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03553742283905566</v>
+        <v>0.03349465025445776</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03489478648359819</v>
+        <v>0.0334828897897391</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03727465319271039</v>
+        <v>0.03374562130032858</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03609043609448213</v>
+        <v>0.0340472202922173</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03468301412318636</v>
+        <v>0.03286890902895139</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0368350243702907</v>
+        <v>0.03404679296284325</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.04093279609524095</v>
+        <v>0.03575935989484147</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03362382917409964</v>
+        <v>0.03204099836178213</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03593887889261647</v>
+        <v>0.03437864258299489</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0385635576863458</v>
+        <v>0.03501269158564616</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007237802745885184</v>
+        <v>0.0071784511201667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00804737264499779</v>
+        <v>0.008000868983977236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00729408966822266</v>
+        <v>0.007238644906813452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007247030948687095</v>
+        <v>0.007192937016543089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007234617962870104</v>
+        <v>0.007178174902288868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007303435344876076</v>
+        <v>0.007202220021915929</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007281342129161853</v>
+        <v>0.007227825385124946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007275557861570512</v>
+        <v>0.007223583300103822</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00729101737054726</v>
+        <v>0.007225065425818251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007351584838067543</v>
+        <v>0.007299652270728789</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007371659200097746</v>
+        <v>0.007276972980106307</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007339348758789318</v>
+        <v>0.007366907114946731</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007322148446117486</v>
+        <v>0.007269945098585967</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0107360727740867</v>
+        <v>0.01066767992702993</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007325210422375578</v>
+        <v>0.007237974746154726</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007274328723402102</v>
+        <v>0.007219901863691709</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007287378974354284</v>
+        <v>0.007236039295361102</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007290415984700504</v>
+        <v>0.007229327334262719</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007252232616918778</v>
+        <v>0.007199750769158766</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009726354198831767</v>
+        <v>0.009611648001160369</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007229227126276365</v>
+        <v>0.007175084167715041</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009265013187894779</v>
+        <v>0.009191375664903609</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007312252668139338</v>
+        <v>0.007250079284798963</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00723794919214589</v>
+        <v>0.007177851703474326</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008961054030580692</v>
+        <v>0.008902494654453388</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007318675632806145</v>
+        <v>0.00726235776920311</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007338354361868918</v>
+        <v>0.007237292090991084</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007094583672737374</v>
+        <v>0.007001101701955016</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008227852991691174</v>
+        <v>0.008193171594487382</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007499824728978832</v>
+        <v>0.007433939157646334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007161142672513682</v>
+        <v>0.007104963674689999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00707454405249491</v>
+        <v>0.007001517628985391</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007558702279166478</v>
+        <v>0.007168920871638086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007410742007702543</v>
+        <v>0.007358619030530995</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007367853401690304</v>
+        <v>0.00732678974514876</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007473027037794973</v>
+        <v>0.007333046284884489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007905317298558277</v>
+        <v>0.007864491295849863</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008043501235597572</v>
+        <v>0.007699569221203736</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007827846666103212</v>
+        <v>0.008346223939591635</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007697935036642164</v>
+        <v>0.007655228995283331</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01293018431242073</v>
+        <v>0.01283562311427362</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007716309129661664</v>
+        <v>0.007424523828276988</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00735642977368149</v>
+        <v>0.007297865667257068</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007453532759299369</v>
+        <v>0.007417030798193923</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007465185806015952</v>
+        <v>0.007359625614398037</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007199701813541853</v>
+        <v>0.00715498605748632</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01184695008632508</v>
+        <v>0.01141786618158827</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007033699659651833</v>
+        <v>0.006977197632162464</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01098363483635856</v>
+        <v>0.01083177652305529</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007629015553180026</v>
+        <v>0.007515061292522411</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0070973235020164</v>
+        <v>0.006998302579527314</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01014216724099403</v>
+        <v>0.01005996076175971</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00767363314417296</v>
+        <v>0.007601565545377999</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00781804172486757</v>
+        <v>0.007428317260742231</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02884490368328275</v>
+        <v>0.02843720186439916</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0284216950349654</v>
+        <v>0.02809213954545188</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02948069036434829</v>
+        <v>0.02911711837508416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02894914047911346</v>
+        <v>0.02860082672781198</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02880893009405495</v>
+        <v>0.02843408185640246</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02958625408137228</v>
+        <v>0.02870568254389158</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02933670104649873</v>
+        <v>0.02899490690038649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02927136508316003</v>
+        <v>0.02894699059861744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0294423272872949</v>
+        <v>0.02896023631247511</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03013012475683108</v>
+        <v>0.02980622461528169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03035687391062489</v>
+        <v>0.0295500515947117</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03000763747704185</v>
+        <v>0.03056917358881606</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02979762716834582</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02897255248840105</v>
+        <v>0.0285934582962162</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02983221359875963</v>
+        <v>0.02910954860215468</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02925748140211625</v>
+        <v>0.0289054070807982</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02940488999003322</v>
+        <v>0.0290876867950893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0294391944189876</v>
+        <v>0.02901187210682843</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02900789571467596</v>
+        <v>0.02867779119808718</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03015365528131589</v>
+        <v>0.02917871315183604</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02872434035887433</v>
+        <v>0.02837659149044635</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02995833969010449</v>
+        <v>0.02947952313566451</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02968584980379974</v>
+        <v>0.0292462749345042</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02882548940912765</v>
+        <v>0.02834663976031132</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02926707844227191</v>
+        <v>0.02887995400277122</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02975840014442124</v>
+        <v>0.02938496606423092</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02998098557398653</v>
+        <v>0.02910730874770302</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03942281154134884</v>
+        <v>0.03770587332174707</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03258097173859</v>
+        <v>0.0322006182786746</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05340101903043145</v>
+        <v>0.05235881995091635</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04178126914291699</v>
+        <v>0.04106407592526071</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04023886216627138</v>
+        <v>0.03897458711413755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05104622309063142</v>
+        <v>0.04176971230447381</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05173355946820754</v>
+        <v>0.05110437846916548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04960501287634863</v>
+        <v>0.04933450302697202</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05003243058450206</v>
+        <v>0.04724415749554852</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06298127551894146</v>
+        <v>0.06268521949742152</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06443904349426578</v>
+        <v>0.05614033991455943</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0613967721037669</v>
+        <v>0.07708447328312724</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06330830701438252</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04131620048193621</v>
+        <v>0.04011227006275412</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0569186891499243</v>
+        <v>0.04963939432962058</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04786802646986433</v>
+        <v>0.04707473007794938</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05285907516027764</v>
+        <v>0.05274112622497849</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04793380449784627</v>
+        <v>0.04602330265129592</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04369004994608502</v>
+        <v>0.04329363838720778</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06368540357939104</v>
+        <v>0.05288630061153392</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03774589772323319</v>
+        <v>0.03703429863562377</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06156415735358899</v>
+        <v>0.05836165523446214</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05703577433323096</v>
+        <v>0.05453083740785649</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04039656365872749</v>
+        <v>0.03840037206471662</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04628489264410724</v>
+        <v>0.04494201930434867</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05772713699099039</v>
+        <v>0.0565259105610334</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06404620641598267</v>
+        <v>0.05276324342278438</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02951634123017742</v>
+        <v>0.02905589000493245</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03028700867200759</v>
+        <v>0.02871082768598518</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03015212791124297</v>
+        <v>0.03087400951775207</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02962057802600812</v>
+        <v>0.03035771787047991</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03067424373109715</v>
+        <v>0.02905276999693574</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03145156771841447</v>
+        <v>0.02932437068442486</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0300081385933934</v>
+        <v>0.03075179804305438</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0299428026300547</v>
+        <v>0.03070388174128535</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03011376483418958</v>
+        <v>0.02957892445300839</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03080156230372575</v>
+        <v>0.03156311575794965</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03102831145751955</v>
+        <v>0.030168739735245</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03187295111408404</v>
+        <v>0.03232606473148394</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03047034177655115</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0308345221460269</v>
+        <v>0.03036514993603241</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03043618861216263</v>
+        <v>0.03088318859136829</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03112279503915844</v>
+        <v>0.03066229822346608</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03007632753692788</v>
+        <v>0.03084457793775722</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03011063196588226</v>
+        <v>0.02963056024736172</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03087320935171816</v>
+        <v>0.02929647933862046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03084616128024906</v>
+        <v>0.02988119270917143</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03058965399591652</v>
+        <v>0.03013348263311422</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03069617608179066</v>
+        <v>0.03125187247943794</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0303572873506944</v>
+        <v>0.02986496307503748</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02956929045237721</v>
+        <v>0.02909796288739825</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0311323920793141</v>
+        <v>0.02949864214330451</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03162371378146344</v>
+        <v>0.03114185720689883</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03065861741692566</v>
+        <v>0.02972689580374914</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02959600645030788</v>
+        <v>0.02917585732677866</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02917279780199053</v>
+        <v>0.02883079500783139</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03023179313137342</v>
+        <v>0.02985577383746366</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02970024324613858</v>
+        <v>0.02933948219019148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02956003286108007</v>
+        <v>0.02917273731878196</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0303373568483974</v>
+        <v>0.02944433800627108</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03008780381352386</v>
+        <v>0.02973356236276599</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03002246785018516</v>
+        <v>0.02968564606099694</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03019343005432003</v>
+        <v>0.02969889177485462</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0308812275238562</v>
+        <v>0.03054488007766119</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03110797667765001</v>
+        <v>0.03028870705709121</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03075874024406698</v>
+        <v>0.03130782905119556</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03054872993537093</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02972352952653516</v>
+        <v>0.02933199037079593</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03058319063689375</v>
+        <v>0.0298480806767344</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03000858416914138</v>
+        <v>0.0296440625431777</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03015599275705834</v>
+        <v>0.0298263422574688</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03019029718601272</v>
+        <v>0.02975052756920794</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02975899848170109</v>
+        <v>0.02941644666046668</v>
       </c>
       <c r="U7" t="n">
-        <v>0.030924595181807</v>
+        <v>0.02999975044042281</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02947544312589945</v>
+        <v>0.02911524695282592</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03070944245712962</v>
+        <v>0.030218178598044</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03043695257082486</v>
+        <v>0.0299849303968837</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02959766062819128</v>
+        <v>0.02916908663949293</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03001818120929703</v>
+        <v>0.02961860946515072</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03050950291144637</v>
+        <v>0.03012362152661042</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03073208834101165</v>
+        <v>0.02984596421008252</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.030728734416129</v>
+        <v>0.03030422812125098</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03183975902436886</v>
+        <v>0.03147431383419299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03289875435375175</v>
+        <v>0.03249929266382526</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03155027051648584</v>
+        <v>0.03117622938367618</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03093177643728569</v>
+        <v>0.03053715046869096</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03332245133110956</v>
+        <v>0.03240203264730458</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03275476503590218</v>
+        <v>0.0323770811891276</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0326894290725635</v>
+        <v>0.03232916488735854</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03286039127669838</v>
+        <v>0.03234241060121622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03354818874623453</v>
+        <v>0.0331883989040228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03377493790002834</v>
+        <v>0.03293222588345281</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03342570146644516</v>
+        <v>0.03395134787755724</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03202640371223479</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03152815554863288</v>
+        <v>0.03112390031164305</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03230770358260999</v>
+        <v>0.03156087411460369</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03083980028293095</v>
+        <v>0.0304746721678606</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03282295397943668</v>
+        <v>0.0324698610838304</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03285725840839106</v>
+        <v>0.03239404639556954</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03242595970407942</v>
+        <v>0.03205996548682828</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0328430921424392</v>
+        <v>0.0319041585497734</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0317221302350249</v>
+        <v>0.03134355356199761</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0333767052001161</v>
+        <v>0.03286199519423557</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03140878421103212</v>
+        <v>0.03095440634922996</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03378860931227307</v>
+        <v>0.03331737747388906</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03112241000471409</v>
+        <v>0.03071883560706419</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0331764641338247</v>
+        <v>0.03276714035297202</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03500168449019253</v>
+        <v>0.03407218185021511</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03170925913265717</v>
+        <v>0.0311526852442155</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03222499957709215</v>
+        <v>0.03170174140589618</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03328399490647504</v>
+        <v>0.03272672023552845</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03253573976825012</v>
+        <v>0.03200406985517346</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03044770008988872</v>
+        <v>0.02998249631057785</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0333895591015433</v>
+        <v>0.0323152846191076</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03314000558862548</v>
+        <v>0.03260450876083078</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03307466962528679</v>
+        <v>0.03255659245906173</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03324563182942165</v>
+        <v>0.0325698381729194</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03393342929895781</v>
+        <v>0.03341582647572599</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03416017845275163</v>
+        <v>0.03315965345515599</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03381094201916859</v>
+        <v>0.03417877544926035</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03360093171047256</v>
+        <v>0.05787512847661368</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03308702416688467</v>
+        <v>0.03249937013633929</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03401435868670534</v>
+        <v>0.03307990273232554</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03306078642228727</v>
+        <v>0.03251500915601422</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03320819453215996</v>
+        <v>0.0326972886555336</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03324249896111434</v>
+        <v>0.03262147396727273</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0328112002568027</v>
+        <v>0.03228739305853148</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03397802827548114</v>
+        <v>0.03287210642908243</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03361117202216007</v>
+        <v>0.03301798642250937</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03376164423223124</v>
+        <v>0.0330891249961088</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03348915434592648</v>
+        <v>0.0328558767949485</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03264986240329289</v>
+        <v>0.03204003303755772</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03250428036590615</v>
+        <v>0.03195048201279782</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03356170468654799</v>
+        <v>0.03299456792467521</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03378429011611327</v>
+        <v>0.03271691060814731</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0071709916798346</v>
+        <v>0.007149997346538095</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008034288054307455</v>
+        <v>0.0080101578941733</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00717030934272227</v>
+        <v>0.007146510392011347</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007206400049154966</v>
+        <v>0.007186452779529296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007206417610019798</v>
+        <v>0.007184469533504005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007190397754920597</v>
+        <v>0.007168275198250897</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007195541070481042</v>
+        <v>0.007174193236894461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007193032904358898</v>
+        <v>0.007173135982381787</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007198939742702343</v>
+        <v>0.007177435323390174</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007177328143401656</v>
+        <v>0.007156507106177729</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007207191966299916</v>
+        <v>0.007186940659828537</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007159300786195248</v>
+        <v>0.007138428685135878</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007206888055681556</v>
+        <v>0.007185720422487028</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01067838283664721</v>
+        <v>0.010654387862262</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007199135401869389</v>
+        <v>0.007181418373780812</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007161071741473846</v>
+        <v>0.007139307823900911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007268625082024281</v>
+        <v>0.007244001430910061</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007206236704288377</v>
+        <v>0.007182590205136233</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007171164018006021</v>
+        <v>0.007151169380174746</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009547261519045454</v>
+        <v>0.009513011562436623</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007199022931968483</v>
+        <v>0.00717713192513294</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009219745921195151</v>
+        <v>0.009184745629210943</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007347355599109352</v>
+        <v>0.007326841502954012</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007196013671653996</v>
+        <v>0.007174828140198125</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008900604224501592</v>
+        <v>0.008881200337656785</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007234435896035571</v>
+        <v>0.007213408412267322</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007141835683788822</v>
+        <v>0.007120646412016193</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006948376056116198</v>
+        <v>0.006927702858997565</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008376382539026001</v>
+        <v>0.008349208579062076</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006944710531648475</v>
+        <v>0.006904055852803086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007200982026945659</v>
+        <v>0.007187776089009062</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007202818633547201</v>
+        <v>0.007175339514707845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007084842700229066</v>
+        <v>0.007056199192721681</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007126835206859495</v>
+        <v>0.007103631813101248</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007107620119902635</v>
+        <v>0.007094791706700666</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00714683859059066</v>
+        <v>0.007122557840944591</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006994015400340829</v>
+        <v>0.006974579896095469</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007202937113973371</v>
+        <v>0.00718751568173111</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006881748055189107</v>
+        <v>0.006861762624782245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007204966723097727</v>
+        <v>0.007183059950569177</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01295131436419624</v>
+        <v>0.01292725894296557</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007148147872489246</v>
+        <v>0.007150756040199914</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006877957840249142</v>
+        <v>0.006851827565799319</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007649066658591924</v>
+        <v>0.007602426917898451</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007196739641532471</v>
+        <v>0.007157312831196366</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006950813152510253</v>
+        <v>0.006937267976569968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01078448066992393</v>
+        <v>0.0107429813060047</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007146672194295757</v>
+        <v>0.007119647853570995</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01084486548829299</v>
+        <v>0.01079758966284551</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008205553285322437</v>
+        <v>0.008188303698959306</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007128179622438697</v>
+        <v>0.007106142211358173</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0100681414692265</v>
+        <v>0.01004835585333777</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007402339456039062</v>
+        <v>0.007381430046038648</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006752835147428499</v>
+        <v>0.006730612167296</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02853499480414816</v>
+        <v>0.0283092769214785</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02853856092402102</v>
+        <v>0.02831013226162609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02852728749257379</v>
+        <v>0.02826989016602061</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02893494862427643</v>
+        <v>0.0287210578074419</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02893514698232304</v>
+        <v>0.02869865613124796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0287541953494801</v>
+        <v>0.02851573366480181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02881229146477738</v>
+        <v>0.02858258063371311</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02878396057461429</v>
+        <v>0.02857063845763142</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02884757444780396</v>
+        <v>0.02861607311956199</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0286065680750553</v>
+        <v>0.02838280765124556</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0289438936927285</v>
+        <v>0.02872656863985784</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02843199421062216</v>
+        <v>0.02820730642498855</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02894046088248824</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02897908477019631</v>
+        <v>0.02875662922670924</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02885289109128286</v>
+        <v>0.0286641918785717</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02842294453696633</v>
+        <v>0.02818853384586816</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02963780899546459</v>
+        <v>0.02937109629847523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02893310356886582</v>
+        <v>0.0286774282528002</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02853694144307389</v>
+        <v>0.02832251558056673</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02834496488333185</v>
+        <v>0.02807770243593866</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0288316356508118</v>
+        <v>0.02859564414197704</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02959767087344163</v>
+        <v>0.02936474667756182</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03052710640376767</v>
+        <v>0.03030681302052748</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02880695028945068</v>
+        <v>0.02853534540384576</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02908601238396496</v>
+        <v>0.02885668108309012</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02925162641191952</v>
+        <v>0.02902553407942158</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02822575196861341</v>
+        <v>0.02799753518194145</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03588365087000686</v>
+        <v>0.03567777744285995</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03653352858239373</v>
+        <v>0.03628320983814183</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03637145798822668</v>
+        <v>0.03562352934641679</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04290291152590993</v>
+        <v>0.04290327242339414</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04379324414663421</v>
+        <v>0.04339734665104892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03870573763098673</v>
+        <v>0.03831689923632879</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04247177344860405</v>
+        <v>0.04219152233452186</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04128965424056453</v>
+        <v>0.04130950058792529</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04094358347239482</v>
+        <v>0.04065286288301245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03736496197934926</v>
+        <v>0.03719416038273549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411453130888373</v>
+        <v>0.04106131929914637</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03459318891146897</v>
+        <v>0.03440857233834133</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03356474378346947</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04251834126758806</v>
+        <v>0.04236307757340517</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04094061672146972</v>
+        <v>0.04133303151029904</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03409923776070775</v>
+        <v>0.03375800636445991</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05739745301966341</v>
+        <v>0.05643339301726888</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04127591642788681</v>
+        <v>0.04063089951779773</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03654363472414034</v>
+        <v>0.03653392677626647</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03297992720729556</v>
+        <v>0.03280961389217637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04054941037521434</v>
+        <v>0.04018936849714051</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05389553295083718</v>
+        <v>0.05357100351038561</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07031892280011107</v>
+        <v>0.07020698731519273</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0415149379919429</v>
+        <v>0.04127106250070525</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04411926879649862</v>
+        <v>0.04385847585086988</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0491590163893105</v>
+        <v>0.04894671903547199</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03126039984616639</v>
+        <v>0.03101181135166116</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02918201800088314</v>
+        <v>0.02998431420464077</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02918558412075601</v>
+        <v>0.02893694752819925</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02917431068930877</v>
+        <v>0.02889670543259376</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03065103535624862</v>
+        <v>0.02934787307401506</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03065123371429522</v>
+        <v>0.03037369341441023</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02940121854621508</v>
+        <v>0.03019077094796408</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02945931466151237</v>
+        <v>0.03025761791687538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02943098377134927</v>
+        <v>0.03024567574079369</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02949459764453894</v>
+        <v>0.03029111040272426</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02925359127179029</v>
+        <v>0.03005784493440783</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03065998042470068</v>
+        <v>0.029353383906431</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03014808094259434</v>
+        <v>0.02988234370815081</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02958630020791263</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02962492409562069</v>
+        <v>0.03043665496915157</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02943416602718187</v>
+        <v>0.02924097538316257</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02906996773370132</v>
+        <v>0.02986357112903043</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03135389572743677</v>
+        <v>0.0299979115650484</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02958012676560081</v>
+        <v>0.03035246553596247</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03025302817504607</v>
+        <v>0.0289493308471399</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02900266750304932</v>
+        <v>0.02875892445726404</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03054772238278398</v>
+        <v>0.0292224594085502</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03030511044599339</v>
+        <v>0.03005686588156447</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03117412960050266</v>
+        <v>0.03198185030368975</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02951221023443831</v>
+        <v>0.02926497422792293</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03080209911593714</v>
+        <v>0.02948349634966329</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0309677131438917</v>
+        <v>0.03070057136258384</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02886892430828477</v>
+        <v>0.02861318425977528</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0291883505799006</v>
+        <v>0.02897214292401181</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02919191669977346</v>
+        <v>0.0289729982641594</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02918064326832623</v>
+        <v>0.02893275616855391</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02958830440002888</v>
+        <v>0.02938392380997521</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02958850275807548</v>
+        <v>0.02936152213378128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02940755112523254</v>
+        <v>0.02917859966733512</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02946564724052983</v>
+        <v>0.02924544663624643</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02943731635036673</v>
+        <v>0.02923350446016474</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0295009302235564</v>
+        <v>0.02927893912209531</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02925992385080775</v>
+        <v>0.02904567365377888</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02959724946848094</v>
+        <v>0.02938943464239115</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02908534998637461</v>
+        <v>0.02887017242752187</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02959381665824069</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02963232315658384</v>
+        <v>0.02941937926472329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02950612947767038</v>
+        <v>0.02932694191658575</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02907630031271877</v>
+        <v>0.02885139984840147</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03029116477121703</v>
+        <v>0.03003396230100855</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02958645934461827</v>
+        <v>0.02934029425533352</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02919029721882634</v>
+        <v>0.02898538158310004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02900789189418539</v>
+        <v>0.02879368990428082</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02948499142656424</v>
+        <v>0.02925851014451035</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03025102664919408</v>
+        <v>0.03002761268009513</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03118046217952012</v>
+        <v>0.03096967902306079</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0294709854881856</v>
+        <v>0.02925261816113131</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0297393681597174</v>
+        <v>0.02951954708562344</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02990498218767196</v>
+        <v>0.02968840008195489</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02887910774436584</v>
+        <v>0.02866040118447476</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03021084301797316</v>
+        <v>0.0299941268525222</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03158588567854353</v>
+        <v>0.03136528659618967</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0315746122470963</v>
+        <v>0.0313250445005842</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03125200257693469</v>
+        <v>0.03104656546861145</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03082465521238345</v>
+        <v>0.030596983473255</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03208590469904393</v>
+        <v>0.03185502954412803</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0318596162192999</v>
+        <v>0.0316377349682767</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0318312853291368</v>
+        <v>0.03162579279219501</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03189489920232647</v>
+        <v>0.03167122745412557</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03165389282957783</v>
+        <v>0.03143796198580915</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03199121844725102</v>
+        <v>0.03178172297442143</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03147931896514443</v>
+        <v>0.03126246075955195</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0309246618749011</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03125544140330695</v>
+        <v>0.03104147435044305</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03105763331739679</v>
+        <v>0.0308774838008086</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02982926630815947</v>
+        <v>0.0296040876859862</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0326851337499871</v>
+        <v>0.03242625063303882</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03198042832338833</v>
+        <v>0.03173258258736379</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03158426619759641</v>
+        <v>0.03137766991513032</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03073280182159302</v>
+        <v>0.0305175300373317</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03150326827726398</v>
+        <v>0.03127527411171339</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03264526516224471</v>
+        <v>0.03242017031605565</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03205912672498583</v>
+        <v>0.0318479579819743</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03322726881592058</v>
+        <v>0.03300581873074764</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03073638471694027</v>
+        <v>0.03051607690633355</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03229895116644202</v>
+        <v>0.03208068841398517</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03270569865075547</v>
+        <v>0.03248408704883737</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0308908161376642</v>
+        <v>0.03064759585507405</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03167937166145945</v>
+        <v>0.03142560055255252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03166809823001222</v>
+        <v>0.03138535845694702</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03189458751488278</v>
+        <v>0.03165716371890014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03026634204169052</v>
+        <v>0.03002258216309753</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03189500674432504</v>
+        <v>0.03163120263470192</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03195310220221581</v>
+        <v>0.03169804892463953</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03192477131205273</v>
+        <v>0.03168610674855785</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03198838518524239</v>
+        <v>0.03173154141048842</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03174737881249374</v>
+        <v>0.03149827594217199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03208470443016694</v>
+        <v>0.03184203693078427</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03157280494806059</v>
+        <v>0.03132277471591498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03208127161992666</v>
+        <v>0.04302163601102808</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03238004084350903</v>
+        <v>0.03212964470104968</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03231042416883117</v>
+        <v>0.03209321929887395</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03156375593181127</v>
+        <v>0.03130400281576828</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03277861973290302</v>
+        <v>0.03248656458940165</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03207391430630425</v>
+        <v>0.03179289654372663</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03167775218051232</v>
+        <v>0.03143798387149315</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03149645504375276</v>
+        <v>0.0312475774816173</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0328783079717395</v>
+        <v>0.03260792681936662</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03273848161088007</v>
+        <v>0.03248021496848824</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03366791714120609</v>
+        <v>0.03342228131145391</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03195844044987159</v>
+        <v>0.03170522044952441</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0317535445758684</v>
+        <v>0.03150359768797617</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03239243714935795</v>
+        <v>0.032141002370348</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03136656270605184</v>
+        <v>0.03111300347286788</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00732777750365122</v>
+        <v>0.007153626716230685</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008028798722223647</v>
+        <v>0.00778719209126994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007311058885359621</v>
+        <v>0.007136774993058167</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007360860646408189</v>
+        <v>0.007185218111676041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007330313206946005</v>
+        <v>0.007153396259489692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007304033377702066</v>
+        <v>0.007129683053827128</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007306527003450253</v>
+        <v>0.007131765602792297</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007301726149730831</v>
+        <v>0.007127886759743312</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007323369701420997</v>
+        <v>0.007149159112417438</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007296040135238512</v>
+        <v>0.007122034910516256</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007350477465755627</v>
+        <v>0.007175329719245832</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007288628882486101</v>
+        <v>0.00711464733264505</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007317177951451484</v>
+        <v>0.007142943355554853</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0108995105508291</v>
+        <v>0.01071139927736181</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007347437083801075</v>
+        <v>0.007178104552138085</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007289833489674258</v>
+        <v>0.007116057875882567</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007408173118091298</v>
+        <v>0.007225262466048848</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007333097915964723</v>
+        <v>0.007155795179668479</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007297254119345895</v>
+        <v>0.007122648875694506</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009241112977212654</v>
+        <v>0.008879220837713924</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007338218415470961</v>
+        <v>0.007162774432563888</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009020268270277253</v>
+        <v>0.008633052274449248</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00752739655821908</v>
+        <v>0.00735304885930066</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007325075381169224</v>
+        <v>0.007150417262024124</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00900579529252612</v>
+        <v>0.008835026474528437</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007374525630388218</v>
+        <v>0.007199657142551646</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007284356575872967</v>
+        <v>0.007110361871011306</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007268757341952415</v>
+        <v>0.007088515966918024</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008329159860513618</v>
+        <v>0.00803525939553551</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007151754216654387</v>
+        <v>0.006970518351272959</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007503622530582068</v>
+        <v>0.007312774658798628</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007290002875419557</v>
+        <v>0.007089926382850963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0070997980854647</v>
+        <v>0.006918148201757101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007120569347320522</v>
+        <v>0.006935879575940045</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00708562516748198</v>
+        <v>0.006907552381358165</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007238015720822645</v>
+        <v>0.007057313735730762</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007044282775700417</v>
+        <v>0.00686504453028928</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007428565011542395</v>
+        <v>0.007241271294909001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007007994342863789</v>
+        <v>0.006827481178786623</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007195097144095631</v>
+        <v>0.00701422295198501</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01332309801573729</v>
+        <v>0.01332255710610002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007407657230097179</v>
+        <v>0.007261604171071569</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006999759677022858</v>
+        <v>0.006822166755600358</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007848184834696084</v>
+        <v>0.007605149408913715</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007306033754262709</v>
+        <v>0.007103438082160139</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007053400022591272</v>
+        <v>0.006869863719533163</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01022738358651022</v>
+        <v>0.009737118131656803</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007342571371399015</v>
+        <v>0.007153154993014189</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01035949635653897</v>
+        <v>0.009811825429137274</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00869073775419717</v>
+        <v>0.008509069244546851</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007251873883690039</v>
+        <v>0.007067967115136823</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01008984896406455</v>
+        <v>0.009910769149269647</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007604654330935516</v>
+        <v>0.007419252177752428</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00697139267995621</v>
+        <v>0.006791147327954685</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02895777689674778</v>
+        <v>0.02857943028095424</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02875407738431835</v>
+        <v>0.02837122684526442</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02876893241219983</v>
+        <v>0.02838908231554518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02933146621318534</v>
+        <v>0.02893626962526954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02898641883194354</v>
+        <v>0.02857682716604942</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02868957607131455</v>
+        <v>0.02830897559947715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02871774272126483</v>
+        <v>0.0283324989480587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02866351487000215</v>
+        <v>0.02828868563146446</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02890491128333393</v>
+        <v>0.02852585301095414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02859928872061546</v>
+        <v>0.02822258630246115</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02921418341121561</v>
+        <v>0.02882457568388498</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02854534560104173</v>
+        <v>0.0281662722843665</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02883805007861687</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02928830492169513</v>
+        <v>0.02933090144672774</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02917984089839408</v>
+        <v>0.02885591869788925</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0285291818037692</v>
+        <v>0.02815507294670193</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02986588234565834</v>
+        <v>0.02938858902922351</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02901787340133945</v>
+        <v>0.02860392407302664</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02861300122956873</v>
+        <v>0.02822952132158745</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02854245835830069</v>
+        <v>0.02812329052329929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02905594572517308</v>
+        <v>0.02866274492542036</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02956816024758107</v>
+        <v>0.02915739981481668</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03121256594739374</v>
+        <v>0.03083199512564788</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02892621005923378</v>
+        <v>0.02850157313637691</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02906688805100516</v>
+        <v>0.02867930815740098</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02948581849344297</v>
+        <v>0.02909936512129188</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.02848509236448548</v>
+        <v>0.02810658245511215</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04056014159504961</v>
+        <v>0.04005962426562668</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03806327427312799</v>
+        <v>0.03746354571591672</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03842161239729228</v>
+        <v>0.03787143518314378</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04652123220207797</v>
+        <v>0.04574351663561509</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04269814077760149</v>
+        <v>0.04159686245870074</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03607762523838932</v>
+        <v>0.03554532539675222</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03811706678271982</v>
+        <v>0.03744770436670915</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03680543670277332</v>
+        <v>0.03633921318283791</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04004808864863588</v>
+        <v>0.03951807041640236</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03527511042681435</v>
+        <v>0.03478514245113463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04395341747970376</v>
+        <v>0.04328637961921517</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03454449483508518</v>
+        <v>0.03400718497079887</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03420261674182654</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04536921351383907</v>
+        <v>0.05142588984201157</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0437562277576265</v>
+        <v>0.04411474668008079</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03391805593490024</v>
+        <v>0.03347736893824266</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05954426415754944</v>
+        <v>0.05715147908023799</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04126255190891742</v>
+        <v>0.04020557695044676</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03575238512089073</v>
+        <v>0.03513441374181575</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03390807014255256</v>
+        <v>0.03340406719852083</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04226179249355606</v>
+        <v>0.0415309687836291</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05161552319388416</v>
+        <v>0.05055074943137196</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07903503863844731</v>
+        <v>0.07848390213239499</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04126494763047771</v>
+        <v>0.04063999353997319</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04156710608861369</v>
+        <v>0.04093631252284547</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0510671328233166</v>
+        <v>0.05040327496577267</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03368995975346877</v>
+        <v>0.03314958475463874</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0309575864360463</v>
+        <v>0.03027277703282232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03075388692361686</v>
+        <v>0.0300645735971325</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03076874195149834</v>
+        <v>0.03008242906741327</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03133127575248384</v>
+        <v>0.02957804263892505</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03098622837124204</v>
+        <v>0.03027017391791751</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03068938561061307</v>
+        <v>0.03000232235134524</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02956172184630791</v>
+        <v>0.03002584569992678</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02950749399504523</v>
+        <v>0.02998203238333253</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02974889040837701</v>
+        <v>0.02916762602460964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03059909825991397</v>
+        <v>0.02886435931611666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03121399295051411</v>
+        <v>0.03051792243575306</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03054515514034025</v>
+        <v>0.02985961903623458</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02967963455622657</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0312723064845758</v>
+        <v>0.03016698653721913</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03116383289714008</v>
+        <v>0.03054803302787039</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03052899134306771</v>
+        <v>0.02984841969857001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03070986147070141</v>
+        <v>0.03108193578109159</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02986185252638253</v>
+        <v>0.03029727082489472</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03061281076886724</v>
+        <v>0.02887129433524295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0305433130186414</v>
+        <v>0.02985824215805976</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02989992485021616</v>
+        <v>0.02930451793907587</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0315521696147586</v>
+        <v>0.03084584825605519</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03205654507243681</v>
+        <v>0.03147376813930338</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02983072809214463</v>
+        <v>0.02925643734096124</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02991086717604824</v>
+        <v>0.02932108117105648</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03032979761848604</v>
+        <v>0.03079271187315996</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.02932444566530245</v>
+        <v>0.02874388184609808</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02953861860827358</v>
+        <v>0.02923347414258215</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02933491909584415</v>
+        <v>0.02902527070689232</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02934977412372563</v>
+        <v>0.02904312617717309</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02991230792471113</v>
+        <v>0.02959031348689745</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02956726054346932</v>
+        <v>0.02923087102767733</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02927041778284035</v>
+        <v>0.02896301946110506</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02929858443279062</v>
+        <v>0.0289865428096866</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02924435658152795</v>
+        <v>0.02894272949309236</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02948575299485973</v>
+        <v>0.02917989687258205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02918013043214126</v>
+        <v>0.02887663016408906</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0297950251227414</v>
+        <v>0.02947861954551288</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02912618731256753</v>
+        <v>0.0288203161459944</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02941889179014266</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02986902730741991</v>
+        <v>0.02998482902132858</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02976056328411885</v>
+        <v>0.02950984627249009</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.029110023515295</v>
+        <v>0.02880911680832983</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03044672405718413</v>
+        <v>0.03004263289085141</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02959871511286524</v>
+        <v>0.02925796793465454</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02919384294109453</v>
+        <v>0.02888356518321536</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02912323827702001</v>
+        <v>0.02881770663979784</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02963678743669887</v>
+        <v>0.02931678878704827</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03014900195910686</v>
+        <v>0.02981144367644458</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03179340765891953</v>
+        <v>0.03148603898727579</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.02950809689180178</v>
+        <v>0.02919722188089719</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02964772976253096</v>
+        <v>0.02933335201902888</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03006666020496877</v>
+        <v>0.02975340898291979</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02906593407601127</v>
+        <v>0.02876062631674005</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03064394139659286</v>
+        <v>0.03024741093382816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03187693630680943</v>
+        <v>0.03139635043666329</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03189179133469092</v>
+        <v>0.03141420590694406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03168932773547792</v>
+        <v>0.03123875463514264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03089640353181416</v>
+        <v>0.03045623482746308</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03211034294152543</v>
+        <v>0.03161551162013386</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0318406016437559</v>
+        <v>0.03135762253945757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03178637379249322</v>
+        <v>0.03131380922286332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03202777020582501</v>
+        <v>0.03155097660235301</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03172214764310654</v>
+        <v>0.03124770989386002</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03233704233370669</v>
+        <v>0.03184969927528386</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03166820452353253</v>
+        <v>0.03119139587576512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03084723046977641</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03160353384310174</v>
+        <v>0.03159311447368408</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03142004992987533</v>
+        <v>0.03104726577572242</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02993300305864808</v>
+        <v>0.02955634403691382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03298874126814941</v>
+        <v>0.03241371262062238</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03214073232383053</v>
+        <v>0.03162904766442552</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03173586015205981</v>
+        <v>0.03125464491298632</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03096436567290643</v>
+        <v>0.03052675050593231</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03178529023332768</v>
+        <v>0.03131598666775716</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0326913015215483</v>
+        <v>0.03218279012355356</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03274806310077692</v>
+        <v>0.03235765106277741</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03347727736360795</v>
+        <v>0.03291619794636801</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03072636521435735</v>
+        <v>0.03032207918344273</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03260867741593404</v>
+        <v>0.03212448871269075</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03310869874573761</v>
+        <v>0.03254935532812447</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03111652619468772</v>
+        <v>0.03074250193803371</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03166884812094579</v>
+        <v>0.03126191911990209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03168370314882727</v>
+        <v>0.03127977459018286</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0320717507813247</v>
+        <v>0.03165903049450453</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03015835297322957</v>
+        <v>0.02979015454127074</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03160434745251182</v>
+        <v>0.03119966847892094</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03163251345789226</v>
+        <v>0.03122319122269636</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03157828560662958</v>
+        <v>0.03117937790610213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03181968201996137</v>
+        <v>0.03141654528559181</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0315140594572429</v>
+        <v>0.03111327857709881</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03212895414784304</v>
+        <v>0.03171526795852265</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03146011633766917</v>
+        <v>0.03105696455900417</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03175282081524431</v>
+        <v>0.03893826925947794</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03245362103135762</v>
+        <v>0.03246272704652452</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03239964618787401</v>
+        <v>0.03204018652722195</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03144395318496648</v>
+        <v>0.03104576582614572</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03278065308228576</v>
+        <v>0.03227928130386117</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03193264413796687</v>
+        <v>0.03149461634766432</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03152777196619616</v>
+        <v>0.03112021359622512</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03145827421597033</v>
+        <v>0.03105558768082934</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03284314961083651</v>
+        <v>0.0323930964138712</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03248293098420851</v>
+        <v>0.03204809208945435</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03412733668402116</v>
+        <v>0.03372268740028556</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03184202591690341</v>
+        <v>0.03143387029390694</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03152584534410496</v>
+        <v>0.03113131014236269</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03240058923007041</v>
+        <v>0.03199005739592956</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0313998631011129</v>
+        <v>0.03099727472974981</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007646978874099716</v>
+        <v>0.007436782585150763</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008353800746814619</v>
+        <v>0.008186660291859341</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00764266526295447</v>
+        <v>0.007450716361015804</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007557632556277147</v>
+        <v>0.007375308796010304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007568922740321223</v>
+        <v>0.007386184070313713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007868280842122977</v>
+        <v>0.007511430671054484</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007565984540407232</v>
+        <v>0.0073952697343962</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007644600464303371</v>
+        <v>0.007474572299008924</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007734932819344997</v>
+        <v>0.007507826854682736</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007725761605560373</v>
+        <v>0.007556037364221619</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007851494050158375</v>
+        <v>0.007507342179812948</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007901170514725714</v>
+        <v>0.007982925237638145</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007736892182816404</v>
+        <v>0.007557694701079122</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01125348942711531</v>
+        <v>0.01099985749042524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00780512056569068</v>
+        <v>0.007498701056345257</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007592744108356592</v>
+        <v>0.007412674552719531</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007601769144771115</v>
+        <v>0.0074330414146355</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00766983342608386</v>
+        <v>0.007461603157074953</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007637885325412541</v>
+        <v>0.007461530377191147</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01020153659204057</v>
+        <v>0.009905570276084038</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007552413055748856</v>
+        <v>0.007375166254851074</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009586200018475337</v>
+        <v>0.009379211976442524</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007776578157230368</v>
+        <v>0.0075075523892885</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007706597468601489</v>
+        <v>0.007444884530719082</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009316077940578607</v>
+        <v>0.009117578150234923</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007694457264878158</v>
+        <v>0.007514845030960245</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007996203351260389</v>
+        <v>0.007626082251826515</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008169666462349581</v>
+        <v>0.007746641110807272</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008582721722271739</v>
+        <v>0.008446154632696705</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008148157546282245</v>
+        <v>0.007853524881439391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007536466547268289</v>
+        <v>0.007311078537689416</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007620082080554139</v>
+        <v>0.007391415562800083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009740173268289876</v>
+        <v>0.008276204776867203</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007600814338465374</v>
+        <v>0.007458143545246569</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008162103784143499</v>
+        <v>0.008024377781636215</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008797013870014778</v>
+        <v>0.008254261671889864</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00873245399785978</v>
+        <v>0.008596822621228547</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009629243505007523</v>
+        <v>0.008251537585072893</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009985110366901121</v>
+        <v>0.01161976295401053</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008819297804857297</v>
+        <v>0.008616077740295333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01401111571101074</v>
+        <v>0.01359686506534136</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009296064773068052</v>
+        <v>0.008188171601303819</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007788419367895856</v>
+        <v>0.00757903750705114</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007856785207676674</v>
+        <v>0.007728385819262176</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008330164182276459</v>
+        <v>0.007921496717580825</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008113820556781941</v>
+        <v>0.007930819462304978</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01322718327543078</v>
+        <v>0.01234906532596228</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007497715976159736</v>
+        <v>0.007308758394061738</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01125804849437938</v>
+        <v>0.0110092864131142</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009104392865808017</v>
+        <v>0.008258800891604417</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008600080558578929</v>
+        <v>0.007808362814511749</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0107467254112469</v>
+        <v>0.01044002085206441</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008514312415864499</v>
+        <v>0.008308207821644199</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0106661326785317</v>
+        <v>0.009104505580327859</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03065654848777625</v>
+        <v>0.02952738679261081</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02909003872427117</v>
+        <v>0.02840809592821007</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0306078242655316</v>
+        <v>0.02968477520085993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02964734072663354</v>
+        <v>0.02883301206492915</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02977486854915265</v>
+        <v>0.02895585329105951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03315625602053403</v>
+        <v>0.0303705712627095</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02974168022948534</v>
+        <v>0.02905848004648309</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03062968325500402</v>
+        <v>0.02995423899476587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03164534119383655</v>
+        <v>0.03032588810420976</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03154643568147138</v>
+        <v>0.03087442438212484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0329666414829879</v>
+        <v>0.03032438987333727</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03352501125579672</v>
+        <v>0.03565254534821861</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0316721606718968</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03042779232606153</v>
+        <v>0.02946482950770291</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03244283164306856</v>
+        <v>0.03022678440865663</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03004394185948289</v>
+        <v>0.02925507547605714</v>
       </c>
       <c r="R4" t="n">
-        <v>0.03014588379750684</v>
+        <v>0.02948512855061742</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03091470116605061</v>
+        <v>0.0298077465705217</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0305538326721156</v>
+        <v>0.02980692448825369</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03233697523806943</v>
+        <v>0.03051628623890119</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0295577364924954</v>
+        <v>0.02880557728964875</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03041260761546518</v>
+        <v>0.02963411980132682</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03212043200935274</v>
+        <v>0.03032676428606478</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03128313862832592</v>
+        <v>0.0295257853482368</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03028674330111489</v>
+        <v>0.02935869304743221</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03119283875275763</v>
+        <v>0.03040913802852814</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03456112792215185</v>
+        <v>0.03164727854507701</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06326404076673216</v>
+        <v>0.05452956275502496</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03702911866279644</v>
+        <v>0.03597411528091737</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06750249354306999</v>
+        <v>0.06164195117204465</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0466675976114448</v>
+        <v>0.04316835776792455</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05076787524975987</v>
+        <v>0.04700356755369058</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1055582885813775</v>
+        <v>0.06869081138729759</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05108711232250988</v>
+        <v>0.04999133975042461</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06799066452763577</v>
+        <v>0.06706612307023599</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08183026278157454</v>
+        <v>0.07001802726529993</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08037427768902267</v>
+        <v>0.07947321601827029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1069108215157654</v>
+        <v>0.07032729628741513</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1190350530494667</v>
+        <v>0.1698194504865421</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09608538313393876</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05857917894618058</v>
+        <v>0.05284703326991388</v>
       </c>
       <c r="P5" t="n">
-        <v>0.09577821179426155</v>
+        <v>0.06753974031881192</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05492281822903958</v>
+        <v>0.05185928871399674</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05904918858300141</v>
+        <v>0.05842760349638603</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06669007415862184</v>
+        <v>0.05855696086239678</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06635797244166633</v>
+        <v>0.0640151666797233</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09679702701036778</v>
+        <v>0.07580012373396054</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04468867796186981</v>
+        <v>0.04238752363409234</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06189293933786524</v>
+        <v>0.05903268188401278</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09637653967158394</v>
+        <v>0.07357731413833052</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0787294871140186</v>
+        <v>0.05842764603727888</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0571199627567574</v>
+        <v>0.05181594326830367</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07662446074124722</v>
+        <v>0.07366602137416806</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1514432225456998</v>
+        <v>0.1039473557087251</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03277130941300278</v>
+        <v>0.03016848678446213</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02978758273662727</v>
+        <v>0.02904919592006137</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03272258519075813</v>
+        <v>0.03032587519271124</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03176210165186006</v>
+        <v>0.03073490282095396</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03188962947437917</v>
+        <v>0.02959695328291082</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03385380003289012</v>
+        <v>0.03227246201873429</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03185644115471185</v>
+        <v>0.02969958003833439</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03132722726736011</v>
+        <v>0.03059533898661719</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03234288520619266</v>
+        <v>0.03096698809606107</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03224397969382747</v>
+        <v>0.03277631513814964</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03508140240821442</v>
+        <v>0.03222628062936207</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03563977218102323</v>
+        <v>0.03629364534006992</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03237444731855575</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03113007897272049</v>
+        <v>0.03138134397493827</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03455682262258124</v>
+        <v>0.03214526376844634</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03215870278470941</v>
+        <v>0.02989617546790844</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03226064472273336</v>
+        <v>0.03138701930664221</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03302946209127713</v>
+        <v>0.03044884656237301</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0312513766844717</v>
+        <v>0.03044802448010499</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03449856547355233</v>
+        <v>0.03251129364157329</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03167249741772192</v>
+        <v>0.02944667728150007</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03117904784075794</v>
+        <v>0.0303425965249685</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03281797602170885</v>
+        <v>0.03222865504208958</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0320809670510095</v>
+        <v>0.03031163152035439</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03098428731347099</v>
+        <v>0.03126058380345702</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03330759967798416</v>
+        <v>0.03231102878455294</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03528790704284579</v>
+        <v>0.03230294504658657</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03153173648249141</v>
+        <v>0.03034864471466989</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02996522671898633</v>
+        <v>0.02922935385026915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03148301226024676</v>
+        <v>0.03050603312291902</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03052252872134871</v>
+        <v>0.02965426998698823</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0306500565438678</v>
+        <v>0.0297771112131186</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03403144401524919</v>
+        <v>0.03119182918476858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0306168682242005</v>
+        <v>0.02987973796854217</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03150487124971917</v>
+        <v>0.03077549691682496</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03252052918855172</v>
+        <v>0.03114714602626885</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03242162367618653</v>
+        <v>0.03169568230418392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03384182947770307</v>
+        <v>0.03114564779539637</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03440019925051188</v>
+        <v>0.03647380327027771</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03254734866661196</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03130285331622746</v>
+        <v>0.03028596292989769</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03331789263323449</v>
+        <v>0.03104791783085142</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03091912985419805</v>
+        <v>0.03007633339811621</v>
       </c>
       <c r="R7" t="n">
-        <v>0.031021071792222</v>
+        <v>0.0303063864726765</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03178988916076576</v>
+        <v>0.03062900449258078</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03142902066683076</v>
+        <v>0.03062818241031277</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03325739552410915</v>
+        <v>0.03142929469970302</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03043292448721056</v>
+        <v>0.02962683521170784</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03128779561018034</v>
+        <v>0.03045537772338591</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0329956200040679</v>
+        <v>0.03114802220812387</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03220515593329747</v>
+        <v>0.03044015991694317</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03116193129583006</v>
+        <v>0.03017995096949129</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03206802674747279</v>
+        <v>0.03123039595058723</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03543631591686701</v>
+        <v>0.03246853646713609</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03277665051396288</v>
+        <v>0.03155172231363985</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03292803350141279</v>
+        <v>0.03206524598035036</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03444581904267321</v>
+        <v>0.03334192525300022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03257060828860579</v>
+        <v>0.03162073654430955</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03216259818847104</v>
+        <v>0.03123456223290254</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03735046705059915</v>
+        <v>0.03436629604465901</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03357967500662695</v>
+        <v>0.03271563009862337</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03446767803214563</v>
+        <v>0.03361138904690619</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03548333597097817</v>
+        <v>0.03398303815635005</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03538443045861299</v>
+        <v>0.03453157443426514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03680463626012952</v>
+        <v>0.03398153992547755</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0373630060329382</v>
+        <v>0.03930969540035931</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03417850116978754</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03330008298232637</v>
+        <v>0.03220410170022824</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03522541907293355</v>
+        <v>0.03288079590520546</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03182643875118239</v>
+        <v>0.03095852567460409</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03398387857464845</v>
+        <v>0.0331422786027577</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03475269594319221</v>
+        <v>0.03346489662266199</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03439182744925721</v>
+        <v>0.03346407454039398</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03538217957697761</v>
+        <v>0.0334686357421074</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03292494874606933</v>
+        <v>0.03201539321463578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03425094000751046</v>
+        <v>0.03329159074809728</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03406037718503257</v>
+        <v>0.03217986518071191</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03687407549354089</v>
+        <v>0.03489787629879275</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03237493458750405</v>
+        <v>0.03135269820027321</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03503083352989925</v>
+        <v>0.03406628808066843</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.04019360532529631</v>
+        <v>0.03701003990850164</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0343588254383374</v>
+        <v>0.03269738851085148</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03397759287126223</v>
+        <v>0.03260562653516257</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03549537841252267</v>
+        <v>0.03388230580781243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03426133791750485</v>
+        <v>0.03279339261665704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03193003494963897</v>
+        <v>0.03078465035267451</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03804381040953976</v>
+        <v>0.0345681011170348</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03462923437647641</v>
+        <v>0.03325601065343557</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03551723740199508</v>
+        <v>0.03415176960171838</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03653289534082764</v>
+        <v>0.03452341871116223</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03643398982846244</v>
+        <v>0.03507195498907734</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03785419562997897</v>
+        <v>0.03452192048028976</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03841256540278779</v>
+        <v>0.03985007595517111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03655971481888788</v>
+        <v>0.08395751248540119</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03570814610617961</v>
+        <v>0.03400288084089353</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03780861255145085</v>
+        <v>0.03483889332113568</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03493149624848861</v>
+        <v>0.03345260533038245</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0350334379444979</v>
+        <v>0.03368265915756991</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03580225531304168</v>
+        <v>0.03400527717747418</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03544138681910668</v>
+        <v>0.03400445509520618</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03727135869531687</v>
+        <v>0.03480693349250098</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03581307399635688</v>
+        <v>0.03418885130533075</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03530016176245625</v>
+        <v>0.03383165040827932</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0370079861563438</v>
+        <v>0.03452429489301728</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0362175220855734</v>
+        <v>0.03381643260183657</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03445968079372075</v>
+        <v>0.03293671480706542</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03608039289974872</v>
+        <v>0.03460666863548063</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03944868206914292</v>
+        <v>0.03584480915202951</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007325526189382612</v>
+        <v>0.007212834344806457</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008209013152153452</v>
+        <v>0.008093826638324768</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007355540781406789</v>
+        <v>0.007239048529640763</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007356533126073559</v>
+        <v>0.007243383570073146</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007363776311930523</v>
+        <v>0.007250384649296576</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007636644473487572</v>
+        <v>0.007384505854404312</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00735540820840232</v>
+        <v>0.007242563393966238</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007358389551097768</v>
+        <v>0.007246065901510271</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007459635860187087</v>
+        <v>0.007304702801045062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007389508488955599</v>
+        <v>0.0072789790978332</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007519563793931654</v>
+        <v>0.007356258627681407</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00736463970092748</v>
+        <v>0.007276492081320297</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007385408096828882</v>
+        <v>0.007274554542361873</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01087266205278982</v>
+        <v>0.01072918774784667</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007500558789053848</v>
+        <v>0.007329608202586578</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007372895135385088</v>
+        <v>0.007257177179703395</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007438348539486446</v>
+        <v>0.007322857128408715</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0074055631434988</v>
+        <v>0.007288632745258864</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007365352374848415</v>
+        <v>0.007255109311216183</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009760245869944801</v>
+        <v>0.009631477087498352</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00735798864796867</v>
+        <v>0.00724420383881848</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009400236682944169</v>
+        <v>0.009280314017044633</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007529467091106918</v>
+        <v>0.007398371915164302</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007602219656454245</v>
+        <v>0.007415140760949734</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009011286643109857</v>
+        <v>0.008903236074109913</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007387506747871755</v>
+        <v>0.007274576689497279</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007635197515347558</v>
+        <v>0.007404356868419605</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006955029492133262</v>
+        <v>0.006864970895388004</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00852139150419709</v>
+        <v>0.008425142644840468</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007170431261489201</v>
+        <v>0.007053212364020294</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007175861713991863</v>
+        <v>0.007082550224337574</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007229354256995967</v>
+        <v>0.00713428251005212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00915918678650823</v>
+        <v>0.00808122178046858</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007171033447772431</v>
+        <v>0.007079865716408475</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007191457922477274</v>
+        <v>0.007104027190110688</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007907105809743607</v>
+        <v>0.00751771997945898</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007410244029308725</v>
+        <v>0.007335517295260242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008332769440449011</v>
+        <v>0.007883417760953202</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007250619570230696</v>
+        <v>0.007331095074390808</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007383739539611448</v>
+        <v>0.007306815734464601</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01303642355015504</v>
+        <v>0.01287605586252786</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008198386919754056</v>
+        <v>0.007694457356875521</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007292208652368224</v>
+        <v>0.007180624478865089</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007764912269639669</v>
+        <v>0.00765478039649295</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007522415287599823</v>
+        <v>0.007402298936621783</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007240919607386841</v>
+        <v>0.007168365841501068</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01121514188223752</v>
+        <v>0.01102553988659921</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007185317174114705</v>
+        <v>0.007087496845684157</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01103648388014385</v>
+        <v>0.01090930906536855</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008411401219219319</v>
+        <v>0.00818998481931589</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008929656809919109</v>
+        <v>0.00830889691462636</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009925256864635499</v>
+        <v>0.009829558141087475</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007398100251742224</v>
+        <v>0.007306338850471424</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009161964006713451</v>
+        <v>0.008232521085125651</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02859999729166273</v>
+        <v>0.02815624731951337</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02882040622653632</v>
+        <v>0.02837286301391759</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02893902591597025</v>
+        <v>0.0284523485963377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02895023490548262</v>
+        <v>0.0285013148722386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0290320500217671</v>
+        <v>0.02858039528272276</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03211422143210995</v>
+        <v>0.03009535599321726</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02893752844289824</v>
+        <v>0.02849205060581146</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02897120408012876</v>
+        <v>0.02853161303975437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0301106125929918</v>
+        <v>0.02919026073113453</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0293227067986516</v>
+        <v>0.02890338273304011</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0307917412967522</v>
+        <v>0.02977629057301581</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02907130244116153</v>
+        <v>0.02889706503998537</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02927639098330675</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02906986373981587</v>
+        <v>0.02858565038558932</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03057707102392332</v>
+        <v>0.02947526176176844</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02913505132755238</v>
+        <v>0.02865712003838613</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02987437763693077</v>
+        <v>0.02939900527328196</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02950405150722306</v>
+        <v>0.0290124251216103</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02904985237744944</v>
+        <v>0.02863376251255659</v>
       </c>
       <c r="U4" t="n">
-        <v>0.02905889451966457</v>
+        <v>0.02843706701722186</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02893917687798001</v>
+        <v>0.0284866901064675</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02995054358919822</v>
+        <v>0.02945497192608794</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03090360359408857</v>
+        <v>0.03025197952820444</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03168574886314058</v>
+        <v>0.03037492059276553</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02898982312860094</v>
+        <v>0.02851845746525141</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.02930009621226322</v>
+        <v>0.02885365550567805</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03207315603297698</v>
+        <v>0.03030809888091201</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03290926605778365</v>
+        <v>0.03244141156753563</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03715100713175316</v>
+        <v>0.03660930360377415</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03952022845025098</v>
+        <v>0.03827416329099733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03886239104434772</v>
+        <v>0.03831025546263486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04124096864269359</v>
+        <v>0.04062371098096143</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08661218061327799</v>
+        <v>0.06208552245025373</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04029614485988314</v>
+        <v>0.03978872291072096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04044944063667563</v>
+        <v>0.04005516361196822</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05706936344131372</v>
+        <v>0.04927754080039609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04495034679038511</v>
+        <v>0.04486181405909188</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06798613241367836</v>
+        <v>0.05841046140331482</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04145600903018169</v>
+        <v>0.04552602595708105</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04127772053137622</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04017078157344611</v>
+        <v>0.03906843999066954</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06484081877303526</v>
+        <v>0.05373146421661853</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04190857737352379</v>
+        <v>0.04087344530208754</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05786580619212583</v>
+        <v>0.05679065400422898</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04690797059052695</v>
+        <v>0.04569336763704205</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04172006366400403</v>
+        <v>0.04175580930868841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.04109985249211374</v>
+        <v>0.0381907476775013</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03864234097502953</v>
+        <v>0.03797985681694827</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05720282259683411</v>
+        <v>0.05581329289604473</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07408524096757735</v>
+        <v>0.06993441089206115</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08811020065840171</v>
+        <v>0.07288647867488052</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03888523776516621</v>
+        <v>0.03798696173372321</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04566086632780743</v>
+        <v>0.04514404288155334</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09963739470589737</v>
+        <v>0.07406769734626495</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02922260339774392</v>
+        <v>0.02990329677101202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03067671852600747</v>
+        <v>0.03011991246541624</v>
       </c>
       <c r="D6" t="n">
-        <v>0.02956163202205143</v>
+        <v>0.03019939804783635</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03080654720495378</v>
+        <v>0.02911680176122886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03088836232123825</v>
+        <v>0.02919588217171301</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03273682753819114</v>
+        <v>0.03071084288220751</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03079384074236939</v>
+        <v>0.02910753749480171</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03082751637959991</v>
+        <v>0.03027866249125302</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03073321869907299</v>
+        <v>0.03093731018263318</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03117901909812275</v>
+        <v>0.02951886962203035</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03141434740283339</v>
+        <v>0.03152334002451446</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03092761474063268</v>
+        <v>0.02951255192897562</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02990019254069829</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02969366529720747</v>
+        <v>0.03033767172814066</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03113555598427608</v>
+        <v>0.03004221942680285</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03099136362702353</v>
+        <v>0.02927260692737638</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03173068993640191</v>
+        <v>0.03114605472478061</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03012665761330424</v>
+        <v>0.02962791201060055</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02967245848353064</v>
+        <v>0.02924924940154685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02972112905012545</v>
+        <v>0.03025058723135611</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03079548917745116</v>
+        <v>0.02910217699545775</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0306360844590926</v>
+        <v>0.03013783239180876</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03152620970016975</v>
+        <v>0.0319990289797031</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03239364867730705</v>
+        <v>0.03110512662010037</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02961242923468213</v>
+        <v>0.03026550691675006</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03115640851173437</v>
+        <v>0.0294691423946683</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03271307630328636</v>
+        <v>0.03092636964126094</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02931986601306162</v>
+        <v>0.02885171578825826</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02954027494793521</v>
+        <v>0.02906833148266249</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02965889463736912</v>
+        <v>0.0291478170650826</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02967010362688151</v>
+        <v>0.0291967833409835</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02975191874316598</v>
+        <v>0.02927586375146765</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03283409015350883</v>
+        <v>0.03079082446196215</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02965739716429712</v>
+        <v>0.02918751907455636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02969107280152764</v>
+        <v>0.02922708150849927</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03083048131439068</v>
+        <v>0.02988572919987943</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03004257552005048</v>
+        <v>0.02959885120178499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03151161001815108</v>
+        <v>0.0304717590417607</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02979117116256042</v>
+        <v>0.02959253350873027</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02999625970470563</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O7" t="n">
-        <v>0.02978961487439406</v>
+        <v>0.02928100263117132</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03129682215850151</v>
+        <v>0.03017061400735045</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02985492004895126</v>
+        <v>0.02935258850713103</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03059424635832965</v>
+        <v>0.03009447374202685</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03022392022862194</v>
+        <v>0.02970789359035519</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02976972109884834</v>
+        <v>0.0293292309813015</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02981668603899396</v>
+        <v>0.02919743943242354</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0296590455993789</v>
+        <v>0.0291821585752124</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03067041231059709</v>
+        <v>0.03015044039483283</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03162347231548745</v>
+        <v>0.03094744799694934</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03244524600891916</v>
+        <v>0.03113685982414604</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02970969184999982</v>
+        <v>0.02921392593399631</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0300199649336621</v>
+        <v>0.02954912397442294</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03279302475437586</v>
+        <v>0.03100356734965691</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03041040517695098</v>
+        <v>0.02991221707570938</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03211085420832178</v>
+        <v>0.03155575206635013</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0322294738977557</v>
+        <v>0.03163523764877024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0314526051943766</v>
+        <v>0.03092441149094667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03107303085646976</v>
+        <v>0.03055866238849206</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03571156536945347</v>
+        <v>0.0335741260572273</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0322279764246837</v>
+        <v>0.031674939658244</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03226165206191422</v>
+        <v>0.03171450209218692</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03340106057477726</v>
+        <v>0.03237314978356707</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03261315478043705</v>
+        <v>0.03208627178547264</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03408218927853766</v>
+        <v>0.03295917962544834</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03236175042294685</v>
+        <v>0.0320799540924179</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0314195602849374</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03152831518429994</v>
+        <v>0.03096640447136682</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03295823919692059</v>
+        <v>0.03178150638552027</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03065459755366764</v>
+        <v>0.03013266758507461</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03316482561871623</v>
+        <v>0.03258189432571451</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03279449948900851</v>
+        <v>0.03219531417404284</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03234030035923492</v>
+        <v>0.03181665156498914</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03166535241674918</v>
+        <v>0.03098884239459103</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03182375016800683</v>
+        <v>0.0312783406687977</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03324128244105994</v>
+        <v>0.03263814140886935</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03255879843580357</v>
+        <v>0.03185830706361602</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03648529009382298</v>
+        <v>0.03504111065064966</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0307727385092596</v>
+        <v>0.03024792146295196</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03259054419404869</v>
+        <v>0.03203654455811059</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03690962965429978</v>
+        <v>0.03498152445515157</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03147933610438697</v>
+        <v>0.03073246669329399</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03263955524773837</v>
+        <v>0.0317969977142692</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03275817493717229</v>
+        <v>0.03187648329668931</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03255248016631668</v>
+        <v>0.03172975461145215</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0306846789917798</v>
+        <v>0.03004985299462376</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03593337123637166</v>
+        <v>0.03351949126253483</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03275667746410028</v>
+        <v>0.03191618530616307</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0327903531013308</v>
+        <v>0.03195574774010599</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03392976161419384</v>
+        <v>0.03261439543148614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03314185581985364</v>
+        <v>0.03232751743339171</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03461089031795423</v>
+        <v>0.03320042527336742</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03289045146236358</v>
+        <v>0.03232119974033698</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03309554000450878</v>
+        <v>0.04546866469835966</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03320046567609576</v>
+        <v>0.03229078387243684</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03477540845529839</v>
+        <v>0.03324150753981114</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03295420113181409</v>
+        <v>0.03208125530770369</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03369352665813281</v>
+        <v>0.03282313997363357</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03332320052842509</v>
+        <v>0.03243655982196191</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03286900139865149</v>
+        <v>0.03205789721290821</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03291767196524632</v>
+        <v>0.03192767248020906</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0338428473642117</v>
+        <v>0.03288930127803495</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03376969261040026</v>
+        <v>0.03287910662643955</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03472275261529061</v>
+        <v>0.03367611422855606</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03554452630872232</v>
+        <v>0.03386552605575275</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03224235047621964</v>
+        <v>0.03143137484918351</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03311924523346525</v>
+        <v>0.03227779020602966</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03589230505417901</v>
+        <v>0.03373223358126363</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -798,7 +798,7 @@
         <v>0.0367374107700861</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.03163646939648202</v>
       </c>
       <c r="O4" t="n">
         <v>0.0309005763312085</v>
@@ -974,7 +974,7 @@
         <v>0.03896062794024636</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.03241491090986934</v>
       </c>
       <c r="O6" t="n">
         <v>0.03167901511466375</v>
@@ -1062,7 +1062,7 @@
         <v>0.03770479706288943</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.03260385568928534</v>
       </c>
       <c r="O7" t="n">
         <v>0.03186782567874123</v>
@@ -1150,7 +1150,7 @@
         <v>0.04094380624257026</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.03438986369007546</v>
       </c>
       <c r="O8" t="n">
         <v>0.03405326796484282</v>
@@ -1238,7 +1238,7 @@
         <v>0.04207735451427001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.03697641314066592</v>
       </c>
       <c r="O9" t="n">
         <v>0.03666827575861643</v>
@@ -1658,7 +1658,7 @@
         <v>0.02836776790765971</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.02852851687009272</v>
       </c>
       <c r="O4" t="n">
         <v>0.028883002966595</v>
@@ -1834,7 +1834,7 @@
         <v>0.02899786889626567</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.02916739175003191</v>
       </c>
       <c r="O6" t="n">
         <v>0.0305978565799218</v>
@@ -1922,7 +1922,7 @@
         <v>0.02902586705786907</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.02918661602030208</v>
       </c>
       <c r="O7" t="n">
         <v>0.02954098588503205</v>
@@ -2010,7 +2010,7 @@
         <v>0.03140986990739528</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.03051272910049671</v>
       </c>
       <c r="O8" t="n">
         <v>0.03115793249104403</v>
@@ -2098,7 +2098,7 @@
         <v>0.03124798986532267</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.03140873882775568</v>
       </c>
       <c r="O9" t="n">
         <v>0.03200378841780435</v>
@@ -2518,7 +2518,7 @@
         <v>0.03583645196724628</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.03043803453402477</v>
       </c>
       <c r="O4" t="n">
         <v>0.03009214811745576</v>
@@ -2694,7 +2694,7 @@
         <v>0.03777830463329263</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.03110653559148245</v>
       </c>
       <c r="O6" t="n">
         <v>0.03075779937348064</v>
@@ -2782,7 +2782,7 @@
         <v>0.0366848694520361</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.0312864520188146</v>
       </c>
       <c r="O7" t="n">
         <v>0.03094044054054025</v>
@@ -2870,7 +2870,7 @@
         <v>0.0395774255519661</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.03288585463579331</v>
       </c>
       <c r="O8" t="n">
         <v>0.03289533802449576</v>
@@ -2958,7 +2958,7 @@
         <v>0.04012160460698933</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.03472318717376777</v>
       </c>
       <c r="O9" t="n">
         <v>0.03472463762764579</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007481092212630256</v>
+        <v>0.007481092212630273</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008224086087521504</v>
+        <v>0.008224086087521513</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007543235702440631</v>
+        <v>0.007543235702440632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007411277708572469</v>
+        <v>0.007411277708572486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007418878629181418</v>
+        <v>0.007418878629181433</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007525318604194777</v>
+        <v>0.007525318604194794</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007385020659844198</v>
+        <v>0.00738502065984421</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007536066997825747</v>
+        <v>0.007536066997825767</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007535671433113979</v>
+        <v>0.007535671433113997</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007575583103447042</v>
+        <v>0.007575583103447054</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007500573148253161</v>
+        <v>0.007500573148253174</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007923708481175986</v>
+        <v>0.007923708481175993</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007462459950291301</v>
+        <v>0.007462459950291304</v>
       </c>
       <c r="O2" t="n">
         <v>0.01103558447693143</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007537485802788431</v>
+        <v>0.007537485802788436</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007419293732054192</v>
+        <v>0.007419293732054208</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007385109738930029</v>
+        <v>0.007385109738930047</v>
       </c>
       <c r="S2" t="n">
-        <v>0.00751522369731546</v>
+        <v>0.007515223697315483</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007488999687191106</v>
+        <v>0.007488999687191114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009946127144837889</v>
+        <v>0.009946127144837896</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00742463233218986</v>
+        <v>0.007424632332189878</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009502292836053446</v>
+        <v>0.009502292836053449</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00753359881186381</v>
+        <v>0.007533598811863835</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007580219287009815</v>
+        <v>0.007580219287009826</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009126443204132006</v>
+        <v>0.009126443204132029</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007562379358743845</v>
+        <v>0.00756237935874386</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00766702231543299</v>
+        <v>0.007667022315432993</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00794164391313649</v>
+        <v>0.007941643913136485</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008565287920587089</v>
+        <v>0.008565287920587092</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008392955524302881</v>
+        <v>0.008392955524302878</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007446203676463131</v>
+        <v>0.007446203676463129</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007503247577263921</v>
+        <v>0.007503247577263916</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008255753460605147</v>
+        <v>0.008255753460605149</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007262408134722215</v>
+        <v>0.007262408134722213</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008343167871000897</v>
+        <v>0.008343167871000893</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008334254627385478</v>
+        <v>0.008334254627385474</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008613857962036077</v>
+        <v>0.00861385796203607</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008083903208969009</v>
+        <v>0.008083903208968993</v>
       </c>
       <c r="M3" t="n">
         <v>0.01110151588006763</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007813886118031681</v>
+        <v>0.007813886118031674</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01369290260572012</v>
+        <v>0.01369290260572013</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008342080219746731</v>
+        <v>0.008342080219746735</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007504750908412333</v>
+        <v>0.007504750908412329</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007262479220377227</v>
+        <v>0.007262479220377229</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008184661330949392</v>
+        <v>0.008184661330949389</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008005593340023513</v>
+        <v>0.008005593340023509</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01226616358183895</v>
+        <v>0.01226616358183896</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007538639168532593</v>
+        <v>0.007538639168532587</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01148199462098838</v>
+        <v>0.01148199462098837</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00832282400881113</v>
+        <v>0.008322824008811132</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008652737612451817</v>
+        <v>0.008652737612451823</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01040394428701783</v>
+        <v>0.01040394428701784</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008526202469607582</v>
+        <v>0.008526202469607579</v>
       </c>
       <c r="AB3" t="n">
         <v>0.009275338085448634</v>
@@ -3351,16 +3351,16 @@
         <v>0.0304975588236481</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02900703257923105</v>
+        <v>0.02900703257923104</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02909288847410532</v>
+        <v>0.02909288847410531</v>
       </c>
       <c r="G4" t="n">
         <v>0.03029517695668897</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02871044713500601</v>
+        <v>0.028710447135006</v>
       </c>
       <c r="I4" t="n">
         <v>0.03041658500725607</v>
@@ -3372,28 +3372,28 @@
         <v>0.03086293759855515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03001566564835623</v>
+        <v>0.03001566564835621</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03476194221082976</v>
+        <v>0.03476194221082977</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.02958515954443966</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02956035371592474</v>
+        <v>0.02956035371592473</v>
       </c>
       <c r="P4" t="n">
         <v>0.03043261106199193</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02909757725201012</v>
+        <v>0.02909757725201011</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02871145332425889</v>
+        <v>0.02871145332425888</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03018115033960048</v>
+        <v>0.03018115033960047</v>
       </c>
       <c r="T4" t="n">
         <v>0.02988493808160509</v>
@@ -3408,19 +3408,19 @@
         <v>0.03020694201044729</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03038870571139439</v>
+        <v>0.03038870571139438</v>
       </c>
       <c r="Y4" t="n">
         <v>0.03085098916890276</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02927472419772466</v>
+        <v>0.02927472419772465</v>
       </c>
       <c r="AA4" t="n">
         <v>0.03071379522810998</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03187450711361332</v>
+        <v>0.03187450711361331</v>
       </c>
     </row>
     <row r="5">
@@ -3430,52 +3430,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05793178179688308</v>
+        <v>0.05793178179688299</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03789331280184381</v>
+        <v>0.0378933128018438</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07438392791408427</v>
+        <v>0.07438392791408423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04545056424681013</v>
+        <v>0.04545056424681011</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04841789483858337</v>
+        <v>0.04841789483858335</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06597107182235198</v>
+        <v>0.06597107182235204</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04207177445458506</v>
+        <v>0.0420717744545851</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07366471938871047</v>
+        <v>0.07366471938871044</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07042604551935754</v>
+        <v>0.07042604551935745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07568340181995019</v>
+        <v>0.07568340181995015</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06349384034694644</v>
+        <v>0.06349384034694619</v>
       </c>
       <c r="M5" t="n">
-        <v>0.155591320553717</v>
+        <v>0.1555913205537166</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.05691540669209519</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05283297005590821</v>
+        <v>0.05283297005590827</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06813693343818995</v>
+        <v>0.06813693343819001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04774458935360805</v>
+        <v>0.04774458935360801</v>
       </c>
       <c r="R5" t="n">
         <v>0.0417969414189364</v>
@@ -3484,31 +3484,31 @@
         <v>0.06444960269866837</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06340515039199905</v>
+        <v>0.06340515039199907</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06771338250896221</v>
+        <v>0.06771338250896265</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04660410178555912</v>
+        <v>0.04660410178555918</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06738522713613626</v>
+        <v>0.06738522713613616</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07175775775447757</v>
+        <v>0.07175775775447781</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07961064053515415</v>
+        <v>0.07961064053515413</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04838394391763711</v>
+        <v>0.04838394391763699</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07645564246728148</v>
+        <v>0.07645564246728143</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1041645559971452</v>
+        <v>0.1041645559971451</v>
       </c>
     </row>
     <row r="6">
@@ -3518,52 +3518,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03164390661184542</v>
+        <v>0.03164390661184541</v>
       </c>
       <c r="C6" t="n">
         <v>0.02920855876578983</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03234584591667116</v>
+        <v>0.03234584591667115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03085531967225411</v>
+        <v>0.0308553196722541</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02975643415469862</v>
+        <v>0.02975643415469861</v>
       </c>
       <c r="G6" t="n">
         <v>0.03095872263728227</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02937399281559931</v>
+        <v>0.0293739928155993</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03108013068784938</v>
+        <v>0.03108013068784937</v>
       </c>
       <c r="J6" t="n">
         <v>0.03225678460242314</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03271122469157821</v>
+        <v>0.03271122469157819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03186395274137929</v>
+        <v>0.03186395274137927</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03542548789142303</v>
+        <v>0.03542548789142302</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.03025652522111839</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03140738840010798</v>
+        <v>0.03140738840010796</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03228116071993831</v>
+        <v>0.03228116071993829</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03094586434503318</v>
+        <v>0.03094586434503317</v>
       </c>
       <c r="R6" t="n">
         <v>0.02937499900485219</v>
@@ -3572,31 +3572,31 @@
         <v>0.03202943743262354</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0305484837621984</v>
+        <v>0.03054848376219839</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03098270711013342</v>
+        <v>0.03098270711013343</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03098272832854128</v>
+        <v>0.03098272832854127</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03205375960083968</v>
+        <v>0.03205375960083967</v>
       </c>
       <c r="X6" t="n">
         <v>0.03105225139198768</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03163255448248716</v>
+        <v>0.03163255448248718</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03112301129074772</v>
+        <v>0.03112301129074771</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03256208232113304</v>
+        <v>0.03256208232113303</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03254666347487276</v>
+        <v>0.03254666347487275</v>
       </c>
     </row>
     <row r="7">
@@ -3606,70 +3606,70 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03056538093685765</v>
+        <v>0.03056538093685764</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02931477450323181</v>
+        <v>0.0293147745032318</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03126732024168337</v>
+        <v>0.03126732024168336</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02977679399726633</v>
+        <v>0.02977679399726632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0298626498921406</v>
+        <v>0.02986264989214059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03106493837472426</v>
+        <v>0.03106493837472424</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02948020855304129</v>
+        <v>0.02948020855304128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03118634642529135</v>
+        <v>0.03118634642529134</v>
       </c>
       <c r="J7" t="n">
         <v>0.03117825892743536</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03163269901659042</v>
+        <v>0.03163269901659041</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03078542706639151</v>
+        <v>0.0307854270663915</v>
       </c>
       <c r="M7" t="n">
         <v>0.03553170362886503</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.03035492096247493</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03032999800630683</v>
+        <v>0.03032999800630682</v>
       </c>
       <c r="P7" t="n">
         <v>0.03120225535237403</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02986733867004539</v>
+        <v>0.02986733867004538</v>
       </c>
       <c r="R7" t="n">
         <v>0.02948121474229417</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03095091175763576</v>
+        <v>0.03095091175763575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03065469949964036</v>
+        <v>0.03065469949964035</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03108752753200402</v>
+        <v>0.03108752753200405</v>
       </c>
       <c r="V7" t="n">
         <v>0.02990420265355349</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03097670342848256</v>
+        <v>0.03097670342848255</v>
       </c>
       <c r="X7" t="n">
         <v>0.03115846712942966</v>
@@ -3678,13 +3678,13 @@
         <v>0.03168506684268185</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03004448561575994</v>
+        <v>0.03004448561575992</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03148355664614526</v>
+        <v>0.03148355664614525</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03264426853164859</v>
+        <v>0.03264426853164858</v>
       </c>
     </row>
     <row r="8">
@@ -3697,7 +3697,7 @@
         <v>0.03168754043985508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03196084526942956</v>
+        <v>0.03196084526942957</v>
       </c>
       <c r="D8" t="n">
         <v>0.03391339100788113</v>
@@ -3706,10 +3706,10 @@
         <v>0.0316114269684195</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0312222169595927</v>
+        <v>0.03122221695959269</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03402700206869191</v>
+        <v>0.0340270020686919</v>
       </c>
       <c r="H8" t="n">
         <v>0.03212627931923903</v>
@@ -3721,16 +3721,16 @@
         <v>0.03382432969363312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03427876978278818</v>
+        <v>0.03427876978278819</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03343149783258927</v>
+        <v>0.03343149783258928</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0381777743950634</v>
+        <v>0.03817777439506338</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.03181970555483961</v>
       </c>
       <c r="O8" t="n">
         <v>0.03211952742372912</v>
@@ -3739,10 +3739,10 @@
         <v>0.0329122106770685</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03069001482829871</v>
+        <v>0.0306900148282987</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03212728550849192</v>
+        <v>0.03212728550849191</v>
       </c>
       <c r="S8" t="n">
         <v>0.03359698252383352</v>
@@ -3751,10 +3751,10 @@
         <v>0.03330077026583812</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03299020230124296</v>
+        <v>0.03299020230124294</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0321326729302132</v>
+        <v>0.03213267293021321</v>
       </c>
       <c r="W8" t="n">
         <v>0.03362307368670959</v>
@@ -3763,7 +3763,7 @@
         <v>0.03212081278289178</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03584463332411716</v>
+        <v>0.03584463332411715</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03113833768468146</v>
@@ -3782,55 +3782,55 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03256832043924216</v>
+        <v>0.03256832043924215</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03222458651359311</v>
+        <v>0.0322245865135931</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03417713225204468</v>
+        <v>0.03417713225204467</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03247730312462758</v>
+        <v>0.03247730312462757</v>
       </c>
       <c r="F9" t="n">
         <v>0.03068187395365026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03397474985567524</v>
+        <v>0.03397474985567523</v>
       </c>
       <c r="H9" t="n">
         <v>0.03239002056340259</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03409615843565265</v>
+        <v>0.03409615843565264</v>
       </c>
       <c r="J9" t="n">
         <v>0.03408807093779666</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03454251102695172</v>
+        <v>0.03454251102695171</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03369523907675281</v>
+        <v>0.03369523907675278</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03844151563922634</v>
+        <v>0.03844151563922632</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.03326473297283624</v>
       </c>
       <c r="O9" t="n">
         <v>0.03354046280116058</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03447808161140435</v>
+        <v>0.03447808161140434</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03277715015099637</v>
+        <v>0.03277715015099638</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03239102675265548</v>
+        <v>0.03239102675265547</v>
       </c>
       <c r="S9" t="n">
         <v>0.03386072376799706</v>
@@ -3839,28 +3839,28 @@
         <v>0.03356451151000166</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0339987348579367</v>
+        <v>0.03399873485793672</v>
       </c>
       <c r="V9" t="n">
         <v>0.03386052382566147</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03388651543884387</v>
+        <v>0.03388651543884386</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03406827913979097</v>
+        <v>0.03406827913979096</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03459487885304316</v>
+        <v>0.03459487885304315</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03240753393583813</v>
+        <v>0.03240753393583812</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03439336865650656</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0355540805420099</v>
+        <v>0.03555408054200989</v>
       </c>
     </row>
   </sheetData>
@@ -4032,76 +4032,76 @@
         <v>0.007992881077880048</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007454710015921661</v>
+        <v>0.007454710015921665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007367446389494956</v>
+        <v>0.007367446389494959</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007416890822354559</v>
+        <v>0.007416890822354561</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007490515446361968</v>
+        <v>0.00749051544636197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007367668761145762</v>
+        <v>0.007367668761145768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007506074024950227</v>
+        <v>0.00750607402495023</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007505257487954521</v>
+        <v>0.00750525748795452</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007602955034147556</v>
+        <v>0.007602955034147561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007464613552584954</v>
+        <v>0.007464613552584958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00780619353238025</v>
+        <v>0.007806193532380243</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007399661908215388</v>
+        <v>0.00739966190821539</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01099748239706914</v>
+        <v>0.01099748239706915</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007497950387116007</v>
+        <v>0.00749795038711601</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007398352201380029</v>
+        <v>0.007398352201380033</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007401590444100451</v>
+        <v>0.007401590444100448</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007487153535406462</v>
+        <v>0.007487153535406467</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007486112368008678</v>
+        <v>0.00748611236800868</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009307240109582199</v>
+        <v>0.009307240109582192</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007450887950810063</v>
+        <v>0.007450887950810065</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008894756892727508</v>
+        <v>0.00889475689272751</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007536035361137734</v>
+        <v>0.007536035361137736</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007687650871134873</v>
+        <v>0.007687650871134871</v>
       </c>
       <c r="Z2" t="n">
         <v>0.009088541692710351</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007565414387709814</v>
+        <v>0.007565414387709819</v>
       </c>
       <c r="AB2" t="n">
         <v>0.007623334722469011</v>
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007776702308175517</v>
+        <v>0.007776702308175515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008175491834692298</v>
+        <v>0.008175491834692296</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007866363878466761</v>
+        <v>0.007866363878466748</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007241096012581428</v>
+        <v>0.007241096012581421</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007597615377276059</v>
+        <v>0.007597615377276057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008114573241440708</v>
+        <v>0.008114573241440709</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007247246474768863</v>
+        <v>0.007247246474768858</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00823606162778495</v>
+        <v>0.008236061627784943</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008224145418745466</v>
+        <v>0.008224145418745461</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008916849696444065</v>
+        <v>0.008916849696444067</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007933933360867972</v>
+        <v>0.00793393336086797</v>
       </c>
       <c r="M3" t="n">
         <v>0.01036599316217175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007474014727826175</v>
+        <v>0.007474014727826169</v>
       </c>
       <c r="O3" t="n">
         <v>0.01361370461209229</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00816709611282407</v>
+        <v>0.008167096112824066</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00746317548438988</v>
+        <v>0.007463175484389881</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007489825414846129</v>
+        <v>0.007489825414846127</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008092473983327273</v>
+        <v>0.008092473983327275</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008094041213886204</v>
+        <v>0.008094041213886207</v>
       </c>
       <c r="U3" t="n">
         <v>0.01121869642688095</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007832417432241057</v>
+        <v>0.007832417432241067</v>
       </c>
       <c r="W3" t="n">
         <v>0.01011730497784809</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00844644325535927</v>
+        <v>0.008446443255359268</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009530861288186211</v>
+        <v>0.009530861288186194</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0102790017357928</v>
+        <v>0.01027900173579279</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008657148381475868</v>
+        <v>0.008657148381475865</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009069769710583996</v>
+        <v>0.009069769710583991</v>
       </c>
     </row>
     <row r="4">
@@ -4202,43 +4202,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02956135878390836</v>
+        <v>0.02956135878390838</v>
       </c>
       <c r="C4" t="n">
         <v>0.02850227808351988</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0296950817960196</v>
+        <v>0.02969508179601961</v>
       </c>
       <c r="E4" t="n">
         <v>0.02870939899227867</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02926789660699073</v>
+        <v>0.02926789660699074</v>
       </c>
       <c r="G4" t="n">
         <v>0.0300995206041548</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02871191078237047</v>
+        <v>0.02871191078237049</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03027526190660888</v>
+        <v>0.0302752619066089</v>
       </c>
       <c r="J4" t="n">
         <v>0.03026271036785023</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03136957747295885</v>
+        <v>0.03136957747295886</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02980694679848354</v>
+        <v>0.02980694679848355</v>
       </c>
       <c r="M4" t="n">
         <v>0.03364200235167233</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.02907328809609673</v>
       </c>
       <c r="O4" t="n">
         <v>0.02949968020661994</v>
@@ -4247,7 +4247,7 @@
         <v>0.03018350168021333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02905849435489634</v>
+        <v>0.02905849435489635</v>
       </c>
       <c r="R4" t="n">
         <v>0.02909507179608883</v>
@@ -4256,13 +4256,13 @@
         <v>0.03006154627335687</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03004978580863818</v>
+        <v>0.0300497858086382</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03026529266210696</v>
+        <v>0.03026529266210697</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02963045688007014</v>
+        <v>0.02963045688007012</v>
       </c>
       <c r="W4" t="n">
         <v>0.02943580504785048</v>
@@ -4274,7 +4274,7 @@
         <v>0.03227903125661983</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02912182111148044</v>
+        <v>0.02912182111148045</v>
       </c>
       <c r="AA4" t="n">
         <v>0.03094553860189397</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05298552436115461</v>
+        <v>0.05298552436115465</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03675010563135804</v>
+        <v>0.03675010563135805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05802909422149736</v>
+        <v>0.05802909422149718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03931927279075519</v>
+        <v>0.0393192727907552</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05107940764866583</v>
+        <v>0.05107940764866575</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06138068018514217</v>
+        <v>0.06138068018514201</v>
       </c>
       <c r="H5" t="n">
         <v>0.04172855647337101</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06990234841168924</v>
+        <v>0.06990234841168921</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06658065956518383</v>
+        <v>0.06658065956518375</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08373465140924569</v>
+        <v>0.08373465140924578</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05839460987786833</v>
+        <v>0.05839460987786836</v>
       </c>
       <c r="M5" t="n">
         <v>0.129756770314089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.04730731015945097</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05159625405982938</v>
+        <v>0.05159625405982929</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06258583482015505</v>
+        <v>0.06258583482015484</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04627257062139727</v>
+        <v>0.04627257062139724</v>
       </c>
       <c r="R5" t="n">
-        <v>0.04875320515066761</v>
+        <v>0.04875320515066758</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06169100882781992</v>
+        <v>0.0616910088278199</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06614604006180133</v>
+        <v>0.06614604006180136</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06597677571024316</v>
+        <v>0.0659767757102432</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05378845965408752</v>
+        <v>0.05378845965408751</v>
       </c>
       <c r="W5" t="n">
         <v>0.05334724273366663</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07409808184696874</v>
+        <v>0.07409808184696859</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1055954178856139</v>
+        <v>0.1055954178856138</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04485349439444131</v>
+        <v>0.04485349439444132</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08049885470723309</v>
+        <v>0.08049885470723304</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0970038524623046</v>
+        <v>0.09700385246230452</v>
       </c>
     </row>
     <row r="6">
@@ -4378,28 +4378,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03024438879428697</v>
+        <v>0.03024438879428695</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02918530809389848</v>
+        <v>0.02918530809389847</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03155525101198631</v>
+        <v>0.03155525101198633</v>
       </c>
       <c r="E6" t="n">
         <v>0.03056956820824539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02995092661736934</v>
+        <v>0.02995092661736931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0307825506145334</v>
+        <v>0.03078255061453336</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03057207999833717</v>
+        <v>0.03057207999833721</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03095829191698748</v>
+        <v>0.03095829191698746</v>
       </c>
       <c r="J6" t="n">
         <v>0.03212287958381695</v>
@@ -4408,55 +4408,55 @@
         <v>0.03322974668892557</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03048997680886216</v>
+        <v>0.03048997680886214</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03432503236205092</v>
+        <v>0.0343250323620509</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.02976915172245526</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03038543629827072</v>
+        <v>0.03038543629827074</v>
       </c>
       <c r="P6" t="n">
         <v>0.03204678621191787</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03091866357086305</v>
+        <v>0.03091866357086306</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03095524101205555</v>
+        <v>0.03095524101205556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03074457628373545</v>
+        <v>0.03074457628373544</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03190995502460492</v>
+        <v>0.03190995502460491</v>
       </c>
       <c r="U6" t="n">
         <v>0.03217268653519442</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03031348689044874</v>
+        <v>0.03031348689044868</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03018910577477274</v>
+        <v>0.03018910577477275</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03129671899212093</v>
+        <v>0.03129671899212092</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03309168413951881</v>
+        <v>0.03309168413951877</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02980485112185904</v>
+        <v>0.02980485112185902</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03280570781786066</v>
+        <v>0.03280570781786069</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03227853219121329</v>
+        <v>0.03227853219121331</v>
       </c>
     </row>
     <row r="7">
@@ -4478,7 +4478,7 @@
         <v>0.02946805157955232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03002654919426439</v>
+        <v>0.0300265491942644</v>
       </c>
       <c r="G7" t="n">
         <v>0.03085817319142846</v>
@@ -4487,7 +4487,7 @@
         <v>0.02947056336964414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03103391449388254</v>
+        <v>0.03103391449388255</v>
       </c>
       <c r="J7" t="n">
         <v>0.03102136295512389</v>
@@ -4496,25 +4496,25 @@
         <v>0.03212823006023251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03056559938575719</v>
+        <v>0.0305655993857572</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03440065493894599</v>
+        <v>0.03440065493894598</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.02983194068337039</v>
       </c>
       <c r="O7" t="n">
         <v>0.03025821499116957</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03094203646476295</v>
+        <v>0.03094203646476294</v>
       </c>
       <c r="Q7" t="n">
         <v>0.02981714694217</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02985372438336249</v>
+        <v>0.02985372438336248</v>
       </c>
       <c r="S7" t="n">
         <v>0.03082019886063052</v>
@@ -4526,25 +4526,25 @@
         <v>0.03106979765395018</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0303891094673438</v>
+        <v>0.03038910946734377</v>
       </c>
       <c r="W7" t="n">
         <v>0.03019445763512415</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03137234156901601</v>
+        <v>0.031372341569016</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03308490850101423</v>
+        <v>0.03308490850101421</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.02988047369875409</v>
+        <v>0.0298804736987541</v>
       </c>
       <c r="AA7" t="n">
         <v>0.03170419118916763</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03233824019181893</v>
+        <v>0.03233824019181894</v>
       </c>
     </row>
     <row r="8">
@@ -4569,19 +4569,19 @@
         <v>0.03136888649782883</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03378278002963694</v>
+        <v>0.03378278002963693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03208316581764011</v>
+        <v>0.03208316581764009</v>
       </c>
       <c r="I8" t="n">
         <v>0.03364651694187851</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03363396540311986</v>
+        <v>0.03363396540311984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03474083250822847</v>
+        <v>0.03474083250822846</v>
       </c>
       <c r="L8" t="n">
         <v>0.03317820183375318</v>
@@ -4590,7 +4590,7 @@
         <v>0.03701325738694285</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.0312781674313343</v>
       </c>
       <c r="O8" t="n">
         <v>0.03202508971159963</v>
@@ -4599,7 +4599,7 @@
         <v>0.03263034149550485</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03062937010071876</v>
+        <v>0.03062937010071877</v>
       </c>
       <c r="R8" t="n">
         <v>0.03246632683135846</v>
@@ -4611,10 +4611,10 @@
         <v>0.03342104084390782</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03294838786757504</v>
+        <v>0.03294838786757502</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03258938897820457</v>
+        <v>0.03258938897820458</v>
       </c>
       <c r="W8" t="n">
         <v>0.0328073557948946</v>
@@ -4623,16 +4623,16 @@
         <v>0.0323224712813359</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03719191304467907</v>
+        <v>0.03719191304467904</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03096044992141643</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03431679363716361</v>
+        <v>0.0343167936371636</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03652260263920224</v>
+        <v>0.03652260263920223</v>
       </c>
     </row>
     <row r="9">
@@ -4648,25 +4648,25 @@
         <v>0.03193538206462079</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03312818577712051</v>
+        <v>0.03312818577712052</v>
       </c>
       <c r="E9" t="n">
         <v>0.03194577023687616</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03073596672870856</v>
+        <v>0.03073596672870857</v>
       </c>
       <c r="G9" t="n">
         <v>0.03353262417475231</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0321450147634714</v>
+        <v>0.03214501476347139</v>
       </c>
       <c r="I9" t="n">
         <v>0.03370836588770978</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03369581434895114</v>
+        <v>0.03369581434895112</v>
       </c>
       <c r="K9" t="n">
         <v>0.03480268145405976</v>
@@ -4675,16 +4675,16 @@
         <v>0.03324005077958445</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03707510633277325</v>
+        <v>0.03707510633277323</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04730731015945099</v>
+        <v>0.03250639207719763</v>
       </c>
       <c r="O9" t="n">
         <v>0.03321527072470754</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03396052826272011</v>
+        <v>0.03396052826272012</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03249159792549386</v>
@@ -4693,25 +4693,25 @@
         <v>0.03252817577718972</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03349465025445776</v>
+        <v>0.03349465025445777</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0334828897897391</v>
+        <v>0.03348288978973912</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03374562130032858</v>
+        <v>0.0337456213003286</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0340472202922173</v>
+        <v>0.03404722029221727</v>
       </c>
       <c r="W9" t="n">
         <v>0.03286890902895139</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03404679296284325</v>
+        <v>0.03404679296284324</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03575935989484147</v>
+        <v>0.03575935989484149</v>
       </c>
       <c r="Z9" t="n">
         <v>0.03204099836178213</v>
@@ -4720,7 +4720,7 @@
         <v>0.03437864258299489</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03501269158564616</v>
+        <v>0.03501269158564617</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>0.03056917358881606</v>
       </c>
       <c r="N4" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.02947066843995421</v>
       </c>
       <c r="O4" t="n">
         <v>0.0285934582962162</v>
@@ -5274,7 +5274,7 @@
         <v>0.03232606473148394</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.03009218375014108</v>
       </c>
       <c r="O6" t="n">
         <v>0.03036514993603241</v>
@@ -5362,7 +5362,7 @@
         <v>0.03130782905119556</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.03020932390233371</v>
       </c>
       <c r="O7" t="n">
         <v>0.02933199037079593</v>
@@ -5450,7 +5450,7 @@
         <v>0.03395134787755724</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.03167834952519114</v>
       </c>
       <c r="O8" t="n">
         <v>0.03112390031164305</v>
@@ -5538,7 +5538,7 @@
         <v>0.03417877544926035</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.03308027030039851</v>
       </c>
       <c r="O9" t="n">
         <v>0.03249937013633929</v>
@@ -5958,7 +5958,7 @@
         <v>0.02820730642498855</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.02871278549774863</v>
       </c>
       <c r="O4" t="n">
         <v>0.02875662922670924</v>
@@ -6134,7 +6134,7 @@
         <v>0.02988234370815081</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.02934311676349852</v>
       </c>
       <c r="O6" t="n">
         <v>0.03043665496915157</v>
@@ -6222,7 +6222,7 @@
         <v>0.02887017242752187</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.02937565150028194</v>
       </c>
       <c r="O7" t="n">
         <v>0.02941937926472329</v>
@@ -6310,7 +6310,7 @@
         <v>0.03126246075955195</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.03070572467261188</v>
       </c>
       <c r="O8" t="n">
         <v>0.03104147435044305</v>
@@ -6398,7 +6398,7 @@
         <v>0.03132277471591498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.03182825378867505</v>
       </c>
       <c r="O9" t="n">
         <v>0.03212964470104968</v>
@@ -6818,7 +6818,7 @@
         <v>0.0281662722843665</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.02845875680753199</v>
       </c>
       <c r="O4" t="n">
         <v>0.02933090144672774</v>
@@ -6994,7 +6994,7 @@
         <v>0.02985961903623458</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.02910488748762038</v>
       </c>
       <c r="O6" t="n">
         <v>0.03016698653721913</v>
@@ -7082,7 +7082,7 @@
         <v>0.0288203161459944</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.0291128006691599</v>
       </c>
       <c r="O7" t="n">
         <v>0.02998482902132858</v>
@@ -7170,7 +7170,7 @@
         <v>0.03119139587576512</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03043186757646984</v>
       </c>
       <c r="O8" t="n">
         <v>0.03159311447368408</v>
@@ -7258,7 +7258,7 @@
         <v>0.03105696455900417</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03134944908216966</v>
       </c>
       <c r="O9" t="n">
         <v>0.03246272704652452</v>
@@ -7678,7 +7678,7 @@
         <v>0.03565254534821861</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.03089314476434292</v>
       </c>
       <c r="O4" t="n">
         <v>0.02946482950770291</v>
@@ -7854,7 +7854,7 @@
         <v>0.03629364534006992</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.0315399408479133</v>
       </c>
       <c r="O6" t="n">
         <v>0.03138134397493827</v>
@@ -7942,7 +7942,7 @@
         <v>0.03647380327027771</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.03171440268640201</v>
       </c>
       <c r="O7" t="n">
         <v>0.03028596292989769</v>
@@ -8030,7 +8030,7 @@
         <v>0.03930969540035931</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.03328459039089632</v>
       </c>
       <c r="O8" t="n">
         <v>0.03220410170022824</v>
@@ -8118,7 +8118,7 @@
         <v>0.03985007595517111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.03509067537129541</v>
       </c>
       <c r="O9" t="n">
         <v>0.03400288084089353</v>
@@ -8538,7 +8538,7 @@
         <v>0.02889706503998537</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.02885340534359542</v>
       </c>
       <c r="O4" t="n">
         <v>0.02858565038558932</v>
@@ -8714,7 +8714,7 @@
         <v>0.02951255192897562</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.02947436722138705</v>
       </c>
       <c r="O6" t="n">
         <v>0.03033767172814066</v>
@@ -8802,7 +8802,7 @@
         <v>0.02959253350873027</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.02954887381234031</v>
       </c>
       <c r="O7" t="n">
         <v>0.02928100263117132</v>
@@ -8890,7 +8890,7 @@
         <v>0.0320799540924179</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.03093019322299967</v>
       </c>
       <c r="O8" t="n">
         <v>0.03096640447136682</v>
@@ -8978,7 +8978,7 @@
         <v>0.03232119974033698</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.03227754004394702</v>
       </c>
       <c r="O9" t="n">
         <v>0.03229078387243684</v>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -586,34 +586,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007696119316465227</v>
+        <v>0.007696119316465232</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00835751589742101</v>
+        <v>0.008357515897421012</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00766398996484345</v>
+        <v>0.007663989964843452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007532857204365965</v>
+        <v>0.007532857204365966</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007601892993471674</v>
+        <v>0.007601892993471676</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007669938811594633</v>
+        <v>0.007669938811594635</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007640597959649022</v>
+        <v>0.007640597959649025</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007700649880570455</v>
+        <v>0.007700649880570457</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007676659024118826</v>
+        <v>0.007676659024118833</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007852395958222631</v>
+        <v>0.007852395958222633</v>
       </c>
       <c r="L2" t="n">
         <v>0.007685870680996753</v>
@@ -622,28 +622,28 @@
         <v>0.008197333323082864</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007741686195258334</v>
+        <v>0.007741686195258336</v>
       </c>
       <c r="O2" t="n">
         <v>0.01139099494745044</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007641030059721635</v>
+        <v>0.007641030059721637</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007582667962853031</v>
+        <v>0.007582667962853032</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007601730932066128</v>
+        <v>0.007601730932066132</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007660498933037447</v>
+        <v>0.007660498933037449</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007708121364560504</v>
+        <v>0.007708121364560509</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01038529570442292</v>
+        <v>0.01038529570442293</v>
       </c>
       <c r="V2" t="n">
         <v>0.007573857199177973</v>
@@ -652,19 +652,19 @@
         <v>0.009749805636603917</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007584749341131482</v>
+        <v>0.007584749341131484</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007613965609021909</v>
+        <v>0.007613965609021912</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009323951350409159</v>
+        <v>0.00932395135040916</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007749259791342908</v>
+        <v>0.007749259791342909</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007829396634781364</v>
+        <v>0.007829396634781367</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008728089609870215</v>
+        <v>0.008797008778351668</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008728972402224972</v>
+        <v>0.008747972015345423</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008510774966525867</v>
+        <v>0.008572538696461917</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007569007474841865</v>
+        <v>0.007597077306881934</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008067899138149709</v>
+        <v>0.008114096155075577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008544279507279999</v>
+        <v>0.008606684883492774</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008346951847014186</v>
+        <v>0.00840312201535396</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008774501165475698</v>
+        <v>0.008845698588926294</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008595825283516193</v>
+        <v>0.008660318778971519</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009858091890570537</v>
+        <v>0.009967550776523667</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008661704951327084</v>
+        <v>0.008728450543207696</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01230766807697448</v>
+        <v>0.01250456764793784</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009063259260790353</v>
+        <v>0.009144429889147342</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01471836742337259</v>
+        <v>0.01478232597851805</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008337586633331171</v>
+        <v>0.008392632570365084</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007927353251508203</v>
+        <v>0.00796837351839034</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008066803731645414</v>
+        <v>0.008112920363895111</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008477378777870441</v>
+        <v>0.008537562944782978</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008827148237065981</v>
+        <v>0.008900161957674572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01373441383133869</v>
+        <v>0.01382947552272026</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007859492656936633</v>
+        <v>0.007897897453847563</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01178212099043783</v>
+        <v>0.01183577643369615</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007942737282818592</v>
+        <v>0.007984343319608367</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008149312327877243</v>
+        <v>0.008198110580634117</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01081382258053577</v>
+        <v>0.01085517232193014</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009115906340264235</v>
+        <v>0.009198794706094256</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009690675843926291</v>
+        <v>0.009793995013778707</v>
       </c>
     </row>
     <row r="4">
@@ -774,13 +774,13 @@
         <v>0.02927764987827068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03005744087425168</v>
+        <v>0.03005744087425167</v>
       </c>
       <c r="G4" t="n">
         <v>0.03082604969257335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03049463127238889</v>
+        <v>0.03049463127238888</v>
       </c>
       <c r="I4" t="n">
         <v>0.03117294534444505</v>
@@ -789,22 +789,22 @@
         <v>0.03089867374285789</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03288698709817079</v>
+        <v>0.03288698709817078</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03100600748649231</v>
+        <v>0.03100600748649232</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0367374107700861</v>
+        <v>0.03673741077008608</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03163646939648202</v>
+        <v>0.03163646939648203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0309005763312085</v>
+        <v>0.03090057633120849</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03049951204148502</v>
+        <v>0.03049951204148501</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0298402853094631</v>
@@ -819,19 +819,19 @@
         <v>0.03125733919316506</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03225265958849392</v>
+        <v>0.03225265958849391</v>
       </c>
       <c r="V4" t="n">
         <v>0.02971963333495604</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03041468461808935</v>
+        <v>0.03041468461808934</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0298637954345995</v>
+        <v>0.02986379543459949</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0301652046913144</v>
+        <v>0.03016520469131439</v>
       </c>
       <c r="Z4" t="n">
         <v>0.02987443694668444</v>
@@ -840,7 +840,7 @@
         <v>0.0317220166482836</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03260628497095551</v>
+        <v>0.0326062849709555</v>
       </c>
     </row>
     <row r="5">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08249636566526927</v>
+        <v>0.0824963656652689</v>
       </c>
       <c r="C5" t="n">
         <v>0.04169803500020147</v>
       </c>
       <c r="D5" t="n">
-        <v>0.08231673608608184</v>
+        <v>0.08231673608608167</v>
       </c>
       <c r="E5" t="n">
         <v>0.04900173767693296</v>
@@ -865,70 +865,70 @@
         <v>0.06837801034458185</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07834887823190348</v>
+        <v>0.07834887823190355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07885424930307507</v>
+        <v>0.07885424930307504</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09189339500903346</v>
+        <v>0.09189339500903355</v>
       </c>
       <c r="J5" t="n">
         <v>0.08200394012308759</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1267501229451507</v>
+        <v>0.1267501229451506</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08418316700212583</v>
+        <v>0.08418316700212569</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2117939049501719</v>
+        <v>0.2117939049501718</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0987789753098786</v>
+        <v>0.09877897530987848</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07723745435558069</v>
+        <v>0.07723745435558058</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07155339864743018</v>
+        <v>0.07155339864743025</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06202228225095356</v>
+        <v>0.06202228225095357</v>
       </c>
       <c r="R5" t="n">
-        <v>0.06837754114812182</v>
+        <v>0.06837754114812179</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07648224913763062</v>
+        <v>0.0764822491376307</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09319036316711354</v>
+        <v>0.09319036316711353</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1081895460815459</v>
+        <v>0.1081895460815458</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05703848503095547</v>
+        <v>0.05703848503095546</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07270760973012436</v>
+        <v>0.0727076097301243</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06281021432539735</v>
+        <v>0.06281021432539728</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06830115859139436</v>
+        <v>0.06830115859139428</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06007965772860182</v>
+        <v>0.06007965772860179</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09966602555880219</v>
+        <v>0.09966602555880236</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1259082719160553</v>
+        <v>0.1259082719160554</v>
       </c>
     </row>
     <row r="6">
@@ -941,7 +941,7 @@
         <v>0.03189208807784966</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03108061161156589</v>
+        <v>0.03108061161156588</v>
       </c>
       <c r="D6" t="n">
         <v>0.03298207190207433</v>
@@ -950,34 +950,34 @@
         <v>0.03150086704843091</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03082775841338734</v>
+        <v>0.03082775841338733</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03304926686273357</v>
+        <v>0.03304926686273359</v>
       </c>
       <c r="H6" t="n">
         <v>0.03271784844254911</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03194326288358072</v>
+        <v>0.0319432628835807</v>
       </c>
       <c r="J6" t="n">
         <v>0.03166899128199355</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03511020426833102</v>
+        <v>0.03511020426833104</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03322922465665253</v>
+        <v>0.03322922465665254</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03896062794024636</v>
+        <v>0.03896062794024634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03241491090986934</v>
+        <v>0.0324149109098693</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03167901511466375</v>
+        <v>0.03167901511466373</v>
       </c>
       <c r="P6" t="n">
         <v>0.03271034522951451</v>
@@ -989,34 +989,34 @@
         <v>0.03227882748628438</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03148973946084691</v>
+        <v>0.0314897394608469</v>
       </c>
       <c r="T6" t="n">
         <v>0.03202765673230071</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03305157905688432</v>
+        <v>0.03305157905688431</v>
       </c>
       <c r="V6" t="n">
         <v>0.03194285050511626</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03262551714935978</v>
+        <v>0.03262551714935977</v>
       </c>
       <c r="X6" t="n">
         <v>0.03208701260475972</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03102982220368663</v>
+        <v>0.03102982220368665</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0306447544858201</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03394523381844384</v>
+        <v>0.03394523381844383</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03339774842348164</v>
+        <v>0.03339774842348163</v>
       </c>
     </row>
     <row r="7">
@@ -1029,10 +1029,10 @@
         <v>0.03208915683151731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02982478073420897</v>
+        <v>0.02982478073420896</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03172624102471741</v>
+        <v>0.0317262410247174</v>
       </c>
       <c r="E7" t="n">
         <v>0.03024503617107399</v>
@@ -1053,52 +1053,52 @@
         <v>0.0318660600356612</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03385437339097411</v>
+        <v>0.03385437339097412</v>
       </c>
       <c r="L7" t="n">
         <v>0.03197339377929563</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03770479706288943</v>
+        <v>0.03770479706288941</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03260385568928534</v>
+        <v>0.03260385568928533</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03186782567874123</v>
+        <v>0.03186782567874122</v>
       </c>
       <c r="P7" t="n">
         <v>0.03146676138901774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03080767160226641</v>
+        <v>0.03080767160226642</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03102299660892747</v>
+        <v>0.03102299660892746</v>
       </c>
       <c r="S7" t="n">
         <v>0.03168680821451455</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03222472548596836</v>
+        <v>0.03222472548596835</v>
       </c>
       <c r="U7" t="n">
         <v>0.03324772941870802</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03068701962775934</v>
+        <v>0.03068701962775935</v>
       </c>
       <c r="W7" t="n">
         <v>0.03138207091089265</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03083118172740281</v>
+        <v>0.0308311817274028</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03116119291337244</v>
+        <v>0.03116119291337243</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03084182323948776</v>
+        <v>0.03084182323948775</v>
       </c>
       <c r="AA7" t="n">
         <v>0.03268940294108691</v>
@@ -1117,40 +1117,40 @@
         <v>0.03345373040786254</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03306378991388972</v>
+        <v>0.03306378991388974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03496525020439815</v>
+        <v>0.03496525020439816</v>
       </c>
       <c r="E8" t="n">
         <v>0.03248596368441473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03268141590337922</v>
+        <v>0.03268141590337924</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03542112159820566</v>
+        <v>0.03542112159820567</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03470102674487294</v>
+        <v>0.03470102674487297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03537934081692912</v>
+        <v>0.03537934081692914</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03510506921534196</v>
+        <v>0.03510506921534199</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03709338257065486</v>
+        <v>0.03709338257065487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03521240295897638</v>
+        <v>0.0352124029589764</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04094380624257026</v>
+        <v>0.04094380624257028</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03438986369007546</v>
+        <v>0.03438986369007548</v>
       </c>
       <c r="O8" t="n">
         <v>0.03405326796484282</v>
@@ -1159,40 +1159,40 @@
         <v>0.03355432624871105</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0318038758007104</v>
+        <v>0.03180387580071041</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03426200578860823</v>
+        <v>0.03426200578860824</v>
       </c>
       <c r="S8" t="n">
         <v>0.03492581739419533</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03546373466564912</v>
+        <v>0.03546373466564913</v>
       </c>
       <c r="U8" t="n">
         <v>0.03557216438800805</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03341304933266174</v>
+        <v>0.03341304933266175</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03462144847064884</v>
+        <v>0.03462144847064883</v>
       </c>
       <c r="X8" t="n">
         <v>0.03199918167331311</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03626287473980418</v>
+        <v>0.03626287473980419</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03217157821218127</v>
+        <v>0.03217157821218128</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03592841212076766</v>
+        <v>0.03592841212076767</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03877068516867014</v>
+        <v>0.03877068516867016</v>
       </c>
     </row>
     <row r="9">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03517095222648742</v>
+        <v>0.03517095222648744</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03419733818558954</v>
+        <v>0.03419733818558956</v>
       </c>
       <c r="D9" t="n">
         <v>0.03609879847609798</v>
@@ -1220,10 +1220,10 @@
         <v>0.03616599255635839</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03583457501657278</v>
+        <v>0.03583457501657279</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03651288908862894</v>
+        <v>0.03651288908862895</v>
       </c>
       <c r="J9" t="n">
         <v>0.0362386174870418</v>
@@ -1232,19 +1232,19 @@
         <v>0.03822693084235471</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0363459512306762</v>
+        <v>0.03634595123067621</v>
       </c>
       <c r="M9" t="n">
         <v>0.04207735451427001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03697641314066592</v>
+        <v>0.03697641314066594</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03666827575861643</v>
+        <v>0.03666827575861644</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03636024118241415</v>
+        <v>0.03636024118241416</v>
       </c>
       <c r="Q9" t="n">
         <v>0.03518022817324816</v>
@@ -1256,31 +1256,31 @@
         <v>0.03605936566589515</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03659728293734897</v>
+        <v>0.03659728293734896</v>
       </c>
       <c r="U9" t="n">
         <v>0.03762120526193256</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0365490854355164</v>
+        <v>0.03654908543551641</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03575462836227324</v>
+        <v>0.03575462836227325</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03520373917878338</v>
+        <v>0.03520373917878339</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03553375036475303</v>
+        <v>0.03553375036475304</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03443616560029664</v>
+        <v>0.03443616560029662</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0370619603924675</v>
+        <v>0.03706196039246751</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03794622871513941</v>
+        <v>0.03794622871513942</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007102043182795017</v>
+        <v>0.007102043182795032</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007774872993368593</v>
+        <v>0.007774872993368589</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007119545097264866</v>
+        <v>0.007119545097264867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007110842871831146</v>
+        <v>0.007110842871831159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007145960523021039</v>
+        <v>0.007145960523021043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007134499321804168</v>
+        <v>0.007134499321804178</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00712713094013656</v>
+        <v>0.007127130940136563</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007126297354616812</v>
+        <v>0.007126297354616814</v>
       </c>
       <c r="J2" t="n">
         <v>0.007144945698305421</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007149309046164588</v>
+        <v>0.007149309046164571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0071934926982334</v>
+        <v>0.007193492698233404</v>
       </c>
       <c r="M2" t="n">
         <v>0.007127511893938396</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007143670112066662</v>
+        <v>0.007143670112066665</v>
       </c>
       <c r="O2" t="n">
         <v>0.0106446137239978</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007149947860654156</v>
+        <v>0.007149947860654158</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007115697387655985</v>
+        <v>0.007115697387655987</v>
       </c>
       <c r="R2" t="n">
         <v>0.007212643807988792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007166809653533706</v>
+        <v>0.007166809653533716</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007142036434390505</v>
+        <v>0.007142036434390515</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008906118136871234</v>
+        <v>0.008906118136871245</v>
       </c>
       <c r="V2" t="n">
         <v>0.007148663739136373</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008628733597425881</v>
+        <v>0.008628733597425888</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00731194987548418</v>
+        <v>0.007311949875484196</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007220983412744571</v>
+        <v>0.007220983412744575</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00879261655011118</v>
+        <v>0.008792616550111199</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007219434459328455</v>
+        <v>0.007219434459328457</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007100993650783291</v>
+        <v>0.007100993650783298</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006761845910665035</v>
+        <v>0.006770957666290682</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007985442416176918</v>
+        <v>0.007999831861889841</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006887519648231667</v>
+        <v>0.006901153136328406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.006823857824328769</v>
+        <v>0.006835047565935032</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007076551013106992</v>
+        <v>0.007096971707380192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006992045809602896</v>
+        <v>0.007009279741082701</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006942933887903045</v>
+        <v>0.00695857107380919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006936231893780178</v>
+        <v>0.00695160100519214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007067471382474629</v>
+        <v>0.007087427120401482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007098221859773187</v>
+        <v>0.007119389469847194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007411448897470647</v>
+        <v>0.007443601098036293</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006956527735630858</v>
+        <v>0.006972719244199033</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00706007604250826</v>
+        <v>0.007079770128192887</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01300667008021278</v>
+        <v>0.01303401106286348</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007101641355318426</v>
+        <v>0.007122697165456015</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006859556889374682</v>
+        <v>0.006872191646661709</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007555158837532472</v>
+        <v>0.00759256464577083</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007221472154537964</v>
+        <v>0.007246842727613712</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007048901352248262</v>
+        <v>0.007068255902649246</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009928943215366619</v>
+        <v>0.009946793946680979</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007092706454601366</v>
+        <v>0.007113501358588266</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009785499253209548</v>
+        <v>0.009817764660964248</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008258507625146769</v>
+        <v>0.008320944048412934</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007612099927590172</v>
+        <v>0.007651283819012464</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009717031650558783</v>
+        <v>0.009733742349415691</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007600767753164808</v>
+        <v>0.007639532851919208</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006762897922553177</v>
+        <v>0.006772121303064172</v>
       </c>
     </row>
     <row r="4">
@@ -1625,22 +1625,22 @@
         <v>0.02805832155463595</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02829016643501352</v>
+        <v>0.02829016643501353</v>
       </c>
       <c r="D4" t="n">
         <v>0.02825601372985135</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02815771809035598</v>
+        <v>0.02815771809035597</v>
       </c>
       <c r="F4" t="n">
         <v>0.02855438811546346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0284249285753059</v>
+        <v>0.02842492857530589</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0283416993147473</v>
+        <v>0.02834169931474731</v>
       </c>
       <c r="I4" t="n">
         <v>0.02833228358283338</v>
@@ -1658,10 +1658,10 @@
         <v>0.02836776790765971</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02852851687009272</v>
+        <v>0.02852851687009273</v>
       </c>
       <c r="O4" t="n">
-        <v>0.028883002966595</v>
+        <v>0.02888300296659501</v>
       </c>
       <c r="P4" t="n">
         <v>0.02859942692829552</v>
@@ -1673,13 +1673,13 @@
         <v>0.0293076064950009</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02878988863567794</v>
+        <v>0.02878988863567795</v>
       </c>
       <c r="T4" t="n">
         <v>0.02851006372921162</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0284065383796258</v>
+        <v>0.02840653837962579</v>
       </c>
       <c r="V4" t="n">
         <v>0.02856466918620933</v>
@@ -1691,10 +1691,10 @@
         <v>0.03042931421040933</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02935848808350407</v>
+        <v>0.02935848808350406</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02840099104848181</v>
+        <v>0.02840099104848182</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02938431002573633</v>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03169416672244479</v>
+        <v>0.03169416672244478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0360702029569763</v>
+        <v>0.03607020295697633</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03558541156868455</v>
+        <v>0.03558541156868456</v>
       </c>
       <c r="E5" t="n">
         <v>0.03304177341375188</v>
@@ -1725,70 +1725,70 @@
         <v>0.04112340195813569</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03743136014709225</v>
+        <v>0.03743136014709236</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03776096578260136</v>
+        <v>0.03776096578260135</v>
       </c>
       <c r="I5" t="n">
         <v>0.03720438981700309</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03996565043625971</v>
+        <v>0.03996565043625974</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04063790142879156</v>
+        <v>0.04063790142879155</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04836939076553773</v>
+        <v>0.04836939076553775</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03772935817291707</v>
+        <v>0.03772935817291706</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04059939329079139</v>
+        <v>0.0405993932907914</v>
       </c>
       <c r="O5" t="n">
         <v>0.04451980316792376</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04017487372252267</v>
+        <v>0.04017487372252265</v>
       </c>
       <c r="Q5" t="n">
         <v>0.03455684977667046</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05583720914522036</v>
+        <v>0.05583720914522037</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04327783171516873</v>
+        <v>0.04327783171516871</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04052433145750613</v>
+        <v>0.04052433145750614</v>
       </c>
       <c r="U5" t="n">
         <v>0.03796275911133244</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04001724025209758</v>
+        <v>0.04001724025209757</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05022345056311965</v>
+        <v>0.05022345056311955</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0728761994427083</v>
+        <v>0.07287619944270837</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0561667403831948</v>
+        <v>0.05616674038319485</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03679375340947513</v>
+        <v>0.03679375340947514</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05571363172911617</v>
+        <v>0.05571363172911626</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03239369276787112</v>
+        <v>0.03239369276787113</v>
       </c>
     </row>
     <row r="6">
@@ -1813,10 +1813,10 @@
         <v>0.03022224058885347</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02905502956391185</v>
+        <v>0.02905502956391184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02897180030335326</v>
+        <v>0.02897180030335325</v>
       </c>
       <c r="I6" t="n">
         <v>0.02896238457143933</v>
@@ -1828,10 +1828,10 @@
         <v>0.02922231221337237</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03075913837375808</v>
+        <v>0.03075913837375809</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02899786889626567</v>
+        <v>0.02899786889626566</v>
       </c>
       <c r="N6" t="n">
         <v>0.02916739175003191</v>
@@ -1843,10 +1843,10 @@
         <v>0.02919237543722827</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02884265306839114</v>
+        <v>0.02884265306839113</v>
       </c>
       <c r="R6" t="n">
-        <v>0.02993770748360685</v>
+        <v>0.02993770748360684</v>
       </c>
       <c r="S6" t="n">
         <v>0.03045774110906795</v>
@@ -1858,22 +1858,22 @@
         <v>0.03011770893663696</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02919477017481528</v>
+        <v>0.02919477017481527</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02979173722260467</v>
+        <v>0.02979173722260461</v>
       </c>
       <c r="X6" t="n">
         <v>0.03209716668379933</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03010740429423167</v>
+        <v>0.03010740429423166</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02903109203708776</v>
+        <v>0.02903109203708775</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03105216249912634</v>
+        <v>0.03105216249912635</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02868947150737794</v>
@@ -1928,7 +1928,7 @@
         <v>0.02954098588503205</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02925740984673256</v>
+        <v>0.02925740984673257</v>
       </c>
       <c r="Q7" t="n">
         <v>0.02887065122999454</v>
@@ -1937,7 +1937,7 @@
         <v>0.02996570564521025</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0294479877858873</v>
+        <v>0.02944798778588729</v>
       </c>
       <c r="T7" t="n">
         <v>0.02916816287942097</v>
@@ -1946,10 +1946,10 @@
         <v>0.02910664460323763</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02922276833641869</v>
+        <v>0.02922276833641868</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02975236297894641</v>
+        <v>0.0297523629789464</v>
       </c>
       <c r="X7" t="n">
         <v>0.03108741336061868</v>
@@ -1964,7 +1964,7 @@
         <v>0.03004240917594568</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.02871789695519868</v>
+        <v>0.02871789695519869</v>
       </c>
     </row>
     <row r="8">
@@ -1992,10 +1992,10 @@
         <v>0.03175001508199615</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03138380131448289</v>
+        <v>0.0313838013144829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03137438558256896</v>
+        <v>0.03137438558256897</v>
       </c>
       <c r="J8" t="n">
         <v>0.03158187887028766</v>
@@ -2016,25 +2016,25 @@
         <v>0.03115793249104403</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03080309461926666</v>
+        <v>0.03080309461926667</v>
       </c>
       <c r="Q8" t="n">
         <v>0.02962173011582959</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03234970849473647</v>
+        <v>0.03234970849473648</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03183199063541352</v>
+        <v>0.03183199063541353</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03155216572894719</v>
+        <v>0.0315521657289472</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03082492874517943</v>
+        <v>0.03082492874517944</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03123275014657776</v>
+        <v>0.03123275014657777</v>
       </c>
       <c r="W8" t="n">
         <v>0.03213663403579273</v>
@@ -2043,16 +2043,16 @@
         <v>0.0319635719548018</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03379923864694042</v>
+        <v>0.03379923864694044</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03005301813156557</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0324264120254719</v>
+        <v>0.03242641202547192</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03252746861861674</v>
+        <v>0.03252746861861675</v>
       </c>
     </row>
     <row r="9">
@@ -2071,7 +2071,7 @@
         <v>0.0311362356875143</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03087040528015794</v>
+        <v>0.03087040528015793</v>
       </c>
       <c r="F9" t="n">
         <v>0.02976120804613738</v>
@@ -2083,16 +2083,16 @@
         <v>0.03122192127241026</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03121250554049633</v>
+        <v>0.03121250554049634</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03141999882821505</v>
+        <v>0.03141999882821504</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03147243318242938</v>
+        <v>0.03147243318242939</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03197150785803103</v>
+        <v>0.03197150785803102</v>
       </c>
       <c r="M9" t="n">
         <v>0.03124798986532267</v>
@@ -2104,10 +2104,10 @@
         <v>0.03200378841780435</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0317725307073855</v>
+        <v>0.03177253070738549</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03109277451836487</v>
+        <v>0.03109277451836486</v>
       </c>
       <c r="R9" t="n">
         <v>0.03218782845266385</v>
@@ -2140,7 +2140,7 @@
         <v>0.03226453198339928</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03094001976265228</v>
+        <v>0.03094001976265229</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0075443296316659</v>
+        <v>0.007544329631665905</v>
       </c>
       <c r="C2" t="n">
         <v>0.008246681699950058</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007527995385463261</v>
+        <v>0.007527995385463256</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007424240227779351</v>
+        <v>0.007424240227779343</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00744059723406823</v>
+        <v>0.007440597234068223</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007556691107137547</v>
+        <v>0.007556691107137542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007433003993414603</v>
+        <v>0.007433003993414595</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007497652399365143</v>
+        <v>0.007497652399365135</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007565228509074531</v>
+        <v>0.007565228509074523</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007689172124900509</v>
+        <v>0.007689172124900515</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007557834672974867</v>
+        <v>0.007557834672974883</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008033673242063517</v>
+        <v>0.008033673242063524</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007551855453321665</v>
+        <v>0.007551855453321657</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01114487375238056</v>
+        <v>0.01114487375238057</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007564353905890818</v>
+        <v>0.007564353905890817</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007449513052714194</v>
+        <v>0.007449513052714199</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007437725116933323</v>
+        <v>0.007437725116933316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007551582254587908</v>
+        <v>0.007551582254587914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007535941869378593</v>
+        <v>0.007535941869378586</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01003893072635196</v>
+        <v>0.01003893072635197</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007424156752661849</v>
+        <v>0.007424156752661847</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009534187549401395</v>
+        <v>0.009534187549401401</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007507396827526695</v>
+        <v>0.007507396827526689</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007495674992106719</v>
+        <v>0.007495674992106711</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009151499581998047</v>
+        <v>0.009151499581998054</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007577737316377063</v>
+        <v>0.007577737316377056</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007712908977996584</v>
+        <v>0.007712908977996636</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00827734994479897</v>
+        <v>0.008332310490506719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008632281780872881</v>
+        <v>0.008650455161603678</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008170962483138547</v>
+        <v>0.008222575728095347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007425301391133398</v>
+        <v>0.007450195760835374</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007545545227237475</v>
+        <v>0.007575090401524655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008367128587065916</v>
+        <v>0.008425210021128039</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007492553981582662</v>
+        <v>0.007520206199305729</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007954530817480931</v>
+        <v>0.007998514047748139</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008432107362248349</v>
+        <v>0.008492764861147875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009314417981099464</v>
+        <v>0.009406834576832846</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008379512550381839</v>
+        <v>0.00843819420379216</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01176899182302802</v>
+        <v>0.01194869604238162</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008339137640073551</v>
+        <v>0.008396582876451493</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01409313403702244</v>
+        <v>0.01414227060274947</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008421193463878327</v>
+        <v>0.008481049702239306</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007607950047760536</v>
+        <v>0.007639562448238013</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007525795118049151</v>
+        <v>0.00755458376636591</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008331028571739932</v>
+        <v>0.008387966564688324</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008227766076801576</v>
+        <v>0.008281428909162926</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01290460283286494</v>
+        <v>0.01298301700417847</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007423058672636131</v>
+        <v>0.007448006341862029</v>
       </c>
       <c r="W3" t="n">
-        <v>0.011688991127637</v>
+        <v>0.01174989566834731</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008022277743802814</v>
+        <v>0.008068619269360342</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007936008597657312</v>
+        <v>0.007979179706594244</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01044409119865304</v>
+        <v>0.01047675455880081</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008522240134174181</v>
+        <v>0.008586078331559704</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009488221277131661</v>
+        <v>0.009586256086211459</v>
       </c>
     </row>
     <row r="4">
@@ -2482,16 +2482,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03035302691637391</v>
+        <v>0.0303530269163739</v>
       </c>
       <c r="C4" t="n">
-        <v>0.028681825088084</v>
+        <v>0.02868182508808399</v>
       </c>
       <c r="D4" t="n">
         <v>0.03016852409139066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0289965618556202</v>
+        <v>0.02899656185562019</v>
       </c>
       <c r="F4" t="n">
         <v>0.02918132176624775</v>
@@ -2506,19 +2506,19 @@
         <v>0.02982578610494909</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03058512910377428</v>
+        <v>0.03058512910377429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03198908950829767</v>
+        <v>0.03198908950829766</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03050557257058464</v>
+        <v>0.03050557257058469</v>
       </c>
       <c r="M4" t="n">
         <v>0.03583645196724628</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03043803453402477</v>
+        <v>0.03043803453402476</v>
       </c>
       <c r="O4" t="n">
         <v>0.03009214811745576</v>
@@ -2527,28 +2527,28 @@
         <v>0.03057921030536559</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02928203003933307</v>
+        <v>0.02928203003933308</v>
       </c>
       <c r="R4" t="n">
         <v>0.02914887988196981</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03043494862864941</v>
+        <v>0.0304349486286494</v>
       </c>
       <c r="T4" t="n">
         <v>0.0302582832827775</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03130252058136029</v>
+        <v>0.03130252058136028</v>
       </c>
       <c r="V4" t="n">
         <v>0.02896990963168201</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03060108759015018</v>
+        <v>0.03060108759015017</v>
       </c>
       <c r="X4" t="n">
-        <v>0.02993585390369219</v>
+        <v>0.02993585390369221</v>
       </c>
       <c r="Y4" t="n">
         <v>0.02971119270846767</v>
@@ -2560,7 +2560,7 @@
         <v>0.03073038208348072</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03223244831166086</v>
+        <v>0.03223244831166085</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06851764147022656</v>
+        <v>0.06851764147022767</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04064354295782927</v>
+        <v>0.04064354295782924</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07069675373887668</v>
+        <v>0.0706967537388767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04567023906179268</v>
+        <v>0.04567023906179294</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05111190029294106</v>
+        <v>0.05111190029294105</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07202208304774559</v>
+        <v>0.07202208304774552</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05015873132064579</v>
+        <v>0.05015873132064577</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06428733883161317</v>
+        <v>0.06428733883161326</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07609218463308888</v>
+        <v>0.07609218463308903</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1012985496127537</v>
+        <v>0.1012985496127536</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07461454720269778</v>
+        <v>0.07461454720269931</v>
       </c>
       <c r="M5" t="n">
-        <v>0.185013424484701</v>
+        <v>0.1850134244847008</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0746161821041017</v>
+        <v>0.07461618210410169</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0631063676824194</v>
+        <v>0.06310636768241937</v>
       </c>
       <c r="P5" t="n">
-        <v>0.07331111415610014</v>
+        <v>0.07331111415610013</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0523332269424039</v>
+        <v>0.05233322694240396</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05091467987338842</v>
+        <v>0.0509146798733884</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07113236148996283</v>
+        <v>0.07113236148996258</v>
       </c>
       <c r="T5" t="n">
-        <v>0.07244348837745418</v>
+        <v>0.07244348837745414</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09001497859277786</v>
+        <v>0.09001497859277774</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04471074536908257</v>
+        <v>0.04471074536908259</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07683950234141068</v>
+        <v>0.0768395023414107</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0653676702311109</v>
+        <v>0.06536767023111113</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0614127384519283</v>
+        <v>0.06141273845192829</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05154875643726826</v>
+        <v>0.05154875643726867</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07924420041175072</v>
+        <v>0.07924420041175083</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1158243396496397</v>
+        <v>0.1158243396496395</v>
       </c>
     </row>
     <row r="6">
@@ -2658,49 +2658,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03101492586976711</v>
+        <v>0.03101492586976712</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03062367775413035</v>
+        <v>0.03062367775413034</v>
       </c>
       <c r="D6" t="n">
         <v>0.03083042304478386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03093841452166655</v>
+        <v>0.03093841452166656</v>
       </c>
       <c r="F6" t="n">
         <v>0.02984322071964094</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03243450813443213</v>
+        <v>0.03243450813443214</v>
       </c>
       <c r="H6" t="n">
         <v>0.03103740528604813</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03176763877099543</v>
+        <v>0.03176763877099544</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03252698176982063</v>
+        <v>0.03252698176982064</v>
       </c>
       <c r="K6" t="n">
         <v>0.03265098846169086</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03244742523663097</v>
+        <v>0.03244742523663099</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03777830463329263</v>
+        <v>0.03777830463329262</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03110653559148245</v>
+        <v>0.03110653559148242</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03075779937348064</v>
+        <v>0.03075779937348053</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03252733924008088</v>
+        <v>0.03252733924008087</v>
       </c>
       <c r="Q6" t="n">
         <v>0.02994392899272628</v>
@@ -2709,25 +2709,25 @@
         <v>0.03109073254801615</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03109684758204262</v>
+        <v>0.03109684758204261</v>
       </c>
       <c r="T6" t="n">
         <v>0.03092018223617069</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03205667720659884</v>
+        <v>0.03205667720659883</v>
       </c>
       <c r="V6" t="n">
         <v>0.02963180858507521</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03133643666781063</v>
+        <v>0.03133643666781062</v>
       </c>
       <c r="X6" t="n">
         <v>0.03187770656973853</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03051923912085962</v>
+        <v>0.03051923912085956</v>
       </c>
       <c r="Z6" t="n">
         <v>0.0300061612253997</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03120144440116373</v>
+        <v>0.03120144440116372</v>
       </c>
       <c r="C7" t="n">
         <v>0.02953024257287382</v>
@@ -2755,7 +2755,7 @@
         <v>0.03101694157618048</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02984497934041002</v>
+        <v>0.02984497934041004</v>
       </c>
       <c r="F7" t="n">
         <v>0.03002973925103757</v>
@@ -2764,7 +2764,7 @@
         <v>0.03134107295317561</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0299439701047916</v>
+        <v>0.02994397010479161</v>
       </c>
       <c r="I7" t="n">
         <v>0.03067420358973892</v>
@@ -2773,10 +2773,10 @@
         <v>0.03143354658856411</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03283750699308748</v>
+        <v>0.03283750699308749</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03135399005537449</v>
+        <v>0.03135399005537443</v>
       </c>
       <c r="M7" t="n">
         <v>0.0366848694520361</v>
@@ -2791,7 +2791,7 @@
         <v>0.03142750272845008</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03013044752412289</v>
+        <v>0.03013044752412288</v>
       </c>
       <c r="R7" t="n">
         <v>0.02999729736675963</v>
@@ -2800,7 +2800,7 @@
         <v>0.03128336611343924</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03110670076756732</v>
+        <v>0.03110670076756731</v>
       </c>
       <c r="U7" t="n">
         <v>0.0322420709304115</v>
@@ -2812,10 +2812,10 @@
         <v>0.03144950507493999</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03078427138848201</v>
+        <v>0.03078427138848203</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03065186786510283</v>
+        <v>0.03065186786510282</v>
       </c>
       <c r="Z7" t="n">
         <v>0.03019267975679632</v>
@@ -2834,49 +2834,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03242577547537955</v>
+        <v>0.03242577547537956</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03242279867280356</v>
+        <v>0.03242279867280357</v>
       </c>
       <c r="D8" t="n">
         <v>0.03390949767611022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03184925482374834</v>
+        <v>0.03184925482374835</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03151396028727513</v>
+        <v>0.03151396028727514</v>
       </c>
       <c r="G8" t="n">
         <v>0.03457954637964848</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03283652620472135</v>
+        <v>0.03283652620472134</v>
       </c>
       <c r="I8" t="n">
         <v>0.03356675968966865</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03432610268849386</v>
+        <v>0.03432610268849387</v>
       </c>
       <c r="K8" t="n">
         <v>0.03573006309301723</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03424654615530418</v>
+        <v>0.03424654615530421</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0395774255519661</v>
+        <v>0.03957742555196612</v>
       </c>
       <c r="N8" t="n">
         <v>0.03288585463579331</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03289533802449576</v>
+        <v>0.03289533802449578</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03329529048620667</v>
+        <v>0.03329529048620668</v>
       </c>
       <c r="Q8" t="n">
         <v>0.03102693430546235</v>
@@ -2888,28 +2888,28 @@
         <v>0.03417592221336898</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03399925686749705</v>
+        <v>0.03399925686749704</v>
       </c>
       <c r="U8" t="n">
         <v>0.0343207386897843</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03225407760493521</v>
+        <v>0.03225407760493523</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03434238902867581</v>
+        <v>0.03434238902867583</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03183365430811307</v>
+        <v>0.03183365430811309</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03520177671616924</v>
+        <v>0.03520177671616925</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03138602269470713</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03447135566820028</v>
+        <v>0.03447135566820029</v>
       </c>
       <c r="AB8" t="n">
         <v>0.03771602243025384</v>
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03359008280986087</v>
+        <v>0.03359008280986088</v>
       </c>
       <c r="C9" t="n">
         <v>0.03296697772782702</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03445367673113367</v>
+        <v>0.03445367673113368</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03303981745277722</v>
+        <v>0.03303981745277724</v>
       </c>
       <c r="F9" t="n">
         <v>0.03105032635203219</v>
@@ -2943,52 +2943,52 @@
         <v>0.0333807052597448</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0341109387446921</v>
+        <v>0.03411093874469211</v>
       </c>
       <c r="J9" t="n">
         <v>0.03487028174351731</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03627424214804068</v>
+        <v>0.03627424214804069</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03479072521032765</v>
+        <v>0.03479072521032766</v>
       </c>
       <c r="M9" t="n">
         <v>0.04012160460698933</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03472318717376777</v>
+        <v>0.03472318717376779</v>
       </c>
       <c r="O9" t="n">
         <v>0.03472463762764579</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03528723979201657</v>
+        <v>0.03528723979201658</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03356718191379306</v>
+        <v>0.03356718191379307</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03343403252171282</v>
+        <v>0.03343403252171283</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03472010126839242</v>
+        <v>0.03472010126839244</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0345434359225205</v>
+        <v>0.03454343592252052</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03567993089294865</v>
+        <v>0.03567993089294866</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03446454048871529</v>
+        <v>0.0344645404887153</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03488624022989319</v>
+        <v>0.0348862402298932</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03422100654343522</v>
+        <v>0.03422100654343523</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03408860302005603</v>
@@ -2997,7 +2997,7 @@
         <v>0.0329975054702708</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03501553472322372</v>
+        <v>0.03501553472322374</v>
       </c>
       <c r="AB9" t="n">
         <v>0.03651760095140388</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007481092212630273</v>
+        <v>0.00748109221263025</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008224086087521513</v>
+        <v>0.008224086087521511</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007543235702440632</v>
+        <v>0.007543235702440611</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007411277708572486</v>
+        <v>0.007411277708572471</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007418878629181433</v>
+        <v>0.007418878629181415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007525318604194794</v>
+        <v>0.00752531860419478</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00738502065984421</v>
+        <v>0.007385020659844193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007536066997825767</v>
+        <v>0.007536066997825746</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007535671433113997</v>
+        <v>0.007535671433113976</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007575583103447054</v>
+        <v>0.00757558310344703</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007500573148253174</v>
+        <v>0.007500573148253164</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007923708481175993</v>
+        <v>0.007923708481175989</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007462459950291304</v>
+        <v>0.007462459950291283</v>
       </c>
       <c r="O2" t="n">
         <v>0.01103558447693143</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007537485802788436</v>
+        <v>0.007537485802788415</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007419293732054208</v>
+        <v>0.007419293732054185</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007385109738930047</v>
+        <v>0.007385109738930021</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007515223697315483</v>
+        <v>0.007515223697315456</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007488999687191114</v>
+        <v>0.007488999687191094</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009946127144837896</v>
+        <v>0.009946127144837873</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007424632332189878</v>
+        <v>0.007424632332189858</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009502292836053449</v>
+        <v>0.009502292836053439</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007533598811863835</v>
+        <v>0.007533598811863812</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007580219287009826</v>
+        <v>0.007580219287009803</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009126443204132029</v>
+        <v>0.009126443204132011</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00756237935874386</v>
+        <v>0.007562379358743844</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007667022315432993</v>
+        <v>0.00766702231543299</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007941643913136485</v>
+        <v>0.007985498151627064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008565287920587092</v>
+        <v>0.008581634259459146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008392955524302878</v>
+        <v>0.008453212154718117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007446203676463129</v>
+        <v>0.007472570506846499</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007503247577263916</v>
+        <v>0.007532045610530339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008255753460605149</v>
+        <v>0.008310693747550455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007262408134722213</v>
+        <v>0.00728259628937592</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008343167871000893</v>
+        <v>0.008401705969945904</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008334254627385474</v>
+        <v>0.008392241444117699</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00861385796203607</v>
+        <v>0.008682237737252265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008083903208968993</v>
+        <v>0.008132909938296346</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01110151588006763</v>
+        <v>0.01125822122233101</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007813886118031674</v>
+        <v>0.007853480557958379</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01369290260572013</v>
+        <v>0.01373151162893089</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008342080219746735</v>
+        <v>0.008399928073541889</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007504750908412329</v>
+        <v>0.007533470962059283</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007262479220377229</v>
+        <v>0.007282644817303699</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008184661330949389</v>
+        <v>0.008237198867764427</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008005593340023509</v>
+        <v>0.008052104273118683</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01226616358183896</v>
+        <v>0.01232187915133841</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007538639168532587</v>
+        <v>0.007568418253916446</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01148199462098837</v>
+        <v>0.01153534417051632</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008322824008811132</v>
+        <v>0.008380581838681185</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008652737612451823</v>
+        <v>0.008721997498838398</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01040394428701784</v>
+        <v>0.01043629970924606</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008526202469607579</v>
+        <v>0.008590910278642453</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009275338085448634</v>
+        <v>0.00936657041816108</v>
       </c>
     </row>
     <row r="4">
@@ -3351,7 +3351,7 @@
         <v>0.0304975588236481</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02900703257923104</v>
+        <v>0.02900703257923105</v>
       </c>
       <c r="F4" t="n">
         <v>0.02909288847410531</v>
@@ -3366,16 +3366,16 @@
         <v>0.03041658500725607</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03040849750940008</v>
+        <v>0.03040849750940007</v>
       </c>
       <c r="K4" t="n">
         <v>0.03086293759855515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03001566564835621</v>
+        <v>0.03001566564835623</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03476194221082977</v>
+        <v>0.03476194221082975</v>
       </c>
       <c r="N4" t="n">
         <v>0.02958515954443966</v>
@@ -3384,16 +3384,16 @@
         <v>0.02956035371592473</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03043261106199193</v>
+        <v>0.03043261106199192</v>
       </c>
       <c r="Q4" t="n">
         <v>0.02909757725201011</v>
       </c>
       <c r="R4" t="n">
-        <v>0.02871145332425888</v>
+        <v>0.02871145332425889</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03018115033960047</v>
+        <v>0.03018115033960048</v>
       </c>
       <c r="T4" t="n">
         <v>0.02988493808160509</v>
@@ -3414,7 +3414,7 @@
         <v>0.03085098916890276</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02927472419772465</v>
+        <v>0.02927472419772466</v>
       </c>
       <c r="AA4" t="n">
         <v>0.03071379522810998</v>
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05793178179688299</v>
+        <v>0.05793178179688305</v>
       </c>
       <c r="C5" t="n">
         <v>0.0378933128018438</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07438392791408423</v>
+        <v>0.07438392791408427</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04545056424681011</v>
+        <v>0.04545056424681009</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04841789483858335</v>
+        <v>0.04841789483858333</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06597107182235204</v>
+        <v>0.06597107182235182</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0420717744545851</v>
+        <v>0.04207177445458506</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07366471938871044</v>
+        <v>0.07366471938871047</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07042604551935745</v>
+        <v>0.07042604551935747</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07568340181995015</v>
+        <v>0.07568340181995016</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06349384034694619</v>
+        <v>0.06349384034694634</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1555913205537166</v>
+        <v>0.1555913205537167</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05691540669209519</v>
+        <v>0.0569154066920952</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05283297005590827</v>
+        <v>0.05283297005590822</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06813693343819001</v>
+        <v>0.06813693343818999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04774458935360801</v>
+        <v>0.04774458935360799</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0417969414189364</v>
+        <v>0.04179694141893638</v>
       </c>
       <c r="S5" t="n">
-        <v>0.06444960269866837</v>
+        <v>0.06444960269866831</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06340515039199907</v>
+        <v>0.06340515039199912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06771338250896265</v>
+        <v>0.06771338250896228</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04660410178555918</v>
+        <v>0.04660410178555912</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06738522713613616</v>
+        <v>0.06738522713613623</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07175775775447781</v>
+        <v>0.0717577577544776</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07961064053515413</v>
+        <v>0.07961064053515418</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04838394391763699</v>
+        <v>0.0483839439176371</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07645564246728143</v>
+        <v>0.07645564246728147</v>
       </c>
       <c r="AB5" t="n">
         <v>0.1041645559971451</v>
@@ -3548,16 +3548,16 @@
         <v>0.03271122469157819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03186395274137927</v>
+        <v>0.03186395274137929</v>
       </c>
       <c r="M6" t="n">
         <v>0.03542548789142302</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03025652522111839</v>
+        <v>0.03025652522111838</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03140738840010796</v>
+        <v>0.03140738840010797</v>
       </c>
       <c r="P6" t="n">
         <v>0.03228116071993829</v>
@@ -3572,31 +3572,31 @@
         <v>0.03202943743262354</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03054848376219839</v>
+        <v>0.0305484837621984</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03098270711013343</v>
+        <v>0.03098270711013341</v>
       </c>
       <c r="V6" t="n">
         <v>0.03098272832854127</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03205375960083967</v>
+        <v>0.03205375960083966</v>
       </c>
       <c r="X6" t="n">
         <v>0.03105225139198768</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03163255448248718</v>
+        <v>0.03163255448248716</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03112301129074771</v>
+        <v>0.03112301129074772</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03256208232113303</v>
+        <v>0.03256208232113304</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03254666347487275</v>
+        <v>0.03254666347487276</v>
       </c>
     </row>
     <row r="7">
@@ -3618,10 +3618,10 @@
         <v>0.02977679399726632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02986264989214059</v>
+        <v>0.0298626498921406</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03106493837472424</v>
+        <v>0.03106493837472425</v>
       </c>
       <c r="H7" t="n">
         <v>0.02948020855304128</v>
@@ -3660,31 +3660,31 @@
         <v>0.03095091175763575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03065469949964035</v>
+        <v>0.03065469949964036</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03108752753200405</v>
+        <v>0.03108752753200403</v>
       </c>
       <c r="V7" t="n">
         <v>0.02990420265355349</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03097670342848255</v>
+        <v>0.03097670342848256</v>
       </c>
       <c r="X7" t="n">
         <v>0.03115846712942966</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03168506684268185</v>
+        <v>0.03168506684268186</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03004448561575992</v>
+        <v>0.03004448561575994</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03148355664614525</v>
+        <v>0.03148355664614526</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03264426853164858</v>
+        <v>0.03264426853164859</v>
       </c>
     </row>
     <row r="8">
@@ -3697,7 +3697,7 @@
         <v>0.03168754043985508</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03196084526942957</v>
+        <v>0.03196084526942956</v>
       </c>
       <c r="D8" t="n">
         <v>0.03391339100788113</v>
@@ -3709,7 +3709,7 @@
         <v>0.03122221695959269</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0340270020686919</v>
+        <v>0.03402700206869189</v>
       </c>
       <c r="H8" t="n">
         <v>0.03212627931923903</v>
@@ -3721,19 +3721,19 @@
         <v>0.03382432969363312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03427876978278819</v>
+        <v>0.03427876978278818</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03343149783258928</v>
+        <v>0.03343149783258927</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03817777439506338</v>
+        <v>0.0381777743950634</v>
       </c>
       <c r="N8" t="n">
         <v>0.03181970555483961</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03211952742372912</v>
+        <v>0.03211952742372913</v>
       </c>
       <c r="P8" t="n">
         <v>0.0329122106770685</v>
@@ -3751,19 +3751,19 @@
         <v>0.03330077026583812</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03299020230124294</v>
+        <v>0.03299020230124295</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03213267293021321</v>
+        <v>0.0321326729302132</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03362307368670959</v>
+        <v>0.03362307368670957</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03212081278289178</v>
+        <v>0.03212081278289176</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03584463332411715</v>
+        <v>0.03584463332411716</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03113833768468146</v>
@@ -3772,7 +3772,7 @@
         <v>0.03412962741234302</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03688219203946477</v>
+        <v>0.03688219203946476</v>
       </c>
     </row>
     <row r="9">
@@ -3791,13 +3791,13 @@
         <v>0.03417713225204467</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03247730312462757</v>
+        <v>0.03247730312462758</v>
       </c>
       <c r="F9" t="n">
         <v>0.03068187395365026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03397474985567523</v>
+        <v>0.03397474985567522</v>
       </c>
       <c r="H9" t="n">
         <v>0.03239002056340259</v>
@@ -3812,13 +3812,13 @@
         <v>0.03454251102695171</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03369523907675278</v>
+        <v>0.0336952390767528</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03844151563922632</v>
+        <v>0.03844151563922633</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03326473297283624</v>
+        <v>0.03326473297283625</v>
       </c>
       <c r="O9" t="n">
         <v>0.03354046280116058</v>
@@ -3827,19 +3827,19 @@
         <v>0.03447808161140434</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03277715015099638</v>
+        <v>0.03277715015099637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03239102675265547</v>
+        <v>0.03239102675265548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03386072376799706</v>
+        <v>0.03386072376799705</v>
       </c>
       <c r="T9" t="n">
         <v>0.03356451151000166</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03399873485793672</v>
+        <v>0.03399873485793668</v>
       </c>
       <c r="V9" t="n">
         <v>0.03386052382566147</v>
@@ -3848,19 +3848,19 @@
         <v>0.03388651543884386</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03406827913979096</v>
+        <v>0.03406827913979097</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03459487885304315</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03240753393583812</v>
+        <v>0.03240753393583813</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03439336865650656</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03555408054200989</v>
+        <v>0.0355540805420099</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007442871364654496</v>
+        <v>0.007442871364654493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007992881077880048</v>
+        <v>0.007992881077880045</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007454710015921665</v>
+        <v>0.007454710015921656</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007367446389494959</v>
+        <v>0.007367446389494954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007416890822354561</v>
+        <v>0.007416890822354554</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00749051544636197</v>
+        <v>0.007490515446361964</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007367668761145768</v>
+        <v>0.00736766876114576</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00750607402495023</v>
+        <v>0.007506074024950224</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00750525748795452</v>
+        <v>0.007505257487954517</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007602955034147561</v>
+        <v>0.007602955034147554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007464613552584958</v>
+        <v>0.007464613552584954</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007806193532380243</v>
+        <v>0.007806193532380241</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00739966190821539</v>
+        <v>0.007399661908215386</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01099748239706915</v>
+        <v>0.01099748239706914</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00749795038711601</v>
+        <v>0.007497950387116004</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007398352201380033</v>
+        <v>0.007398352201380029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007401590444100448</v>
+        <v>0.00740159044410045</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007487153535406467</v>
+        <v>0.00748715353540646</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00748611236800868</v>
+        <v>0.007486112368008674</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009307240109582192</v>
+        <v>0.009307240109582188</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007450887950810065</v>
+        <v>0.007450887950810061</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00889475689272751</v>
+        <v>0.008894756892727496</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007536035361137736</v>
+        <v>0.007536035361137732</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007687650871134871</v>
+        <v>0.007687650871134867</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009088541692710351</v>
+        <v>0.009088541692710348</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007565414387709819</v>
+        <v>0.007565414387709812</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007623334722469011</v>
+        <v>0.007623334722469006</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007776702308175515</v>
+        <v>0.007815082546947509</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008175491834692296</v>
+        <v>0.008190582982974828</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007866363878466748</v>
+        <v>0.007908283517163285</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007241096012581421</v>
+        <v>0.007260541048372143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007597615377276057</v>
+        <v>0.00763006862607963</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008114573241440709</v>
+        <v>0.008164891366781175</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007247246474768858</v>
+        <v>0.007267168317801213</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008236061627784943</v>
+        <v>0.008291119576786759</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008224145418745461</v>
+        <v>0.008278613490685911</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008916849696444067</v>
+        <v>0.008996307926832162</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00793393336086797</v>
+        <v>0.007977999250840999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01036599316217175</v>
+        <v>0.01049712670638987</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007474014727826169</v>
+        <v>0.007501855956414389</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01361370461209229</v>
+        <v>0.01365068400210411</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008167096112824066</v>
+        <v>0.008219153125771046</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007463175484389881</v>
+        <v>0.007490724260244856</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007489825414846127</v>
+        <v>0.007518351382194761</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008092473983327275</v>
+        <v>0.008142065776434849</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008094041213886207</v>
+        <v>0.008143964088037468</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01121869642688095</v>
+        <v>0.01127397299330375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007832417432241067</v>
+        <v>0.007872860966997785</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01011730497784809</v>
+        <v>0.010153156332381</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008446443255359268</v>
+        <v>0.008508958525761952</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009530861288186194</v>
+        <v>0.009631360252241405</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01027900173579279</v>
+        <v>0.01030767973685269</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008657148381475865</v>
+        <v>0.008726738257655955</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009069769710583991</v>
+        <v>0.00915407406670153</v>
       </c>
     </row>
     <row r="4">
@@ -4202,52 +4202,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02956135878390838</v>
+        <v>0.02956135878390837</v>
       </c>
       <c r="C4" t="n">
         <v>0.02850227808351988</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02969508179601961</v>
+        <v>0.02969508179601959</v>
       </c>
       <c r="E4" t="n">
         <v>0.02870939899227867</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02926789660699074</v>
+        <v>0.02926789660699073</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0300995206041548</v>
+        <v>0.03009952060415479</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02871191078237049</v>
+        <v>0.02871191078237048</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0302752619066089</v>
+        <v>0.03027526190660889</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03026271036785023</v>
+        <v>0.03026271036785022</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03136957747295886</v>
+        <v>0.03136957747295885</v>
       </c>
       <c r="L4" t="n">
         <v>0.02980694679848355</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03364200235167233</v>
+        <v>0.03364200235167234</v>
       </c>
       <c r="N4" t="n">
         <v>0.02907328809609673</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02949968020661994</v>
+        <v>0.02949968020661993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03018350168021333</v>
+        <v>0.03018350168021332</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02905849435489635</v>
+        <v>0.02905849435489634</v>
       </c>
       <c r="R4" t="n">
         <v>0.02909507179608883</v>
@@ -4256,13 +4256,13 @@
         <v>0.03006154627335687</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0300497858086382</v>
+        <v>0.03004978580863819</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03026529266210697</v>
+        <v>0.03026529266210695</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02963045688007012</v>
+        <v>0.02963045688007011</v>
       </c>
       <c r="W4" t="n">
         <v>0.02943580504785048</v>
@@ -4271,10 +4271,10 @@
         <v>0.03061368898174234</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.03227903125661983</v>
+        <v>0.03227903125661982</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02912182111148045</v>
+        <v>0.02912182111148044</v>
       </c>
       <c r="AA4" t="n">
         <v>0.03094553860189397</v>
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05298552436115465</v>
+        <v>0.05298552436115466</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03675010563135805</v>
+        <v>0.03675010563135803</v>
       </c>
       <c r="D5" t="n">
         <v>0.05802909422149718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0393192727907552</v>
+        <v>0.03931927279075521</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05107940764866575</v>
+        <v>0.0510794076486658</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06138068018514201</v>
+        <v>0.06138068018514196</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04172855647337101</v>
+        <v>0.04172855647337104</v>
       </c>
       <c r="I5" t="n">
         <v>0.06990234841168921</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06658065956518375</v>
+        <v>0.06658065956518376</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08373465140924578</v>
+        <v>0.08373465140924566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05839460987786836</v>
+        <v>0.05839460987786837</v>
       </c>
       <c r="M5" t="n">
         <v>0.129756770314089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04730731015945097</v>
+        <v>0.04730731015945094</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05159625405982929</v>
+        <v>0.05159625405982927</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06258583482015484</v>
+        <v>0.06258583482015506</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04627257062139724</v>
+        <v>0.04627257062139728</v>
       </c>
       <c r="R5" t="n">
         <v>0.04875320515066758</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0616910088278199</v>
+        <v>0.06169100882781988</v>
       </c>
       <c r="T5" t="n">
-        <v>0.06614604006180136</v>
+        <v>0.06614604006180129</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0659767757102432</v>
+        <v>0.06597677571024313</v>
       </c>
       <c r="V5" t="n">
-        <v>0.05378845965408751</v>
+        <v>0.05378845965408746</v>
       </c>
       <c r="W5" t="n">
         <v>0.05334724273366663</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07409808184696859</v>
+        <v>0.07409808184696862</v>
       </c>
       <c r="Y5" t="n">
         <v>0.1055954178856138</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04485349439444132</v>
+        <v>0.04485349439444131</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.08049885470723304</v>
+        <v>0.0804988547072331</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.09700385246230452</v>
+        <v>0.09700385246230454</v>
       </c>
     </row>
     <row r="6">
@@ -4381,43 +4381,43 @@
         <v>0.03024438879428695</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02918530809389847</v>
+        <v>0.02918530809389846</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03155525101198633</v>
+        <v>0.03155525101198631</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03056956820824539</v>
+        <v>0.03056956820824538</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02995092661736931</v>
+        <v>0.0299509266173693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03078255061453336</v>
+        <v>0.03078255061453335</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03057207999833721</v>
+        <v>0.0305720799983372</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03095829191698746</v>
+        <v>0.03095829191698745</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03212287958381695</v>
+        <v>0.03212287958381694</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03322974668892557</v>
+        <v>0.03322974668892556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03048997680886214</v>
+        <v>0.03048997680886213</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0343250323620509</v>
+        <v>0.03432503236205089</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02976915172245526</v>
+        <v>0.02976915172245533</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03038543629827074</v>
+        <v>0.03038543629827078</v>
       </c>
       <c r="P6" t="n">
         <v>0.03204678621191787</v>
@@ -4426,37 +4426,37 @@
         <v>0.03091866357086306</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03095524101205556</v>
+        <v>0.03095524101205554</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03074457628373544</v>
+        <v>0.03074457628373543</v>
       </c>
       <c r="T6" t="n">
         <v>0.03190995502460491</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03217268653519442</v>
+        <v>0.03217268653519441</v>
       </c>
       <c r="V6" t="n">
         <v>0.03031348689044868</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03018910577477275</v>
+        <v>0.03018910577477274</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03129671899212092</v>
+        <v>0.03129671899212091</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03309168413951877</v>
+        <v>0.0330916841395188</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02980485112185902</v>
+        <v>0.02980485112185901</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03280570781786069</v>
+        <v>0.03280570781786068</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03227853219121331</v>
+        <v>0.03227853219121329</v>
       </c>
     </row>
     <row r="7">
@@ -4472,7 +4472,7 @@
         <v>0.02926093067079354</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03045373438329326</v>
+        <v>0.03045373438329325</v>
       </c>
       <c r="E7" t="n">
         <v>0.02946805157955232</v>
@@ -4481,31 +4481,31 @@
         <v>0.0300265491942644</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03085817319142846</v>
+        <v>0.03085817319142845</v>
       </c>
       <c r="H7" t="n">
         <v>0.02947056336964414</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03103391449388255</v>
+        <v>0.03103391449388254</v>
       </c>
       <c r="J7" t="n">
         <v>0.03102136295512389</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03212823006023251</v>
+        <v>0.0321282300602325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0305655993857572</v>
+        <v>0.03056559938575719</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03440065493894598</v>
+        <v>0.03440065493894599</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02983194068337039</v>
+        <v>0.02983194068337038</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03025821499116957</v>
+        <v>0.03025821499116955</v>
       </c>
       <c r="P7" t="n">
         <v>0.03094203646476294</v>
@@ -4517,34 +4517,34 @@
         <v>0.02985372438336248</v>
       </c>
       <c r="S7" t="n">
-        <v>0.03082019886063052</v>
+        <v>0.03082019886063051</v>
       </c>
       <c r="T7" t="n">
         <v>0.03080843839591186</v>
       </c>
       <c r="U7" t="n">
-        <v>0.03106979765395018</v>
+        <v>0.03106979765395017</v>
       </c>
       <c r="V7" t="n">
-        <v>0.03038910946734377</v>
+        <v>0.03038910946734376</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03019445763512415</v>
+        <v>0.03019445763512414</v>
       </c>
       <c r="X7" t="n">
-        <v>0.031372341569016</v>
+        <v>0.03137234156901601</v>
       </c>
       <c r="Y7" t="n">
         <v>0.03308490850101421</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0298804736987541</v>
+        <v>0.02988047369875409</v>
       </c>
       <c r="AA7" t="n">
         <v>0.03170419118916763</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03233824019181894</v>
+        <v>0.03233824019181893</v>
       </c>
     </row>
     <row r="8">
@@ -4554,13 +4554,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03142793772478503</v>
+        <v>0.03142793772478502</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03187353311878951</v>
+        <v>0.03187353311878949</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03306633683128923</v>
+        <v>0.03306633683128921</v>
       </c>
       <c r="E8" t="n">
         <v>0.03127945839248999</v>
@@ -4569,13 +4569,13 @@
         <v>0.03136888649782883</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03378278002963693</v>
+        <v>0.03378278002963692</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03208316581764009</v>
+        <v>0.0320831658176401</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03364651694187851</v>
+        <v>0.0336465169418785</v>
       </c>
       <c r="J8" t="n">
         <v>0.03363396540311984</v>
@@ -4584,40 +4584,40 @@
         <v>0.03474083250822846</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03317820183375318</v>
+        <v>0.03317820183375316</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03701325738694285</v>
+        <v>0.03701325738694284</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0312781674313343</v>
+        <v>0.03127816743133428</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03202508971159963</v>
+        <v>0.03202508971159961</v>
       </c>
       <c r="P8" t="n">
         <v>0.03263034149550485</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03062937010071877</v>
+        <v>0.03062937010071876</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03246632683135846</v>
+        <v>0.03246632683135844</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0334328013086265</v>
+        <v>0.03343280130862648</v>
       </c>
       <c r="T8" t="n">
         <v>0.03342104084390782</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03294838786757502</v>
+        <v>0.03294838786757501</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03258938897820458</v>
+        <v>0.03258938897820457</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0328073557948946</v>
+        <v>0.03280735579489459</v>
       </c>
       <c r="X8" t="n">
         <v>0.0323224712813359</v>
@@ -4626,13 +4626,13 @@
         <v>0.03719191304467904</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03096044992141643</v>
+        <v>0.03096044992141642</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0343167936371636</v>
+        <v>0.03431679363716359</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03652260263920223</v>
+        <v>0.03652260263920221</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03214205419631892</v>
+        <v>0.03214205419631893</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03193538206462079</v>
+        <v>0.03193538206462078</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03312818577712052</v>
+        <v>0.03312818577712049</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03194577023687616</v>
+        <v>0.03194577023687614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03073596672870857</v>
+        <v>0.03073596672870856</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03353262417475231</v>
+        <v>0.0335326241747523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03214501476347139</v>
+        <v>0.03214501476347138</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03370836588770978</v>
+        <v>0.03370836588770977</v>
       </c>
       <c r="J9" t="n">
         <v>0.03369581434895112</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03480268145405976</v>
+        <v>0.03480268145405974</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03324005077958445</v>
+        <v>0.03324005077958444</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03707510633277323</v>
+        <v>0.03707510633277322</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03250639207719763</v>
+        <v>0.03250639207719762</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03321527072470754</v>
+        <v>0.03321527072470753</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03396052826272012</v>
+        <v>0.0339605282627201</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03249159792549386</v>
+        <v>0.03249159792549385</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03252817577718972</v>
+        <v>0.03252817577718971</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03349465025445777</v>
+        <v>0.03349465025445775</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03348288978973912</v>
+        <v>0.0334828897897391</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0337456213003286</v>
+        <v>0.03374562130032858</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03404722029221727</v>
+        <v>0.03404722029221726</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03286890902895139</v>
+        <v>0.03286890902895138</v>
       </c>
       <c r="X9" t="n">
         <v>0.03404679296284324</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03575935989484149</v>
+        <v>0.03575935989484146</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03204099836178213</v>
+        <v>0.03204099836178211</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03437864258299489</v>
+        <v>0.03437864258299488</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03501269158564617</v>
+        <v>0.03501269158564616</v>
       </c>
     </row>
   </sheetData>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0071784511201667</v>
+        <v>0.007178451120166702</v>
       </c>
       <c r="C2" t="n">
         <v>0.008000868983977236</v>
@@ -4895,10 +4895,10 @@
         <v>0.007238644906813452</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007192937016543089</v>
+        <v>0.00719293701654309</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007178174902288868</v>
+        <v>0.007178174902288866</v>
       </c>
       <c r="G2" t="n">
         <v>0.007202220021915929</v>
@@ -4907,7 +4907,7 @@
         <v>0.007227825385124946</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007223583300103822</v>
+        <v>0.007223583300103823</v>
       </c>
       <c r="J2" t="n">
         <v>0.007225065425818251</v>
@@ -4916,16 +4916,16 @@
         <v>0.007299652270728789</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007276972980106307</v>
+        <v>0.007276972980106308</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007366907114946731</v>
+        <v>0.007366907114946734</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007269945098585967</v>
+        <v>0.007269945098585969</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01066767992702993</v>
+        <v>0.01066767992702992</v>
       </c>
       <c r="P2" t="n">
         <v>0.007237974746154726</v>
@@ -4937,34 +4937,34 @@
         <v>0.007236039295361102</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007229327334262719</v>
+        <v>0.007229327334262721</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007199750769158766</v>
+        <v>0.007199750769158767</v>
       </c>
       <c r="U2" t="n">
         <v>0.009611648001160369</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007175084167715041</v>
+        <v>0.007175084167715038</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009191375664903609</v>
+        <v>0.009191375664903613</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007250079284798963</v>
+        <v>0.007250079284798965</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007177851703474326</v>
+        <v>0.007177851703474328</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008902494654453388</v>
+        <v>0.008902494654453386</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00726235776920311</v>
+        <v>0.007262357769203111</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007237292090991084</v>
+        <v>0.007237292090991085</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007001101701955016</v>
+        <v>0.007017014504927188</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008193171594487382</v>
+        <v>0.008201513281893339</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007433939157646334</v>
+        <v>0.00746532931485148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007104963674689999</v>
+        <v>0.00712443094048902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007001517628985391</v>
+        <v>0.007017612846822254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007168920871638086</v>
+        <v>0.007190786670179984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007358619030530995</v>
+        <v>0.007387431393224672</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00732678974514876</v>
+        <v>0.007354400027191276</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007333046284884489</v>
+        <v>0.007360801908513678</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007864491295849863</v>
+        <v>0.007911312380129432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007699569221203736</v>
+        <v>0.007740348133332815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008346223939591635</v>
+        <v>0.0084104884627265</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007655228995283331</v>
+        <v>0.007694417140093447</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01283562311427362</v>
+        <v>0.012854977576978</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007424523828276988</v>
+        <v>0.007455265549843465</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007297865667257068</v>
+        <v>0.007324437631496241</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007417030798193923</v>
+        <v>0.007447866404802867</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007359625614398037</v>
+        <v>0.007388336208103336</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00715498605748632</v>
+        <v>0.007176510841183968</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01141786618158827</v>
+        <v>0.01145220935761353</v>
       </c>
       <c r="V3" t="n">
-        <v>0.006977197632162464</v>
+        <v>0.006992286304193693</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01083177652305529</v>
+        <v>0.01087104383770174</v>
       </c>
       <c r="X3" t="n">
-        <v>0.007515061292522411</v>
+        <v>0.007549325618454714</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.006998302579527314</v>
+        <v>0.007014182107129482</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01005996076175971</v>
+        <v>0.01008569842754931</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007601565545377999</v>
+        <v>0.007638750348806742</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007428317260742231</v>
+        <v>0.007459493134656154</v>
       </c>
     </row>
     <row r="4">
@@ -5062,19 +5062,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02843720186439916</v>
+        <v>0.02843720186439917</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02809213954545188</v>
+        <v>0.02809213954545189</v>
       </c>
       <c r="D4" t="n">
         <v>0.02911711837508416</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02860082672781198</v>
+        <v>0.02860082672781199</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02843408185640246</v>
+        <v>0.02843408185640245</v>
       </c>
       <c r="G4" t="n">
         <v>0.02870568254389158</v>
@@ -5086,13 +5086,13 @@
         <v>0.02894699059861744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02896023631247511</v>
+        <v>0.02896023631247514</v>
       </c>
       <c r="K4" t="n">
         <v>0.02980622461528169</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0295500515947117</v>
+        <v>0.02955005159471171</v>
       </c>
       <c r="M4" t="n">
         <v>0.03056917358881606</v>
@@ -5107,13 +5107,13 @@
         <v>0.02910954860215468</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0289054070807982</v>
+        <v>0.02890540708079819</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0290876867950893</v>
+        <v>0.02908768679508931</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02901187210682843</v>
+        <v>0.02901187210682844</v>
       </c>
       <c r="T4" t="n">
         <v>0.02867779119808718</v>
@@ -5122,10 +5122,10 @@
         <v>0.02917871315183604</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02837659149044635</v>
+        <v>0.02837659149044643</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02947952313566451</v>
+        <v>0.0294795231356645</v>
       </c>
       <c r="X4" t="n">
         <v>0.0292462749345042</v>
@@ -5156,79 +5156,79 @@
         <v>0.0322006182786746</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05235881995091635</v>
+        <v>0.05235881995091628</v>
       </c>
       <c r="E5" t="n">
         <v>0.04106407592526071</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03897458711413755</v>
+        <v>0.03897458711413752</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04176971230447381</v>
+        <v>0.04176971230447392</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05110437846916548</v>
+        <v>0.05110437846916547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04933450302697202</v>
+        <v>0.049334503026972</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04724415749554852</v>
+        <v>0.04724415749554857</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06268521949742152</v>
+        <v>0.06268521949742156</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05614033991455943</v>
+        <v>0.05614033991455947</v>
       </c>
       <c r="M5" t="n">
-        <v>0.07708447328312724</v>
+        <v>0.07708447328312723</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05787512847661368</v>
+        <v>0.05787512847661376</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04011227006275412</v>
+        <v>0.04011227006275409</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04963939432962058</v>
+        <v>0.04963939432962062</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04707473007794938</v>
+        <v>0.04707473007794937</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05274112622497849</v>
+        <v>0.05274112622497855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04602330265129592</v>
+        <v>0.04602330265129593</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04329363838720778</v>
+        <v>0.04329363838720781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05288630061153392</v>
+        <v>0.05288630061153386</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03703429863562377</v>
+        <v>0.0370342986356238</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05836165523446214</v>
+        <v>0.05836165523446221</v>
       </c>
       <c r="X5" t="n">
-        <v>0.05453083740785649</v>
+        <v>0.05453083740785653</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03840037206471662</v>
+        <v>0.0384003720647166</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04494201930434867</v>
+        <v>0.04494201930434866</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0565259105610334</v>
+        <v>0.05652591056103339</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.05276324342278438</v>
+        <v>0.05276324342278439</v>
       </c>
     </row>
     <row r="6">
@@ -5241,52 +5241,52 @@
         <v>0.02905589000493245</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02871082768598518</v>
+        <v>0.02871082768598517</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03087400951775207</v>
+        <v>0.03087400951775209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03035771787047991</v>
+        <v>0.03035771787047992</v>
       </c>
       <c r="F6" t="n">
         <v>0.02905276999693574</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02932437068442486</v>
+        <v>0.02932437068442487</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03075179804305438</v>
+        <v>0.03075179804305442</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03070388174128535</v>
+        <v>0.03070388174128537</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02957892445300839</v>
+        <v>0.02957892445300842</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03156311575794965</v>
+        <v>0.03156311575794963</v>
       </c>
       <c r="L6" t="n">
-        <v>0.030168739735245</v>
+        <v>0.03016873973524501</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03232606473148394</v>
+        <v>0.03232606473148399</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03009218375014108</v>
+        <v>0.03009218375014111</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03036514993603241</v>
+        <v>0.03036514993603247</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03088318859136829</v>
+        <v>0.0308831885913683</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03066229822346608</v>
+        <v>0.03066229822346613</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03084457793775722</v>
+        <v>0.03084457793775724</v>
       </c>
       <c r="S6" t="n">
         <v>0.02963056024736172</v>
@@ -5298,22 +5298,22 @@
         <v>0.02988119270917143</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03013348263311422</v>
+        <v>0.03013348263311436</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03125187247943794</v>
+        <v>0.03125187247943792</v>
       </c>
       <c r="X6" t="n">
         <v>0.02986496307503748</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02909796288739825</v>
+        <v>0.02909796288739826</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.02949864214330451</v>
+        <v>0.0294986421433045</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03114185720689883</v>
+        <v>0.03114185720689886</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02972689580374914</v>
@@ -5332,7 +5332,7 @@
         <v>0.02883079500783139</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02985577383746366</v>
+        <v>0.02985577383746365</v>
       </c>
       <c r="E7" t="n">
         <v>0.02933948219019148</v>
@@ -5350,7 +5350,7 @@
         <v>0.02968564606099694</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02969889177485462</v>
+        <v>0.02969889177485464</v>
       </c>
       <c r="K7" t="n">
         <v>0.03054488007766119</v>
@@ -5374,7 +5374,7 @@
         <v>0.0296440625431777</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0298263422574688</v>
+        <v>0.02982634225746881</v>
       </c>
       <c r="S7" t="n">
         <v>0.02975052756920794</v>
@@ -5417,16 +5417,16 @@
         <v>0.03030422812125098</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03147431383419299</v>
+        <v>0.031474313834193</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03249929266382526</v>
+        <v>0.03249929266382528</v>
       </c>
       <c r="E8" t="n">
         <v>0.03117622938367618</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03053715046869096</v>
+        <v>0.03053715046869097</v>
       </c>
       <c r="G8" t="n">
         <v>0.03240203264730458</v>
@@ -5438,58 +5438,58 @@
         <v>0.03232916488735854</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03234241060121622</v>
+        <v>0.03234241060121625</v>
       </c>
       <c r="K8" t="n">
         <v>0.0331883989040228</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03293222588345281</v>
+        <v>0.03293222588345283</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03395134787755724</v>
+        <v>0.03395134787755726</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03167834952519114</v>
+        <v>0.03167834952519116</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03112390031164305</v>
+        <v>0.03112390031164306</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03156087411460369</v>
+        <v>0.0315608741146037</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0304746721678606</v>
+        <v>0.03047467216786061</v>
       </c>
       <c r="R8" t="n">
         <v>0.0324698610838304</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03239404639556954</v>
+        <v>0.03239404639556956</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03205996548682828</v>
+        <v>0.0320599654868283</v>
       </c>
       <c r="U8" t="n">
         <v>0.0319041585497734</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03134355356199761</v>
+        <v>0.03134355356199769</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03286199519423557</v>
+        <v>0.03286199519423558</v>
       </c>
       <c r="X8" t="n">
         <v>0.03095440634922996</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03331737747388906</v>
+        <v>0.03331737747388908</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03071883560706419</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03276714035297202</v>
+        <v>0.03276714035297203</v>
       </c>
       <c r="AB8" t="n">
         <v>0.03407218185021511</v>
@@ -5526,13 +5526,13 @@
         <v>0.03255659245906173</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0325698381729194</v>
+        <v>0.03256983817291943</v>
       </c>
       <c r="K9" t="n">
         <v>0.03341582647572599</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03315965345515599</v>
+        <v>0.033159653455156</v>
       </c>
       <c r="M9" t="n">
         <v>0.03417877544926035</v>
@@ -5562,13 +5562,13 @@
         <v>0.03287210642908243</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03301798642250937</v>
+        <v>0.03301798642250942</v>
       </c>
       <c r="W9" t="n">
         <v>0.0330891249961088</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0328558767949485</v>
+        <v>0.03285587679494849</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03204003303755772</v>
@@ -5746,16 +5746,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007149997346538095</v>
+        <v>0.007149997346538093</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0080101578941733</v>
+        <v>0.008010157894173302</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007146510392011347</v>
+        <v>0.007146510392011345</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007186452779529296</v>
+        <v>0.007186452779529298</v>
       </c>
       <c r="F2" t="n">
         <v>0.007184469533504005</v>
@@ -5764,28 +5764,28 @@
         <v>0.007168275198250897</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007174193236894461</v>
+        <v>0.007174193236894459</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007173135982381787</v>
+        <v>0.007173135982381783</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007177435323390174</v>
+        <v>0.007177435323390171</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007156507106177729</v>
+        <v>0.007156507106177727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007186940659828537</v>
+        <v>0.007186940659828532</v>
       </c>
       <c r="M2" t="n">
         <v>0.007138428685135878</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007185720422487028</v>
+        <v>0.007185720422487025</v>
       </c>
       <c r="O2" t="n">
-        <v>0.010654387862262</v>
+        <v>0.01065438786226199</v>
       </c>
       <c r="P2" t="n">
         <v>0.007181418373780812</v>
@@ -5794,37 +5794,37 @@
         <v>0.007139307823900911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007244001430910061</v>
+        <v>0.007244001430910059</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007182590205136233</v>
+        <v>0.007182590205136232</v>
       </c>
       <c r="T2" t="n">
         <v>0.007151169380174746</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009513011562436623</v>
+        <v>0.00951301156243662</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00717713192513294</v>
+        <v>0.007177131925132939</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009184745629210943</v>
+        <v>0.00918474562921094</v>
       </c>
       <c r="X2" t="n">
         <v>0.007326841502954012</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007174828140198125</v>
+        <v>0.007174828140198123</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008881200337656785</v>
+        <v>0.008881200337656787</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007213408412267322</v>
+        <v>0.007213408412267324</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007120646412016193</v>
+        <v>0.007120646412016194</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006927702858997565</v>
+        <v>0.006941961520416757</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008349208579062076</v>
+        <v>0.008363635342645255</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006904055852803086</v>
+        <v>0.006917590037095665</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007187776089009062</v>
+        <v>0.007211106723863879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007175339514707845</v>
+        <v>0.007198607175522684</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007056199192721681</v>
+        <v>0.007075036079624389</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007103631813101248</v>
+        <v>0.007124308441960684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007094791706700666</v>
+        <v>0.007115117777018134</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007122557840944591</v>
+        <v>0.00714377966958223</v>
       </c>
       <c r="K3" t="n">
-        <v>0.006974579896095469</v>
+        <v>0.00699063550015337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00718751568173111</v>
+        <v>0.007211134482673546</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006861762624782245</v>
+        <v>0.006873920914210652</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007183059950569177</v>
+        <v>0.007206468832337398</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01292725894296557</v>
+        <v>0.01295139785537127</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007150756040199914</v>
+        <v>0.007172834977453224</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006851827565799319</v>
+        <v>0.00686351300358846</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007602426917898451</v>
+        <v>0.007640853620217086</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007157312831196366</v>
+        <v>0.007179777691662178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006937267976569968</v>
+        <v>0.00695199208905826</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0107429813060047</v>
+        <v>0.01075335215850795</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007119647853570995</v>
+        <v>0.007140718212436733</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01079758966284551</v>
+        <v>0.01083548044761032</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008188303698959306</v>
+        <v>0.008247577696922633</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007106142211358173</v>
+        <v>0.007126768075006796</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01004835585333777</v>
+        <v>0.01007475625119604</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007381430046038648</v>
+        <v>0.007411773703218341</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006730612167296</v>
+        <v>0.006738024157407862</v>
       </c>
     </row>
     <row r="4">
@@ -5922,13 +5922,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0283092769214785</v>
+        <v>0.02830927692147851</v>
       </c>
       <c r="C4" t="n">
         <v>0.02831013226162609</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02826989016602061</v>
+        <v>0.0282698901660206</v>
       </c>
       <c r="E4" t="n">
         <v>0.0287210578074419</v>
@@ -5937,7 +5937,7 @@
         <v>0.02869865613124796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02851573366480181</v>
+        <v>0.02851573366480182</v>
       </c>
       <c r="H4" t="n">
         <v>0.02858258063371311</v>
@@ -5958,16 +5958,16 @@
         <v>0.02820730642498855</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02871278549774863</v>
+        <v>0.02871278549774862</v>
       </c>
       <c r="O4" t="n">
         <v>0.02875662922670924</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0286641918785717</v>
+        <v>0.02866419187857169</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02818853384586816</v>
+        <v>0.02818853384586817</v>
       </c>
       <c r="R4" t="n">
         <v>0.02937109629847523</v>
@@ -5994,7 +5994,7 @@
         <v>0.02853534540384576</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02885668108309012</v>
+        <v>0.02885668108309013</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02902553407942158</v>
@@ -6010,55 +6010,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03567777744285995</v>
+        <v>0.03567777744285998</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03628320983814183</v>
+        <v>0.03628320983814187</v>
       </c>
       <c r="D5" t="n">
         <v>0.03562352934641679</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04290327242339414</v>
+        <v>0.04290327242339412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04339734665104892</v>
+        <v>0.04339734665104893</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03831689923632879</v>
+        <v>0.03831689923632884</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04219152233452186</v>
+        <v>0.0421915223345219</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04130950058792529</v>
+        <v>0.04130950058792533</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04065286288301245</v>
+        <v>0.04065286288301247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03719416038273549</v>
+        <v>0.0371941603827355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04106131929914637</v>
+        <v>0.04106131929914638</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03440857233834133</v>
+        <v>0.03440857233834132</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04302163601102808</v>
+        <v>0.04302163601102813</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04236307757340517</v>
+        <v>0.0423630775734052</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04133303151029904</v>
+        <v>0.04133303151029907</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03375800636445991</v>
+        <v>0.03375800636445992</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05643339301726888</v>
+        <v>0.05643339301726892</v>
       </c>
       <c r="S5" t="n">
         <v>0.04063089951779773</v>
@@ -6070,13 +6070,13 @@
         <v>0.03280961389217637</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04018936849714051</v>
+        <v>0.04018936849714054</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05357100351038561</v>
+        <v>0.05357100351038559</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07020698731519273</v>
+        <v>0.07020698731519275</v>
       </c>
       <c r="Y5" t="n">
         <v>0.04127106250070525</v>
@@ -6085,7 +6085,7 @@
         <v>0.04385847585086988</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04894671903547199</v>
+        <v>0.04894671903547197</v>
       </c>
       <c r="AB5" t="n">
         <v>0.03101181135166116</v>
@@ -6119,7 +6119,7 @@
         <v>0.03025761791687538</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03024567574079369</v>
+        <v>0.03024567574079368</v>
       </c>
       <c r="J6" t="n">
         <v>0.03029111040272426</v>
@@ -6137,16 +6137,16 @@
         <v>0.02934311676349852</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03043665496915157</v>
+        <v>0.03043665496915156</v>
       </c>
       <c r="P6" t="n">
         <v>0.02924097538316257</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02986357112903043</v>
+        <v>0.02986357112903044</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0299979115650484</v>
+        <v>0.02999791156504839</v>
       </c>
       <c r="S6" t="n">
         <v>0.03035246553596247</v>
@@ -6173,7 +6173,7 @@
         <v>0.02948349634966329</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03070057136258384</v>
+        <v>0.03070057136258385</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02861318425977528</v>
@@ -6186,7 +6186,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02897214292401181</v>
+        <v>0.02897214292401182</v>
       </c>
       <c r="C7" t="n">
         <v>0.0289729982641594</v>
@@ -6198,10 +6198,10 @@
         <v>0.02938392380997521</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02936152213378128</v>
+        <v>0.02936152213378129</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02917859966733512</v>
+        <v>0.02917859966733513</v>
       </c>
       <c r="H7" t="n">
         <v>0.02924544663624643</v>
@@ -6231,7 +6231,7 @@
         <v>0.02932694191658575</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02885139984840147</v>
+        <v>0.02885139984840148</v>
       </c>
       <c r="R7" t="n">
         <v>0.03003396230100855</v>
@@ -6249,7 +6249,7 @@
         <v>0.02925851014451035</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03002761268009513</v>
+        <v>0.03002761268009514</v>
       </c>
       <c r="X7" t="n">
         <v>0.03096967902306079</v>
@@ -6274,13 +6274,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0299941268525222</v>
+        <v>0.02999412685252221</v>
       </c>
       <c r="C8" t="n">
         <v>0.03136528659618967</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0313250445005842</v>
+        <v>0.03132504450058419</v>
       </c>
       <c r="E8" t="n">
         <v>0.03104656546861145</v>
@@ -6295,10 +6295,10 @@
         <v>0.0316377349682767</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03162579279219501</v>
+        <v>0.031625792792195</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03167122745412557</v>
+        <v>0.03167122745412558</v>
       </c>
       <c r="K8" t="n">
         <v>0.03143796198580915</v>
@@ -6307,19 +6307,19 @@
         <v>0.03178172297442143</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03126246075955195</v>
+        <v>0.03126246075955196</v>
       </c>
       <c r="N8" t="n">
         <v>0.03070572467261188</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03104147435044305</v>
+        <v>0.03104147435044306</v>
       </c>
       <c r="P8" t="n">
         <v>0.0308774838008086</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0296040876859862</v>
+        <v>0.02960408768598621</v>
       </c>
       <c r="R8" t="n">
         <v>0.03242625063303882</v>
@@ -6340,7 +6340,7 @@
         <v>0.03242017031605565</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0318479579819743</v>
+        <v>0.03184795798197429</v>
       </c>
       <c r="Y8" t="n">
         <v>0.03300581873074764</v>
@@ -6352,7 +6352,7 @@
         <v>0.03208068841398517</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.03248408704883737</v>
+        <v>0.03248408704883736</v>
       </c>
     </row>
     <row r="9">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03064759585507405</v>
+        <v>0.03064759585507406</v>
       </c>
       <c r="C9" t="n">
         <v>0.03142560055255252</v>
@@ -6380,7 +6380,7 @@
         <v>0.03163120263470192</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03169804892463953</v>
+        <v>0.03169804892463954</v>
       </c>
       <c r="I9" t="n">
         <v>0.03168610674855785</v>
@@ -6398,10 +6398,10 @@
         <v>0.03132277471591498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03182825378867505</v>
+        <v>0.03182825378867506</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03212964470104968</v>
+        <v>0.03212964470104969</v>
       </c>
       <c r="P9" t="n">
         <v>0.03209321929887395</v>
@@ -6410,34 +6410,34 @@
         <v>0.03130400281576828</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03248656458940165</v>
+        <v>0.03248656458940166</v>
       </c>
       <c r="S9" t="n">
         <v>0.03179289654372663</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03143798387149315</v>
+        <v>0.03143798387149316</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0312475774816173</v>
+        <v>0.03124757748161731</v>
       </c>
       <c r="V9" t="n">
         <v>0.03260792681936662</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03248021496848824</v>
+        <v>0.03248021496848825</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03342228131145391</v>
+        <v>0.0334222813114539</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03170522044952441</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03150359768797617</v>
+        <v>0.03150359768797618</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.032141002370348</v>
+        <v>0.03214100237034801</v>
       </c>
       <c r="AB9" t="n">
         <v>0.03111300347286788</v>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007153626716230685</v>
+        <v>0.00715362671623068</v>
       </c>
       <c r="C2" t="n">
         <v>0.00778719209126994</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007136774993058167</v>
+        <v>0.007136774993058173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007185218111676041</v>
+        <v>0.007185218111676038</v>
       </c>
       <c r="F2" t="n">
         <v>0.007153396259489692</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007129683053827128</v>
+        <v>0.007129683053827125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007131765602792297</v>
+        <v>0.007131765602792295</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007127886759743312</v>
+        <v>0.007127886759743314</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007149159112417438</v>
+        <v>0.007149159112417439</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007122034910516256</v>
+        <v>0.007122034910516251</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007175329719245832</v>
+        <v>0.00717532971924583</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00711464733264505</v>
+        <v>0.007114647332645051</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007142943355554853</v>
+        <v>0.007142943355554849</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01071139927736181</v>
+        <v>0.01071139927736182</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007178104552138085</v>
+        <v>0.007178104552138086</v>
       </c>
       <c r="Q2" t="n">
         <v>0.007116057875882567</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007225262466048848</v>
+        <v>0.00722526246604885</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007155795179668479</v>
+        <v>0.007155795179668482</v>
       </c>
       <c r="T2" t="n">
         <v>0.007122648875694506</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008879220837713924</v>
+        <v>0.008879220837713923</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007162774432563888</v>
+        <v>0.007162774432563884</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008633052274449248</v>
+        <v>0.008633052274449245</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00735304885930066</v>
+        <v>0.007353048859300663</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007150417262024124</v>
+        <v>0.007150417262024116</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008835026474528437</v>
+        <v>0.008835026474528444</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007199657142551646</v>
+        <v>0.007199657142551643</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007110361871011306</v>
+        <v>0.007110361871011303</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007088515966918024</v>
+        <v>0.007109030510061922</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00803525939553551</v>
+        <v>0.008051335463484331</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006970518351272959</v>
+        <v>0.006987009664495074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007312774658798628</v>
+        <v>0.007341177238293796</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007089926382850963</v>
+        <v>0.007110719715992701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006918148201757101</v>
+        <v>0.006932681964049629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006935879575940045</v>
+        <v>0.006951174012458799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006907552381358165</v>
+        <v>0.006921805546805626</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007057313735730762</v>
+        <v>0.007076817058312492</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00686504453028928</v>
+        <v>0.00687778059495371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007241271294909001</v>
+        <v>0.007267349804314348</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006827481178786623</v>
+        <v>0.006838991335763866</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00701422295198501</v>
+        <v>0.00703222205035742</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01332255710610002</v>
+        <v>0.01335966969013817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007261604171071569</v>
+        <v>0.007288194434409677</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006822166755600358</v>
+        <v>0.006833379123028238</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007605149408913715</v>
+        <v>0.007644248833599224</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007103438082160139</v>
+        <v>0.007124547169073171</v>
       </c>
       <c r="T3" t="n">
-        <v>0.006869863719533163</v>
+        <v>0.00688277343175479</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009737118131656803</v>
+        <v>0.009748495075514778</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007153154993014189</v>
+        <v>0.007175986765921296</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009811825429137274</v>
+        <v>0.009845366621952293</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008509069244546851</v>
+        <v>0.00858041618124479</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007067967115136823</v>
+        <v>0.007087829055266616</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009910769149269647</v>
+        <v>0.009933515112849381</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007419252177752428</v>
+        <v>0.007451521355799817</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.006791147327954685</v>
+        <v>0.006801288958385661</v>
       </c>
     </row>
     <row r="4">
@@ -6788,13 +6788,13 @@
         <v>0.02837122684526442</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02838908231554518</v>
+        <v>0.02838908231554519</v>
       </c>
       <c r="E4" t="n">
         <v>0.02893626962526954</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02857682716604942</v>
+        <v>0.02857682716604943</v>
       </c>
       <c r="G4" t="n">
         <v>0.02830897559947715</v>
@@ -6803,7 +6803,7 @@
         <v>0.0283324989480587</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02828868563146446</v>
+        <v>0.02828868563146445</v>
       </c>
       <c r="J4" t="n">
         <v>0.02852585301095414</v>
@@ -6818,10 +6818,10 @@
         <v>0.0281662722843665</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02845875680753199</v>
+        <v>0.028458756807532</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02933090144672774</v>
+        <v>0.02933090144672773</v>
       </c>
       <c r="P4" t="n">
         <v>0.02885591869788925</v>
@@ -6836,13 +6836,13 @@
         <v>0.02860392407302664</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02822952132158745</v>
+        <v>0.02822952132158746</v>
       </c>
       <c r="U4" t="n">
         <v>0.02812329052329929</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02866274492542036</v>
+        <v>0.02866274492542037</v>
       </c>
       <c r="W4" t="n">
         <v>0.02915739981481668</v>
@@ -6854,7 +6854,7 @@
         <v>0.02850157313637691</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02867930815740098</v>
+        <v>0.02867930815740099</v>
       </c>
       <c r="AA4" t="n">
         <v>0.02909936512129188</v>
@@ -6873,19 +6873,19 @@
         <v>0.04005962426562668</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03746354571591672</v>
+        <v>0.03746354571591671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03787143518314378</v>
+        <v>0.03787143518314377</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04574351663561509</v>
+        <v>0.04574351663561505</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04159686245870074</v>
+        <v>0.04159686245870075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03554532539675222</v>
+        <v>0.03554532539675223</v>
       </c>
       <c r="H5" t="n">
         <v>0.03744770436670915</v>
@@ -6894,10 +6894,10 @@
         <v>0.03633921318283791</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03951807041640236</v>
+        <v>0.03951807041640237</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03478514245113463</v>
+        <v>0.03478514245113465</v>
       </c>
       <c r="L5" t="n">
         <v>0.04328637961921517</v>
@@ -6906,49 +6906,49 @@
         <v>0.03400718497079887</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03893826925947795</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05142588984201157</v>
+        <v>0.0514258898420116</v>
       </c>
       <c r="P5" t="n">
-        <v>0.04411474668008079</v>
+        <v>0.04411474668008084</v>
       </c>
       <c r="Q5" t="n">
         <v>0.03347736893824266</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05715147908023799</v>
+        <v>0.05715147908023801</v>
       </c>
       <c r="S5" t="n">
         <v>0.04020557695044676</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03513441374181575</v>
+        <v>0.03513441374181578</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03340406719852083</v>
+        <v>0.03340406719852085</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0415309687836291</v>
+        <v>0.04153096878362908</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05055074943137196</v>
+        <v>0.05055074943137195</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07848390213239499</v>
+        <v>0.07848390213239498</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04063999353997319</v>
+        <v>0.04063999353997316</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.04093631252284547</v>
+        <v>0.04093631252284551</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05040327496577267</v>
+        <v>0.05040327496577277</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03314958475463874</v>
+        <v>0.03314958475463873</v>
       </c>
     </row>
     <row r="6">
@@ -6958,10 +6958,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03027277703282232</v>
+        <v>0.03027277703282233</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0300645735971325</v>
+        <v>0.03006457359713251</v>
       </c>
       <c r="D6" t="n">
         <v>0.03008242906741327</v>
@@ -6979,19 +6979,19 @@
         <v>0.03002584569992678</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02998203238333253</v>
+        <v>0.02998203238333254</v>
       </c>
       <c r="J6" t="n">
         <v>0.02916762602460964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02886435931611666</v>
+        <v>0.02886435931611665</v>
       </c>
       <c r="L6" t="n">
         <v>0.03051792243575306</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02985961903623458</v>
+        <v>0.02985961903623459</v>
       </c>
       <c r="N6" t="n">
         <v>0.02910488748762038</v>
@@ -7000,19 +7000,19 @@
         <v>0.03016698653721913</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03054803302787039</v>
+        <v>0.0305480330278704</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02984841969857001</v>
+        <v>0.02984841969857002</v>
       </c>
       <c r="R6" t="n">
         <v>0.03108193578109159</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03029727082489472</v>
+        <v>0.03029727082489473</v>
       </c>
       <c r="T6" t="n">
-        <v>0.02887129433524295</v>
+        <v>0.02887129433524296</v>
       </c>
       <c r="U6" t="n">
         <v>0.02985824215805976</v>
@@ -7021,19 +7021,19 @@
         <v>0.02930451793907587</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03084584825605519</v>
+        <v>0.0308458482560552</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03147376813930338</v>
+        <v>0.03147376813930337</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.02925643734096124</v>
+        <v>0.02925643734096122</v>
       </c>
       <c r="Z6" t="n">
         <v>0.02932108117105648</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03079271187315996</v>
+        <v>0.03079271187315997</v>
       </c>
       <c r="AB6" t="n">
         <v>0.02874388184609808</v>
@@ -7064,7 +7064,7 @@
         <v>0.02896301946110506</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0289865428096866</v>
+        <v>0.02898654280968661</v>
       </c>
       <c r="I7" t="n">
         <v>0.02894272949309236</v>
@@ -7088,10 +7088,10 @@
         <v>0.02998482902132858</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02950984627249009</v>
+        <v>0.0295098462724901</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02880911680832983</v>
+        <v>0.02880911680832984</v>
       </c>
       <c r="R7" t="n">
         <v>0.03004263289085141</v>
@@ -7100,13 +7100,13 @@
         <v>0.02925796793465454</v>
       </c>
       <c r="T7" t="n">
-        <v>0.02888356518321536</v>
+        <v>0.02888356518321537</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02881770663979784</v>
+        <v>0.02881770663979785</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02931678878704827</v>
+        <v>0.02931678878704828</v>
       </c>
       <c r="W7" t="n">
         <v>0.02981144367644458</v>
@@ -7137,31 +7137,31 @@
         <v>0.03024741093382816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03139635043666329</v>
+        <v>0.0313963504366633</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03141420590694406</v>
+        <v>0.03141420590694407</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03123875463514264</v>
+        <v>0.03123875463514265</v>
       </c>
       <c r="F8" t="n">
         <v>0.03045623482746308</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03161551162013386</v>
+        <v>0.03161551162013387</v>
       </c>
       <c r="H8" t="n">
         <v>0.03135762253945757</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03131380922286332</v>
+        <v>0.03131380922286334</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03155097660235301</v>
+        <v>0.03155097660235302</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03124770989386002</v>
+        <v>0.03124770989386003</v>
       </c>
       <c r="L8" t="n">
         <v>0.03184969927528386</v>
@@ -7182,34 +7182,34 @@
         <v>0.02955634403691382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03241371262062238</v>
+        <v>0.03241371262062239</v>
       </c>
       <c r="S8" t="n">
         <v>0.03162904766442552</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03125464491298632</v>
+        <v>0.03125464491298633</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03052675050593231</v>
+        <v>0.03052675050593232</v>
       </c>
       <c r="V8" t="n">
-        <v>0.03131598666775716</v>
+        <v>0.03131598666775717</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03218279012355356</v>
+        <v>0.03218279012355357</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03235765106277741</v>
+        <v>0.03235765106277742</v>
       </c>
       <c r="Y8" t="n">
         <v>0.03291619794636801</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03032207918344273</v>
+        <v>0.03032207918344274</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03212448871269075</v>
+        <v>0.03212448871269077</v>
       </c>
       <c r="AB8" t="n">
         <v>0.03254935532812447</v>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03074250193803371</v>
+        <v>0.03074250193803372</v>
       </c>
       <c r="C9" t="n">
         <v>0.03126191911990209</v>
@@ -7240,16 +7240,16 @@
         <v>0.03119966847892094</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03122319122269636</v>
+        <v>0.03122319122269637</v>
       </c>
       <c r="I9" t="n">
         <v>0.03117937790610213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03141654528559181</v>
+        <v>0.03141654528559182</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03111327857709881</v>
+        <v>0.03111327857709883</v>
       </c>
       <c r="L9" t="n">
         <v>0.03171526795852265</v>
@@ -7258,31 +7258,31 @@
         <v>0.03105696455900417</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03134944908216966</v>
+        <v>0.03134944908216967</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03246272704652452</v>
+        <v>0.03246272704652453</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03204018652722195</v>
+        <v>0.03204018652722196</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03104576582614572</v>
+        <v>0.03104576582614573</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03227928130386117</v>
+        <v>0.03227928130386118</v>
       </c>
       <c r="S9" t="n">
         <v>0.03149461634766432</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03112021359622512</v>
+        <v>0.03112021359622513</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03105558768082934</v>
+        <v>0.03105558768082935</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0323930964138712</v>
+        <v>0.03239309641387121</v>
       </c>
       <c r="W9" t="n">
         <v>0.03204809208945435</v>
@@ -7291,7 +7291,7 @@
         <v>0.03372268740028556</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03143387029390694</v>
+        <v>0.03143387029390695</v>
       </c>
       <c r="Z9" t="n">
         <v>0.03113131014236269</v>
@@ -7300,7 +7300,7 @@
         <v>0.03199005739592956</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03099727472974981</v>
+        <v>0.03099727472974982</v>
       </c>
     </row>
   </sheetData>
@@ -7466,82 +7466,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007436782585150763</v>
+        <v>0.007436782585150761</v>
       </c>
       <c r="C2" t="n">
         <v>0.008186660291859341</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007450716361015804</v>
+        <v>0.0074507163610158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007375308796010304</v>
+        <v>0.007375308796010296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007386184070313713</v>
+        <v>0.00738618407031371</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007511430671054484</v>
+        <v>0.007511430671054479</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0073952697343962</v>
+        <v>0.007395269734396192</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007474572299008924</v>
+        <v>0.007474572299008915</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007507826854682736</v>
+        <v>0.007507826854682729</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007556037364221619</v>
+        <v>0.007556037364221614</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007507342179812948</v>
+        <v>0.007507342179812924</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007982925237638145</v>
+        <v>0.007982925237638147</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007557694701079122</v>
+        <v>0.007557694701079119</v>
       </c>
       <c r="O2" t="n">
         <v>0.01099985749042524</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007498701056345257</v>
+        <v>0.007498701056345258</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007412674552719531</v>
+        <v>0.007412674552719526</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0074330414146355</v>
+        <v>0.007433041414635496</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007461603157074953</v>
+        <v>0.007461603157074947</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007461530377191147</v>
+        <v>0.007461530377191146</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009905570276084038</v>
+        <v>0.009905570276084023</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007375166254851074</v>
+        <v>0.007375166254851068</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009379211976442524</v>
+        <v>0.009379211976442517</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0075075523892885</v>
+        <v>0.007507552389288488</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007444884530719082</v>
+        <v>0.007444884530719078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009117578150234923</v>
+        <v>0.009117578150234919</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007514845030960245</v>
+        <v>0.00751484503096024</v>
       </c>
       <c r="AB2" t="n">
         <v>0.007626082251826515</v>
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007746641110807272</v>
+        <v>0.007783990025425571</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008446154632696705</v>
+        <v>0.008458855593266651</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007853524881439391</v>
+        <v>0.007894937856379347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007311078537689416</v>
+        <v>0.007332999191440121</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007391415562800083</v>
+        <v>0.007416545659111026</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008276204776867203</v>
+        <v>0.008332246799163124</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007458143545246569</v>
+        <v>0.007485636654938453</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008024377781636215</v>
+        <v>0.008071930704996745</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008254261671889864</v>
+        <v>0.008309797214036851</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008596822621228547</v>
+        <v>0.008664889478930623</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008251537585072893</v>
+        <v>0.008306851921380009</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01161976295401053</v>
+        <v>0.01179599478720485</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008616077740295333</v>
+        <v>0.008684383514994171</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01359686506534136</v>
+        <v>0.01363279421456771</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008188171601303819</v>
+        <v>0.008240904890551253</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00757903750705114</v>
+        <v>0.007610718761605314</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007728385819262176</v>
+        <v>0.007765441699103478</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007921496717580825</v>
+        <v>0.007965174733799839</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007930819462304978</v>
+        <v>0.007975004211531713</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01234906532596228</v>
+        <v>0.01241067055259643</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007308758394061738</v>
+        <v>0.007330730365065193</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0110092864131142</v>
+        <v>0.01104928549958328</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008258800891604417</v>
+        <v>0.008314596641105284</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007808362814511749</v>
+        <v>0.007848080448287125</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01044002085206441</v>
+        <v>0.01047366883091158</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008308207821644199</v>
+        <v>0.008365542821717252</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009104505580327859</v>
+        <v>0.009190057185309755</v>
       </c>
     </row>
     <row r="4">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02952738679261081</v>
+        <v>0.02952738679261076</v>
       </c>
       <c r="C4" t="n">
         <v>0.02840809592821007</v>
@@ -7657,28 +7657,28 @@
         <v>0.02895585329105951</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0303705712627095</v>
+        <v>0.03037057126270951</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02905848004648309</v>
+        <v>0.02905848004648308</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02995423899476587</v>
+        <v>0.02995423899476588</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03032588810420976</v>
+        <v>0.03032588810420975</v>
       </c>
       <c r="K4" t="n">
         <v>0.03087442438212484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03032438987333727</v>
+        <v>0.03032438987333717</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03565254534821861</v>
+        <v>0.03565254534821862</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03089314476434292</v>
+        <v>0.03089314476434293</v>
       </c>
       <c r="O4" t="n">
         <v>0.02946482950770291</v>
@@ -7687,37 +7687,37 @@
         <v>0.03022678440865663</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02925507547605714</v>
+        <v>0.02925507547605713</v>
       </c>
       <c r="R4" t="n">
         <v>0.02948512855061742</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0298077465705217</v>
+        <v>0.02980774657052169</v>
       </c>
       <c r="T4" t="n">
         <v>0.02980692448825369</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03051628623890119</v>
+        <v>0.03051628623890118</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02880557728964875</v>
+        <v>0.02880557728964876</v>
       </c>
       <c r="W4" t="n">
         <v>0.02963411980132682</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03032676428606478</v>
+        <v>0.03032676428606475</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0295257853482368</v>
+        <v>0.02952578534823679</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02935869304743221</v>
+        <v>0.0293586930474322</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03040913802852814</v>
+        <v>0.03040913802852813</v>
       </c>
       <c r="AB4" t="n">
         <v>0.03164727854507701</v>
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05452956275502496</v>
+        <v>0.05452956275502453</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03597411528091737</v>
+        <v>0.03597411528091739</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06164195117204465</v>
+        <v>0.06164195117204464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04316835776792455</v>
+        <v>0.04316835776792445</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04700356755369058</v>
+        <v>0.04700356755369056</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06869081138729759</v>
+        <v>0.06869081138729757</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04999133975042461</v>
+        <v>0.04999133975042467</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06706612307023599</v>
+        <v>0.067066123070236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07001802726529993</v>
+        <v>0.07001802726529988</v>
       </c>
       <c r="K5" t="n">
         <v>0.07947321601827029</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07032729628741513</v>
+        <v>0.07032729628741365</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1698194504865421</v>
+        <v>0.1698194504865422</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08395751248540119</v>
+        <v>0.08395751248540127</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05284703326991388</v>
+        <v>0.05284703326991391</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06753974031881192</v>
+        <v>0.06753974031881189</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05185928871399674</v>
+        <v>0.0518592887139966</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05842760349638603</v>
+        <v>0.05842760349638613</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05855696086239678</v>
+        <v>0.05855696086239659</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0640151666797233</v>
+        <v>0.06401516667972321</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07580012373396054</v>
+        <v>0.07580012373396049</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04238752363409234</v>
+        <v>0.04238752363409238</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05903268188401278</v>
+        <v>0.05903268188401264</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07357731413833052</v>
+        <v>0.07357731413833039</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05842764603727888</v>
+        <v>0.05842764603727883</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.05181594326830367</v>
+        <v>0.05181594326830328</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07366602137416806</v>
+        <v>0.07366602137416796</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1039473557087251</v>
+        <v>0.103947355708725</v>
       </c>
     </row>
     <row r="6">
@@ -7818,22 +7818,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03016848678446213</v>
+        <v>0.0301684867844621</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02904919592006137</v>
+        <v>0.02904919592006138</v>
       </c>
       <c r="D6" t="n">
         <v>0.03032587519271124</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03073490282095396</v>
+        <v>0.03073490282095395</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02959695328291082</v>
+        <v>0.02959695328291083</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03227246201873429</v>
+        <v>0.0322724620187343</v>
       </c>
       <c r="H6" t="n">
         <v>0.02969958003833439</v>
@@ -7848,49 +7848,49 @@
         <v>0.03277631513814964</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03222628062936207</v>
+        <v>0.03222628062936191</v>
       </c>
       <c r="M6" t="n">
         <v>0.03629364534006992</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0315399408479133</v>
+        <v>0.03153994084791326</v>
       </c>
       <c r="O6" t="n">
         <v>0.03138134397493827</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03214526376844634</v>
+        <v>0.03214526376844633</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02989617546790844</v>
+        <v>0.02989617546790843</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03138701930664221</v>
+        <v>0.03138701930664222</v>
       </c>
       <c r="S6" t="n">
         <v>0.03044884656237301</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03044802448010499</v>
+        <v>0.030448024480105</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03251129364157329</v>
+        <v>0.03251129364157328</v>
       </c>
       <c r="V6" t="n">
         <v>0.02944667728150007</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0303425965249685</v>
+        <v>0.03034259652496848</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03222865504208958</v>
+        <v>0.03222865504208955</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03031163152035439</v>
+        <v>0.03031163152035441</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03126058380345702</v>
+        <v>0.031260583803457</v>
       </c>
       <c r="AA6" t="n">
         <v>0.03231102878455294</v>
@@ -7906,13 +7906,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03034864471466989</v>
+        <v>0.03034864471466986</v>
       </c>
       <c r="C7" t="n">
         <v>0.02922935385026915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03050603312291902</v>
+        <v>0.03050603312291903</v>
       </c>
       <c r="E7" t="n">
         <v>0.02965426998698823</v>
@@ -7921,7 +7921,7 @@
         <v>0.0297771112131186</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03119182918476858</v>
+        <v>0.03119182918476859</v>
       </c>
       <c r="H7" t="n">
         <v>0.02987973796854217</v>
@@ -7930,16 +7930,16 @@
         <v>0.03077549691682496</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03114714602626885</v>
+        <v>0.03114714602626884</v>
       </c>
       <c r="K7" t="n">
         <v>0.03169568230418392</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03114564779539637</v>
+        <v>0.03114564779539622</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03647380327027771</v>
+        <v>0.03647380327027772</v>
       </c>
       <c r="N7" t="n">
         <v>0.03171440268640201</v>
@@ -7948,7 +7948,7 @@
         <v>0.03028596292989769</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03104791783085142</v>
+        <v>0.03104791783085141</v>
       </c>
       <c r="Q7" t="n">
         <v>0.03007633339811621</v>
@@ -7972,19 +7972,19 @@
         <v>0.03045537772338591</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03114802220812387</v>
+        <v>0.03114802220812384</v>
       </c>
       <c r="Y7" t="n">
         <v>0.03044015991694317</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03017995096949129</v>
+        <v>0.03017995096949128</v>
       </c>
       <c r="AA7" t="n">
         <v>0.03123039595058723</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03246853646713609</v>
+        <v>0.03246853646713611</v>
       </c>
     </row>
     <row r="8">
@@ -7994,22 +7994,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03155172231363985</v>
+        <v>0.03155172231363982</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03206524598035036</v>
+        <v>0.03206524598035037</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03334192525300022</v>
+        <v>0.03334192525300023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03162073654430955</v>
+        <v>0.03162073654430954</v>
       </c>
       <c r="F8" t="n">
         <v>0.03123456223290254</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03436629604465901</v>
+        <v>0.03436629604465903</v>
       </c>
       <c r="H8" t="n">
         <v>0.03271563009862337</v>
@@ -8018,16 +8018,16 @@
         <v>0.03361138904690619</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03398303815635005</v>
+        <v>0.03398303815635006</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03453157443426514</v>
+        <v>0.03453157443426513</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03398153992547755</v>
+        <v>0.03398153992547748</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03930969540035931</v>
+        <v>0.0393096954003593</v>
       </c>
       <c r="N8" t="n">
         <v>0.03328459039089632</v>
@@ -8045,7 +8045,7 @@
         <v>0.0331422786027577</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03346489662266199</v>
+        <v>0.033464896622662</v>
       </c>
       <c r="T8" t="n">
         <v>0.03346407454039398</v>
@@ -8057,16 +8057,16 @@
         <v>0.03201539321463578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03329159074809728</v>
+        <v>0.03329159074809729</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03217986518071191</v>
+        <v>0.03217986518071188</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03489787629879275</v>
+        <v>0.03489787629879276</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03135269820027321</v>
+        <v>0.03135269820027319</v>
       </c>
       <c r="AA8" t="n">
         <v>0.03406628808066843</v>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03269738851085148</v>
+        <v>0.03269738851085144</v>
       </c>
       <c r="C9" t="n">
         <v>0.03260562653516257</v>
@@ -8091,55 +8091,55 @@
         <v>0.03388230580781243</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03279339261665704</v>
+        <v>0.03279339261665703</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03078465035267451</v>
+        <v>0.0307846503526745</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0345681011170348</v>
+        <v>0.03456810111703481</v>
       </c>
       <c r="H9" t="n">
         <v>0.03325601065343557</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03415176960171838</v>
+        <v>0.03415176960171836</v>
       </c>
       <c r="J9" t="n">
         <v>0.03452341871116223</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03507195498907734</v>
+        <v>0.03507195498907733</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03452192048028976</v>
+        <v>0.0345219204802896</v>
       </c>
       <c r="M9" t="n">
         <v>0.03985007595517111</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03509067537129541</v>
+        <v>0.0350906753712954</v>
       </c>
       <c r="O9" t="n">
         <v>0.03400288084089353</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03483889332113568</v>
+        <v>0.03483889332113566</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03345260533038245</v>
+        <v>0.03345260533038243</v>
       </c>
       <c r="R9" t="n">
-        <v>0.03368265915756991</v>
+        <v>0.0336826591575699</v>
       </c>
       <c r="S9" t="n">
-        <v>0.03400527717747418</v>
+        <v>0.03400527717747417</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03400445509520618</v>
+        <v>0.03400445509520617</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03480693349250098</v>
+        <v>0.03480693349250097</v>
       </c>
       <c r="V9" t="n">
         <v>0.03418885130533075</v>
@@ -8148,16 +8148,16 @@
         <v>0.03383165040827932</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03452429489301728</v>
+        <v>0.03452429489301724</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.03381643260183657</v>
+        <v>0.03381643260183658</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03293671480706542</v>
+        <v>0.0329367148070654</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03460666863548063</v>
+        <v>0.03460666863548062</v>
       </c>
       <c r="AB9" t="n">
         <v>0.03584480915202951</v>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007212834344806457</v>
+        <v>0.007212834344806449</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008093826638324768</v>
+        <v>0.008093826638324761</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007239048529640763</v>
+        <v>0.007239048529640758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007243383570073146</v>
+        <v>0.007243383570073134</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007250384649296576</v>
+        <v>0.007250384649296578</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007384505854404312</v>
+        <v>0.007384505854404293</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007242563393966238</v>
+        <v>0.007242563393966231</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007246065901510271</v>
+        <v>0.007246065901510259</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007304702801045062</v>
+        <v>0.00730470280104506</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0072789790978332</v>
+        <v>0.007278979097833193</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007356258627681407</v>
+        <v>0.007356258627681391</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007276492081320297</v>
+        <v>0.007276492081320302</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007274554542361873</v>
+        <v>0.007274554542361867</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01072918774784667</v>
+        <v>0.01072918774784669</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007329608202586578</v>
+        <v>0.00732960820258657</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007257177179703395</v>
+        <v>0.00725717717970338</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007322857128408715</v>
+        <v>0.007322857128408723</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007288632745258864</v>
+        <v>0.007288632745258861</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007255109311216183</v>
+        <v>0.007255109311216174</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009631477087498352</v>
+        <v>0.009631477087498369</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00724420383881848</v>
+        <v>0.00724420383881847</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009280314017044633</v>
+        <v>0.009280314017044645</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007398371915164302</v>
+        <v>0.007398371915164295</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007415140760949734</v>
+        <v>0.007415140760949721</v>
       </c>
       <c r="Z2" t="n">
         <v>0.008903236074109913</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007274576689497279</v>
+        <v>0.007274576689497297</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007404356868419605</v>
+        <v>0.007404356868419609</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.006864970895388004</v>
+        <v>0.006874825734870514</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008425142644840468</v>
+        <v>0.0084399461310049</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007053212364020294</v>
+        <v>0.007069815304073658</v>
       </c>
       <c r="E3" t="n">
-        <v>0.007082550224337574</v>
+        <v>0.007099959041670909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00713428251005212</v>
+        <v>0.007153839962195889</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00808122178046858</v>
+        <v>0.008134026242812308</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007079865716408475</v>
+        <v>0.007097452742437326</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007104027190110688</v>
+        <v>0.007122439054506399</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00751771997945898</v>
+        <v>0.007550693776683797</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007335517295260242</v>
+        <v>0.007362227982017122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007883417760953202</v>
+        <v>0.007929395847885639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007331095074390808</v>
+        <v>0.007357781919883026</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007306815734464601</v>
+        <v>0.00733234402603333</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01287605586252786</v>
+        <v>0.01289539892069259</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007694457356875521</v>
+        <v>0.007733439638113127</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007180624478865089</v>
+        <v>0.007201787142861883</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00765478039649295</v>
+        <v>0.007692799549811028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007402298936621783</v>
+        <v>0.007431182183919248</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007168365841501068</v>
+        <v>0.007189057822464443</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01102553988659921</v>
+        <v>0.01104315388988469</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007087496845684157</v>
+        <v>0.007105216532137274</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01090930906536855</v>
+        <v>0.01094818795377322</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00818998481931589</v>
+        <v>0.008246995126725021</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00830889691462636</v>
+        <v>0.008369876958276394</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009829558141087475</v>
+        <v>0.009847445930554536</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007306338850471424</v>
+        <v>0.007331818508673616</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.008232521085125651</v>
+        <v>0.008290856406642313</v>
       </c>
     </row>
     <row r="4">
@@ -8511,7 +8511,7 @@
         <v>0.0284523485963377</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0285013148722386</v>
+        <v>0.02850131487223861</v>
       </c>
       <c r="F4" t="n">
         <v>0.02858039528272276</v>
@@ -8532,22 +8532,22 @@
         <v>0.02890338273304011</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02977629057301581</v>
+        <v>0.02977629057301582</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02889706503998537</v>
+        <v>0.02889706503998536</v>
       </c>
       <c r="N4" t="n">
         <v>0.02885340534359542</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02858565038558932</v>
+        <v>0.02858565038558933</v>
       </c>
       <c r="P4" t="n">
         <v>0.02947526176176844</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02865712003838613</v>
+        <v>0.02865712003838614</v>
       </c>
       <c r="R4" t="n">
         <v>0.02939900527328196</v>
@@ -8556,7 +8556,7 @@
         <v>0.0290124251216103</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02863376251255659</v>
+        <v>0.0286337625125566</v>
       </c>
       <c r="U4" t="n">
         <v>0.02843706701722186</v>
@@ -8580,7 +8580,7 @@
         <v>0.02885365550567805</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.03030809888091201</v>
+        <v>0.03030809888091202</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03244141156753563</v>
+        <v>0.03244141156753562</v>
       </c>
       <c r="C5" t="n">
         <v>0.03660930360377415</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03827416329099733</v>
+        <v>0.03827416329099734</v>
       </c>
       <c r="E5" t="n">
         <v>0.03831025546263486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04062371098096143</v>
+        <v>0.04062371098096142</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06208552245025373</v>
+        <v>0.06208552245025359</v>
       </c>
       <c r="H5" t="n">
         <v>0.03978872291072096</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04005516361196822</v>
+        <v>0.04005516361196821</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04927754080039609</v>
+        <v>0.049277540800396</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04486181405909188</v>
+        <v>0.04486181405909187</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05841046140331482</v>
+        <v>0.05841046140331485</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04552602595708105</v>
+        <v>0.04552602595708107</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04546866469835966</v>
+        <v>0.04546866469835961</v>
       </c>
       <c r="O5" t="n">
         <v>0.03906843999066954</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05373146421661853</v>
+        <v>0.05373146421661851</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04087344530208754</v>
+        <v>0.04087344530208756</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05679065400422898</v>
+        <v>0.05679065400422902</v>
       </c>
       <c r="S5" t="n">
-        <v>0.04569336763704205</v>
+        <v>0.04569336763704206</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04175580930868841</v>
+        <v>0.04175580930868848</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0381907476775013</v>
+        <v>0.03819074767750132</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03797985681694827</v>
+        <v>0.03797985681694825</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05581329289604473</v>
+        <v>0.05581329289604471</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06993441089206115</v>
+        <v>0.06993441089206112</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07288647867488052</v>
+        <v>0.07288647867488049</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03798696173372321</v>
+        <v>0.03798696173372322</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04514404288155334</v>
+        <v>0.0451440428815533</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07406769734626495</v>
+        <v>0.07406769734626502</v>
       </c>
     </row>
     <row r="6">
@@ -8684,7 +8684,7 @@
         <v>0.03011991246541624</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03019939804783635</v>
+        <v>0.03019939804783636</v>
       </c>
       <c r="E6" t="n">
         <v>0.02911680176122886</v>
@@ -8714,13 +8714,13 @@
         <v>0.02951255192897562</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02947436722138705</v>
+        <v>0.02947436722138706</v>
       </c>
       <c r="O6" t="n">
         <v>0.03033767172814066</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03004221942680285</v>
+        <v>0.03004221942680286</v>
       </c>
       <c r="Q6" t="n">
         <v>0.02927260692737638</v>
@@ -8735,28 +8735,28 @@
         <v>0.02924924940154685</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03025058723135611</v>
+        <v>0.03025058723135612</v>
       </c>
       <c r="V6" t="n">
         <v>0.02910217699545775</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03013783239180876</v>
+        <v>0.03013783239180872</v>
       </c>
       <c r="X6" t="n">
         <v>0.0319990289797031</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03110512662010037</v>
+        <v>0.03110512662010038</v>
       </c>
       <c r="Z6" t="n">
         <v>0.03026550691675006</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0294691423946683</v>
+        <v>0.02946914239466829</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03092636964126094</v>
+        <v>0.03092636964126095</v>
       </c>
     </row>
     <row r="7">
@@ -8766,22 +8766,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02885171578825826</v>
+        <v>0.02885171578825827</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02906833148266249</v>
+        <v>0.02906833148266248</v>
       </c>
       <c r="D7" t="n">
         <v>0.0291478170650826</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0291967833409835</v>
+        <v>0.02919678334098352</v>
       </c>
       <c r="F7" t="n">
         <v>0.02927586375146765</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03079082446196215</v>
+        <v>0.03079082446196214</v>
       </c>
       <c r="H7" t="n">
         <v>0.02918751907455636</v>
@@ -8790,19 +8790,19 @@
         <v>0.02922708150849927</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02988572919987943</v>
+        <v>0.02988572919987944</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02959885120178499</v>
+        <v>0.02959885120178501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0304717590417607</v>
+        <v>0.03047175904176071</v>
       </c>
       <c r="M7" t="n">
         <v>0.02959253350873027</v>
       </c>
       <c r="N7" t="n">
-        <v>0.02954887381234031</v>
+        <v>0.02954887381234032</v>
       </c>
       <c r="O7" t="n">
         <v>0.02928100263117132</v>
@@ -8814,7 +8814,7 @@
         <v>0.02935258850713103</v>
       </c>
       <c r="R7" t="n">
-        <v>0.03009447374202685</v>
+        <v>0.03009447374202686</v>
       </c>
       <c r="S7" t="n">
         <v>0.02970789359035519</v>
@@ -8823,7 +8823,7 @@
         <v>0.0293292309813015</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02919743943242354</v>
+        <v>0.02919743943242353</v>
       </c>
       <c r="V7" t="n">
         <v>0.0291821585752124</v>
@@ -8841,10 +8841,10 @@
         <v>0.02921392593399631</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02954912397442294</v>
+        <v>0.02954912397442295</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.03100356734965691</v>
+        <v>0.03100356734965692</v>
       </c>
     </row>
     <row r="8">
@@ -8857,7 +8857,7 @@
         <v>0.02991221707570938</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03155575206635013</v>
+        <v>0.03155575206635012</v>
       </c>
       <c r="D8" t="n">
         <v>0.03163523764877024</v>
@@ -8866,22 +8866,22 @@
         <v>0.03092441149094667</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03055866238849206</v>
+        <v>0.03055866238849205</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0335741260572273</v>
+        <v>0.03357412605722727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.031674939658244</v>
+        <v>0.03167493965824399</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03171450209218692</v>
+        <v>0.03171450209218691</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03237314978356707</v>
+        <v>0.03237314978356708</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03208627178547264</v>
+        <v>0.03208627178547266</v>
       </c>
       <c r="L8" t="n">
         <v>0.03295917962544834</v>
@@ -8893,7 +8893,7 @@
         <v>0.03093019322299967</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03096640447136682</v>
+        <v>0.03096640447136683</v>
       </c>
       <c r="P8" t="n">
         <v>0.03178150638552027</v>
@@ -8902,28 +8902,28 @@
         <v>0.03013266758507461</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03258189432571451</v>
+        <v>0.0325818943257145</v>
       </c>
       <c r="S8" t="n">
-        <v>0.03219531417404284</v>
+        <v>0.03219531417404283</v>
       </c>
       <c r="T8" t="n">
-        <v>0.03181665156498914</v>
+        <v>0.03181665156498913</v>
       </c>
       <c r="U8" t="n">
         <v>0.03098884239459103</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0312783406687977</v>
+        <v>0.03127834066879771</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03263814140886935</v>
+        <v>0.03263814140886936</v>
       </c>
       <c r="X8" t="n">
         <v>0.03185830706361602</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.03504111065064966</v>
+        <v>0.03504111065064967</v>
       </c>
       <c r="Z8" t="n">
         <v>0.03024792146295196</v>
@@ -8942,28 +8942,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03073246669329399</v>
+        <v>0.030732466693294</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0317969977142692</v>
+        <v>0.03179699771426921</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03187648329668931</v>
+        <v>0.03187648329668932</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03172975461145215</v>
+        <v>0.03172975461145214</v>
       </c>
       <c r="F9" t="n">
         <v>0.03004985299462376</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03351949126253483</v>
+        <v>0.03351949126253481</v>
       </c>
       <c r="H9" t="n">
         <v>0.03191618530616307</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03195574774010599</v>
+        <v>0.031955747740106</v>
       </c>
       <c r="J9" t="n">
         <v>0.03261439543148614</v>
@@ -8975,19 +8975,19 @@
         <v>0.03320042527336742</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03232119974033698</v>
+        <v>0.03232119974033699</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03227754004394702</v>
+        <v>0.03227754004394703</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03229078387243684</v>
+        <v>0.03229078387243686</v>
       </c>
       <c r="P9" t="n">
         <v>0.03324150753981114</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03208125530770369</v>
+        <v>0.0320812553077037</v>
       </c>
       <c r="R9" t="n">
         <v>0.03282313997363357</v>
@@ -8999,28 +8999,28 @@
         <v>0.03205789721290821</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03192767248020906</v>
+        <v>0.03192767248020907</v>
       </c>
       <c r="V9" t="n">
-        <v>0.03288930127803495</v>
+        <v>0.03288930127803496</v>
       </c>
       <c r="W9" t="n">
         <v>0.03287910662643955</v>
       </c>
       <c r="X9" t="n">
-        <v>0.03367611422855606</v>
+        <v>0.03367611422855605</v>
       </c>
       <c r="Y9" t="n">
         <v>0.03386552605575275</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03143137484918351</v>
+        <v>0.03143137484918352</v>
       </c>
       <c r="AA9" t="n">
         <v>0.03227779020602966</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03373223358126363</v>
+        <v>0.03373223358126362</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007696119316465232</v>
+        <v>0.007696119316465234</v>
       </c>
       <c r="C2" t="n">
         <v>0.008357515897421008</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007663989964843451</v>
+        <v>0.007663989964843448</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007532857204365966</v>
+        <v>0.007532857204365963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007601892993471675</v>
+        <v>0.007601892993471679</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007669938811594634</v>
+        <v>0.007669938811594638</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007640597959649022</v>
+        <v>0.007640597959649023</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007700649880570455</v>
+        <v>0.007700649880570454</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007676659024118831</v>
+        <v>0.007676659024118828</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007852395958222633</v>
+        <v>0.007852395958222631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007685870680996754</v>
+        <v>0.007685870680996756</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008197333323082864</v>
+        <v>0.008197333323082862</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007741686195258334</v>
+        <v>0.007741686195258329</v>
       </c>
       <c r="O2" t="n">
         <v>0.01139099494745044</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007641030059721635</v>
+        <v>0.007641030059721637</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007582667962853031</v>
+        <v>0.007582667962853029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007601730932066131</v>
+        <v>0.00760173093206614</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007660498933037449</v>
+        <v>0.00766049893303744</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007708121364560507</v>
+        <v>0.007708121364560503</v>
       </c>
       <c r="U2" t="n">
         <v>0.01038529570442293</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007573857199177972</v>
+        <v>0.007573857199177976</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009749805636603919</v>
+        <v>0.009749805636603914</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007584749341131484</v>
+        <v>0.007584749341131486</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007613965609021912</v>
+        <v>0.007613965609021915</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009323951350409159</v>
+        <v>0.009323951350409148</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007749259791342908</v>
+        <v>0.007749259791342913</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007829396634781367</v>
+        <v>0.007829396634781364</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01707053974528716</v>
+        <v>0.009534834586131025</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01333321677129536</v>
+        <v>0.008856490805195186</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01640313811507152</v>
+        <v>0.00937094093807956</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01447286995269044</v>
+        <v>0.009438655395016472</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01496908661249922</v>
+        <v>0.008876982329982477</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01647226386991318</v>
+        <v>0.009348851712950372</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01588481809631911</v>
+        <v>0.0092082461443013</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0172690297665439</v>
+        <v>0.009680240188078055</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01665926046112116</v>
+        <v>0.009430539970592157</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02079019167576309</v>
+        <v>0.01089787400778651</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01686818660201773</v>
+        <v>0.009505114625414864</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02881954200163606</v>
+        <v>0.01372610447917591</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01819088164096298</v>
+        <v>0.009976321414531602</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0203277098116384</v>
+        <v>0.01308235836340361</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01579630142209298</v>
+        <v>0.009114782892138226</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01449672844544675</v>
+        <v>0.008697301505562758</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01496262875243442</v>
+        <v>0.008876091509465021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01626484127065007</v>
+        <v>0.009277228325607522</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01743697743218243</v>
+        <v>0.009734704396017651</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02206071544106171</v>
+        <v>0.01297258997316934</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01425981669768106</v>
+        <v>0.008588259559357794</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01777828990672443</v>
+        <v>0.01120855866781936</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01454980307320092</v>
+        <v>0.008718075830080805</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01521351687553351</v>
+        <v>0.008936574905711567</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01627051019866728</v>
+        <v>0.01042529014167671</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0183517913513676</v>
+        <v>0.01002584641325941</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02023238932509439</v>
+        <v>0.01076298408589469</v>
       </c>
     </row>
     <row r="4">
@@ -762,82 +762,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0824963656652692</v>
+        <v>0.08249636566526906</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04169803500020147</v>
+        <v>0.04169803500020148</v>
       </c>
       <c r="D4" t="n">
-        <v>0.08231673608608167</v>
+        <v>0.08231673608608171</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04900173767693296</v>
+        <v>0.04900173767693309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06837801034458185</v>
+        <v>0.0683780103445818</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07834887823190351</v>
+        <v>0.07834887823190348</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07885424930307498</v>
+        <v>0.078854249303075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09189339500903353</v>
+        <v>0.09189339500903347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08200394012308755</v>
+        <v>0.08200394012308761</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1267501229451509</v>
+        <v>0.1267501229451507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.084183167002126</v>
+        <v>0.08418316700212529</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2117939049501719</v>
+        <v>0.2117939049501722</v>
       </c>
       <c r="N4" t="n">
-        <v>0.09877897530987863</v>
+        <v>0.09877897530987866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07723745435558049</v>
+        <v>0.07723745435558046</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07155339864743017</v>
+        <v>0.07155339864743016</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06202228225095359</v>
+        <v>0.06202228225095354</v>
       </c>
       <c r="R4" t="n">
-        <v>0.06837754114812183</v>
+        <v>0.06837754114812185</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07648224913763063</v>
+        <v>0.07648224913763076</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09319036316711356</v>
+        <v>0.09319036316711342</v>
       </c>
       <c r="U4" t="n">
         <v>0.1081895460815458</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05703848503095543</v>
+        <v>0.05703848503095542</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0727076097301243</v>
+        <v>0.07270760973012433</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06281021432539734</v>
+        <v>0.06281021432539706</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.06830115859139414</v>
+        <v>0.06830115859139418</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06007965772860176</v>
+        <v>0.0600796577286018</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0996660255588023</v>
+        <v>0.09966602555880219</v>
       </c>
       <c r="AB4" t="n">
         <v>0.1259082719160554</v>
@@ -850,52 +850,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03345373040786253</v>
+        <v>0.03345373040786249</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03306378991388973</v>
+        <v>0.03306378991388972</v>
       </c>
       <c r="D5" t="n">
         <v>0.03496525020439815</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03248596368441472</v>
+        <v>0.03248596368441471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03268141590337922</v>
+        <v>0.03268141590337921</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03542112159820565</v>
+        <v>0.03542112159820564</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03470102674487295</v>
+        <v>0.03470102674487294</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03537934081692912</v>
+        <v>0.03537934081692911</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03510506921534197</v>
+        <v>0.03510506921534196</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03709338257065486</v>
+        <v>0.03709338257065489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03521240295897639</v>
+        <v>0.03521240295897637</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04094380624257025</v>
+        <v>0.04094380624257026</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09877897530987863</v>
+        <v>0.03438986369007545</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03405326796484283</v>
+        <v>0.03405326796484281</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03355432624871105</v>
+        <v>0.03355432624871102</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03180387580071041</v>
+        <v>0.0318038758007104</v>
       </c>
       <c r="R5" t="n">
         <v>0.03426200578860823</v>
@@ -904,31 +904,31 @@
         <v>0.03492581739419531</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03546373466564912</v>
+        <v>0.03546373466564914</v>
       </c>
       <c r="U5" t="n">
         <v>0.03557216438800805</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03341304933266174</v>
+        <v>0.03341304933266175</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03462144847064882</v>
+        <v>0.03462144847064881</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03199918167331311</v>
+        <v>0.03199918167331308</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03626287473980417</v>
+        <v>0.03626287473980418</v>
       </c>
       <c r="Z5" t="n">
         <v>0.03217157821218128</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03592841212076766</v>
+        <v>0.03592841212076768</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03877068516867015</v>
+        <v>0.03877068516867013</v>
       </c>
     </row>
     <row r="6">
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03517095222648745</v>
+        <v>0.03517095222648742</v>
       </c>
       <c r="C6" t="n">
         <v>0.03419733818558954</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03609879847609799</v>
+        <v>0.03609879847609797</v>
       </c>
       <c r="E6" t="n">
         <v>0.03431969032755119</v>
@@ -953,70 +953,70 @@
         <v>0.03242182694518193</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0361659925563584</v>
+        <v>0.03616599255635838</v>
       </c>
       <c r="H6" t="n">
         <v>0.0358345750165728</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03651288908862895</v>
+        <v>0.03651288908862897</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0362386174870418</v>
+        <v>0.03623861748704178</v>
       </c>
       <c r="K6" t="n">
         <v>0.03822693084235472</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03634595123067621</v>
+        <v>0.03634595123067618</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04207735451427003</v>
+        <v>0.04207735451427</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09877897530987863</v>
+        <v>0.03697641314066592</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03666827575861644</v>
+        <v>0.03666827575861643</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03636024118241416</v>
+        <v>0.03636024118241415</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03518022817324817</v>
+        <v>0.03518022817324813</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03539555406030807</v>
+        <v>0.03539555406030805</v>
       </c>
       <c r="S6" t="n">
         <v>0.03605936566589515</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03659728293734896</v>
+        <v>0.03659728293734895</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03762120526193255</v>
+        <v>0.03762120526193256</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03654908543551641</v>
+        <v>0.0365490854355164</v>
       </c>
       <c r="W6" t="n">
         <v>0.03575462836227325</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03520373917878339</v>
+        <v>0.03520373917878338</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03553375036475303</v>
+        <v>0.03553375036475301</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03443616560029663</v>
+        <v>0.03443616560029661</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03706196039246751</v>
+        <v>0.03706196039246749</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03794622871513941</v>
+        <v>0.0379462287151394</v>
       </c>
     </row>
   </sheetData>
@@ -1185,82 +1185,82 @@
         <v>0.007102043182795017</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007774872993368589</v>
+        <v>0.007774872993368592</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007119545097264868</v>
+        <v>0.007119545097264864</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00711084287183115</v>
+        <v>0.007110842871831149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007145960523021044</v>
+        <v>0.00714596052302104</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007134499321804171</v>
+        <v>0.007134499321804167</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007127130940136566</v>
+        <v>0.007127130940136565</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007126297354616814</v>
+        <v>0.007126297354616821</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007144945698305435</v>
+        <v>0.007144945698305419</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007149309046164573</v>
+        <v>0.007149309046164577</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007193492698233405</v>
+        <v>0.007193492698233404</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007127511893938392</v>
+        <v>0.007127511893938394</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007143670112066672</v>
+        <v>0.00714367011206666</v>
       </c>
       <c r="O2" t="n">
         <v>0.01064461372399779</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00714994786065418</v>
+        <v>0.007149947860654163</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007115697387655989</v>
+        <v>0.007115697387655988</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007212643807988796</v>
+        <v>0.007212643807988794</v>
       </c>
       <c r="S2" t="n">
         <v>0.007166809653533707</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007142036434390501</v>
+        <v>0.007142036434390503</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008906118136871246</v>
+        <v>0.008906118136871232</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007148663739136375</v>
+        <v>0.007148663739136371</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008628733597425886</v>
+        <v>0.008628733597425874</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007311949875484183</v>
+        <v>0.007311949875484185</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007220983412744577</v>
+        <v>0.007220983412744573</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008792616550111187</v>
+        <v>0.008792616550111191</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007219434459328457</v>
+        <v>0.007219434459328452</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007100993650783297</v>
+        <v>0.0071009936507833</v>
       </c>
     </row>
     <row r="3">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0112296216042586</v>
+        <v>0.007308125461400946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01236569092399391</v>
+        <v>0.008128756504597592</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01164403113077137</v>
+        <v>0.007454043132910335</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01269782866394599</v>
+        <v>0.008646889224416178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01226623761638599</v>
+        <v>0.007669283984777847</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01197688084703055</v>
+        <v>0.007556534492741407</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01182765298816607</v>
+        <v>0.007524555708847461</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01180351899402403</v>
+        <v>0.007512057578991284</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01222625999933682</v>
+        <v>0.007646827775623668</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01233489862571468</v>
+        <v>0.007678907825883673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01334698280988413</v>
+        <v>0.008015802216690286</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01187635585001215</v>
+        <v>0.007533784844267054</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01220256140597386</v>
+        <v>0.007649758389789189</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01637711725435763</v>
+        <v>0.01133523577952508</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01232952964661388</v>
+        <v>0.007674890388863371</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01155226658504275</v>
+        <v>0.0074194083390863</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01382798450523156</v>
+        <v>0.00822320637754281</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01272463236847276</v>
+        <v>0.007805895991743392</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01217019741239464</v>
+        <v>0.007640510161972684</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01380189756291</v>
+        <v>0.009345018936501866</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01230418482185303</v>
+        <v>0.007666476528747392</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01479481529604246</v>
+        <v>0.009479480498837</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01612593800173152</v>
+        <v>0.00897596258655497</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01399622201501098</v>
+        <v>0.008269697606246761</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01358827929638817</v>
+        <v>0.009196690531350802</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01395803689745727</v>
+        <v>0.008255153673904829</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01123819000144971</v>
+        <v>0.007318027898316157</v>
       </c>
     </row>
     <row r="4">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03169416672244479</v>
+        <v>0.03169416672244478</v>
       </c>
       <c r="C4" t="n">
         <v>0.03607020295697631</v>
@@ -1367,34 +1367,34 @@
         <v>0.03558541156868456</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03304177341375189</v>
+        <v>0.03304177341375188</v>
       </c>
       <c r="F4" t="n">
         <v>0.04112340195813569</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03743136014709227</v>
+        <v>0.03743136014709224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03776096578260135</v>
+        <v>0.03776096578260137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03720438981700311</v>
+        <v>0.03720438981700308</v>
       </c>
       <c r="J4" t="n">
         <v>0.03996565043625971</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04063790142879157</v>
+        <v>0.04063790142879155</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04836939076553776</v>
+        <v>0.04836939076553775</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03772935817291709</v>
+        <v>0.03772935817291707</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04059939329079138</v>
+        <v>0.04059939329079137</v>
       </c>
       <c r="O4" t="n">
         <v>0.04451980316792379</v>
@@ -1406,34 +1406,34 @@
         <v>0.03455684977667046</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05583720914522036</v>
+        <v>0.05583720914522034</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04327783171516875</v>
+        <v>0.04327783171516872</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04052433145750615</v>
+        <v>0.04052433145750616</v>
       </c>
       <c r="U4" t="n">
-        <v>0.03796275911133247</v>
+        <v>0.03796275911133244</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04001724025209757</v>
+        <v>0.04001724025209753</v>
       </c>
       <c r="W4" t="n">
         <v>0.0502234505631196</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07287619944270833</v>
+        <v>0.07287619944270834</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05616674038319482</v>
+        <v>0.05616674038319481</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03679375340947512</v>
+        <v>0.03679375340947513</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0557136317291162</v>
+        <v>0.05571363172911619</v>
       </c>
       <c r="AB4" t="n">
         <v>0.03239369276787113</v>
@@ -1455,10 +1455,10 @@
         <v>0.03129811572958693</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03047314457245763</v>
+        <v>0.03047314457245762</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03044437377686809</v>
+        <v>0.03044437377686808</v>
       </c>
       <c r="G5" t="n">
         <v>0.03175001508199615</v>
@@ -1470,31 +1470,31 @@
         <v>0.03137438558256896</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03158187887028766</v>
+        <v>0.03158187887028764</v>
       </c>
       <c r="K5" t="n">
         <v>0.031634313224502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03213338790010364</v>
+        <v>0.03213338790010365</v>
       </c>
       <c r="M5" t="n">
         <v>0.03140986990739528</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04059939329079138</v>
+        <v>0.0305127291004967</v>
       </c>
       <c r="O5" t="n">
         <v>0.03115793249104403</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03080309461926667</v>
+        <v>0.03080309461926665</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02962173011582959</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03234970849473648</v>
+        <v>0.03234970849473647</v>
       </c>
       <c r="S5" t="n">
         <v>0.03183199063541352</v>
@@ -1506,10 +1506,10 @@
         <v>0.03082492874517943</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03123275014657775</v>
+        <v>0.0312327501465777</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03213663403579273</v>
+        <v>0.03213663403579272</v>
       </c>
       <c r="X5" t="n">
         <v>0.0319635719548018</v>
@@ -1518,7 +1518,7 @@
         <v>0.03379923864694042</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03005301813156558</v>
+        <v>0.03005301813156556</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0324264120254719</v>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0302126418715583</v>
+        <v>0.03021264187155829</v>
       </c>
       <c r="C6" t="n">
         <v>0.03117038839267649</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03113623568751431</v>
+        <v>0.0311362356875143</v>
       </c>
       <c r="E6" t="n">
         <v>0.03087040528015794</v>
@@ -1552,7 +1552,7 @@
         <v>0.03130515101388558</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03122192127241027</v>
+        <v>0.03122192127241026</v>
       </c>
       <c r="I6" t="n">
         <v>0.03121250554049634</v>
@@ -1561,16 +1561,16 @@
         <v>0.03141999882821504</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03147243318242939</v>
+        <v>0.03147243318242938</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03197150785803103</v>
+        <v>0.03197150785803102</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03124798986532268</v>
+        <v>0.03124798986532267</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04059939329079138</v>
+        <v>0.03140873882775568</v>
       </c>
       <c r="O6" t="n">
         <v>0.03200378841780437</v>
@@ -1588,31 +1588,31 @@
         <v>0.03167011059334089</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03139028568687458</v>
+        <v>0.03139028568687457</v>
       </c>
       <c r="U6" t="n">
         <v>0.03133007842090992</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03228256650750855</v>
+        <v>0.03228256650750851</v>
       </c>
       <c r="W6" t="n">
         <v>0.03197448578640003</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0333095361680723</v>
+        <v>0.03330953616807229</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03228202812478816</v>
+        <v>0.03228202812478817</v>
       </c>
       <c r="Z6" t="n">
         <v>0.03084355905743734</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0322645319833993</v>
+        <v>0.03226453198339928</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03094001976265229</v>
+        <v>0.03094001976265228</v>
       </c>
     </row>
   </sheetData>
@@ -1778,85 +1778,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007544329631665904</v>
+        <v>0.007544329631665896</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008246681699950062</v>
+        <v>0.008246681699950074</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007527995385463265</v>
+        <v>0.007527995385463258</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007424240227779355</v>
+        <v>0.007424240227779346</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007440597234068233</v>
+        <v>0.007440597234068223</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007556691107137552</v>
+        <v>0.007556691107137541</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007433003993414605</v>
+        <v>0.007433003993414609</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007497652399365147</v>
+        <v>0.007497652399365139</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007565228509074534</v>
+        <v>0.007565228509074525</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007689172124900514</v>
+        <v>0.007689172124900505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007557834672974873</v>
+        <v>0.007557834672974872</v>
       </c>
       <c r="M2" t="n">
-        <v>0.00803367324206352</v>
+        <v>0.008033673242063524</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007551855453321671</v>
+        <v>0.007551855453321662</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01114487375238057</v>
+        <v>0.01114487375238056</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00756435390589082</v>
+        <v>0.007564353905890806</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007449513052714196</v>
+        <v>0.007449513052714189</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007437725116933327</v>
+        <v>0.00743772511693332</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007551582254587912</v>
+        <v>0.007551582254587915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007535941869378598</v>
+        <v>0.007535941869378591</v>
       </c>
       <c r="U2" t="n">
         <v>0.01003893072635196</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007424156752661854</v>
+        <v>0.007424156752661844</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009534187549401399</v>
+        <v>0.00953418754940139</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007507396827526699</v>
+        <v>0.007507396827526698</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007495674992106721</v>
+        <v>0.007495674992106711</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009151499581998046</v>
+        <v>0.009151499581998042</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007577737316377065</v>
+        <v>0.007577737316377057</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007712908977996636</v>
+        <v>0.007712908977996639</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01576413281608246</v>
+        <v>0.00901672719691053</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01322461251012541</v>
+        <v>0.008735994011893211</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01544920310117069</v>
+        <v>0.008965089992645271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01419011952295181</v>
+        <v>0.009287510458050929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01341767588322111</v>
+        <v>0.008253649565911316</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01605274470920736</v>
+        <v>0.009127425867802446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01324421962083768</v>
+        <v>0.008202143341015183</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0147468028972999</v>
+        <v>0.00872349204484086</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01628444300579742</v>
+        <v>0.009227227267422594</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01919317046334976</v>
+        <v>0.01020160560745808</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01610528947590749</v>
+        <v>0.009169272631099882</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02721725110756913</v>
+        <v>0.01308151556135916</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01598780022751106</v>
+        <v>0.009139433258058514</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01885103671791134</v>
+        <v>0.01244913947087985</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01621893676272762</v>
+        <v>0.009183678058010309</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01361067616773505</v>
+        <v>0.008315283375179609</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01334953134432545</v>
+        <v>0.008236343984339162</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01594469935925103</v>
+        <v>0.00908956894998696</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01563686286927086</v>
+        <v>0.009029377944626486</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02032338106820262</v>
+        <v>0.0121815042154483</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01299934799312354</v>
+        <v>0.008082198647005677</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01827646132181305</v>
+        <v>0.0112106693949934</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01496419027701364</v>
+        <v>0.008787518533771519</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01467462769170705</v>
+        <v>0.008673548429137951</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01540781529284711</v>
+        <v>0.01002837602978791</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01657737561327645</v>
+        <v>0.009333819149195309</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0197260173059443</v>
+        <v>0.01051249048404</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0685176414702265</v>
+        <v>0.06851764147022679</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04064354295782923</v>
+        <v>0.04064354295782924</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07069675373887675</v>
+        <v>0.0706967537388766</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04567023906179279</v>
+        <v>0.0456702390617934</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05111190029294101</v>
+        <v>0.05111190029294106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07202208304774553</v>
+        <v>0.07202208304774542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0501587313206458</v>
+        <v>0.05015873132064581</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06428733883161315</v>
+        <v>0.06428733883161318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07609218463308895</v>
+        <v>0.07609218463308898</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1012985496127537</v>
+        <v>0.1012985496127538</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07461454720269775</v>
+        <v>0.07461454720270241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1850134244847007</v>
+        <v>0.1850134244847008</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07461618210410167</v>
+        <v>0.0746161821041017</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06310636768241935</v>
+        <v>0.06310636768241946</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07331111415610013</v>
+        <v>0.07331111415610019</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.05233322694240389</v>
+        <v>0.05233322694240395</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05091467987338844</v>
+        <v>0.05091467987338841</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07113236148996278</v>
+        <v>0.07113236148996283</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07244348837745417</v>
+        <v>0.07244348837745423</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09001497859277782</v>
+        <v>0.09001497859277781</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04471074536908261</v>
+        <v>0.04471074536908257</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07683950234141061</v>
+        <v>0.07683950234141065</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06536767023111081</v>
+        <v>0.0653676702311109</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0614127384519283</v>
+        <v>0.06141273845192837</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0515487564372682</v>
+        <v>0.05154875643726881</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.07924420041175084</v>
+        <v>0.07924420041175093</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1158243396496392</v>
+        <v>0.1158243396496397</v>
       </c>
     </row>
     <row r="5">
@@ -2042,25 +2042,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03242577547537954</v>
+        <v>0.03242577547537955</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03242279867280357</v>
+        <v>0.03242279867280358</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03390949767611023</v>
+        <v>0.03390949767611024</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03184925482374835</v>
+        <v>0.03184925482374839</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03151396028727515</v>
+        <v>0.03151396028727516</v>
       </c>
       <c r="G5" t="n">
         <v>0.0345795463796485</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03283652620472136</v>
+        <v>0.03283652620472137</v>
       </c>
       <c r="I5" t="n">
         <v>0.03356675968966866</v>
@@ -2072,34 +2072,34 @@
         <v>0.03573006309301724</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0342465461553042</v>
+        <v>0.03424654615530438</v>
       </c>
       <c r="M5" t="n">
         <v>0.03957742555196612</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07461618210410167</v>
+        <v>0.03288585463579333</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03289533802449579</v>
+        <v>0.03289533802449578</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03329529048620667</v>
+        <v>0.0332952904862067</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03102693430546235</v>
+        <v>0.03102693430546237</v>
       </c>
       <c r="R5" t="n">
         <v>0.03288985346668939</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03417592221336899</v>
+        <v>0.034175922213369</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03399925686749704</v>
+        <v>0.03399925686749707</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0343207386897843</v>
+        <v>0.03432073868978431</v>
       </c>
       <c r="V5" t="n">
         <v>0.03225407760493523</v>
@@ -2108,16 +2108,16 @@
         <v>0.03434238902867583</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03183365430811307</v>
+        <v>0.0318336543081131</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03520177671616925</v>
+        <v>0.03520177671616926</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03138602269470714</v>
+        <v>0.03138602269470715</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0344713556682003</v>
+        <v>0.03447135566820031</v>
       </c>
       <c r="AB5" t="n">
         <v>0.03771602243025387</v>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03359008280986087</v>
+        <v>0.03359008280986089</v>
       </c>
       <c r="C6" t="n">
         <v>0.03296697772782702</v>
@@ -2139,7 +2139,7 @@
         <v>0.03445367673113367</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03303981745277723</v>
+        <v>0.03303981745277726</v>
       </c>
       <c r="F6" t="n">
         <v>0.03105032635203219</v>
@@ -2151,25 +2151,25 @@
         <v>0.0333807052597448</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03411093874469211</v>
+        <v>0.03411093874469212</v>
       </c>
       <c r="J6" t="n">
         <v>0.03487028174351731</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0362742421480407</v>
+        <v>0.03627424214804071</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03479072521032766</v>
+        <v>0.03479072521032763</v>
       </c>
       <c r="M6" t="n">
         <v>0.04012160460698933</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07461618210410167</v>
+        <v>0.03472318717376779</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0347246376276458</v>
+        <v>0.03472463762764579</v>
       </c>
       <c r="P6" t="n">
         <v>0.03528723979201658</v>
@@ -2196,19 +2196,19 @@
         <v>0.0348862402298932</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03422100654343522</v>
+        <v>0.03422100654343529</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03408860302005604</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0329975054702708</v>
+        <v>0.03299750547027081</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03501553472322373</v>
+        <v>0.03501553472322374</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03651760095140388</v>
+        <v>0.0365176009514039</v>
       </c>
     </row>
   </sheetData>
@@ -2374,85 +2374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007481092212630267</v>
+        <v>0.007481092212630277</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008224086087521511</v>
+        <v>0.008224086087521515</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007543235702440622</v>
+        <v>0.007543235702440632</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007411277708572478</v>
+        <v>0.007411277708572491</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00741887862918143</v>
+        <v>0.007418878629181439</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007525318604194788</v>
+        <v>0.007525318604194797</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007385020659844207</v>
+        <v>0.007385020659844216</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007536066997825759</v>
+        <v>0.007536066997825769</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007535671433113992</v>
+        <v>0.007535671433113995</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007575583103447044</v>
+        <v>0.007575583103447055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00750057314825317</v>
+        <v>0.007500573148253181</v>
       </c>
       <c r="M2" t="n">
         <v>0.007923708481175991</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007462459950291298</v>
+        <v>0.007462459950291309</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01103558447693143</v>
+        <v>0.01103558447693144</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007537485802788432</v>
+        <v>0.007537485802788438</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0074192937320542</v>
+        <v>0.00741929373205421</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007385109738930036</v>
+        <v>0.007385109738930044</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007515223697315472</v>
+        <v>0.007515223697315479</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007488999687191107</v>
+        <v>0.00748899968719112</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009946127144837887</v>
+        <v>0.009946127144837896</v>
       </c>
       <c r="V2" t="n">
-        <v>0.00742463233218987</v>
+        <v>0.00742463233218988</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009502292836053442</v>
+        <v>0.009502292836053455</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007533598811863827</v>
+        <v>0.007533598811863838</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00758021928700982</v>
+        <v>0.007580219287009827</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009126443204132025</v>
+        <v>0.009126443204132029</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007562379358743852</v>
+        <v>0.007562379358743863</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00766702231543299</v>
+        <v>0.007667022315432991</v>
       </c>
     </row>
     <row r="3">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01470012827676129</v>
+        <v>0.008657422407245449</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01301756991222758</v>
+        <v>0.008657172300199868</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01620088546895065</v>
+        <v>0.009214875283757591</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01428501459050701</v>
+        <v>0.009314705967579939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01330637601225212</v>
+        <v>0.00820390578413571</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01572009551583875</v>
+        <v>0.008999206956379565</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01251657122658743</v>
+        <v>0.007939235601543365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01604215648884351</v>
+        <v>0.009168194364841797</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01599536531434601</v>
+        <v>0.009117858534443085</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01693909802270727</v>
+        <v>0.009397448637382901</v>
       </c>
       <c r="L3" t="n">
-        <v>0.015172112313407</v>
+        <v>0.008838147425764298</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02506168175609205</v>
+        <v>0.01232347769775156</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01430366115275951</v>
+        <v>0.008548975766059251</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01779086235935632</v>
+        <v>0.01205241644226256</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01599069651772445</v>
+        <v>0.009092336906226387</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01330179634466028</v>
+        <v>0.008195804059329093</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01251493035984391</v>
+        <v>0.007935568941537073</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01549681567886366</v>
+        <v>0.008926009768539097</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01493737809213869</v>
+        <v>0.008779010578649944</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01820735204333863</v>
+        <v>0.01145465188999923</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01340120568577695</v>
+        <v>0.008205890303126491</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01755585689818145</v>
+        <v>0.01096592588943209</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01597113882605631</v>
+        <v>0.00912739690189592</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01703228450298118</v>
+        <v>0.009478242274722845</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01532999097974704</v>
+        <v>0.009975447986336764</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01661541541155856</v>
+        <v>0.009341541389232407</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01905808662439362</v>
+        <v>0.01027169524953453</v>
       </c>
     </row>
     <row r="4">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05793178179688297</v>
+        <v>0.05793178179688311</v>
       </c>
       <c r="C4" t="n">
         <v>0.03789331280184379</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07438392791408416</v>
+        <v>0.07438392791408427</v>
       </c>
       <c r="E4" t="n">
         <v>0.04545056424681009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04841789483858333</v>
+        <v>0.04841789483858335</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06597107182235205</v>
+        <v>0.0659710718223521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04207177445458507</v>
+        <v>0.0420717744545851</v>
       </c>
       <c r="I4" t="n">
         <v>0.07366471938871044</v>
@@ -2577,58 +2577,58 @@
         <v>0.07042604551935749</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07568340181995016</v>
+        <v>0.07568340181995024</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06349384034694645</v>
+        <v>0.06349384034694638</v>
       </c>
       <c r="M4" t="n">
-        <v>0.155591320553717</v>
+        <v>0.1555913205537167</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.05691540669209522</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05283297005590818</v>
+        <v>0.05283297005590823</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06813693343818994</v>
+        <v>0.06813693343819001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04774458935360795</v>
+        <v>0.04774458935360796</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04179694141893638</v>
+        <v>0.04179694141893637</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06444960269866827</v>
+        <v>0.06444960269866831</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06340515039199904</v>
+        <v>0.06340515039199915</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06771338250896221</v>
+        <v>0.06771338250896218</v>
       </c>
       <c r="V4" t="n">
         <v>0.04660410178555907</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06738522713613618</v>
+        <v>0.06738522713613612</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07175775775447753</v>
+        <v>0.0717577577544776</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07961064053515404</v>
+        <v>0.07961064053515415</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04838394391763708</v>
+        <v>0.04838394391763706</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.07645564246728145</v>
+        <v>0.07645564246728155</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1041645559971453</v>
+        <v>0.1041645559971454</v>
       </c>
     </row>
     <row r="5">
@@ -2638,22 +2638,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03168754043985506</v>
+        <v>0.03168754043985508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03196084526942955</v>
+        <v>0.03196084526942956</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03391339100788111</v>
+        <v>0.03391339100788113</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03161142696841949</v>
+        <v>0.0316114269684195</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03122221695959268</v>
+        <v>0.03122221695959269</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03402700206869189</v>
+        <v>0.0340270020686919</v>
       </c>
       <c r="H5" t="n">
         <v>0.03212627931923903</v>
@@ -2662,61 +2662,61 @@
         <v>0.03383241719148909</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0338243296936331</v>
+        <v>0.03382432969363312</v>
       </c>
       <c r="K5" t="n">
         <v>0.03427876978278818</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03343149783258925</v>
+        <v>0.03343149783258927</v>
       </c>
       <c r="M5" t="n">
         <v>0.03817777439506338</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.0318197055548396</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03211952742372911</v>
+        <v>0.03211952742372912</v>
       </c>
       <c r="P5" t="n">
         <v>0.0329122106770685</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03069001482829869</v>
+        <v>0.0306900148282987</v>
       </c>
       <c r="R5" t="n">
         <v>0.03212728550849191</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0335969825238335</v>
+        <v>0.03359698252383352</v>
       </c>
       <c r="T5" t="n">
         <v>0.03330077026583812</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03299020230124294</v>
+        <v>0.03299020230124295</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03213267293021319</v>
+        <v>0.03213267293021321</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03362307368670956</v>
+        <v>0.03362307368670957</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03212081278289176</v>
+        <v>0.03212081278289177</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03584463332411713</v>
+        <v>0.03584463332411715</v>
       </c>
       <c r="Z5" t="n">
         <v>0.03113833768468146</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.034129627412343</v>
+        <v>0.03412962741234302</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03688219203946475</v>
+        <v>0.03688219203946476</v>
       </c>
     </row>
     <row r="6">
@@ -2726,22 +2726,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03256832043924215</v>
+        <v>0.03256832043924217</v>
       </c>
       <c r="C6" t="n">
         <v>0.0322245865135931</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03417713225204465</v>
+        <v>0.03417713225204467</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03247730312462757</v>
+        <v>0.03247730312462758</v>
       </c>
       <c r="F6" t="n">
         <v>0.03068187395365026</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03397474985567522</v>
+        <v>0.03397474985567523</v>
       </c>
       <c r="H6" t="n">
         <v>0.03239002056340259</v>
@@ -2762,31 +2762,31 @@
         <v>0.03844151563922633</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0569154066920952</v>
+        <v>0.03326473297283625</v>
       </c>
       <c r="O6" t="n">
         <v>0.03354046280116058</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03447808161140434</v>
+        <v>0.03447808161140435</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03277715015099637</v>
+        <v>0.03277715015099638</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03239102675265547</v>
+        <v>0.03239102675265548</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03386072376799704</v>
+        <v>0.03386072376799706</v>
       </c>
       <c r="T6" t="n">
         <v>0.03356451151000166</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03399873485793668</v>
+        <v>0.03399873485793669</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03386052382566147</v>
+        <v>0.03386052382566149</v>
       </c>
       <c r="W6" t="n">
         <v>0.03388651543884386</v>
@@ -2795,16 +2795,16 @@
         <v>0.03406827913979096</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03459487885304315</v>
+        <v>0.03459487885304316</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03240753393583812</v>
+        <v>0.03240753393583813</v>
       </c>
       <c r="AA6" t="n">
         <v>0.03439336865650656</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03555408054200989</v>
+        <v>0.0355540805420099</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007442871364654503</v>
+        <v>0.007442871364654493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007992881077880048</v>
+        <v>0.007992881077880046</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007454710015921667</v>
+        <v>0.007454710015921658</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007367446389494966</v>
+        <v>0.007367446389494954</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007416890822354568</v>
+        <v>0.007416890822354557</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007490515446361976</v>
+        <v>0.007490515446361965</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007367668761145774</v>
+        <v>0.007367668761145762</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007506074024950233</v>
+        <v>0.007506074024950224</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00750525748795453</v>
+        <v>0.007505257487954519</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007602955034147565</v>
+        <v>0.007602955034147556</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007464613552584963</v>
+        <v>0.007464613552584953</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007806193532380248</v>
+        <v>0.00780619353238025</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007399661908215402</v>
+        <v>0.007399661908215386</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01099748239706916</v>
+        <v>0.01099748239706914</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007497950387116013</v>
+        <v>0.007497950387116005</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007398352201380036</v>
+        <v>0.007398352201380029</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007401590444100463</v>
+        <v>0.007401590444100451</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007487153535406472</v>
+        <v>0.00748715353540646</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007486112368008684</v>
+        <v>0.007486112368008678</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009307240109582204</v>
+        <v>0.009307240109582195</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007450887950810073</v>
+        <v>0.007450887950810062</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008894756892727512</v>
+        <v>0.008894756892727507</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007536035361137742</v>
+        <v>0.007536035361137733</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00768765087113488</v>
+        <v>0.007687650871134869</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00908854169271036</v>
+        <v>0.009088541692710348</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00756541438770982</v>
+        <v>0.007565414387709809</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007623334722469013</v>
+        <v>0.007623334722469009</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01411097220409294</v>
+        <v>0.008402309737280093</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01260871278130648</v>
+        <v>0.008333719253456114</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01442950734184292</v>
+        <v>0.008537269192748954</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01362293572143822</v>
+        <v>0.009073420342922606</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01355809526453232</v>
+        <v>0.008243916142329432</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01520891110550747</v>
+        <v>0.008766591815459501</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01240863672304274</v>
+        <v>0.007857280889892545</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01563736756797688</v>
+        <v>0.008971969874845767</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01558552701186591</v>
+        <v>0.008918386265634843</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01787248764640403</v>
+        <v>0.009665231399530974</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01463166886078283</v>
+        <v>0.008592153621017664</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02261954569643395</v>
+        <v>0.01136314263129466</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01313903530007437</v>
+        <v>0.008100881802275299</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01754210386553087</v>
+        <v>0.01191429186953648</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01537140177616872</v>
+        <v>0.008821698686017555</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01310979504198139</v>
+        <v>0.008079088458303388</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01319968120302989</v>
+        <v>0.008132227836156971</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01514129447037099</v>
+        <v>0.008754359206362864</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01516757827294923</v>
+        <v>0.008815617122337388</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01746011399084302</v>
+        <v>0.01072775188552837</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01429821283266823</v>
+        <v>0.008455030804147086</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01534018550665861</v>
+        <v>0.009814885770070374</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01632224893070903</v>
+        <v>0.009185020019763694</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01982504717132887</v>
+        <v>0.01041464536592754</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01489964976608211</v>
+        <v>0.009770669168553549</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01698163151659631</v>
+        <v>0.009427217463663243</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01833505006469125</v>
+        <v>0.009956585485472918</v>
       </c>
     </row>
     <row r="4">
@@ -3146,28 +3146,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05298552436115465</v>
+        <v>0.05298552436115467</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03675010563135802</v>
+        <v>0.03675010563135803</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05802909422149721</v>
+        <v>0.05802909422149731</v>
       </c>
       <c r="E4" t="n">
         <v>0.0393192727907552</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05107940764866582</v>
+        <v>0.05107940764866583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06138068018514221</v>
+        <v>0.06138068018514192</v>
       </c>
       <c r="H4" t="n">
         <v>0.04172855647337104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06990234841168919</v>
+        <v>0.06990234841168923</v>
       </c>
       <c r="J4" t="n">
         <v>0.06658065956518379</v>
@@ -3176,52 +3176,52 @@
         <v>0.08373465140924578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05839460987786835</v>
+        <v>0.05839460987786838</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1297567703140891</v>
+        <v>0.129756770314089</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04730731015945103</v>
+        <v>0.04730731015945102</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05159625405982935</v>
+        <v>0.05159625405982936</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06258583482015502</v>
+        <v>0.06258583482015508</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04627257062139725</v>
+        <v>0.04627257062139724</v>
       </c>
       <c r="R4" t="n">
-        <v>0.04875320515066762</v>
+        <v>0.04875320515066761</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06169100882781992</v>
+        <v>0.06169100882781993</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0661460400618013</v>
+        <v>0.06614604006180136</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06597677571024327</v>
+        <v>0.06597677571024313</v>
       </c>
       <c r="V4" t="n">
-        <v>0.05378845965408752</v>
+        <v>0.05378845965408754</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05334724273366666</v>
+        <v>0.05334724273366664</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07409808184696871</v>
+        <v>0.07409808184696873</v>
       </c>
       <c r="Y4" t="n">
         <v>0.105595417885614</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04485349439444133</v>
+        <v>0.04485349439444131</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.08049885470723299</v>
+        <v>0.0804988547072331</v>
       </c>
       <c r="AB4" t="n">
         <v>0.09700385246230457</v>
@@ -3234,13 +3234,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03142793772478501</v>
+        <v>0.03142793772478503</v>
       </c>
       <c r="C5" t="n">
         <v>0.03187353311878952</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03306633683128921</v>
+        <v>0.03306633683128923</v>
       </c>
       <c r="E5" t="n">
         <v>0.03127945839249</v>
@@ -3255,10 +3255,10 @@
         <v>0.03208316581764011</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03364651694187852</v>
+        <v>0.03364651694187851</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03363396540311984</v>
+        <v>0.03363396540311986</v>
       </c>
       <c r="K5" t="n">
         <v>0.03474083250822847</v>
@@ -3267,19 +3267,19 @@
         <v>0.03317820183375318</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03701325738694285</v>
+        <v>0.03701325738694286</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04730731015945103</v>
+        <v>0.0312781674313343</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03202508971159965</v>
+        <v>0.03202508971159963</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03263034149550487</v>
+        <v>0.03263034149550485</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03062937010071878</v>
+        <v>0.03062937010071877</v>
       </c>
       <c r="R5" t="n">
         <v>0.03246632683135846</v>
@@ -3288,31 +3288,31 @@
         <v>0.0334328013086265</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03342104084390782</v>
+        <v>0.03342104084390783</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03294838786757501</v>
+        <v>0.03294838786757502</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03258938897820459</v>
+        <v>0.03258938897820458</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03280735579489462</v>
+        <v>0.0328073557948946</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0323224712813359</v>
+        <v>0.03232247128133591</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03719191304467905</v>
+        <v>0.03719191304467907</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03096044992141644</v>
+        <v>0.03096044992141643</v>
       </c>
       <c r="AA5" t="n">
         <v>0.0343167936371636</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03652260263920225</v>
+        <v>0.03652260263920224</v>
       </c>
     </row>
     <row r="6">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03214205419631894</v>
+        <v>0.03214205419631893</v>
       </c>
       <c r="C6" t="n">
         <v>0.03193538206462079</v>
@@ -3331,16 +3331,16 @@
         <v>0.03312818577712051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03194577023687615</v>
+        <v>0.03194577023687616</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03073596672870857</v>
+        <v>0.03073596672870856</v>
       </c>
       <c r="G6" t="n">
         <v>0.0335326241747523</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03214501476347138</v>
+        <v>0.03214501476347139</v>
       </c>
       <c r="I6" t="n">
         <v>0.03370836588770978</v>
@@ -3349,58 +3349,58 @@
         <v>0.03369581434895112</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03480268145405974</v>
+        <v>0.03480268145405976</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03324005077958443</v>
+        <v>0.03324005077958445</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03707510633277322</v>
+        <v>0.03707510633277324</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04730731015945103</v>
+        <v>0.03250639207719763</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03321527072470755</v>
+        <v>0.03321527072470754</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03396052826272013</v>
+        <v>0.03396052826272012</v>
       </c>
       <c r="Q6" t="n">
         <v>0.03249159792549386</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03252817577718971</v>
+        <v>0.03252817577718973</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03349465025445775</v>
+        <v>0.03349465025445777</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0334828897897391</v>
+        <v>0.03348288978973911</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03374562130032859</v>
+        <v>0.03374562130032858</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03404722029221728</v>
+        <v>0.03404722029221727</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03286890902895138</v>
+        <v>0.03286890902895139</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03404679296284324</v>
+        <v>0.03404679296284325</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03575935989484148</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03204099836178214</v>
+        <v>0.03204099836178213</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03437864258299488</v>
+        <v>0.03437864258299489</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03501269158564618</v>
+        <v>0.03501269158564617</v>
       </c>
     </row>
   </sheetData>
@@ -3566,34 +3566,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007178451120166703</v>
+        <v>0.007178451120166702</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008000868983977238</v>
+        <v>0.008000868983977236</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007238644906813451</v>
+        <v>0.007238644906813454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00719293701654309</v>
+        <v>0.007192937016543091</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007178174902288866</v>
+        <v>0.007178174902288869</v>
       </c>
       <c r="G2" t="n">
         <v>0.007202220021915931</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007227825385124946</v>
+        <v>0.007227825385124947</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007223583300103822</v>
+        <v>0.007223583300103825</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007225065425818253</v>
+        <v>0.007225065425818256</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007299652270728789</v>
+        <v>0.007299652270728791</v>
       </c>
       <c r="L2" t="n">
         <v>0.007276972980106309</v>
@@ -3602,7 +3602,7 @@
         <v>0.007366907114946732</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007269945098585968</v>
+        <v>0.007269945098585967</v>
       </c>
       <c r="O2" t="n">
         <v>0.01066767992702992</v>
@@ -3617,34 +3617,34 @@
         <v>0.007236039295361103</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007229327334262721</v>
+        <v>0.007229327334262722</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007199750769158767</v>
+        <v>0.00719975076915877</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009611648001160371</v>
+        <v>0.009611648001160373</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007175084167715041</v>
+        <v>0.007175084167715042</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009191375664903613</v>
+        <v>0.009191375664903609</v>
       </c>
       <c r="X2" t="n">
         <v>0.007250079284798963</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007177851703474327</v>
+        <v>0.007177851703474329</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008902494654453393</v>
+        <v>0.008902494654453391</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007262357769203112</v>
+        <v>0.007262357769203113</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007237292090991088</v>
+        <v>0.007237292090991087</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01199906901865408</v>
+        <v>0.007630268152058002</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01215420852525073</v>
+        <v>0.00825317190128223</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0134197733582872</v>
+        <v>0.008136668332293373</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01354294769175842</v>
+        <v>0.008963728202172736</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01201264512420985</v>
+        <v>0.007646669697430912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01254587950378341</v>
+        <v>0.007806357316052255</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01318114374068454</v>
+        <v>0.008064888579122966</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01307192321866885</v>
+        <v>0.008018912248807434</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01308604504569972</v>
+        <v>0.007997433788938881</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01483369877728596</v>
+        <v>0.008587443299656095</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01428186370626119</v>
+        <v>0.008382266481671065</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01642921784232027</v>
+        <v>0.009127488413728603</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0141372850181726</v>
+        <v>0.008370748241354259</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01579118874612409</v>
+        <v>0.01120867713365801</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01336612019103965</v>
+        <v>0.008095214188754852</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0129761777042577</v>
+        <v>0.007969090974140365</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01336816089734599</v>
+        <v>0.008128874800716718</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01317273348878235</v>
+        <v>0.008002039570861316</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01251195701458053</v>
+        <v>0.007815197069760462</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01605412024422425</v>
+        <v>0.0105687771610999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01192264523414857</v>
+        <v>0.007604348571610768</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01606842068477016</v>
+        <v>0.01030185343312875</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01368394937893138</v>
+        <v>0.008224372376467967</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01199486953649307</v>
+        <v>0.007636944234795153</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0145871755635744</v>
+        <v>0.009612847193840075</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01395544112220659</v>
+        <v>0.008313662906346801</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01340050071013403</v>
+        <v>0.008137339804150032</v>
       </c>
     </row>
     <row r="4">
@@ -3742,73 +3742,73 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03770587332174708</v>
+        <v>0.03770587332174707</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03220061827867459</v>
+        <v>0.0322006182786746</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05235881995091631</v>
+        <v>0.05235881995091632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04106407592526069</v>
+        <v>0.04106407592526067</v>
       </c>
       <c r="F4" t="n">
         <v>0.03897458711413753</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04176971230447383</v>
+        <v>0.04176971230447381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05110437846916549</v>
+        <v>0.05110437846916546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04933450302697199</v>
+        <v>0.04933450302697201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04724415749554856</v>
+        <v>0.04724415749554853</v>
       </c>
       <c r="K4" t="n">
         <v>0.06268521949742149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05614033991455949</v>
+        <v>0.05614033991455945</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07708447328312723</v>
+        <v>0.07708447328312722</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0578751284766137</v>
+        <v>0.05787512847661362</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0401122700627541</v>
+        <v>0.04011227006275406</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04963939432962058</v>
+        <v>0.04963939432962061</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04707473007794936</v>
+        <v>0.04707473007794932</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05274112622497851</v>
+        <v>0.05274112622497849</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04602330265129593</v>
+        <v>0.04602330265129596</v>
       </c>
       <c r="T4" t="n">
-        <v>0.04329363838720779</v>
+        <v>0.04329363838720777</v>
       </c>
       <c r="U4" t="n">
-        <v>0.05288630061153389</v>
+        <v>0.05288630061153399</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0370342986356238</v>
+        <v>0.03703429863562374</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05836165523446214</v>
+        <v>0.05836165523446216</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05453083740785648</v>
+        <v>0.05453083740785652</v>
       </c>
       <c r="Y4" t="n">
         <v>0.03840037206471662</v>
@@ -3817,10 +3817,10 @@
         <v>0.04494201930434866</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.05652591056103341</v>
+        <v>0.05652591056103336</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05276324342278441</v>
+        <v>0.0527632434227844</v>
       </c>
     </row>
     <row r="5">
@@ -3833,10 +3833,10 @@
         <v>0.03030422812125098</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03147431383419299</v>
+        <v>0.03147431383419298</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03249929266382528</v>
+        <v>0.03249929266382526</v>
       </c>
       <c r="E5" t="n">
         <v>0.03117622938367618</v>
@@ -3845,13 +3845,13 @@
         <v>0.03053715046869097</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03240203264730458</v>
+        <v>0.03240203264730457</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03237708118912761</v>
+        <v>0.03237708118912758</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03232916488735856</v>
+        <v>0.03232916488735853</v>
       </c>
       <c r="J5" t="n">
         <v>0.03234241060121625</v>
@@ -3860,37 +3860,37 @@
         <v>0.0331883989040228</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03293222588345282</v>
+        <v>0.03293222588345281</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03395134787755725</v>
+        <v>0.03395134787755723</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0578751284766137</v>
+        <v>0.03167834952519114</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03112390031164306</v>
+        <v>0.03112390031164305</v>
       </c>
       <c r="P5" t="n">
         <v>0.03156087411460369</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03047467216786061</v>
+        <v>0.0304746721678606</v>
       </c>
       <c r="R5" t="n">
         <v>0.0324698610838304</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03239404639556955</v>
+        <v>0.03239404639556954</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03205996548682828</v>
+        <v>0.03205996548682827</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03190415854977341</v>
+        <v>0.03190415854977339</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03134355356199768</v>
+        <v>0.03134355356199767</v>
       </c>
       <c r="W5" t="n">
         <v>0.03286199519423556</v>
@@ -3902,13 +3902,13 @@
         <v>0.03331737747388906</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03071883560706419</v>
+        <v>0.03071883560706418</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03276714035297203</v>
+        <v>0.03276714035297202</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03407218185021512</v>
+        <v>0.03407218185021511</v>
       </c>
     </row>
     <row r="6">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03115268524421551</v>
+        <v>0.0311526852442155</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03170174140589617</v>
+        <v>0.03170174140589618</v>
       </c>
       <c r="D6" t="n">
         <v>0.03272672023552845</v>
@@ -3930,16 +3930,16 @@
         <v>0.03200406985517346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02998249631057786</v>
+        <v>0.02998249631057785</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03231528461910759</v>
+        <v>0.0323152846191076</v>
       </c>
       <c r="H6" t="n">
         <v>0.03260450876083078</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03255659245906173</v>
+        <v>0.03255659245906172</v>
       </c>
       <c r="J6" t="n">
         <v>0.03256983817291943</v>
@@ -3954,7 +3954,7 @@
         <v>0.03417877544926035</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0578751284766137</v>
+        <v>0.03308027030039851</v>
       </c>
       <c r="O6" t="n">
         <v>0.03249937013633929</v>
@@ -3963,7 +3963,7 @@
         <v>0.03307990273232553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03251500915601421</v>
+        <v>0.03251500915601422</v>
       </c>
       <c r="R6" t="n">
         <v>0.0326972886555336</v>
@@ -3972,10 +3972,10 @@
         <v>0.03262147396727273</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03228739305853147</v>
+        <v>0.03228739305853148</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03287210642908244</v>
+        <v>0.03287210642908243</v>
       </c>
       <c r="V6" t="n">
         <v>0.03301798642250942</v>
@@ -3984,16 +3984,16 @@
         <v>0.0330891249961088</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03285587679494849</v>
+        <v>0.0328558767949485</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03204003303755772</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03195048201279781</v>
+        <v>0.03195048201279782</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03299456792467522</v>
+        <v>0.03299456792467521</v>
       </c>
       <c r="AB6" t="n">
         <v>0.03271691060814731</v>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007149997346538092</v>
+        <v>0.007149997346538088</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008010157894173302</v>
+        <v>0.008010157894173298</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007146510392011347</v>
+        <v>0.007146510392011342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007186452779529298</v>
+        <v>0.007186452779529293</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007184469533504003</v>
+        <v>0.007184469533504005</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007168275198250898</v>
+        <v>0.007168275198250893</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007174193236894459</v>
+        <v>0.007174193236894454</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007173135982381788</v>
+        <v>0.007173135982381786</v>
       </c>
       <c r="J2" t="n">
         <v>0.007177435323390176</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007156507106177728</v>
+        <v>0.007156507106177722</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007186940659828537</v>
+        <v>0.007186940659828533</v>
       </c>
       <c r="M2" t="n">
         <v>0.007138428685135878</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007185720422487028</v>
+        <v>0.007185720422487022</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01065438786226199</v>
+        <v>0.010654387862262</v>
       </c>
       <c r="P2" t="n">
         <v>0.007181418373780814</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00713930782390091</v>
+        <v>0.007139307823900909</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007244001430910061</v>
+        <v>0.007244001430910058</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007182590205136232</v>
+        <v>0.007182590205136227</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007151169380174746</v>
+        <v>0.007151169380174742</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009513011562436627</v>
+        <v>0.00951301156243662</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007177131925132939</v>
+        <v>0.007177131925132934</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009184745629210943</v>
+        <v>0.009184745629210938</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007326841502954014</v>
+        <v>0.00732684150295401</v>
       </c>
       <c r="Y2" t="n">
         <v>0.007174828140198122</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008881200337656787</v>
+        <v>0.008881200337656785</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007213408412267324</v>
+        <v>0.007213408412267315</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007120646412016197</v>
+        <v>0.007120646412016193</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01180136808493392</v>
+        <v>0.007554821078728249</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01267465141618338</v>
+        <v>0.008424436264738825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01173251052679151</v>
+        <v>0.007536641833967369</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0138552243194286</v>
+        <v>0.009061817641463753</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01262488854052409</v>
+        <v>0.007843199831030918</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01222133215359522</v>
+        <v>0.007686008109125739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0123881109922979</v>
+        <v>0.007773508210277802</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01235642470305013</v>
+        <v>0.007755047387354612</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01244010856064001</v>
+        <v>0.007766860481682871</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01196367493054391</v>
+        <v>0.007610292313743983</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01265777506803625</v>
+        <v>0.007820871262051186</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0116026599126743</v>
+        <v>0.007488243628239607</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0126405425398038</v>
+        <v>0.007843716884733684</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01617525487106376</v>
+        <v>0.01131803474217975</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01252201309704737</v>
+        <v>0.007796727604561175</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01156230229731626</v>
+        <v>0.007472722465340515</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01401863923158318</v>
+        <v>0.008336241100312563</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01255370862339587</v>
+        <v>0.007792456297379911</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01184162372969513</v>
+        <v>0.007573616490160642</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01382135899833558</v>
+        <v>0.009812124754886688</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01242691405196853</v>
+        <v>0.007758635825635534</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01591407795012328</v>
+        <v>0.0102319462726809</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01593241604354607</v>
+        <v>0.008957650669535388</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0123860999729975</v>
+        <v>0.007762834485392588</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01460010398516188</v>
+        <v>0.009602818417616725</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0132804311488229</v>
+        <v>0.008070815495041508</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01116871555765358</v>
+        <v>0.007345060597693425</v>
       </c>
     </row>
     <row r="4">
@@ -4341,52 +4341,52 @@
         <v>0.03567777744285996</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03628320983814187</v>
+        <v>0.03628320983814185</v>
       </c>
       <c r="D4" t="n">
         <v>0.03562352934641679</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04290327242339412</v>
+        <v>0.04290327242339414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04339734665104894</v>
+        <v>0.04339734665104892</v>
       </c>
       <c r="G4" t="n">
         <v>0.03831689923632885</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04219152233452186</v>
+        <v>0.04219152233452187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0413095005879253</v>
+        <v>0.04130950058792528</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04065286288301247</v>
+        <v>0.04065286288301245</v>
       </c>
       <c r="K4" t="n">
         <v>0.0371941603827355</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04106131929914639</v>
+        <v>0.04106131929914637</v>
       </c>
       <c r="M4" t="n">
         <v>0.03440857233834131</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04302163601102811</v>
+        <v>0.04302163601102812</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04236307757340519</v>
+        <v>0.04236307757340518</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04133303151029907</v>
+        <v>0.04133303151029908</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03375800636445991</v>
+        <v>0.03375800636445992</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05643339301726889</v>
+        <v>0.05643339301726888</v>
       </c>
       <c r="S4" t="n">
         <v>0.04063089951779773</v>
@@ -4398,19 +4398,19 @@
         <v>0.03280961389217637</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0401893684971405</v>
+        <v>0.04018936849714049</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0535710035103856</v>
+        <v>0.05357100351038559</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07020698731519272</v>
+        <v>0.07020698731519279</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04127106250070527</v>
+        <v>0.04127106250070524</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04385847585086988</v>
+        <v>0.04385847585086983</v>
       </c>
       <c r="AA4" t="n">
         <v>0.04894671903547194</v>
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02999412685252222</v>
+        <v>0.02999412685252221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03136528659618969</v>
+        <v>0.03136528659618967</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03132504450058421</v>
+        <v>0.03132504450058419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03104656546861147</v>
+        <v>0.03104656546861145</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03059698347325501</v>
+        <v>0.030596983473255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03185502954412805</v>
+        <v>0.03185502954412803</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03163773496827672</v>
+        <v>0.0316377349682767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03162579279219502</v>
+        <v>0.03162579279219501</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03167122745412559</v>
+        <v>0.03167122745412558</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03143796198580918</v>
+        <v>0.03143796198580915</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03178172297442145</v>
+        <v>0.03178172297442143</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03126246075955198</v>
+        <v>0.03126246075955195</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04302163601102811</v>
+        <v>0.03070572467261188</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03104147435044306</v>
+        <v>0.03104147435044305</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03087748380080861</v>
+        <v>0.0308774838008086</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02960408768598621</v>
+        <v>0.0296040876859862</v>
       </c>
       <c r="R5" t="n">
-        <v>0.03242625063303883</v>
+        <v>0.03242625063303882</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03173258258736381</v>
+        <v>0.03173258258736379</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03137766991513034</v>
+        <v>0.03137766991513032</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03051753003733171</v>
+        <v>0.0305175300373317</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03127527411171341</v>
+        <v>0.03127527411171339</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03242017031605567</v>
+        <v>0.03242017031605565</v>
       </c>
       <c r="X5" t="n">
         <v>0.0318479579819743</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03300581873074766</v>
+        <v>0.03300581873074764</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03051607690633357</v>
+        <v>0.03051607690633355</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03208068841398519</v>
+        <v>0.03208068841398517</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03248408704883739</v>
+        <v>0.03248408704883736</v>
       </c>
     </row>
     <row r="6">
@@ -4517,10 +4517,10 @@
         <v>0.03064759585507405</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03142560055255252</v>
+        <v>0.03142560055255251</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03138535845694703</v>
+        <v>0.03138535845694702</v>
       </c>
       <c r="E6" t="n">
         <v>0.03165716371890014</v>
@@ -4529,43 +4529,43 @@
         <v>0.03002258216309753</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03163120263470193</v>
+        <v>0.03163120263470192</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03169804892463954</v>
+        <v>0.03169804892463953</v>
       </c>
       <c r="I6" t="n">
         <v>0.03168610674855785</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03173154141048842</v>
+        <v>0.03173154141048841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.031498275942172</v>
+        <v>0.03149827594217199</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03184203693078427</v>
+        <v>0.03184203693078426</v>
       </c>
       <c r="M6" t="n">
         <v>0.03132277471591498</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04302163601102811</v>
+        <v>0.03182825378867505</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03212964470104969</v>
+        <v>0.03212964470104968</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03209321929887395</v>
+        <v>0.03209321929887394</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03130400281576828</v>
+        <v>0.03130400281576827</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03248656458940166</v>
+        <v>0.03248656458940165</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03179289654372663</v>
+        <v>0.03179289654372662</v>
       </c>
       <c r="T6" t="n">
         <v>0.03143798387149315</v>
@@ -4574,19 +4574,19 @@
         <v>0.0312475774816173</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03260792681936661</v>
+        <v>0.03260792681936662</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03248021496848825</v>
+        <v>0.03248021496848824</v>
       </c>
       <c r="X6" t="n">
         <v>0.03342228131145391</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.03170522044952442</v>
+        <v>0.03170522044952441</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03150359768797618</v>
+        <v>0.03150359768797617</v>
       </c>
       <c r="AA6" t="n">
         <v>0.032141002370348</v>
@@ -4758,85 +4758,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007153626716230687</v>
+        <v>0.00715362671623068</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00778719209126994</v>
+        <v>0.007787192091269941</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007136774993058181</v>
+        <v>0.007136774993058176</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007185218111676045</v>
+        <v>0.007185218111676041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0071533962594897</v>
+        <v>0.007153396259489695</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00712968305382713</v>
+        <v>0.007129683053827123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007131765602792302</v>
+        <v>0.007131765602792297</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007127886759743319</v>
+        <v>0.007127886759743315</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007149159112417439</v>
+        <v>0.007149159112417435</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007122034910516259</v>
+        <v>0.007122034910516252</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007175329719245835</v>
+        <v>0.00717532971924583</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007114647332645052</v>
+        <v>0.007114647332645055</v>
       </c>
       <c r="N2" t="n">
         <v>0.007142943355554851</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01071139927736182</v>
+        <v>0.01071139927736181</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007178104552138081</v>
+        <v>0.007178104552138086</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007116057875882574</v>
+        <v>0.007116057875882569</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007225262466048856</v>
+        <v>0.007225262466048855</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007155795179668488</v>
+        <v>0.007155795179668483</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007122648875694515</v>
+        <v>0.007122648875694509</v>
       </c>
       <c r="U2" t="n">
         <v>0.008879220837713924</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007162774432563881</v>
+        <v>0.007162774432563886</v>
       </c>
       <c r="W2" t="n">
-        <v>0.008633052274449245</v>
+        <v>0.008633052274449243</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007353048859300671</v>
+        <v>0.007353048859300662</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007150417262024125</v>
+        <v>0.007150417262024122</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008835026474528449</v>
+        <v>0.008835026474528442</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007199657142551649</v>
+        <v>0.007199657142551644</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007110361871011307</v>
+        <v>0.007110361871011295</v>
       </c>
     </row>
     <row r="3">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01228565283006013</v>
+        <v>0.007665623782246971</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0125266022275358</v>
+        <v>0.008186568146683166</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01191272067708673</v>
+        <v>0.007548591084057529</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01429854166340679</v>
+        <v>0.009195422046252611</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01230688125014169</v>
+        <v>0.007687620220281475</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0117345884307507</v>
+        <v>0.007478235002667975</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01180223511109001</v>
+        <v>0.007517138113634502</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01170718417784933</v>
+        <v>0.007481114640351555</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01219073108689495</v>
+        <v>0.007635297702117038</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01156777045993025</v>
+        <v>0.007428593317114133</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01279343885194328</v>
+        <v>0.007822965951758173</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01145226950171429</v>
+        <v>0.007389588839254955</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01205219356896245</v>
+        <v>0.007595398888754527</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01730435495143968</v>
+        <v>0.0116601787309694</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01284522756392242</v>
+        <v>0.00784889001122209</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01142771900060248</v>
+        <v>0.007379104492924909</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01398948690150747</v>
+        <v>0.008280139291403872</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01233874402071084</v>
+        <v>0.007678807850714794</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01158376746145525</v>
+        <v>0.007436868042199668</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01320589304867689</v>
+        <v>0.009144627851208384</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01249781284875968</v>
+        <v>0.007733831649686672</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0149102878110652</v>
+        <v>0.009507147147101866</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01694800612966393</v>
+        <v>0.009240107836654176</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01222448402987811</v>
+        <v>0.007658192764854513</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0141617360827897</v>
+        <v>0.009395782603916944</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01336616273220384</v>
+        <v>0.008050787164984932</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01132849279042276</v>
+        <v>0.00735119638953916</v>
       </c>
     </row>
     <row r="4">
@@ -4934,58 +4934,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0400596242656267</v>
+        <v>0.04005962426562669</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0374635457159167</v>
+        <v>0.03746354571591672</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03787143518314379</v>
+        <v>0.03787143518314378</v>
       </c>
       <c r="E4" t="n">
         <v>0.04574351663561509</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04159686245870073</v>
+        <v>0.04159686245870074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03554532539675211</v>
+        <v>0.03554532539675222</v>
       </c>
       <c r="H4" t="n">
         <v>0.03744770436670918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03633921318283792</v>
+        <v>0.03633921318283793</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03951807041640238</v>
+        <v>0.03951807041640237</v>
       </c>
       <c r="K4" t="n">
         <v>0.03478514245113464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04328637961921517</v>
+        <v>0.04328637961921519</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03400718497079887</v>
+        <v>0.03400718497079888</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03893826925947795</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05142588984201156</v>
+        <v>0.05142588984201157</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04411474668008081</v>
+        <v>0.04411474668008079</v>
       </c>
       <c r="Q4" t="n">
         <v>0.03347736893824266</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05715147908023804</v>
+        <v>0.057151479080238</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04020557695044676</v>
+        <v>0.04020557695044679</v>
       </c>
       <c r="T4" t="n">
         <v>0.03513441374181576</v>
@@ -4997,16 +4997,16 @@
         <v>0.04153096878362909</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05055074943137192</v>
+        <v>0.05055074943137195</v>
       </c>
       <c r="X4" t="n">
-        <v>0.07848390213239498</v>
+        <v>0.07848390213239495</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04063999353997316</v>
+        <v>0.04063999353997318</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04093631252284548</v>
+        <v>0.04093631252284549</v>
       </c>
       <c r="AA4" t="n">
         <v>0.05040327496577265</v>
@@ -5037,13 +5037,13 @@
         <v>0.03045623482746308</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03161551162013386</v>
+        <v>0.03161551162013387</v>
       </c>
       <c r="H5" t="n">
         <v>0.03135762253945758</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03131380922286333</v>
+        <v>0.03131380922286334</v>
       </c>
       <c r="J5" t="n">
         <v>0.03155097660235302</v>
@@ -5055,10 +5055,10 @@
         <v>0.03184969927528387</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03119139587576512</v>
+        <v>0.03119139587576513</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03043186757646984</v>
       </c>
       <c r="O5" t="n">
         <v>0.03159311447368408</v>
@@ -5079,7 +5079,7 @@
         <v>0.03125464491298633</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03052675050593232</v>
+        <v>0.03052675050593231</v>
       </c>
       <c r="V5" t="n">
         <v>0.03131598666775717</v>
@@ -5097,10 +5097,10 @@
         <v>0.03032207918344274</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03212448871269076</v>
+        <v>0.03212448871269075</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03254935532812448</v>
+        <v>0.03254935532812447</v>
       </c>
     </row>
     <row r="6">
@@ -5113,10 +5113,10 @@
         <v>0.03074250193803371</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0312619191199021</v>
+        <v>0.03126191911990209</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03127977459018287</v>
+        <v>0.03127977459018286</v>
       </c>
       <c r="E6" t="n">
         <v>0.03165903049450453</v>
@@ -5125,7 +5125,7 @@
         <v>0.02979015454127074</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03119966847892093</v>
+        <v>0.03119966847892094</v>
       </c>
       <c r="H6" t="n">
         <v>0.03122319122269637</v>
@@ -5137,34 +5137,34 @@
         <v>0.03141654528559182</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03111327857709883</v>
+        <v>0.03111327857709882</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03171526795852266</v>
+        <v>0.03171526795852265</v>
       </c>
       <c r="M6" t="n">
         <v>0.03105696455900418</v>
       </c>
       <c r="N6" t="n">
-        <v>0.03893826925947794</v>
+        <v>0.03134944908216967</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03246272704652453</v>
+        <v>0.03246272704652452</v>
       </c>
       <c r="P6" t="n">
         <v>0.03204018652722196</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03104576582614573</v>
+        <v>0.03104576582614572</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03227928130386119</v>
+        <v>0.03227928130386117</v>
       </c>
       <c r="S6" t="n">
         <v>0.03149461634766432</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03112021359622513</v>
+        <v>0.03112021359622512</v>
       </c>
       <c r="U6" t="n">
         <v>0.03105558768082935</v>
@@ -5182,7 +5182,7 @@
         <v>0.03143387029390696</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0311313101423627</v>
+        <v>0.03113131014236269</v>
       </c>
       <c r="AA6" t="n">
         <v>0.03199005739592956</v>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007436782585150761</v>
+        <v>0.007436782585150756</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00818666029185927</v>
+        <v>0.008186660291859349</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007450716361015772</v>
+        <v>0.0074507163610158</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007375308796010314</v>
+        <v>0.007375308796010294</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007386184070313683</v>
+        <v>0.007386184070313702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007511430671054433</v>
+        <v>0.007511430671054491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007395269734396187</v>
+        <v>0.007395269734396213</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007474572299008913</v>
+        <v>0.00747457229900893</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007507826854682743</v>
+        <v>0.00750782685468273</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007556037364221652</v>
+        <v>0.007556037364221629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007507342179812954</v>
+        <v>0.007507342179812967</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007982925237638185</v>
+        <v>0.007982925237638149</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007557694701079039</v>
+        <v>0.007557694701079139</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01099985749042525</v>
+        <v>0.01099985749042526</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007498701056345246</v>
+        <v>0.007498701056345255</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007412674552719479</v>
+        <v>0.007412674552719533</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007433041414635522</v>
+        <v>0.007433041414635515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007461603157074984</v>
+        <v>0.007461603157074954</v>
       </c>
       <c r="T2" t="n">
-        <v>0.007461530377191123</v>
+        <v>0.00746153037719117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009905570276084007</v>
+        <v>0.009905570276084064</v>
       </c>
       <c r="V2" t="n">
-        <v>0.007375166254851047</v>
+        <v>0.007375166254851065</v>
       </c>
       <c r="W2" t="n">
-        <v>0.00937921197644255</v>
+        <v>0.009379211976442535</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007507552389288445</v>
+        <v>0.007507552389288512</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00744488453071912</v>
+        <v>0.007444884530719078</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.009117578150234871</v>
+        <v>0.009117578150234926</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.007514845030960251</v>
+        <v>0.007514845030960246</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007626082251826485</v>
+        <v>0.007626082251826518</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01410956273084593</v>
+        <v>0.008433404092057515</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01268768348834189</v>
+        <v>0.008526397239130755</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0144787232477273</v>
+        <v>0.008602421280361117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01388896227458816</v>
+        <v>0.00916369183463518</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01297918913618282</v>
+        <v>0.008074697498391717</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01582922773536066</v>
+        <v>0.009005605014768249</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01319690101729127</v>
+        <v>0.008161821638551949</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01504150397324737</v>
+        <v>0.008797871850293149</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0157774909762849</v>
+        <v>0.00900624346636616</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01692069238493431</v>
+        <v>0.009380702966262007</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01576006985455675</v>
+        <v>0.009007820294593806</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02684381461618824</v>
+        <v>0.0127691420467408</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01695407589182945</v>
+        <v>0.00945033108737061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01754715724239388</v>
+        <v>0.01195084492167723</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01552981402078418</v>
+        <v>0.008925174754312832</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01358339137526234</v>
+        <v>0.008275297490762995</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01407660863153372</v>
+        <v>0.008468948722594752</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01468806667686242</v>
+        <v>0.008614495478787445</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01473287816485911</v>
+        <v>0.00868982781817767</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01871364850755253</v>
+        <v>0.01158359837699195</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01269282880792376</v>
+        <v>0.007955318870685863</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01628492233098876</v>
+        <v>0.01047644492073909</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01580061862833001</v>
+        <v>0.009054142610786967</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01432418094636917</v>
+        <v>0.00852843197885747</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01546415251065958</v>
+        <v>0.0100163573037827</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01594625991070354</v>
+        <v>0.009091830035040228</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01854369774160039</v>
+        <v>0.01006502487691688</v>
       </c>
     </row>
     <row r="4">
@@ -5530,70 +5530,70 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05452956275502487</v>
+        <v>0.054529562755025</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03597411528091739</v>
+        <v>0.0359741152809174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06164195117204464</v>
+        <v>0.06164195117204466</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04316835776792444</v>
+        <v>0.04316835776792455</v>
       </c>
       <c r="F4" t="n">
         <v>0.04700356755369059</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0686908113872976</v>
+        <v>0.06869081138729763</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04999133975042464</v>
+        <v>0.04999133975042463</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06706612307023593</v>
+        <v>0.06706612307023596</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07001802726529986</v>
+        <v>0.07001802726529992</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07947321601827032</v>
+        <v>0.07947321601827037</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07032729628741466</v>
+        <v>0.07032729628741514</v>
       </c>
       <c r="M4" t="n">
-        <v>0.169819450486542</v>
+        <v>0.1698194504865421</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08395751248540131</v>
+        <v>0.0839575124854013</v>
       </c>
       <c r="O4" t="n">
         <v>0.05284703326991386</v>
       </c>
       <c r="P4" t="n">
-        <v>0.06753974031881191</v>
+        <v>0.06753974031881194</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0518592887139968</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05842760349638604</v>
+        <v>0.05842760349638602</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05855696086239676</v>
+        <v>0.05855696086239677</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06401516667972325</v>
+        <v>0.0640151666797233</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07580012373396054</v>
+        <v>0.0758001237339609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.04238752363409239</v>
+        <v>0.04238752363409234</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05903268188401276</v>
+        <v>0.05903268188401283</v>
       </c>
       <c r="X4" t="n">
         <v>0.07357731413833055</v>
@@ -5602,13 +5602,13 @@
         <v>0.05842764603727888</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05181594326830368</v>
+        <v>0.05181594326830363</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0736660213741681</v>
+        <v>0.07366602137416818</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1039473557087252</v>
+        <v>0.1039473557087251</v>
       </c>
     </row>
     <row r="5">
@@ -5618,55 +5618,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03155172231363985</v>
+        <v>0.03155172231363986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03206524598035036</v>
+        <v>0.03206524598035038</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03334192525300024</v>
+        <v>0.03334192525300023</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03162073654430955</v>
+        <v>0.03162073654430957</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03123456223290253</v>
+        <v>0.03123456223290256</v>
       </c>
       <c r="G5" t="n">
         <v>0.03436629604465902</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03271563009862338</v>
+        <v>0.03271563009862337</v>
       </c>
       <c r="I5" t="n">
         <v>0.03361138904690619</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03398303815635005</v>
+        <v>0.03398303815635006</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03453157443426514</v>
+        <v>0.03453157443426517</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03398153992547755</v>
+        <v>0.03398153992547757</v>
       </c>
       <c r="M5" t="n">
         <v>0.03930969540035929</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08395751248540131</v>
+        <v>0.03328459039089632</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03220410170022823</v>
+        <v>0.03220410170022824</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03288079590520546</v>
+        <v>0.03288079590520547</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03095852567460409</v>
+        <v>0.0309585256746041</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0331422786027577</v>
+        <v>0.03314227860275771</v>
       </c>
       <c r="S5" t="n">
         <v>0.03346489662266199</v>
@@ -5675,28 +5675,28 @@
         <v>0.03346407454039398</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0334686357421074</v>
+        <v>0.03346863574210741</v>
       </c>
       <c r="V5" t="n">
         <v>0.03201539321463578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03329159074809729</v>
+        <v>0.03329159074809728</v>
       </c>
       <c r="X5" t="n">
-        <v>0.03217986518071189</v>
+        <v>0.03217986518071191</v>
       </c>
       <c r="Y5" t="n">
         <v>0.03489787629879276</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03135269820027321</v>
+        <v>0.03135269820027323</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03406628808066844</v>
+        <v>0.03406628808066845</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03701003990850163</v>
+        <v>0.03701003990850164</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03269738851085149</v>
+        <v>0.03269738851085151</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03260562653516257</v>
+        <v>0.03260562653516255</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03388230580781243</v>
+        <v>0.03388230580781241</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03279339261665704</v>
+        <v>0.03279339261665702</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0307846503526745</v>
+        <v>0.03078465035267453</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0345681011170348</v>
+        <v>0.03456810111703481</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03325601065343557</v>
+        <v>0.03325601065343559</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03415176960171837</v>
+        <v>0.03415176960171835</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03452341871116224</v>
+        <v>0.03452341871116227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03507195498907733</v>
+        <v>0.03507195498907734</v>
       </c>
       <c r="L6" t="n">
         <v>0.03452192048028976</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03985007595517111</v>
+        <v>0.03985007595517112</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08395751248540131</v>
+        <v>0.0350906753712954</v>
       </c>
       <c r="O6" t="n">
         <v>0.03400288084089354</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03483889332113567</v>
+        <v>0.03483889332113566</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03345260533038243</v>
+        <v>0.03345260533038245</v>
       </c>
       <c r="R6" t="n">
-        <v>0.03368265915756991</v>
+        <v>0.03368265915756988</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0340052771774742</v>
+        <v>0.03400527717747422</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03400445509520619</v>
+        <v>0.03400445509520618</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03480693349250098</v>
+        <v>0.034806933492501</v>
       </c>
       <c r="V6" t="n">
         <v>0.03418885130533075</v>
       </c>
       <c r="W6" t="n">
-        <v>0.03383165040827932</v>
+        <v>0.03383165040827931</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03452429489301728</v>
+        <v>0.03452429489301725</v>
       </c>
       <c r="Y6" t="n">
         <v>0.03381643260183657</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03293671480706542</v>
+        <v>0.03293671480706541</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.03460666863548063</v>
+        <v>0.03460666863548065</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03584480915202951</v>
+        <v>0.03584480915202953</v>
       </c>
     </row>
   </sheetData>
@@ -5950,25 +5950,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007212834344806453</v>
+        <v>0.007212834344806452</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008093826638324768</v>
+        <v>0.008093826638324766</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007239048529640764</v>
+        <v>0.00723904852964076</v>
       </c>
       <c r="E2" t="n">
         <v>0.007243383570073144</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007250384649296576</v>
+        <v>0.007250384649296574</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007384505854404308</v>
+        <v>0.007384505854404309</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007242563393966236</v>
+        <v>0.007242563393966237</v>
       </c>
       <c r="I2" t="n">
         <v>0.007246065901510271</v>
@@ -5977,34 +5977,34 @@
         <v>0.00730470280104506</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007278979097833197</v>
+        <v>0.007278979097833199</v>
       </c>
       <c r="L2" t="n">
-        <v>0.007356258627681407</v>
+        <v>0.007356258627681403</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007276492081320297</v>
+        <v>0.007276492081320293</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007274554542361871</v>
+        <v>0.00727455454236187</v>
       </c>
       <c r="O2" t="n">
         <v>0.01072918774784667</v>
       </c>
       <c r="P2" t="n">
-        <v>0.007329608202586577</v>
+        <v>0.007329608202586574</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.007257177179703394</v>
+        <v>0.007257177179703393</v>
       </c>
       <c r="R2" t="n">
         <v>0.007322857128408713</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007288632745258866</v>
+        <v>0.007288632745258862</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00725510931121618</v>
+        <v>0.007255109311216181</v>
       </c>
       <c r="U2" t="n">
         <v>0.009631477087498352</v>
@@ -6013,22 +6013,22 @@
         <v>0.007244203838818478</v>
       </c>
       <c r="W2" t="n">
-        <v>0.009280314017044629</v>
+        <v>0.009280314017044627</v>
       </c>
       <c r="X2" t="n">
         <v>0.007398371915164302</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.007415140760949734</v>
+        <v>0.007415140760949732</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.008903236074109913</v>
+        <v>0.008903236074109909</v>
       </c>
       <c r="AA2" t="n">
         <v>0.007274576689497279</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.007404356868419604</v>
+        <v>0.0074043568684196</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01145386331340117</v>
+        <v>0.007477143297577696</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01276905559777315</v>
+        <v>0.008497423467969367</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01207285958839102</v>
+        <v>0.007695724718668653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01335985424397105</v>
+        <v>0.008925783573338507</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01234274390928259</v>
+        <v>0.007787762164284041</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01540429298444105</v>
+        <v>0.008780712569380719</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01216280468420482</v>
+        <v>0.007735941001459332</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01223915931929243</v>
+        <v>0.007757474548086958</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01357920696425362</v>
+        <v>0.008189317838748371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01299935322361949</v>
+        <v>0.007994591215404634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01477341552862656</v>
+        <v>0.008584304254104932</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0129940965554827</v>
+        <v>0.007999799404096836</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01289491561705951</v>
+        <v>0.00798105671890747</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01580553799002322</v>
+        <v>0.01124503297109541</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01413707872326522</v>
+        <v>0.008380286312060843</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01249069504566256</v>
+        <v>0.007825601227788871</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01404055478741275</v>
+        <v>0.008392364349141848</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01320294830210786</v>
+        <v>0.008055214128396791</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01244875961181161</v>
+        <v>0.007828219265120813</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01455480189187763</v>
+        <v>0.01010509165091945</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01217697245908371</v>
+        <v>0.007717512077630251</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01607701726028098</v>
+        <v>0.01035490780953169</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01578535192876285</v>
+        <v>0.008967462765330246</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01615559156646942</v>
+        <v>0.009095270838502067</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01385080074307818</v>
+        <v>0.009379112460145653</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01289100938468442</v>
+        <v>0.007976304301035504</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01591269211072567</v>
+        <v>0.009054553790595405</v>
       </c>
     </row>
     <row r="4">
@@ -6126,7 +6126,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03244141156753562</v>
+        <v>0.03244141156753561</v>
       </c>
       <c r="C4" t="n">
         <v>0.03660930360377414</v>
@@ -6135,13 +6135,13 @@
         <v>0.03827416329099732</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03831025546263483</v>
+        <v>0.03831025546263485</v>
       </c>
       <c r="F4" t="n">
         <v>0.04062371098096143</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06208552245025358</v>
+        <v>0.06208552245025355</v>
       </c>
       <c r="H4" t="n">
         <v>0.03978872291072096</v>
@@ -6153,31 +6153,31 @@
         <v>0.04927754080039603</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04486181405909187</v>
+        <v>0.04486181405909186</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05841046140331485</v>
+        <v>0.05841046140331486</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04552602595708106</v>
+        <v>0.04552602595708104</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04546866469835963</v>
+        <v>0.04546866469835962</v>
       </c>
       <c r="O4" t="n">
-        <v>0.03906843999066954</v>
+        <v>0.03906843999066956</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0537314642166185</v>
+        <v>0.05373146421661851</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04087344530208753</v>
+        <v>0.04087344530208752</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05679065400422902</v>
+        <v>0.05679065400422903</v>
       </c>
       <c r="S4" t="n">
-        <v>0.04569336763704206</v>
+        <v>0.04569336763704204</v>
       </c>
       <c r="T4" t="n">
         <v>0.04175580930868846</v>
@@ -6186,25 +6186,25 @@
         <v>0.0381907476775013</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03797985681694825</v>
+        <v>0.03797985681694826</v>
       </c>
       <c r="W4" t="n">
-        <v>0.05581329289604469</v>
+        <v>0.05581329289604468</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06993441089206116</v>
+        <v>0.06993441089206119</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07288647867488053</v>
+        <v>0.07288647867488045</v>
       </c>
       <c r="Z4" t="n">
         <v>0.03798696173372321</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04514404288155332</v>
+        <v>0.04514404288155329</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.07406769734626496</v>
+        <v>0.07406769734626495</v>
       </c>
     </row>
     <row r="5">
@@ -6217,10 +6217,10 @@
         <v>0.02991221707570938</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03155575206635012</v>
+        <v>0.03155575206635013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03163523764877023</v>
+        <v>0.03163523764877024</v>
       </c>
       <c r="E5" t="n">
         <v>0.03092441149094667</v>
@@ -6235,10 +6235,10 @@
         <v>0.03167493965824399</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0317145020921869</v>
+        <v>0.03171450209218691</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03237314978356705</v>
+        <v>0.03237314978356706</v>
       </c>
       <c r="K5" t="n">
         <v>0.03208627178547264</v>
@@ -6250,7 +6250,7 @@
         <v>0.03207995409241789</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04546866469835963</v>
+        <v>0.03093019322299966</v>
       </c>
       <c r="O5" t="n">
         <v>0.03096640447136682</v>
@@ -6265,7 +6265,7 @@
         <v>0.03258189432571449</v>
       </c>
       <c r="S5" t="n">
-        <v>0.03219531417404282</v>
+        <v>0.03219531417404283</v>
       </c>
       <c r="T5" t="n">
         <v>0.03181665156498913</v>
@@ -6274,7 +6274,7 @@
         <v>0.03098884239459103</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03127834066879769</v>
+        <v>0.0312783406687977</v>
       </c>
       <c r="W5" t="n">
         <v>0.03263814140886934</v>
@@ -6283,16 +6283,16 @@
         <v>0.03185830706361602</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.03504111065064965</v>
+        <v>0.03504111065064966</v>
       </c>
       <c r="Z5" t="n">
         <v>0.03024792146295196</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03203654455811057</v>
+        <v>0.03203654455811058</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03498152445515156</v>
+        <v>0.03498152445515157</v>
       </c>
     </row>
     <row r="6">
@@ -6308,40 +6308,40 @@
         <v>0.03179699771426919</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03187648329668932</v>
+        <v>0.0318764832966893</v>
       </c>
       <c r="E6" t="n">
         <v>0.03172975461145214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03004985299462375</v>
+        <v>0.03004985299462376</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03351949126253481</v>
+        <v>0.0335194912625348</v>
       </c>
       <c r="H6" t="n">
         <v>0.03191618530616306</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03195574774010598</v>
+        <v>0.03195574774010597</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03261439543148614</v>
+        <v>0.03261439543148613</v>
       </c>
       <c r="K6" t="n">
         <v>0.0323275174333917</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03320042527336742</v>
+        <v>0.03320042527336741</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03232119974033698</v>
+        <v>0.03232119974033697</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04546866469835963</v>
+        <v>0.03227754004394702</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03229078387243684</v>
+        <v>0.03229078387243683</v>
       </c>
       <c r="P6" t="n">
         <v>0.03324150753981113</v>
@@ -6353,13 +6353,13 @@
         <v>0.03282313997363356</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03243655982196191</v>
+        <v>0.0324365598219619</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03205789721290821</v>
+        <v>0.0320578972129082</v>
       </c>
       <c r="U6" t="n">
-        <v>0.03192767248020907</v>
+        <v>0.03192767248020906</v>
       </c>
       <c r="V6" t="n">
         <v>0.03288930127803495</v>
@@ -6380,7 +6380,7 @@
         <v>0.03227779020602965</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.03373223358126362</v>
+        <v>0.03373223358126361</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia eutrophication terrestrial results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.009534834586131025</v>
+        <v>0.008954928008202117</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008856490805195186</v>
+        <v>0.00870637715370293</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00937094093807956</v>
+        <v>0.008788990055977245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009438655395016472</v>
+        <v>0.009211766417285848</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008876982329982477</v>
+        <v>0.008442675339521357</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009348851712950372</v>
+        <v>0.008811906259879895</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0092082461443013</v>
+        <v>0.008661967462696764</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009680240188078055</v>
+        <v>0.008996093538840358</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009430539970592157</v>
+        <v>0.008853637382037155</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01089787400778651</v>
+        <v>0.009844066568627727</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009505114625414864</v>
+        <v>0.008905102936744963</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01372610447917591</v>
+        <v>0.01176669751158453</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009976321414531602</v>
+        <v>0.009220545616926515</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01308235836340361</v>
+        <v>0.01255864054679428</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009114782892138226</v>
+        <v>0.008649989532349774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008697301505562758</v>
+        <v>0.008331461794956706</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008876091509465021</v>
+        <v>0.008441769334898822</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009277228325607522</v>
+        <v>0.008759913251194143</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009734704396017651</v>
+        <v>0.009037033158743572</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01297258997316934</v>
+        <v>0.01211904404787009</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008588259559357794</v>
+        <v>0.008276661502643525</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01120855866781936</v>
+        <v>0.01072994554851041</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008718075830080805</v>
+        <v>0.008343710050704752</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008936574905711567</v>
+        <v>0.008504646061332461</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01042529014167671</v>
+        <v>0.01008149863297631</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01002584641325941</v>
+        <v>0.009261130959121676</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01076298408589469</v>
+        <v>0.009715435486022215</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007308125461400946</v>
+        <v>0.007255597192720855</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008128756504597592</v>
+        <v>0.008023215594072894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007454043132910335</v>
+        <v>0.007354266808300846</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008646889224416178</v>
+        <v>0.008578393807438613</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007669283984777847</v>
+        <v>0.007502482307601952</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007556534492741407</v>
+        <v>0.00743530549352092</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007524555708847461</v>
+        <v>0.007398045711088076</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007512057578991284</v>
+        <v>0.007392546874223241</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007646827775623668</v>
+        <v>0.007494649189155237</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007678907825883673</v>
+        <v>0.007518800523135397</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008015802216690286</v>
+        <v>0.007763177610724665</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007533784844267054</v>
+        <v>0.007408012642523813</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007649758389789189</v>
+        <v>0.007489328904069662</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01133523577952508</v>
+        <v>0.01112919087113974</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007674890388863371</v>
+        <v>0.007520798456384719</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0074194083390863</v>
+        <v>0.007332233450207772</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00822320637754281</v>
+        <v>0.007877820356366349</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007805895991743392</v>
+        <v>0.0076145473041466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007640510161972684</v>
+        <v>0.007480804816641286</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009345018936501866</v>
+        <v>0.009217311141425199</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007666476528747392</v>
+        <v>0.007513956426915824</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009479480498837</v>
+        <v>0.009203176788367849</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00897596258655497</v>
+        <v>0.008426962125659774</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008269697606246761</v>
+        <v>0.007921301215386806</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009196690531350802</v>
+        <v>0.009083311610300611</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008255153673904829</v>
+        <v>0.007912329653658274</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007318027898316157</v>
+        <v>0.007256570152058064</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00901672719691053</v>
+        <v>0.00855522893963628</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008735994011893211</v>
+        <v>0.008586825496255109</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008965089992645271</v>
+        <v>0.008475418236065898</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009287510458050929</v>
+        <v>0.009082176967223665</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008253649565911316</v>
+        <v>0.007985655574184538</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009127425867802446</v>
+        <v>0.008625820167615298</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008202143341015183</v>
+        <v>0.007944488464342406</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00872349204484086</v>
+        <v>0.008306133042767722</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009227227267422594</v>
+        <v>0.008678209575923516</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01020160560745808</v>
+        <v>0.009368871235284465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009169272631099882</v>
+        <v>0.00863691959506512</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01308151556135916</v>
+        <v>0.01129678722386934</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009139433258058514</v>
+        <v>0.00860625570379963</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01244913947087985</v>
+        <v>0.01204903219474776</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009183678058010309</v>
+        <v>0.00866773924390488</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008315283375179609</v>
+        <v>0.008033931988192832</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008236343984339162</v>
+        <v>0.007970314097496285</v>
       </c>
       <c r="S3" t="n">
-        <v>0.00908956894998696</v>
+        <v>0.008597880586232396</v>
       </c>
       <c r="T3" t="n">
-        <v>0.009029377944626486</v>
+        <v>0.008519955596364157</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0121815042154483</v>
+        <v>0.01147618223515243</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008082198647005677</v>
+        <v>0.007887984313668592</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0112106693949934</v>
+        <v>0.01065293414682159</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008787518533771519</v>
+        <v>0.008358594314944061</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.008673548429137951</v>
+        <v>0.00829018746527904</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.01002837602978791</v>
+        <v>0.009757117055503839</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009333819149195309</v>
+        <v>0.008748961853415812</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01051249048404</v>
+        <v>0.009509514321010944</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008657422407245449</v>
+        <v>0.008291024817413072</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008657172300199868</v>
+        <v>0.00853110971034177</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009214875283757591</v>
+        <v>0.008647000493340334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009314705967579939</v>
+        <v>0.009097880920567885</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00820390578413571</v>
+        <v>0.007950220811257082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008999206956379565</v>
+        <v>0.008536360841584626</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007939235601543365</v>
+        <v>0.007761838221168538</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009168194364841797</v>
+        <v>0.008608483895313367</v>
       </c>
       <c r="J3" t="n">
-        <v>0.009117858534443085</v>
+        <v>0.008599473839625456</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009397448637382901</v>
+        <v>0.008817624869132679</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008838147425764298</v>
+        <v>0.008403414624794735</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01232347769775156</v>
+        <v>0.01077134522148725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008548975766059251</v>
+        <v>0.008192887470975654</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01205241644226256</v>
+        <v>0.01174823350346258</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009092336906226387</v>
+        <v>0.008603543075234431</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008195804059329093</v>
+        <v>0.007950792012953907</v>
       </c>
       <c r="R3" t="n">
-        <v>0.007935568941537073</v>
+        <v>0.007761700106247821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008926009768539097</v>
+        <v>0.008481167707887136</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008779010578649944</v>
+        <v>0.008343740031068782</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01145465188999923</v>
+        <v>0.01096982488572367</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008205890303126491</v>
+        <v>0.007975938979288964</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01096592588943209</v>
+        <v>0.01048386114548633</v>
       </c>
       <c r="X3" t="n">
-        <v>0.00912739690189592</v>
+        <v>0.008591723719859242</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009478242274722845</v>
+        <v>0.008848851021507734</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009975447986336764</v>
+        <v>0.009724523363819789</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009341541389232407</v>
+        <v>0.008749931256949044</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01027169524953453</v>
+        <v>0.009340479586251647</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008402309737280093</v>
+        <v>0.008096251254177343</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008333719253456114</v>
+        <v>0.008221797021243265</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008537269192748954</v>
+        <v>0.008168403775739467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009073420342922606</v>
+        <v>0.008931282731832519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008243916142329432</v>
+        <v>0.007958486792876029</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008766591815459501</v>
+        <v>0.008360026388178588</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007857280889892545</v>
+        <v>0.007684355767938087</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008971969874845767</v>
+        <v>0.008458643056239419</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008918386265634843</v>
+        <v>0.008447390048083973</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009665231399530974</v>
+        <v>0.008988959796814982</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008592153621017664</v>
+        <v>0.008220043495904689</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01136314263129466</v>
+        <v>0.01012722340084692</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008100881802275299</v>
+        <v>0.007861215817904121</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01191429186953648</v>
+        <v>0.01162521598655226</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008821698686017555</v>
+        <v>0.008400791167060061</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008079088458303388</v>
+        <v>0.007852469656508694</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008132227836156971</v>
+        <v>0.007874344569962435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008754359206362864</v>
+        <v>0.008343338275170965</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008815617122337388</v>
+        <v>0.008347456834324926</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01072775188552837</v>
+        <v>0.01026511770380814</v>
       </c>
       <c r="V3" t="n">
-        <v>0.008455030804147086</v>
+        <v>0.008139585049762641</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009814885770070374</v>
+        <v>0.009502594084983211</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009185020019763694</v>
+        <v>0.008622350402265996</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01041464536592754</v>
+        <v>0.00947096793239535</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009770669168553549</v>
+        <v>0.00956301331796453</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009427217463663243</v>
+        <v>0.00878691396620775</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009956585485472918</v>
+        <v>0.009113260252280497</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007630268152058002</v>
+        <v>0.007513619376545897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00825317190128223</v>
+        <v>0.008198030892630727</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008136668332293373</v>
+        <v>0.007853465723463009</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008963728202172736</v>
+        <v>0.008809001131263332</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007646669697430912</v>
+        <v>0.00751486108951295</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007806357316052255</v>
+        <v>0.007644469142295118</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008064888579122966</v>
+        <v>0.007795181772296435</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008018912248807434</v>
+        <v>0.007769730617495678</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007997433788938881</v>
+        <v>0.007773326259855875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008587443299656095</v>
+        <v>0.008189367386369415</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008382266481671065</v>
+        <v>0.008059149841761879</v>
       </c>
       <c r="M3" t="n">
-        <v>0.009127488413728603</v>
+        <v>0.008566872319857984</v>
       </c>
       <c r="N3" t="n">
-        <v>0.008370748241354259</v>
+        <v>0.008026007282942185</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01120867713365801</v>
+        <v>0.01106520744021888</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008095214188754852</v>
+        <v>0.007844335992247509</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007969090974140365</v>
+        <v>0.007746349417004378</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008128874800716718</v>
+        <v>0.007840764414737524</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008002039570861316</v>
+        <v>0.00779309970347547</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007815197069760462</v>
+        <v>0.007634811752639172</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0105687771610999</v>
+        <v>0.01028102011435309</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007604348571610768</v>
+        <v>0.007494982285819915</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01030185343312875</v>
+        <v>0.00995141878391779</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008224372376467967</v>
+        <v>0.007916819550788937</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007636944234795153</v>
+        <v>0.007511936562836998</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009612847193840075</v>
+        <v>0.009415223441790833</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008313662906346801</v>
+        <v>0.007983982629464493</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.008137339804150032</v>
+        <v>0.007849199675684889</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007554821078728249</v>
+        <v>0.007454527799397555</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008424436264738825</v>
+        <v>0.008316409214413418</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007536641833967369</v>
+        <v>0.007436538661434276</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009061817641463753</v>
+        <v>0.008874363091318428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007843199831030918</v>
+        <v>0.007649138502922822</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007686008109125739</v>
+        <v>0.007554596092745892</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007773508210277802</v>
+        <v>0.007593386987465265</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007755047387354612</v>
+        <v>0.007586056253069907</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007766860481682871</v>
+        <v>0.007606850281856019</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007610292313743983</v>
+        <v>0.007491542018095131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007820871262051186</v>
+        <v>0.007657049535944566</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007488243628239607</v>
+        <v>0.007402881655148439</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007843716884733684</v>
+        <v>0.00765464240372707</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01131803474217975</v>
+        <v>0.01113794541444086</v>
       </c>
       <c r="P3" t="n">
-        <v>0.007796727604561175</v>
+        <v>0.007628632200545743</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007472722465340515</v>
+        <v>0.007395442415619673</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008336241100312563</v>
+        <v>0.007984024086010576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007792456297379911</v>
+        <v>0.007633511910721431</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007573616490160642</v>
+        <v>0.007462540667779695</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009812124754886688</v>
+        <v>0.009746254788915432</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007758635825635534</v>
+        <v>0.00760429333412522</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0102319462726809</v>
+        <v>0.009916263821247743</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008957650669535388</v>
+        <v>0.008441211072873033</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007762834485392588</v>
+        <v>0.007594579555610504</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009602818417616725</v>
+        <v>0.009404879769287024</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008070815495041508</v>
+        <v>0.007809947834062983</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.007345060597693425</v>
+        <v>0.007300466709713075</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007665623782246971</v>
+        <v>0.00751278275763665</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008186568146683166</v>
+        <v>0.008064272904680665</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007548591084057529</v>
+        <v>0.007421306513421207</v>
       </c>
       <c r="E3" t="n">
-        <v>0.009195422046252611</v>
+        <v>0.008974437171611286</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007687620220281475</v>
+        <v>0.00751508149139512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007478235002667975</v>
+        <v>0.007379681382456911</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007517138113634502</v>
+        <v>0.007394550106103487</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007481114640351555</v>
+        <v>0.007372146029618246</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007635297702117038</v>
+        <v>0.007488698891104558</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007428593317114133</v>
+        <v>0.007338658889000629</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007822965951758173</v>
+        <v>0.007631984067586414</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007389588839254955</v>
+        <v>0.007308885699741315</v>
       </c>
       <c r="N3" t="n">
-        <v>0.007595398888754527</v>
+        <v>0.007455358617575095</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0116601787309694</v>
+        <v>0.01137155288219071</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00784889001122209</v>
+        <v>0.007647712567355557</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007379104492924909</v>
+        <v>0.007305035516448496</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008280139291403872</v>
+        <v>0.007919009444906878</v>
       </c>
       <c r="S3" t="n">
-        <v>0.007678807850714794</v>
+        <v>0.0075244131196682</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007436868042199668</v>
+        <v>0.007342554436436418</v>
       </c>
       <c r="U3" t="n">
-        <v>0.009144627851208384</v>
+        <v>0.009071622202417601</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007733831649686672</v>
+        <v>0.007563234898019575</v>
       </c>
       <c r="W3" t="n">
-        <v>0.009507147147101866</v>
+        <v>0.009227496686306578</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009240107836654176</v>
+        <v>0.008624556984365832</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.007658192764854513</v>
+        <v>0.007497463895825389</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009395782603916944</v>
+        <v>0.009233004593540805</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.008050787164984932</v>
+        <v>0.007772280820905889</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00735119638953916</v>
+        <v>0.007280700147813381</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.008433404092057515</v>
+        <v>0.008128884910228833</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008526397239130755</v>
+        <v>0.008429711197076271</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008602421280361117</v>
+        <v>0.008215000830706715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00916369183463518</v>
+        <v>0.008986317692500563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008074697498391717</v>
+        <v>0.007853073167926126</v>
       </c>
       <c r="G3" t="n">
-        <v>0.009005605014768249</v>
+        <v>0.008542338974185269</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008161821638551949</v>
+        <v>0.007905807341926092</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008797871850293149</v>
+        <v>0.008349009008607413</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00900624346636616</v>
+        <v>0.008526624849318534</v>
       </c>
       <c r="K3" t="n">
-        <v>0.009380702966262007</v>
+        <v>0.008794920038454643</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009007820294593806</v>
+        <v>0.008524497436102773</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0127691420467408</v>
+        <v>0.01116341590026491</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00945033108737061</v>
+        <v>0.008811319990110393</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01195084492167723</v>
+        <v>0.011665635265236</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008925174754312832</v>
+        <v>0.00847391520378476</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.008275297490762995</v>
+        <v>0.007999361220480979</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008468948722594752</v>
+        <v>0.008117462498218179</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008614495478787445</v>
+        <v>0.008265312856597561</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00868982781817767</v>
+        <v>0.008275575414046504</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01158359837699195</v>
+        <v>0.01103843851011725</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007955318870685863</v>
+        <v>0.007786924996261432</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01047644492073909</v>
+        <v>0.01011952229063402</v>
       </c>
       <c r="X3" t="n">
-        <v>0.009054142610786967</v>
+        <v>0.008532108931572432</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00852843197885747</v>
+        <v>0.008178539782003991</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0100163573037827</v>
+        <v>0.009742172783381792</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.009091830035040228</v>
+        <v>0.008569720862708524</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.01006502487691688</v>
+        <v>0.00919673057357373</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007477143297577696</v>
+        <v>0.007416062125584095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008497423467969367</v>
+        <v>0.008385797429767115</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007695724718668653</v>
+        <v>0.007563818519048799</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008925783573338507</v>
+        <v>0.008794042059714081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007787762164284041</v>
+        <v>0.007627438445540194</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008780712569380719</v>
+        <v>0.008365228032798634</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007735941001459332</v>
+        <v>0.007585168371314835</v>
       </c>
       <c r="I3" t="n">
-        <v>0.007757474548086958</v>
+        <v>0.007603799683151859</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008189317838748371</v>
+        <v>0.007926095444299204</v>
       </c>
       <c r="K3" t="n">
-        <v>0.007994591215404634</v>
+        <v>0.007784185199580203</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008584304254104932</v>
+        <v>0.008211749731846145</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007999799404096836</v>
+        <v>0.007780815950114151</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00798105671890747</v>
+        <v>0.007762248535792985</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01124503297109541</v>
+        <v>0.01110467155712855</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008380286312060843</v>
+        <v>0.008063734915541427</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007825601227788871</v>
+        <v>0.007663064364586719</v>
       </c>
       <c r="R3" t="n">
-        <v>0.008392364349141848</v>
+        <v>0.008035704213364747</v>
       </c>
       <c r="S3" t="n">
-        <v>0.008055214128396791</v>
+        <v>0.007835565723976352</v>
       </c>
       <c r="T3" t="n">
-        <v>0.007828219265120813</v>
+        <v>0.007654096380157974</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01010509165091945</v>
+        <v>0.009974907320606533</v>
       </c>
       <c r="V3" t="n">
-        <v>0.007717512077630251</v>
+        <v>0.007589809954605648</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01035490780953169</v>
+        <v>0.01001146603888788</v>
       </c>
       <c r="X3" t="n">
-        <v>0.008967462765330246</v>
+        <v>0.00845357850498289</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.009095270838502067</v>
+        <v>0.008546046585813748</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.009379112460145653</v>
+        <v>0.009251725819948339</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.007976304301035504</v>
+        <v>0.007761651891723521</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.009054553790595405</v>
+        <v>0.008488514265005388</v>
       </c>
     </row>
     <row r="4">
